--- a/public/plantilla-mensual.xlsx
+++ b/public/plantilla-mensual.xlsx
@@ -25,7 +25,7 @@
     <numFmt numFmtId="169" formatCode="&quot;$ &quot;#,##0"/>
     <numFmt numFmtId="170" formatCode="\$\ #,##0.00"/>
   </numFmts>
-  <fonts count="167">
+  <fonts count="168">
     <font>
       <name val="Calibri"/>
       <charset val="1"/>
@@ -1225,6 +1225,10 @@
       <sz val="8"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <color rgb="008A8F99"/>
+      <sz val="8"/>
+    </font>
   </fonts>
   <fills count="76">
     <fill>
@@ -6506,7 +6510,7 @@
     <xf numFmtId="0" fontId="28" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1383">
+  <cellXfs count="1384">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
@@ -9962,6 +9966,7 @@
     <xf numFmtId="169" fontId="39" fillId="3" borderId="117" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="167" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="5">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -10182,7 +10187,7 @@
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
-                  <a:t/>
+                  <a:t>None</a:t>
                 </a:r>
                 <a:endParaRPr lang="es-CO"/>
               </a:p>
@@ -10378,7 +10383,7 @@
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:t/>
+              <a:t>None</a:t>
             </a:r>
             <a:endParaRPr lang="es-CO"/>
           </a:p>
@@ -10469,7 +10474,7 @@
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:t/>
+              <a:t>None</a:t>
             </a:r>
             <a:endParaRPr lang="es-CO"/>
           </a:p>
@@ -10502,7 +10507,7 @@
             </a:defRPr>
           </a:pPr>
           <a:r>
-            <a:t/>
+            <a:t>None</a:t>
           </a:r>
           <a:endParaRPr lang="es-CO"/>
         </a:p>
@@ -10910,7 +10915,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F241"/>
+  <dimension ref="A1:F258"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
   <cols>
     <col width="8" customWidth="1" style="592" min="1" max="1"/>
@@ -11318,76 +11323,76 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="82" t="n"/>
-      <c r="B24" s="693" t="inlineStr">
+      <c r="A24" s="81" t="inlineStr">
+        <is>
+          <t>1.10</t>
+        </is>
+      </c>
+      <c r="B24" s="403" t="inlineStr">
+        <is>
+          <t>Desmantelamiento de estructuras metálicas existentes</t>
+        </is>
+      </c>
+      <c r="C24" s="272" t="inlineStr">
+        <is>
+          <t>KG</t>
+        </is>
+      </c>
+      <c r="D24" s="273" t="n"/>
+      <c r="E24" s="1295" t="n"/>
+      <c r="F24" s="1296">
+        <f>D24*E24</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="82" t="n"/>
+      <c r="B25" s="693" t="inlineStr">
         <is>
           <t>SUBTOTAL CAPÍTULO 1 - PRELIMINARES</t>
         </is>
       </c>
-      <c r="C24" s="536" t="n"/>
-      <c r="D24" s="536" t="n"/>
-      <c r="E24" s="536" t="n"/>
-      <c r="F24" s="1297">
-        <f>SUM(F15:F23)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="83" t="n"/>
-      <c r="B25" s="694" t="n"/>
-      <c r="C25" s="694" t="n"/>
-      <c r="D25" s="694" t="n"/>
-      <c r="E25" s="694" t="n"/>
-      <c r="F25" s="695" t="n"/>
+      <c r="C25" s="536" t="n"/>
+      <c r="D25" s="536" t="n"/>
+      <c r="E25" s="536" t="n"/>
+      <c r="F25" s="1297">
+        <f>SUM(F15:F24)</f>
+        <v/>
+      </c>
     </row>
     <row r="26">
-      <c r="A26" s="189" t="inlineStr">
+      <c r="A26" s="83" t="n"/>
+      <c r="B26" s="694" t="n"/>
+      <c r="C26" s="694" t="n"/>
+      <c r="D26" s="694" t="n"/>
+      <c r="E26" s="694" t="n"/>
+      <c r="F26" s="695" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="189" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="B26" s="705" t="inlineStr">
+      <c r="B27" s="705" t="inlineStr">
         <is>
           <t>MOVIMIENTO DE TIERRAS</t>
         </is>
       </c>
-      <c r="C26" s="587" t="n"/>
-      <c r="D26" s="587" t="n"/>
-      <c r="E26" s="587" t="n"/>
-      <c r="F26" s="588" t="n"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="81" t="inlineStr">
-        <is>
-          <t>2.1</t>
-        </is>
-      </c>
-      <c r="B27" s="403" t="inlineStr">
-        <is>
-          <t>Excavación manual en material común</t>
-        </is>
-      </c>
-      <c r="C27" s="272" t="inlineStr">
-        <is>
-          <t>M³</t>
-        </is>
-      </c>
-      <c r="D27" s="273" t="n"/>
-      <c r="E27" s="1295" t="n"/>
-      <c r="F27" s="1296">
-        <f>D27*E27</f>
-        <v/>
-      </c>
+      <c r="C27" s="587" t="n"/>
+      <c r="D27" s="587" t="n"/>
+      <c r="E27" s="587" t="n"/>
+      <c r="F27" s="588" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="81" t="inlineStr">
         <is>
-          <t>2.2</t>
+          <t>2.1</t>
         </is>
       </c>
       <c r="B28" s="403" t="inlineStr">
         <is>
-          <t>Excavación mecánica</t>
+          <t>Excavación manual en material común</t>
         </is>
       </c>
       <c r="C28" s="272" t="inlineStr">
@@ -11405,12 +11410,12 @@
     <row r="29">
       <c r="A29" s="81" t="inlineStr">
         <is>
-          <t>2.3</t>
+          <t>2.2</t>
         </is>
       </c>
       <c r="B29" s="403" t="inlineStr">
         <is>
-          <t>Excavación en roca</t>
+          <t>Excavación mecánica</t>
         </is>
       </c>
       <c r="C29" s="272" t="inlineStr">
@@ -11428,17 +11433,17 @@
     <row r="30">
       <c r="A30" s="81" t="inlineStr">
         <is>
-          <t>2.4</t>
+          <t>2.3</t>
         </is>
       </c>
       <c r="B30" s="403" t="inlineStr">
         <is>
-          <t>Perfilado y conformación de excavaciones</t>
+          <t>Excavación en roca</t>
         </is>
       </c>
       <c r="C30" s="272" t="inlineStr">
         <is>
-          <t>M²</t>
+          <t>M³</t>
         </is>
       </c>
       <c r="D30" s="273" t="n"/>
@@ -11451,17 +11456,17 @@
     <row r="31">
       <c r="A31" s="81" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>2.4</t>
         </is>
       </c>
       <c r="B31" s="403" t="inlineStr">
         <is>
-          <t>Relleno con material seleccionado compactado</t>
+          <t>Perfilado y conformación de excavaciones</t>
         </is>
       </c>
       <c r="C31" s="272" t="inlineStr">
         <is>
-          <t>M³</t>
+          <t>M²</t>
         </is>
       </c>
       <c r="D31" s="273" t="n"/>
@@ -11474,12 +11479,12 @@
     <row r="32">
       <c r="A32" s="81" t="inlineStr">
         <is>
-          <t>2.6</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="B32" s="403" t="inlineStr">
         <is>
-          <t>Relleno con material proveniente de excavación</t>
+          <t>Relleno con material seleccionado compactado</t>
         </is>
       </c>
       <c r="C32" s="272" t="inlineStr">
@@ -11497,12 +11502,12 @@
     <row r="33">
       <c r="A33" s="81" t="inlineStr">
         <is>
-          <t>2.7</t>
+          <t>2.6</t>
         </is>
       </c>
       <c r="B33" s="403" t="inlineStr">
         <is>
-          <t>Suministro, extendido y compactación de subbase</t>
+          <t>Relleno con material proveniente de excavación</t>
         </is>
       </c>
       <c r="C33" s="272" t="inlineStr">
@@ -11520,12 +11525,12 @@
     <row r="34">
       <c r="A34" s="81" t="inlineStr">
         <is>
-          <t>2.8</t>
+          <t>2.7</t>
         </is>
       </c>
       <c r="B34" s="403" t="inlineStr">
         <is>
-          <t>Suministro, extendido y compactación de base granular</t>
+          <t>Suministro, extendido y compactación de subbase</t>
         </is>
       </c>
       <c r="C34" s="272" t="inlineStr">
@@ -11543,12 +11548,12 @@
     <row r="35">
       <c r="A35" s="81" t="inlineStr">
         <is>
-          <t>2.9</t>
+          <t>2.8</t>
         </is>
       </c>
       <c r="B35" s="403" t="inlineStr">
         <is>
-          <t>Cargue de material sobrante</t>
+          <t>Suministro, extendido y compactación de base granular</t>
         </is>
       </c>
       <c r="C35" s="272" t="inlineStr">
@@ -11566,12 +11571,12 @@
     <row r="36">
       <c r="A36" s="81" t="inlineStr">
         <is>
-          <t>2.10</t>
+          <t>2.9</t>
         </is>
       </c>
       <c r="B36" s="403" t="inlineStr">
         <is>
-          <t>Transporte de material sobrante</t>
+          <t>Cargue de material sobrante</t>
         </is>
       </c>
       <c r="C36" s="272" t="inlineStr">
@@ -11589,12 +11594,12 @@
     <row r="37">
       <c r="A37" s="81" t="inlineStr">
         <is>
-          <t>2.11</t>
+          <t>2.10</t>
         </is>
       </c>
       <c r="B37" s="403" t="inlineStr">
         <is>
-          <t>Disposición final de sobrantes</t>
+          <t>Transporte de material sobrante</t>
         </is>
       </c>
       <c r="C37" s="272" t="inlineStr">
@@ -11610,76 +11615,76 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="82" t="n"/>
-      <c r="B38" s="693" t="inlineStr">
+      <c r="A38" s="81" t="inlineStr">
+        <is>
+          <t>2.11</t>
+        </is>
+      </c>
+      <c r="B38" s="403" t="inlineStr">
+        <is>
+          <t>Disposición final de sobrantes</t>
+        </is>
+      </c>
+      <c r="C38" s="272" t="inlineStr">
+        <is>
+          <t>M³</t>
+        </is>
+      </c>
+      <c r="D38" s="273" t="n"/>
+      <c r="E38" s="1295" t="n"/>
+      <c r="F38" s="1296">
+        <f>D38*E38</f>
+        <v/>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="82" t="n"/>
+      <c r="B39" s="693" t="inlineStr">
         <is>
           <t>SUBTOTAL CAPÍTULO 2 - MOVIMIENTO DE TIERRAS</t>
         </is>
       </c>
-      <c r="C38" s="536" t="n"/>
-      <c r="D38" s="536" t="n"/>
-      <c r="E38" s="536" t="n"/>
-      <c r="F38" s="1297">
-        <f>SUM(F27:F37)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="83" t="n"/>
-      <c r="B39" s="694" t="n"/>
-      <c r="C39" s="694" t="n"/>
-      <c r="D39" s="694" t="n"/>
-      <c r="E39" s="694" t="n"/>
-      <c r="F39" s="695" t="n"/>
+      <c r="C39" s="536" t="n"/>
+      <c r="D39" s="536" t="n"/>
+      <c r="E39" s="536" t="n"/>
+      <c r="F39" s="1297">
+        <f>SUM(F28:F38)</f>
+        <v/>
+      </c>
     </row>
     <row r="40">
-      <c r="A40" s="189" t="inlineStr">
+      <c r="A40" s="83" t="n"/>
+      <c r="B40" s="694" t="n"/>
+      <c r="C40" s="694" t="n"/>
+      <c r="D40" s="694" t="n"/>
+      <c r="E40" s="694" t="n"/>
+      <c r="F40" s="695" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="189" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="B40" s="705" t="inlineStr">
+      <c r="B41" s="705" t="inlineStr">
         <is>
           <t>CIMENTACIONES</t>
         </is>
       </c>
-      <c r="C40" s="587" t="n"/>
-      <c r="D40" s="587" t="n"/>
-      <c r="E40" s="587" t="n"/>
-      <c r="F40" s="588" t="n"/>
-    </row>
-    <row r="41">
-      <c r="A41" s="81" t="inlineStr">
-        <is>
-          <t>3.1</t>
-        </is>
-      </c>
-      <c r="B41" s="403" t="inlineStr">
-        <is>
-          <t>Concreto de limpieza / solado</t>
-        </is>
-      </c>
-      <c r="C41" s="272" t="inlineStr">
-        <is>
-          <t>M³</t>
-        </is>
-      </c>
-      <c r="D41" s="273" t="n"/>
-      <c r="E41" s="1295" t="n"/>
-      <c r="F41" s="1296">
-        <f>D41*E41</f>
-        <v/>
-      </c>
+      <c r="C41" s="587" t="n"/>
+      <c r="D41" s="587" t="n"/>
+      <c r="E41" s="587" t="n"/>
+      <c r="F41" s="588" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="81" t="inlineStr">
         <is>
-          <t>3.2</t>
+          <t>3.1</t>
         </is>
       </c>
       <c r="B42" s="403" t="inlineStr">
         <is>
-          <t>Concreto para zapatas</t>
+          <t>Concreto de limpieza / solado</t>
         </is>
       </c>
       <c r="C42" s="272" t="inlineStr">
@@ -11697,12 +11702,12 @@
     <row r="43">
       <c r="A43" s="81" t="inlineStr">
         <is>
-          <t>3.3</t>
+          <t>3.2</t>
         </is>
       </c>
       <c r="B43" s="403" t="inlineStr">
         <is>
-          <t>Concreto para vigas de cimentación</t>
+          <t>Concreto para zapatas</t>
         </is>
       </c>
       <c r="C43" s="272" t="inlineStr">
@@ -11720,12 +11725,12 @@
     <row r="44">
       <c r="A44" s="81" t="inlineStr">
         <is>
-          <t>3.4</t>
+          <t>3.3</t>
         </is>
       </c>
       <c r="B44" s="403" t="inlineStr">
         <is>
-          <t>Concreto para losas de cimentación</t>
+          <t>Concreto para vigas de cimentación</t>
         </is>
       </c>
       <c r="C44" s="272" t="inlineStr">
@@ -11743,12 +11748,12 @@
     <row r="45">
       <c r="A45" s="81" t="inlineStr">
         <is>
-          <t>3.5</t>
+          <t>3.4</t>
         </is>
       </c>
       <c r="B45" s="403" t="inlineStr">
         <is>
-          <t>Concreto para pedestales</t>
+          <t>Concreto para losas de cimentación</t>
         </is>
       </c>
       <c r="C45" s="272" t="inlineStr">
@@ -11766,17 +11771,17 @@
     <row r="46">
       <c r="A46" s="81" t="inlineStr">
         <is>
-          <t>3.6</t>
+          <t>3.5</t>
         </is>
       </c>
       <c r="B46" s="403" t="inlineStr">
         <is>
-          <t>Acero de refuerzo en cimentación</t>
+          <t>Concreto para pedestales</t>
         </is>
       </c>
       <c r="C46" s="272" t="inlineStr">
         <is>
-          <t>KG</t>
+          <t>M³</t>
         </is>
       </c>
       <c r="D46" s="273" t="n"/>
@@ -11789,17 +11794,17 @@
     <row r="47">
       <c r="A47" s="81" t="inlineStr">
         <is>
-          <t>3.7</t>
+          <t>3.6</t>
         </is>
       </c>
       <c r="B47" s="403" t="inlineStr">
         <is>
-          <t>Formaleta para elementos de cimentación</t>
+          <t>Acero de refuerzo en cimentación</t>
         </is>
       </c>
       <c r="C47" s="272" t="inlineStr">
         <is>
-          <t>M²</t>
+          <t>KG</t>
         </is>
       </c>
       <c r="D47" s="273" t="n"/>
@@ -11810,76 +11815,76 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="82" t="n"/>
-      <c r="B48" s="693" t="inlineStr">
+      <c r="A48" s="81" t="inlineStr">
+        <is>
+          <t>3.7</t>
+        </is>
+      </c>
+      <c r="B48" s="403" t="inlineStr">
+        <is>
+          <t>Formaleta para elementos de cimentación</t>
+        </is>
+      </c>
+      <c r="C48" s="272" t="inlineStr">
+        <is>
+          <t>M²</t>
+        </is>
+      </c>
+      <c r="D48" s="273" t="n"/>
+      <c r="E48" s="1295" t="n"/>
+      <c r="F48" s="1296">
+        <f>D48*E48</f>
+        <v/>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="82" t="n"/>
+      <c r="B49" s="693" t="inlineStr">
         <is>
           <t>SUBTOTAL CAPÍTULO 3 - CIMENTACIONES</t>
         </is>
       </c>
-      <c r="C48" s="536" t="n"/>
-      <c r="D48" s="536" t="n"/>
-      <c r="E48" s="536" t="n"/>
-      <c r="F48" s="1297">
-        <f>SUM(F41:F47)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="83" t="n"/>
-      <c r="B49" s="694" t="n"/>
-      <c r="C49" s="694" t="n"/>
-      <c r="D49" s="694" t="n"/>
-      <c r="E49" s="694" t="n"/>
-      <c r="F49" s="695" t="n"/>
+      <c r="C49" s="536" t="n"/>
+      <c r="D49" s="536" t="n"/>
+      <c r="E49" s="536" t="n"/>
+      <c r="F49" s="1297">
+        <f>SUM(F42:F48)</f>
+        <v/>
+      </c>
     </row>
     <row r="50">
-      <c r="A50" s="189" t="inlineStr">
+      <c r="A50" s="83" t="n"/>
+      <c r="B50" s="694" t="n"/>
+      <c r="C50" s="694" t="n"/>
+      <c r="D50" s="694" t="n"/>
+      <c r="E50" s="694" t="n"/>
+      <c r="F50" s="695" t="n"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="189" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="B50" s="692" t="inlineStr">
+      <c r="B51" s="692" t="inlineStr">
         <is>
           <t>ESTRUCTURA</t>
         </is>
       </c>
-      <c r="C50" s="536" t="n"/>
-      <c r="D50" s="536" t="n"/>
-      <c r="E50" s="536" t="n"/>
-      <c r="F50" s="536" t="n"/>
-    </row>
-    <row r="51">
-      <c r="A51" s="81" t="inlineStr">
-        <is>
-          <t>4.1</t>
-        </is>
-      </c>
-      <c r="B51" s="403" t="inlineStr">
-        <is>
-          <t>Concreto para columnas</t>
-        </is>
-      </c>
-      <c r="C51" s="272" t="inlineStr">
-        <is>
-          <t>M³</t>
-        </is>
-      </c>
-      <c r="D51" s="273" t="n"/>
-      <c r="E51" s="1295" t="n"/>
-      <c r="F51" s="1296">
-        <f>D51*E51</f>
-        <v/>
-      </c>
+      <c r="C51" s="536" t="n"/>
+      <c r="D51" s="536" t="n"/>
+      <c r="E51" s="536" t="n"/>
+      <c r="F51" s="536" t="n"/>
     </row>
     <row r="52">
       <c r="A52" s="81" t="inlineStr">
         <is>
-          <t>4.2</t>
-        </is>
-      </c>
-      <c r="B52" s="404" t="inlineStr">
-        <is>
-          <t>Concreto para vigas</t>
+          <t>4.1</t>
+        </is>
+      </c>
+      <c r="B52" s="403" t="inlineStr">
+        <is>
+          <t>Concreto para columnas</t>
         </is>
       </c>
       <c r="C52" s="272" t="inlineStr">
@@ -11887,7 +11892,9 @@
           <t>M³</t>
         </is>
       </c>
-      <c r="F52">
+      <c r="D52" s="273" t="n"/>
+      <c r="E52" s="1295" t="n"/>
+      <c r="F52" s="1296">
         <f>D52*E52</f>
         <v/>
       </c>
@@ -11895,12 +11902,12 @@
     <row r="53">
       <c r="A53" s="81" t="inlineStr">
         <is>
-          <t>4.3</t>
-        </is>
-      </c>
-      <c r="B53" s="403" t="inlineStr">
-        <is>
-          <t>Concreto para losas</t>
+          <t>4.2</t>
+        </is>
+      </c>
+      <c r="B53" s="404" t="inlineStr">
+        <is>
+          <t>Concreto para vigas</t>
         </is>
       </c>
       <c r="C53" s="272" t="inlineStr">
@@ -11908,9 +11915,7 @@
           <t>M³</t>
         </is>
       </c>
-      <c r="D53" s="273" t="n"/>
-      <c r="E53" s="1295" t="n"/>
-      <c r="F53" s="1296">
+      <c r="F53">
         <f>D53*E53</f>
         <v/>
       </c>
@@ -11918,12 +11923,12 @@
     <row r="54">
       <c r="A54" s="81" t="inlineStr">
         <is>
-          <t>4.4</t>
+          <t>4.3</t>
         </is>
       </c>
       <c r="B54" s="403" t="inlineStr">
         <is>
-          <t>Concreto para escaleras</t>
+          <t>Concreto para losas</t>
         </is>
       </c>
       <c r="C54" s="272" t="inlineStr">
@@ -11941,12 +11946,12 @@
     <row r="55">
       <c r="A55" s="81" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>4.4</t>
         </is>
       </c>
       <c r="B55" s="403" t="inlineStr">
         <is>
-          <t>Concreto para muros estructurales</t>
+          <t>Concreto para escaleras</t>
         </is>
       </c>
       <c r="C55" s="272" t="inlineStr">
@@ -11964,17 +11969,17 @@
     <row r="56">
       <c r="A56" s="81" t="inlineStr">
         <is>
-          <t>4.6</t>
+          <t>4.5</t>
         </is>
       </c>
       <c r="B56" s="403" t="inlineStr">
         <is>
-          <t>Acero de refuerzo de columnas</t>
+          <t>Concreto para muros estructurales</t>
         </is>
       </c>
       <c r="C56" s="272" t="inlineStr">
         <is>
-          <t>KG</t>
+          <t>M³</t>
         </is>
       </c>
       <c r="D56" s="273" t="n"/>
@@ -11987,12 +11992,12 @@
     <row r="57">
       <c r="A57" s="81" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>4.6</t>
         </is>
       </c>
       <c r="B57" s="403" t="inlineStr">
         <is>
-          <t>Acero de refuerzo de vigas</t>
+          <t>Acero de refuerzo de columnas</t>
         </is>
       </c>
       <c r="C57" s="272" t="inlineStr">
@@ -12010,12 +12015,12 @@
     <row r="58">
       <c r="A58" s="81" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>4.7</t>
         </is>
       </c>
       <c r="B58" s="403" t="inlineStr">
         <is>
-          <t>Acero de refuerzo de losas</t>
+          <t>Acero de refuerzo de vigas</t>
         </is>
       </c>
       <c r="C58" s="272" t="inlineStr">
@@ -12023,6 +12028,8 @@
           <t>KG</t>
         </is>
       </c>
+      <c r="D58" s="273" t="n"/>
+      <c r="E58" s="1295" t="n"/>
       <c r="F58" s="1296">
         <f>D58*E58</f>
         <v/>
@@ -12031,21 +12038,19 @@
     <row r="59">
       <c r="A59" s="81" t="inlineStr">
         <is>
-          <t>4.9</t>
+          <t>4.8</t>
         </is>
       </c>
       <c r="B59" s="403" t="inlineStr">
         <is>
-          <t>Formaleta de columnas</t>
+          <t>Acero de refuerzo de losas</t>
         </is>
       </c>
       <c r="C59" s="272" t="inlineStr">
         <is>
-          <t>M²</t>
-        </is>
-      </c>
-      <c r="D59" s="273" t="n"/>
-      <c r="E59" s="1295" t="n"/>
+          <t>KG</t>
+        </is>
+      </c>
       <c r="F59" s="1296">
         <f>D59*E59</f>
         <v/>
@@ -12054,12 +12059,12 @@
     <row r="60">
       <c r="A60" s="81" t="inlineStr">
         <is>
-          <t>4.10</t>
-        </is>
-      </c>
-      <c r="B60" s="404" t="inlineStr">
-        <is>
-          <t>Formaleta de vigas</t>
+          <t>4.9</t>
+        </is>
+      </c>
+      <c r="B60" s="403" t="inlineStr">
+        <is>
+          <t>Formaleta de columnas</t>
         </is>
       </c>
       <c r="C60" s="272" t="inlineStr">
@@ -12067,7 +12072,9 @@
           <t>M²</t>
         </is>
       </c>
-      <c r="F60">
+      <c r="D60" s="273" t="n"/>
+      <c r="E60" s="1295" t="n"/>
+      <c r="F60" s="1296">
         <f>D60*E60</f>
         <v/>
       </c>
@@ -12075,12 +12082,12 @@
     <row r="61">
       <c r="A61" s="81" t="inlineStr">
         <is>
-          <t>4.11</t>
-        </is>
-      </c>
-      <c r="B61" s="403" t="inlineStr">
-        <is>
-          <t>Formaleta de losas</t>
+          <t>4.10</t>
+        </is>
+      </c>
+      <c r="B61" s="404" t="inlineStr">
+        <is>
+          <t>Formaleta de vigas</t>
         </is>
       </c>
       <c r="C61" s="272" t="inlineStr">
@@ -12088,9 +12095,7 @@
           <t>M²</t>
         </is>
       </c>
-      <c r="D61" s="273" t="n"/>
-      <c r="E61" s="1295" t="n"/>
-      <c r="F61" s="1296">
+      <c r="F61">
         <f>D61*E61</f>
         <v/>
       </c>
@@ -12098,12 +12103,12 @@
     <row r="62">
       <c r="A62" s="81" t="inlineStr">
         <is>
-          <t>4.12</t>
+          <t>4.11</t>
         </is>
       </c>
       <c r="B62" s="403" t="inlineStr">
         <is>
-          <t>Formaleta de escaleras</t>
+          <t>Formaleta de losas</t>
         </is>
       </c>
       <c r="C62" s="272" t="inlineStr">
@@ -12121,17 +12126,17 @@
     <row r="63">
       <c r="A63" s="81" t="inlineStr">
         <is>
-          <t>4.13</t>
+          <t>4.12</t>
         </is>
       </c>
       <c r="B63" s="403" t="inlineStr">
         <is>
-          <t>Suministro y montaje de perfiles metálicos</t>
+          <t>Formaleta de escaleras</t>
         </is>
       </c>
       <c r="C63" s="272" t="inlineStr">
         <is>
-          <t>KG</t>
+          <t>M²</t>
         </is>
       </c>
       <c r="D63" s="273" t="n"/>
@@ -12144,12 +12149,12 @@
     <row r="64">
       <c r="A64" s="81" t="inlineStr">
         <is>
-          <t>4.14</t>
+          <t>4.13</t>
         </is>
       </c>
       <c r="B64" s="403" t="inlineStr">
         <is>
-          <t>Placas, pernos y conexiones metálicas</t>
+          <t>Suministro y montaje de perfiles metálicos</t>
         </is>
       </c>
       <c r="C64" s="272" t="inlineStr">
@@ -12165,122 +12170,122 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="82" t="n"/>
-      <c r="B65" s="693" t="inlineStr">
+      <c r="A65" s="81" t="inlineStr">
+        <is>
+          <t>4.14</t>
+        </is>
+      </c>
+      <c r="B65" s="403" t="inlineStr">
+        <is>
+          <t>Placas, pernos y conexiones metálicas</t>
+        </is>
+      </c>
+      <c r="C65" s="272" t="inlineStr">
+        <is>
+          <t>KG</t>
+        </is>
+      </c>
+      <c r="D65" s="273" t="n"/>
+      <c r="E65" s="1295" t="n"/>
+      <c r="F65" s="1296">
+        <f>D65*E65</f>
+        <v/>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="81" t="inlineStr">
+        <is>
+          <t>4.15</t>
+        </is>
+      </c>
+      <c r="B66" s="403" t="inlineStr">
+        <is>
+          <t>Grouting cementoso para reparación estructural</t>
+        </is>
+      </c>
+      <c r="C66" s="272" t="inlineStr">
+        <is>
+          <t>M²</t>
+        </is>
+      </c>
+      <c r="D66" s="273" t="n"/>
+      <c r="E66" s="1295" t="n"/>
+      <c r="F66" s="1296">
+        <f>D66*E66</f>
+        <v/>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="81" t="inlineStr">
+        <is>
+          <t>4.16</t>
+        </is>
+      </c>
+      <c r="B67" s="403" t="inlineStr">
+        <is>
+          <t>Grouting epóxico para reparación estructural</t>
+        </is>
+      </c>
+      <c r="C67" s="272" t="inlineStr">
+        <is>
+          <t>M²</t>
+        </is>
+      </c>
+      <c r="D67" s="273" t="n"/>
+      <c r="E67" s="1295" t="n"/>
+      <c r="F67" s="1296">
+        <f>D67*E67</f>
+        <v/>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="82" t="n"/>
+      <c r="B68" s="693" t="inlineStr">
         <is>
           <t>SUBTOTAL CAPÍTULO 4 - ESTRUCTURA</t>
         </is>
       </c>
-      <c r="C65" s="536" t="n"/>
-      <c r="D65" s="536" t="n"/>
-      <c r="E65" s="536" t="n"/>
-      <c r="F65" s="1297">
-        <f>SUM(F51:F64)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" s="83" t="n"/>
-      <c r="B66" s="694" t="n"/>
-      <c r="C66" s="694" t="n"/>
-      <c r="D66" s="694" t="n"/>
-      <c r="E66" s="694" t="n"/>
-      <c r="F66" s="695" t="n"/>
-    </row>
-    <row r="67">
-      <c r="A67" s="189" t="inlineStr">
+      <c r="C68" s="536" t="n"/>
+      <c r="D68" s="536" t="n"/>
+      <c r="E68" s="536" t="n"/>
+      <c r="F68" s="1297">
+        <f>SUM(F52:F67)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="83" t="n"/>
+      <c r="B69" s="694" t="n"/>
+      <c r="C69" s="694" t="n"/>
+      <c r="D69" s="694" t="n"/>
+      <c r="E69" s="694" t="n"/>
+      <c r="F69" s="695" t="n"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="189" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="B67" s="705" t="inlineStr">
+      <c r="B70" s="705" t="inlineStr">
         <is>
           <t>MAMPOSTERÍA</t>
         </is>
       </c>
-      <c r="C67" s="587" t="n"/>
-      <c r="D67" s="587" t="n"/>
-      <c r="E67" s="587" t="n"/>
-      <c r="F67" s="588" t="n"/>
-    </row>
-    <row r="68">
-      <c r="A68" s="81" t="inlineStr">
-        <is>
-          <t>5.1</t>
-        </is>
-      </c>
-      <c r="B68" s="403" t="inlineStr">
-        <is>
-          <t>Mampostería en bloque de concreto</t>
-        </is>
-      </c>
-      <c r="C68" s="272" t="inlineStr">
-        <is>
-          <t>M²</t>
-        </is>
-      </c>
-      <c r="D68" s="273" t="n"/>
-      <c r="E68" s="1295" t="n"/>
-      <c r="F68" s="1296">
-        <f>D68*E68</f>
-        <v/>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" s="81" t="inlineStr">
-        <is>
-          <t>5.2</t>
-        </is>
-      </c>
-      <c r="B69" s="403" t="inlineStr">
-        <is>
-          <t>Mampostería en ladrillo</t>
-        </is>
-      </c>
-      <c r="C69" s="272" t="inlineStr">
-        <is>
-          <t>M²</t>
-        </is>
-      </c>
-      <c r="D69" s="273" t="n"/>
-      <c r="E69" s="1295" t="n"/>
-      <c r="F69" s="1296">
-        <f>D69*E69</f>
-        <v/>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" s="81" t="inlineStr">
-        <is>
-          <t>5.3</t>
-        </is>
-      </c>
-      <c r="B70" s="403" t="inlineStr">
-        <is>
-          <t>Mampostería estructural</t>
-        </is>
-      </c>
-      <c r="C70" s="272" t="inlineStr">
-        <is>
-          <t>M²</t>
-        </is>
-      </c>
-      <c r="D70" s="273" t="n"/>
-      <c r="E70" s="1295" t="n"/>
-      <c r="F70" s="1296">
-        <f>D70*E70</f>
-        <v/>
-      </c>
+      <c r="C70" s="587" t="n"/>
+      <c r="D70" s="587" t="n"/>
+      <c r="E70" s="587" t="n"/>
+      <c r="F70" s="588" t="n"/>
     </row>
     <row r="71">
       <c r="A71" s="81" t="inlineStr">
         <is>
-          <t>5.4</t>
+          <t>5.1</t>
         </is>
       </c>
       <c r="B71" s="403" t="inlineStr">
         <is>
-          <t>Muros en sistema liviano / drywall</t>
+          <t>Mampostería en bloque de concreto</t>
         </is>
       </c>
       <c r="C71" s="272" t="inlineStr">
@@ -12298,17 +12303,17 @@
     <row r="72">
       <c r="A72" s="81" t="inlineStr">
         <is>
-          <t>5.5</t>
+          <t>5.2</t>
         </is>
       </c>
       <c r="B72" s="403" t="inlineStr">
         <is>
-          <t>Dinteles sobre vanos</t>
+          <t>Mampostería en ladrillo</t>
         </is>
       </c>
       <c r="C72" s="272" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>M²</t>
         </is>
       </c>
       <c r="D72" s="273" t="n"/>
@@ -12321,17 +12326,17 @@
     <row r="73">
       <c r="A73" s="81" t="inlineStr">
         <is>
-          <t>5.6</t>
+          <t>5.3</t>
         </is>
       </c>
       <c r="B73" s="403" t="inlineStr">
         <is>
-          <t>Alfajías y remates</t>
+          <t>Mampostería estructural</t>
         </is>
       </c>
       <c r="C73" s="272" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>M²</t>
         </is>
       </c>
       <c r="D73" s="273" t="n"/>
@@ -12344,17 +12349,17 @@
     <row r="74">
       <c r="A74" s="81" t="inlineStr">
         <is>
-          <t>5.7</t>
+          <t>5.4</t>
         </is>
       </c>
       <c r="B74" s="403" t="inlineStr">
         <is>
-          <t>Anclajes y refuerzos de mampostería</t>
+          <t>Muros en sistema liviano / drywall</t>
         </is>
       </c>
       <c r="C74" s="272" t="inlineStr">
         <is>
-          <t>UND</t>
+          <t>M²</t>
         </is>
       </c>
       <c r="D74" s="273" t="n"/>
@@ -12365,61 +12370,93 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="82" t="n"/>
-      <c r="B75" s="693" t="inlineStr">
-        <is>
-          <t>SUBTOTAL CAPÍTULO 5 - MAMPOSTERÍA</t>
-        </is>
-      </c>
-      <c r="C75" s="536" t="n"/>
-      <c r="D75" s="536" t="n"/>
-      <c r="E75" s="536" t="n"/>
-      <c r="F75" s="1297">
-        <f>SUM(F68:F74)</f>
+      <c r="A75" s="81" t="inlineStr">
+        <is>
+          <t>5.5</t>
+        </is>
+      </c>
+      <c r="B75" s="403" t="inlineStr">
+        <is>
+          <t>Dinteles sobre vanos</t>
+        </is>
+      </c>
+      <c r="C75" s="272" t="inlineStr">
+        <is>
+          <t>ML</t>
+        </is>
+      </c>
+      <c r="D75" s="273" t="n"/>
+      <c r="E75" s="1295" t="n"/>
+      <c r="F75" s="1296">
+        <f>D75*E75</f>
         <v/>
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="83" t="n"/>
-      <c r="B76" s="694" t="n"/>
-      <c r="C76" s="536" t="n"/>
-      <c r="D76" s="536" t="n"/>
-      <c r="E76" s="536" t="n"/>
-      <c r="F76" s="695" t="n"/>
+      <c r="A76" s="81" t="inlineStr">
+        <is>
+          <t>5.6</t>
+        </is>
+      </c>
+      <c r="B76" s="403" t="inlineStr">
+        <is>
+          <t>Alfajías y remates</t>
+        </is>
+      </c>
+      <c r="C76" s="272" t="inlineStr">
+        <is>
+          <t>ML</t>
+        </is>
+      </c>
+      <c r="D76" s="273" t="n"/>
+      <c r="E76" s="1295" t="n"/>
+      <c r="F76" s="1296">
+        <f>D76*E76</f>
+        <v/>
+      </c>
     </row>
     <row r="77">
-      <c r="A77" s="189" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="B77" s="704" t="inlineStr">
-        <is>
-          <t>CUBIERTAS</t>
-        </is>
-      </c>
-      <c r="C77" s="536" t="n"/>
-      <c r="D77" s="536" t="n"/>
-      <c r="E77" s="536" t="n"/>
-      <c r="F77" s="536" t="n"/>
+      <c r="A77" s="81" t="inlineStr">
+        <is>
+          <t>5.7</t>
+        </is>
+      </c>
+      <c r="B77" s="403" t="inlineStr">
+        <is>
+          <t>Anclajes y refuerzos de mampostería</t>
+        </is>
+      </c>
+      <c r="C77" s="272" t="inlineStr">
+        <is>
+          <t>UND</t>
+        </is>
+      </c>
+      <c r="D77" s="273" t="n"/>
+      <c r="E77" s="1295" t="n"/>
+      <c r="F77" s="1296">
+        <f>D77*E77</f>
+        <v/>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="81" t="inlineStr">
         <is>
-          <t>6.1</t>
-        </is>
-      </c>
-      <c r="B78" s="404" t="inlineStr">
-        <is>
-          <t>Estructura metálica o de madera para cubierta</t>
+          <t>5.8</t>
+        </is>
+      </c>
+      <c r="B78" s="403" t="inlineStr">
+        <is>
+          <t>Mampostería en ladrillo tolete a la vista (reforzada)</t>
         </is>
       </c>
       <c r="C78" s="272" t="inlineStr">
         <is>
-          <t>KG</t>
-        </is>
-      </c>
-      <c r="F78">
+          <t>M²</t>
+        </is>
+      </c>
+      <c r="D78" s="273" t="n"/>
+      <c r="E78" s="1295" t="n"/>
+      <c r="F78" s="1296">
         <f>D78*E78</f>
         <v/>
       </c>
@@ -12427,17 +12464,17 @@
     <row r="79">
       <c r="A79" s="81" t="inlineStr">
         <is>
-          <t>6.2</t>
+          <t>5.9</t>
         </is>
       </c>
       <c r="B79" s="403" t="inlineStr">
         <is>
-          <t>Cerchas y elementos estructurales</t>
+          <t>Mampostería en ladrillo a la vista (no reforzada)</t>
         </is>
       </c>
       <c r="C79" s="272" t="inlineStr">
         <is>
-          <t>KG</t>
+          <t>M²</t>
         </is>
       </c>
       <c r="D79" s="273" t="n"/>
@@ -12448,93 +12485,61 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="81" t="inlineStr">
-        <is>
-          <t>6.3</t>
-        </is>
-      </c>
-      <c r="B80" s="403" t="inlineStr">
-        <is>
-          <t>Suministro e instalación de teja</t>
-        </is>
-      </c>
-      <c r="C80" s="272" t="inlineStr">
-        <is>
-          <t>M²</t>
-        </is>
-      </c>
-      <c r="D80" s="273" t="n"/>
-      <c r="E80" s="1295" t="n"/>
-      <c r="F80" s="1296">
-        <f>D80*E80</f>
+      <c r="A80" s="82" t="n"/>
+      <c r="B80" s="693" t="inlineStr">
+        <is>
+          <t>SUBTOTAL CAPÍTULO 5 - MAMPOSTERÍA</t>
+        </is>
+      </c>
+      <c r="C80" s="536" t="n"/>
+      <c r="D80" s="536" t="n"/>
+      <c r="E80" s="536" t="n"/>
+      <c r="F80" s="1297">
+        <f>SUM(F71:F79)</f>
         <v/>
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="81" t="inlineStr">
-        <is>
-          <t>6.4</t>
-        </is>
-      </c>
-      <c r="B81" s="403" t="inlineStr">
-        <is>
-          <t>Impermeabilización de cubierta</t>
-        </is>
-      </c>
-      <c r="C81" s="272" t="inlineStr">
-        <is>
-          <t>M²</t>
-        </is>
-      </c>
-      <c r="D81" s="273" t="n"/>
-      <c r="E81" s="1295" t="n"/>
-      <c r="F81" s="1296">
-        <f>D81*E81</f>
-        <v/>
-      </c>
+      <c r="A81" s="83" t="n"/>
+      <c r="B81" s="694" t="n"/>
+      <c r="C81" s="536" t="n"/>
+      <c r="D81" s="536" t="n"/>
+      <c r="E81" s="536" t="n"/>
+      <c r="F81" s="695" t="n"/>
     </row>
     <row r="82">
-      <c r="A82" s="81" t="inlineStr">
-        <is>
-          <t>6.5</t>
-        </is>
-      </c>
-      <c r="B82" s="403" t="inlineStr">
-        <is>
-          <t>Aislamiento térmico/acústico</t>
-        </is>
-      </c>
-      <c r="C82" s="272" t="inlineStr">
-        <is>
-          <t>M²</t>
-        </is>
-      </c>
-      <c r="D82" s="273" t="n"/>
-      <c r="E82" s="1295" t="n"/>
-      <c r="F82" s="1296">
-        <f>D82*E82</f>
-        <v/>
-      </c>
+      <c r="A82" s="189" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B82" s="704" t="inlineStr">
+        <is>
+          <t>CUBIERTAS</t>
+        </is>
+      </c>
+      <c r="C82" s="536" t="n"/>
+      <c r="D82" s="536" t="n"/>
+      <c r="E82" s="536" t="n"/>
+      <c r="F82" s="536" t="n"/>
     </row>
     <row r="83">
       <c r="A83" s="81" t="inlineStr">
         <is>
-          <t>6.6</t>
-        </is>
-      </c>
-      <c r="B83" s="403" t="inlineStr">
-        <is>
-          <t>Canales de aguas lluvias</t>
+          <t>6.1</t>
+        </is>
+      </c>
+      <c r="B83" s="404" t="inlineStr">
+        <is>
+          <t>Estructura metálica o de madera para cubierta</t>
         </is>
       </c>
       <c r="C83" s="272" t="inlineStr">
         <is>
-          <t>ML</t>
-        </is>
-      </c>
-      <c r="D83" s="273" t="n"/>
-      <c r="E83" s="1295" t="n"/>
-      <c r="F83" s="1296">
+          <t>KG</t>
+        </is>
+      </c>
+      <c r="F83">
         <f>D83*E83</f>
         <v/>
       </c>
@@ -12542,17 +12547,17 @@
     <row r="84">
       <c r="A84" s="81" t="inlineStr">
         <is>
-          <t>6.7</t>
+          <t>6.2</t>
         </is>
       </c>
       <c r="B84" s="403" t="inlineStr">
         <is>
-          <t>Bajantes de aguas lluvias</t>
+          <t>Cerchas y elementos estructurales</t>
         </is>
       </c>
       <c r="C84" s="272" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>KG</t>
         </is>
       </c>
       <c r="D84" s="273" t="n"/>
@@ -12563,58 +12568,88 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="82" t="n"/>
-      <c r="B85" s="693" t="inlineStr">
-        <is>
-          <t>SUBTOTAL CAPÍTULO 6 - CUBIERTAS</t>
-        </is>
-      </c>
-      <c r="C85" s="536" t="n"/>
-      <c r="D85" s="536" t="n"/>
-      <c r="E85" s="536" t="n"/>
-      <c r="F85" s="1297">
-        <f>SUM(F78:F84)</f>
+      <c r="A85" s="81" t="inlineStr">
+        <is>
+          <t>6.3</t>
+        </is>
+      </c>
+      <c r="B85" s="403" t="inlineStr">
+        <is>
+          <t>Suministro e instalación de teja</t>
+        </is>
+      </c>
+      <c r="C85" s="272" t="inlineStr">
+        <is>
+          <t>M²</t>
+        </is>
+      </c>
+      <c r="D85" s="273" t="n"/>
+      <c r="E85" s="1295" t="n"/>
+      <c r="F85" s="1296">
+        <f>D85*E85</f>
         <v/>
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="83" t="n"/>
-      <c r="B86" s="694" t="n"/>
-      <c r="C86" s="694" t="n"/>
-      <c r="D86" s="694" t="n"/>
-      <c r="E86" s="694" t="n"/>
-      <c r="F86" s="695" t="n"/>
+      <c r="A86" s="81" t="inlineStr">
+        <is>
+          <t>6.4</t>
+        </is>
+      </c>
+      <c r="B86" s="403" t="inlineStr">
+        <is>
+          <t>Impermeabilización de cubierta</t>
+        </is>
+      </c>
+      <c r="C86" s="272" t="inlineStr">
+        <is>
+          <t>M²</t>
+        </is>
+      </c>
+      <c r="D86" s="273" t="n"/>
+      <c r="E86" s="1295" t="n"/>
+      <c r="F86" s="1296">
+        <f>D86*E86</f>
+        <v/>
+      </c>
     </row>
     <row r="87">
-      <c r="A87" s="189" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="B87" s="692" t="inlineStr">
-        <is>
-          <t>IMPERMEABILIZACIONES</t>
-        </is>
-      </c>
-      <c r="C87" s="536" t="n"/>
-      <c r="D87" s="536" t="n"/>
-      <c r="E87" s="536" t="n"/>
-      <c r="F87" s="536" t="n"/>
+      <c r="A87" s="81" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="B87" s="403" t="inlineStr">
+        <is>
+          <t>Aislamiento térmico/acústico</t>
+        </is>
+      </c>
+      <c r="C87" s="272" t="inlineStr">
+        <is>
+          <t>M²</t>
+        </is>
+      </c>
+      <c r="D87" s="273" t="n"/>
+      <c r="E87" s="1295" t="n"/>
+      <c r="F87" s="1296">
+        <f>D87*E87</f>
+        <v/>
+      </c>
     </row>
     <row r="88">
       <c r="A88" s="81" t="inlineStr">
         <is>
-          <t>7.1</t>
+          <t>6.6</t>
         </is>
       </c>
       <c r="B88" s="403" t="inlineStr">
         <is>
-          <t>Impermeabilización de losas y terrazas</t>
+          <t>Canales de aguas lluvias</t>
         </is>
       </c>
       <c r="C88" s="272" t="inlineStr">
         <is>
-          <t>M²</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="D88" s="273" t="n"/>
@@ -12627,20 +12662,22 @@
     <row r="89">
       <c r="A89" s="81" t="inlineStr">
         <is>
-          <t>7.2</t>
-        </is>
-      </c>
-      <c r="B89" s="404" t="inlineStr">
-        <is>
-          <t>Impermeabilización de muros</t>
+          <t>6.7</t>
+        </is>
+      </c>
+      <c r="B89" s="403" t="inlineStr">
+        <is>
+          <t>Bajantes de aguas lluvias</t>
         </is>
       </c>
       <c r="C89" s="272" t="inlineStr">
         <is>
-          <t>M²</t>
-        </is>
-      </c>
-      <c r="F89">
+          <t>ML</t>
+        </is>
+      </c>
+      <c r="D89" s="273" t="n"/>
+      <c r="E89" s="1295" t="n"/>
+      <c r="F89" s="1296">
         <f>D89*E89</f>
         <v/>
       </c>
@@ -12648,12 +12685,12 @@
     <row r="90">
       <c r="A90" s="81" t="inlineStr">
         <is>
-          <t>7.3</t>
+          <t>6.8</t>
         </is>
       </c>
       <c r="B90" s="403" t="inlineStr">
         <is>
-          <t>Impermeabilización de zonas húmedas</t>
+          <t>Cielo raso Dry Wall</t>
         </is>
       </c>
       <c r="C90" s="272" t="inlineStr">
@@ -12669,74 +12706,76 @@
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="82" t="n"/>
-      <c r="B91" s="693" t="inlineStr">
-        <is>
-          <t>SUBTOTAL CAPÍTULO 7 - IMPERMEABILIZACIONES</t>
-        </is>
-      </c>
-      <c r="C91" s="536" t="n"/>
-      <c r="D91" s="536" t="n"/>
-      <c r="E91" s="536" t="n"/>
-      <c r="F91" s="1297">
-        <f>SUM(F88:F90)</f>
+      <c r="A91" s="81" t="inlineStr">
+        <is>
+          <t>6.9</t>
+        </is>
+      </c>
+      <c r="B91" s="403" t="inlineStr">
+        <is>
+          <t>Cielo raso en lámina acústica de fibra mineral</t>
+        </is>
+      </c>
+      <c r="C91" s="272" t="inlineStr">
+        <is>
+          <t>M²</t>
+        </is>
+      </c>
+      <c r="D91" s="273" t="n"/>
+      <c r="E91" s="1295" t="n"/>
+      <c r="F91" s="1296">
+        <f>D91*E91</f>
         <v/>
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="83" t="n"/>
-      <c r="B92" s="694" t="n"/>
+      <c r="A92" s="82" t="n"/>
+      <c r="B92" s="693" t="inlineStr">
+        <is>
+          <t>SUBTOTAL CAPÍTULO 6 - CUBIERTAS</t>
+        </is>
+      </c>
       <c r="C92" s="536" t="n"/>
       <c r="D92" s="536" t="n"/>
       <c r="E92" s="536" t="n"/>
-      <c r="F92" s="695" t="n"/>
+      <c r="F92" s="1297">
+        <f>SUM(F83:F91)</f>
+        <v/>
+      </c>
     </row>
     <row r="93">
-      <c r="A93" s="189" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="B93" s="692" t="inlineStr">
-        <is>
-          <t>PAÑETES Y REVOQUES</t>
-        </is>
-      </c>
-      <c r="C93" s="536" t="n"/>
-      <c r="D93" s="536" t="n"/>
-      <c r="E93" s="536" t="n"/>
-      <c r="F93" s="536" t="n"/>
+      <c r="A93" s="83" t="n"/>
+      <c r="B93" s="694" t="n"/>
+      <c r="C93" s="694" t="n"/>
+      <c r="D93" s="694" t="n"/>
+      <c r="E93" s="694" t="n"/>
+      <c r="F93" s="695" t="n"/>
     </row>
     <row r="94">
-      <c r="A94" s="81" t="inlineStr">
-        <is>
-          <t>8.1</t>
-        </is>
-      </c>
-      <c r="B94" s="404" t="inlineStr">
-        <is>
-          <t>Pañete / revoque interior</t>
-        </is>
-      </c>
-      <c r="C94" s="272" t="inlineStr">
-        <is>
-          <t>M²</t>
-        </is>
-      </c>
-      <c r="F94">
-        <f>D94*E94</f>
-        <v/>
-      </c>
+      <c r="A94" s="189" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B94" s="692" t="inlineStr">
+        <is>
+          <t>IMPERMEABILIZACIONES</t>
+        </is>
+      </c>
+      <c r="C94" s="536" t="n"/>
+      <c r="D94" s="536" t="n"/>
+      <c r="E94" s="536" t="n"/>
+      <c r="F94" s="536" t="n"/>
     </row>
     <row r="95">
       <c r="A95" s="81" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>7.1</t>
         </is>
       </c>
       <c r="B95" s="403" t="inlineStr">
         <is>
-          <t>Pañete / revoque exterior</t>
+          <t>Impermeabilización de losas y terrazas</t>
         </is>
       </c>
       <c r="C95" s="272" t="inlineStr">
@@ -12754,12 +12793,12 @@
     <row r="96">
       <c r="A96" s="81" t="inlineStr">
         <is>
-          <t>8.3</t>
-        </is>
-      </c>
-      <c r="B96" s="403" t="inlineStr">
-        <is>
-          <t>Pañete impermeabilizado</t>
+          <t>7.2</t>
+        </is>
+      </c>
+      <c r="B96" s="404" t="inlineStr">
+        <is>
+          <t>Impermeabilización de muros</t>
         </is>
       </c>
       <c r="C96" s="272" t="inlineStr">
@@ -12767,9 +12806,7 @@
           <t>M²</t>
         </is>
       </c>
-      <c r="D96" s="273" t="n"/>
-      <c r="E96" s="1295" t="n"/>
-      <c r="F96" s="1296">
+      <c r="F96">
         <f>D96*E96</f>
         <v/>
       </c>
@@ -12777,12 +12814,12 @@
     <row r="97">
       <c r="A97" s="81" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>7.3</t>
         </is>
       </c>
       <c r="B97" s="403" t="inlineStr">
         <is>
-          <t>Estuco plástico o tradicional</t>
+          <t>Impermeabilización de zonas húmedas</t>
         </is>
       </c>
       <c r="C97" s="272" t="inlineStr">
@@ -12790,82 +12827,84 @@
           <t>M²</t>
         </is>
       </c>
+      <c r="D97" s="273" t="n"/>
+      <c r="E97" s="1295" t="n"/>
       <c r="F97" s="1296">
         <f>D97*E97</f>
         <v/>
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="82" t="n"/>
-      <c r="B98" s="693" t="inlineStr">
-        <is>
-          <t>SUBTOTAL CAPÍTULO 8 - PAÑETES Y REVOQUES</t>
-        </is>
-      </c>
-      <c r="C98" s="536" t="n"/>
-      <c r="D98" s="536" t="n"/>
-      <c r="E98" s="536" t="n"/>
-      <c r="F98" s="1297">
-        <f>SUM(F94:F97)</f>
+      <c r="A98" s="81" t="inlineStr">
+        <is>
+          <t>7.4</t>
+        </is>
+      </c>
+      <c r="B98" s="403" t="inlineStr">
+        <is>
+          <t>Geomembrana HDPE para impermeabilización de terrenos</t>
+        </is>
+      </c>
+      <c r="C98" s="272" t="inlineStr">
+        <is>
+          <t>M²</t>
+        </is>
+      </c>
+      <c r="D98" s="273" t="n"/>
+      <c r="E98" s="1295" t="n"/>
+      <c r="F98" s="1296">
+        <f>D98*E98</f>
         <v/>
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="83" t="n"/>
-      <c r="B99" s="695" t="n"/>
+      <c r="A99" s="82" t="n"/>
+      <c r="B99" s="693" t="inlineStr">
+        <is>
+          <t>SUBTOTAL CAPÍTULO 7 - IMPERMEABILIZACIONES</t>
+        </is>
+      </c>
       <c r="C99" s="536" t="n"/>
       <c r="D99" s="536" t="n"/>
       <c r="E99" s="536" t="n"/>
-      <c r="F99" s="585" t="n"/>
+      <c r="F99" s="1297">
+        <f>SUM(F95:F98)</f>
+        <v/>
+      </c>
     </row>
     <row r="100">
-      <c r="A100" s="189" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="B100" s="692" t="inlineStr">
-        <is>
-          <t>PISOS Y ENCHAPES</t>
-        </is>
-      </c>
+      <c r="A100" s="83" t="n"/>
+      <c r="B100" s="694" t="n"/>
       <c r="C100" s="536" t="n"/>
       <c r="D100" s="536" t="n"/>
       <c r="E100" s="536" t="n"/>
-      <c r="F100" s="536" t="n"/>
+      <c r="F100" s="695" t="n"/>
     </row>
     <row r="101">
-      <c r="A101" s="81" t="inlineStr">
-        <is>
-          <t>9.1</t>
-        </is>
-      </c>
-      <c r="B101" s="403" t="inlineStr">
-        <is>
-          <t>Mortero de nivelación</t>
-        </is>
-      </c>
-      <c r="C101" s="272" t="inlineStr">
-        <is>
-          <t>M²</t>
-        </is>
-      </c>
-      <c r="D101" s="273" t="n"/>
-      <c r="E101" s="1295" t="n"/>
-      <c r="F101" s="1296">
-        <f>D101*E101</f>
-        <v/>
-      </c>
+      <c r="A101" s="189" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B101" s="692" t="inlineStr">
+        <is>
+          <t>PAÑETES Y REVOQUES</t>
+        </is>
+      </c>
+      <c r="C101" s="536" t="n"/>
+      <c r="D101" s="536" t="n"/>
+      <c r="E101" s="536" t="n"/>
+      <c r="F101" s="536" t="n"/>
     </row>
     <row r="102">
       <c r="A102" s="81" t="inlineStr">
         <is>
-          <t>9.2</t>
-        </is>
-      </c>
-      <c r="B102" s="403" t="inlineStr">
-        <is>
-          <t>Piso cerámico</t>
+          <t>8.1</t>
+        </is>
+      </c>
+      <c r="B102" s="404" t="inlineStr">
+        <is>
+          <t>Pañete / revoque interior</t>
         </is>
       </c>
       <c r="C102" s="272" t="inlineStr">
@@ -12873,9 +12912,7 @@
           <t>M²</t>
         </is>
       </c>
-      <c r="D102" s="273" t="n"/>
-      <c r="E102" s="1295" t="n"/>
-      <c r="F102" s="1296">
+      <c r="F102">
         <f>D102*E102</f>
         <v/>
       </c>
@@ -12883,12 +12920,12 @@
     <row r="103">
       <c r="A103" s="81" t="inlineStr">
         <is>
-          <t>9.3</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="B103" s="403" t="inlineStr">
         <is>
-          <t>Piso en porcelanato</t>
+          <t>Pañete / revoque exterior</t>
         </is>
       </c>
       <c r="C103" s="272" t="inlineStr">
@@ -12906,12 +12943,12 @@
     <row r="104">
       <c r="A104" s="81" t="inlineStr">
         <is>
-          <t>9.4</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="B104" s="403" t="inlineStr">
         <is>
-          <t>Piso vinílico</t>
+          <t>Pañete impermeabilizado</t>
         </is>
       </c>
       <c r="C104" s="272" t="inlineStr">
@@ -12929,12 +12966,12 @@
     <row r="105">
       <c r="A105" s="81" t="inlineStr">
         <is>
-          <t>9.5</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="B105" s="403" t="inlineStr">
         <is>
-          <t>Piso laminado</t>
+          <t>Estuco plástico o tradicional</t>
         </is>
       </c>
       <c r="C105" s="272" t="inlineStr">
@@ -12942,126 +12979,128 @@
           <t>M²</t>
         </is>
       </c>
-      <c r="D105" s="273" t="n"/>
-      <c r="E105" s="1295" t="n"/>
       <c r="F105" s="1296">
         <f>D105*E105</f>
         <v/>
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="81" t="inlineStr">
-        <is>
-          <t>9.6</t>
-        </is>
-      </c>
-      <c r="B106" s="403" t="inlineStr">
-        <is>
-          <t>Enchape cerámico en muros</t>
-        </is>
-      </c>
-      <c r="C106" s="272" t="inlineStr">
+      <c r="A106" s="82" t="n"/>
+      <c r="B106" s="693" t="inlineStr">
+        <is>
+          <t>SUBTOTAL CAPÍTULO 8 - PAÑETES Y REVOQUES</t>
+        </is>
+      </c>
+      <c r="C106" s="536" t="n"/>
+      <c r="D106" s="536" t="n"/>
+      <c r="E106" s="536" t="n"/>
+      <c r="F106" s="1297">
+        <f>SUM(F102:F105)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="83" t="n"/>
+      <c r="B107" s="695" t="n"/>
+      <c r="C107" s="536" t="n"/>
+      <c r="D107" s="536" t="n"/>
+      <c r="E107" s="536" t="n"/>
+      <c r="F107" s="585" t="n"/>
+    </row>
+    <row r="108">
+      <c r="A108" s="189" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B108" s="692" t="inlineStr">
+        <is>
+          <t>PISOS Y ENCHAPES</t>
+        </is>
+      </c>
+      <c r="C108" s="536" t="n"/>
+      <c r="D108" s="536" t="n"/>
+      <c r="E108" s="536" t="n"/>
+      <c r="F108" s="536" t="n"/>
+    </row>
+    <row r="109">
+      <c r="A109" s="81" t="inlineStr">
+        <is>
+          <t>9.1</t>
+        </is>
+      </c>
+      <c r="B109" s="403" t="inlineStr">
+        <is>
+          <t>Mortero de nivelación</t>
+        </is>
+      </c>
+      <c r="C109" s="272" t="inlineStr">
         <is>
           <t>M²</t>
         </is>
       </c>
-      <c r="F106" s="1296">
-        <f>D106*E106</f>
-        <v/>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" s="81" t="inlineStr">
-        <is>
-          <t>9.7</t>
-        </is>
-      </c>
-      <c r="B107" s="403" t="inlineStr">
-        <is>
-          <t>Guardaescoba</t>
-        </is>
-      </c>
-      <c r="C107" s="272" t="inlineStr">
-        <is>
-          <t>ML</t>
-        </is>
-      </c>
-      <c r="D107" s="273" t="n"/>
-      <c r="E107" s="1295" t="n"/>
-      <c r="F107" s="1296">
-        <f>D107*E107</f>
-        <v/>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" s="81" t="inlineStr">
-        <is>
-          <t>9.8</t>
-        </is>
-      </c>
-      <c r="B108" s="404" t="inlineStr">
-        <is>
-          <t>Juntas de dilatación / construcción</t>
-        </is>
-      </c>
-      <c r="C108" s="272" t="inlineStr">
-        <is>
-          <t>ML</t>
-        </is>
-      </c>
-      <c r="F108">
-        <f>D108*E108</f>
-        <v/>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" s="82" t="n"/>
-      <c r="B109" s="693" t="inlineStr">
-        <is>
-          <t>SUBTOTAL CAPÍTULO 9 - PISOS Y ENCHAPES</t>
-        </is>
-      </c>
-      <c r="C109" s="536" t="n"/>
-      <c r="D109" s="536" t="n"/>
-      <c r="E109" s="536" t="n"/>
-      <c r="F109" s="1297">
-        <f>SUM(F101:F108)</f>
+      <c r="D109" s="273" t="n"/>
+      <c r="E109" s="1295" t="n"/>
+      <c r="F109" s="1296">
+        <f>D109*E109</f>
         <v/>
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="83" t="n"/>
-      <c r="B110" s="694" t="n"/>
-      <c r="C110" s="694" t="n"/>
-      <c r="D110" s="694" t="n"/>
-      <c r="E110" s="694" t="n"/>
-      <c r="F110" s="695" t="n"/>
+      <c r="A110" s="81" t="inlineStr">
+        <is>
+          <t>9.2</t>
+        </is>
+      </c>
+      <c r="B110" s="403" t="inlineStr">
+        <is>
+          <t>Piso cerámico</t>
+        </is>
+      </c>
+      <c r="C110" s="272" t="inlineStr">
+        <is>
+          <t>M²</t>
+        </is>
+      </c>
+      <c r="D110" s="273" t="n"/>
+      <c r="E110" s="1295" t="n"/>
+      <c r="F110" s="1296">
+        <f>D110*E110</f>
+        <v/>
+      </c>
     </row>
     <row r="111">
-      <c r="A111" s="189" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="B111" s="692" t="inlineStr">
-        <is>
-          <t>PINTURA</t>
-        </is>
-      </c>
-      <c r="C111" s="536" t="n"/>
-      <c r="D111" s="536" t="n"/>
-      <c r="E111" s="536" t="n"/>
-      <c r="F111" s="536" t="n"/>
+      <c r="A111" s="81" t="inlineStr">
+        <is>
+          <t>9.3</t>
+        </is>
+      </c>
+      <c r="B111" s="403" t="inlineStr">
+        <is>
+          <t>Piso en porcelanato</t>
+        </is>
+      </c>
+      <c r="C111" s="272" t="inlineStr">
+        <is>
+          <t>M²</t>
+        </is>
+      </c>
+      <c r="D111" s="273" t="n"/>
+      <c r="E111" s="1295" t="n"/>
+      <c r="F111" s="1296">
+        <f>D111*E111</f>
+        <v/>
+      </c>
     </row>
     <row r="112">
       <c r="A112" s="81" t="inlineStr">
         <is>
-          <t>10.1</t>
+          <t>9.4</t>
         </is>
       </c>
       <c r="B112" s="403" t="inlineStr">
         <is>
-          <t>Pintura vinílica interior</t>
+          <t>Piso vinílico</t>
         </is>
       </c>
       <c r="C112" s="272" t="inlineStr">
@@ -13079,12 +13118,12 @@
     <row r="113">
       <c r="A113" s="81" t="inlineStr">
         <is>
-          <t>10.2</t>
+          <t>9.5</t>
         </is>
       </c>
       <c r="B113" s="403" t="inlineStr">
         <is>
-          <t>Pintura exterior</t>
+          <t>Piso laminado</t>
         </is>
       </c>
       <c r="C113" s="272" t="inlineStr">
@@ -13102,12 +13141,12 @@
     <row r="114">
       <c r="A114" s="81" t="inlineStr">
         <is>
-          <t>10.3</t>
+          <t>9.6</t>
         </is>
       </c>
       <c r="B114" s="403" t="inlineStr">
         <is>
-          <t>Pintura esmalte en superficies metálicas/madera</t>
+          <t>Enchape cerámico en muros</t>
         </is>
       </c>
       <c r="C114" s="272" t="inlineStr">
@@ -13115,8 +13154,6 @@
           <t>M²</t>
         </is>
       </c>
-      <c r="D114" s="273" t="n"/>
-      <c r="E114" s="1295" t="n"/>
       <c r="F114" s="1296">
         <f>D114*E114</f>
         <v/>
@@ -13125,17 +13162,17 @@
     <row r="115">
       <c r="A115" s="81" t="inlineStr">
         <is>
-          <t>10.4</t>
+          <t>9.7</t>
         </is>
       </c>
       <c r="B115" s="403" t="inlineStr">
         <is>
-          <t>Pintura anticorrosiva</t>
+          <t>Guardaescoba</t>
         </is>
       </c>
       <c r="C115" s="272" t="inlineStr">
         <is>
-          <t>M²</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="D115" s="273" t="n"/>
@@ -13148,147 +13185,145 @@
     <row r="116">
       <c r="A116" s="81" t="inlineStr">
         <is>
-          <t>10.5</t>
-        </is>
-      </c>
-      <c r="B116" s="403" t="inlineStr">
-        <is>
-          <t>Sellador / imprimante</t>
+          <t>9.8</t>
+        </is>
+      </c>
+      <c r="B116" s="404" t="inlineStr">
+        <is>
+          <t>Juntas de dilatación / construcción</t>
         </is>
       </c>
       <c r="C116" s="272" t="inlineStr">
         <is>
+          <t>ML</t>
+        </is>
+      </c>
+      <c r="F116">
+        <f>D116*E116</f>
+        <v/>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="81" t="inlineStr">
+        <is>
+          <t>9.9</t>
+        </is>
+      </c>
+      <c r="B117" s="404" t="inlineStr">
+        <is>
+          <t>Piso en concreto afinado con endurecedor de cuarzo</t>
+        </is>
+      </c>
+      <c r="C117" s="272" t="inlineStr">
+        <is>
           <t>M²</t>
         </is>
       </c>
-      <c r="F116" s="1296">
-        <f>D116*E116</f>
-        <v/>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" s="82" t="n"/>
-      <c r="B117" s="693" t="inlineStr">
-        <is>
-          <t>SUBTOTAL CAPÍTULO 10 - PINTURA</t>
-        </is>
-      </c>
-      <c r="C117" s="536" t="n"/>
-      <c r="D117" s="536" t="n"/>
-      <c r="E117" s="536" t="n"/>
-      <c r="F117" s="1297">
-        <f>SUM(F112:F116)</f>
+      <c r="F117">
+        <f>D117*E117</f>
         <v/>
       </c>
     </row>
     <row r="118">
-      <c r="A118" s="83" t="n"/>
-      <c r="B118" s="695" t="n"/>
-      <c r="C118" s="536" t="n"/>
-      <c r="D118" s="536" t="n"/>
-      <c r="E118" s="536" t="n"/>
-      <c r="F118" s="585" t="n"/>
+      <c r="A118" s="81" t="inlineStr">
+        <is>
+          <t>9.10</t>
+        </is>
+      </c>
+      <c r="B118" s="404" t="inlineStr">
+        <is>
+          <t>Baldosa de granito</t>
+        </is>
+      </c>
+      <c r="C118" s="272" t="inlineStr">
+        <is>
+          <t>M²</t>
+        </is>
+      </c>
+      <c r="F118">
+        <f>D118*E118</f>
+        <v/>
+      </c>
     </row>
     <row r="119">
-      <c r="A119" s="189" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="B119" s="692" t="inlineStr">
-        <is>
-          <t>CARPINTERÍA</t>
-        </is>
-      </c>
-      <c r="C119" s="536" t="n"/>
-      <c r="D119" s="536" t="n"/>
-      <c r="E119" s="536" t="n"/>
-      <c r="F119" s="536" t="n"/>
+      <c r="A119" s="81" t="inlineStr">
+        <is>
+          <t>9.11</t>
+        </is>
+      </c>
+      <c r="B119" s="404" t="inlineStr">
+        <is>
+          <t>Enchape en granito pulido</t>
+        </is>
+      </c>
+      <c r="C119" s="272" t="inlineStr">
+        <is>
+          <t>M²</t>
+        </is>
+      </c>
+      <c r="F119">
+        <f>D119*E119</f>
+        <v/>
+      </c>
     </row>
     <row r="120">
-      <c r="A120" s="81" t="inlineStr">
-        <is>
-          <t>11.1</t>
-        </is>
-      </c>
-      <c r="B120" s="403" t="inlineStr">
-        <is>
-          <t>Puertas de madera</t>
-        </is>
-      </c>
-      <c r="C120" s="272" t="inlineStr">
-        <is>
-          <t>UND</t>
-        </is>
-      </c>
-      <c r="D120" s="273" t="n"/>
-      <c r="E120" s="1295" t="n"/>
-      <c r="F120" s="1296">
-        <f>D120*E120</f>
+      <c r="A120" s="82" t="n"/>
+      <c r="B120" s="693" t="inlineStr">
+        <is>
+          <t>SUBTOTAL CAPÍTULO 9 - PISOS Y ENCHAPES</t>
+        </is>
+      </c>
+      <c r="C120" s="536" t="n"/>
+      <c r="D120" s="536" t="n"/>
+      <c r="E120" s="536" t="n"/>
+      <c r="F120" s="1297">
+        <f>SUM(F109:F119)</f>
         <v/>
       </c>
     </row>
     <row r="121">
-      <c r="A121" s="81" t="inlineStr">
-        <is>
-          <t>11.2</t>
-        </is>
-      </c>
-      <c r="B121" s="403" t="inlineStr">
-        <is>
-          <t>Muebles fijos de madera</t>
-        </is>
-      </c>
-      <c r="C121" s="272" t="inlineStr">
-        <is>
-          <t>ML</t>
-        </is>
-      </c>
-      <c r="F121" s="1296">
-        <f>D121*E121</f>
-        <v/>
-      </c>
+      <c r="A121" s="83" t="n"/>
+      <c r="B121" s="694" t="n"/>
+      <c r="C121" s="694" t="n"/>
+      <c r="D121" s="694" t="n"/>
+      <c r="E121" s="694" t="n"/>
+      <c r="F121" s="695" t="n"/>
     </row>
     <row r="122">
-      <c r="A122" s="81" t="inlineStr">
-        <is>
-          <t>11.3</t>
-        </is>
-      </c>
-      <c r="B122" s="403" t="inlineStr">
-        <is>
-          <t>Puertas metálicas</t>
-        </is>
-      </c>
-      <c r="C122" s="272" t="inlineStr">
-        <is>
-          <t>UND</t>
-        </is>
-      </c>
-      <c r="D122" s="273" t="n"/>
-      <c r="E122" s="1295" t="n"/>
-      <c r="F122" s="1296">
-        <f>D122*E122</f>
-        <v/>
-      </c>
+      <c r="A122" s="189" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B122" s="692" t="inlineStr">
+        <is>
+          <t>PINTURA</t>
+        </is>
+      </c>
+      <c r="C122" s="536" t="n"/>
+      <c r="D122" s="536" t="n"/>
+      <c r="E122" s="536" t="n"/>
+      <c r="F122" s="536" t="n"/>
     </row>
     <row r="123">
       <c r="A123" s="81" t="inlineStr">
         <is>
-          <t>11.4</t>
-        </is>
-      </c>
-      <c r="B123" s="404" t="inlineStr">
-        <is>
-          <t>Barandas metálicas</t>
+          <t>10.1</t>
+        </is>
+      </c>
+      <c r="B123" s="403" t="inlineStr">
+        <is>
+          <t>Pintura vinílica interior</t>
         </is>
       </c>
       <c r="C123" s="272" t="inlineStr">
         <is>
-          <t>ML</t>
-        </is>
-      </c>
-      <c r="F123">
+          <t>M²</t>
+        </is>
+      </c>
+      <c r="D123" s="273" t="n"/>
+      <c r="E123" s="1295" t="n"/>
+      <c r="F123" s="1296">
         <f>D123*E123</f>
         <v/>
       </c>
@@ -13296,17 +13331,17 @@
     <row r="124">
       <c r="A124" s="81" t="inlineStr">
         <is>
-          <t>11.5</t>
+          <t>10.2</t>
         </is>
       </c>
       <c r="B124" s="403" t="inlineStr">
         <is>
-          <t>Pasamanos</t>
+          <t>Pintura exterior</t>
         </is>
       </c>
       <c r="C124" s="272" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>M²</t>
         </is>
       </c>
       <c r="D124" s="273" t="n"/>
@@ -13319,12 +13354,12 @@
     <row r="125">
       <c r="A125" s="81" t="inlineStr">
         <is>
-          <t>11.6</t>
+          <t>10.3</t>
         </is>
       </c>
       <c r="B125" s="403" t="inlineStr">
         <is>
-          <t>Ventanas de aluminio</t>
+          <t>Pintura esmalte en superficies metálicas/madera</t>
         </is>
       </c>
       <c r="C125" s="272" t="inlineStr">
@@ -13342,12 +13377,12 @@
     <row r="126">
       <c r="A126" s="81" t="inlineStr">
         <is>
-          <t>11.7</t>
+          <t>10.4</t>
         </is>
       </c>
       <c r="B126" s="403" t="inlineStr">
         <is>
-          <t>Divisiones de aluminio</t>
+          <t>Pintura anticorrosiva</t>
         </is>
       </c>
       <c r="C126" s="272" t="inlineStr">
@@ -13363,79 +13398,79 @@
       </c>
     </row>
     <row r="127">
-      <c r="A127" s="82" t="n"/>
-      <c r="B127" s="693" t="inlineStr">
-        <is>
-          <t>SUBTOTAL CAPÍTULO 11 - CARPINTERÍA</t>
-        </is>
-      </c>
-      <c r="C127" s="536" t="n"/>
-      <c r="D127" s="536" t="n"/>
-      <c r="E127" s="536" t="n"/>
-      <c r="F127" s="1297">
-        <f>SUM(F120:F126)</f>
+      <c r="A127" s="81" t="inlineStr">
+        <is>
+          <t>10.5</t>
+        </is>
+      </c>
+      <c r="B127" s="403" t="inlineStr">
+        <is>
+          <t>Sellador / imprimante</t>
+        </is>
+      </c>
+      <c r="C127" s="272" t="inlineStr">
+        <is>
+          <t>M²</t>
+        </is>
+      </c>
+      <c r="F127" s="1296">
+        <f>D127*E127</f>
         <v/>
       </c>
     </row>
     <row r="128">
-      <c r="A128" s="83" t="n"/>
-      <c r="B128" s="694" t="n"/>
-      <c r="C128" s="694" t="n"/>
-      <c r="D128" s="694" t="n"/>
-      <c r="E128" s="694" t="n"/>
-      <c r="F128" s="695" t="n"/>
+      <c r="A128" s="82" t="n"/>
+      <c r="B128" s="693" t="inlineStr">
+        <is>
+          <t>SUBTOTAL CAPÍTULO 10 - PINTURA</t>
+        </is>
+      </c>
+      <c r="C128" s="536" t="n"/>
+      <c r="D128" s="536" t="n"/>
+      <c r="E128" s="536" t="n"/>
+      <c r="F128" s="1297">
+        <f>SUM(F123:F127)</f>
+        <v/>
+      </c>
     </row>
     <row r="129">
-      <c r="A129" s="189" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="B129" s="692" t="inlineStr">
-        <is>
-          <t>VIDRIOS</t>
-        </is>
-      </c>
+      <c r="A129" s="83" t="n"/>
+      <c r="B129" s="695" t="n"/>
       <c r="C129" s="536" t="n"/>
       <c r="D129" s="536" t="n"/>
       <c r="E129" s="536" t="n"/>
-      <c r="F129" s="536" t="n"/>
+      <c r="F129" s="585" t="n"/>
     </row>
     <row r="130">
-      <c r="A130" s="81" t="inlineStr">
-        <is>
-          <t>12.1</t>
-        </is>
-      </c>
-      <c r="B130" s="403" t="inlineStr">
-        <is>
-          <t>Vidrio templado</t>
-        </is>
-      </c>
-      <c r="C130" s="272" t="inlineStr">
-        <is>
-          <t>M²</t>
-        </is>
-      </c>
-      <c r="F130" s="1296">
-        <f>D130*E130</f>
-        <v/>
-      </c>
+      <c r="A130" s="189" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B130" s="692" t="inlineStr">
+        <is>
+          <t>CARPINTERÍA</t>
+        </is>
+      </c>
+      <c r="C130" s="536" t="n"/>
+      <c r="D130" s="536" t="n"/>
+      <c r="E130" s="536" t="n"/>
+      <c r="F130" s="536" t="n"/>
     </row>
     <row r="131">
       <c r="A131" s="81" t="inlineStr">
         <is>
-          <t>12.2</t>
+          <t>11.1</t>
         </is>
       </c>
       <c r="B131" s="403" t="inlineStr">
         <is>
-          <t>Vidrio laminado</t>
+          <t>Puertas de madera</t>
         </is>
       </c>
       <c r="C131" s="272" t="inlineStr">
         <is>
-          <t>M²</t>
+          <t>UND</t>
         </is>
       </c>
       <c r="D131" s="273" t="n"/>
@@ -13448,20 +13483,20 @@
     <row r="132">
       <c r="A132" s="81" t="inlineStr">
         <is>
-          <t>12.3</t>
-        </is>
-      </c>
-      <c r="B132" s="404" t="inlineStr">
-        <is>
-          <t>Espejos</t>
+          <t>11.2</t>
+        </is>
+      </c>
+      <c r="B132" s="403" t="inlineStr">
+        <is>
+          <t>Muebles fijos de madera</t>
         </is>
       </c>
       <c r="C132" s="272" t="inlineStr">
         <is>
-          <t>M²</t>
-        </is>
-      </c>
-      <c r="F132">
+          <t>ML</t>
+        </is>
+      </c>
+      <c r="F132" s="1296">
         <f>D132*E132</f>
         <v/>
       </c>
@@ -13469,17 +13504,17 @@
     <row r="133">
       <c r="A133" s="81" t="inlineStr">
         <is>
-          <t>12.4</t>
+          <t>11.3</t>
         </is>
       </c>
       <c r="B133" s="403" t="inlineStr">
         <is>
-          <t>Sellos y silicona</t>
+          <t>Puertas metálicas</t>
         </is>
       </c>
       <c r="C133" s="272" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>UND</t>
         </is>
       </c>
       <c r="D133" s="273" t="n"/>
@@ -13490,60 +13525,90 @@
       </c>
     </row>
     <row r="134">
-      <c r="A134" s="82" t="n"/>
-      <c r="B134" s="693" t="inlineStr">
-        <is>
-          <t>SUBTOTAL CAPÍTULO 12 - VIDRIOS</t>
-        </is>
-      </c>
-      <c r="C134" s="536" t="n"/>
-      <c r="D134" s="536" t="n"/>
-      <c r="E134" s="536" t="n"/>
-      <c r="F134" s="1297">
-        <f>SUM(F130:F133)</f>
+      <c r="A134" s="81" t="inlineStr">
+        <is>
+          <t>11.4</t>
+        </is>
+      </c>
+      <c r="B134" s="404" t="inlineStr">
+        <is>
+          <t>Barandas metálicas</t>
+        </is>
+      </c>
+      <c r="C134" s="272" t="inlineStr">
+        <is>
+          <t>ML</t>
+        </is>
+      </c>
+      <c r="F134">
+        <f>D134*E134</f>
         <v/>
       </c>
     </row>
     <row r="135">
-      <c r="A135" s="83" t="n"/>
-      <c r="B135" s="694" t="n"/>
-      <c r="C135" s="694" t="n"/>
-      <c r="D135" s="694" t="n"/>
-      <c r="E135" s="694" t="n"/>
-      <c r="F135" s="695" t="n"/>
+      <c r="A135" s="81" t="inlineStr">
+        <is>
+          <t>11.5</t>
+        </is>
+      </c>
+      <c r="B135" s="403" t="inlineStr">
+        <is>
+          <t>Pasamanos</t>
+        </is>
+      </c>
+      <c r="C135" s="272" t="inlineStr">
+        <is>
+          <t>ML</t>
+        </is>
+      </c>
+      <c r="D135" s="273" t="n"/>
+      <c r="E135" s="1295" t="n"/>
+      <c r="F135" s="1296">
+        <f>D135*E135</f>
+        <v/>
+      </c>
     </row>
     <row r="136">
-      <c r="A136" s="189" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="B136" s="692" t="inlineStr">
-        <is>
-          <t>INSTALACIONES HIDROSANITARIAS</t>
-        </is>
-      </c>
-      <c r="C136" s="536" t="n"/>
-      <c r="D136" s="536" t="n"/>
-      <c r="E136" s="536" t="n"/>
-      <c r="F136" s="536" t="n"/>
+      <c r="A136" s="81" t="inlineStr">
+        <is>
+          <t>11.6</t>
+        </is>
+      </c>
+      <c r="B136" s="403" t="inlineStr">
+        <is>
+          <t>Ventanas de aluminio</t>
+        </is>
+      </c>
+      <c r="C136" s="272" t="inlineStr">
+        <is>
+          <t>M²</t>
+        </is>
+      </c>
+      <c r="D136" s="273" t="n"/>
+      <c r="E136" s="1295" t="n"/>
+      <c r="F136" s="1296">
+        <f>D136*E136</f>
+        <v/>
+      </c>
     </row>
     <row r="137">
       <c r="A137" s="81" t="inlineStr">
         <is>
-          <t>13.1</t>
+          <t>11.7</t>
         </is>
       </c>
       <c r="B137" s="403" t="inlineStr">
         <is>
-          <t>Tubería de agua fría</t>
+          <t>Divisiones de aluminio</t>
         </is>
       </c>
       <c r="C137" s="272" t="inlineStr">
         <is>
-          <t>ML</t>
-        </is>
-      </c>
+          <t>M²</t>
+        </is>
+      </c>
+      <c r="D137" s="273" t="n"/>
+      <c r="E137" s="1295" t="n"/>
       <c r="F137" s="1296">
         <f>D137*E137</f>
         <v/>
@@ -13552,17 +13617,17 @@
     <row r="138">
       <c r="A138" s="81" t="inlineStr">
         <is>
-          <t>13.2</t>
+          <t>11.8</t>
         </is>
       </c>
       <c r="B138" s="403" t="inlineStr">
         <is>
-          <t>Tubería de agua caliente</t>
+          <t>Puerta antipánico</t>
         </is>
       </c>
       <c r="C138" s="272" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>UND</t>
         </is>
       </c>
       <c r="D138" s="273" t="n"/>
@@ -13573,90 +13638,60 @@
       </c>
     </row>
     <row r="139">
-      <c r="A139" s="81" t="inlineStr">
-        <is>
-          <t>13.3</t>
-        </is>
-      </c>
-      <c r="B139" s="403" t="inlineStr">
-        <is>
-          <t>Válvulas y accesorios</t>
-        </is>
-      </c>
-      <c r="C139" s="272" t="inlineStr">
-        <is>
-          <t>UND</t>
-        </is>
-      </c>
-      <c r="F139" s="1296">
-        <f>D139*E139</f>
+      <c r="A139" s="82" t="n"/>
+      <c r="B139" s="693" t="inlineStr">
+        <is>
+          <t>SUBTOTAL CAPÍTULO 11 - CARPINTERÍA</t>
+        </is>
+      </c>
+      <c r="C139" s="536" t="n"/>
+      <c r="D139" s="536" t="n"/>
+      <c r="E139" s="536" t="n"/>
+      <c r="F139" s="1297">
+        <f>SUM(F131:F138)</f>
         <v/>
       </c>
     </row>
     <row r="140">
-      <c r="A140" s="81" t="inlineStr">
-        <is>
-          <t>13.4</t>
-        </is>
-      </c>
-      <c r="B140" s="403" t="inlineStr">
-        <is>
-          <t>Tubería sanitaria</t>
-        </is>
-      </c>
-      <c r="C140" s="272" t="inlineStr">
-        <is>
-          <t>ML</t>
-        </is>
-      </c>
-      <c r="D140" s="273" t="n"/>
-      <c r="E140" s="1295" t="n"/>
-      <c r="F140" s="1296">
-        <f>D140*E140</f>
-        <v/>
-      </c>
+      <c r="A140" s="83" t="n"/>
+      <c r="B140" s="694" t="n"/>
+      <c r="C140" s="694" t="n"/>
+      <c r="D140" s="694" t="n"/>
+      <c r="E140" s="694" t="n"/>
+      <c r="F140" s="695" t="n"/>
     </row>
     <row r="141">
-      <c r="A141" s="81" t="inlineStr">
-        <is>
-          <t>13.5</t>
-        </is>
-      </c>
-      <c r="B141" s="403" t="inlineStr">
-        <is>
-          <t>Tubería de aguas lluvias</t>
-        </is>
-      </c>
-      <c r="C141" s="272" t="inlineStr">
-        <is>
-          <t>ML</t>
-        </is>
-      </c>
-      <c r="D141" s="273" t="n"/>
-      <c r="E141" s="1295" t="n"/>
-      <c r="F141" s="1296">
-        <f>D141*E141</f>
-        <v/>
-      </c>
+      <c r="A141" s="189" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B141" s="692" t="inlineStr">
+        <is>
+          <t>VIDRIOS</t>
+        </is>
+      </c>
+      <c r="C141" s="536" t="n"/>
+      <c r="D141" s="536" t="n"/>
+      <c r="E141" s="536" t="n"/>
+      <c r="F141" s="536" t="n"/>
     </row>
     <row r="142">
       <c r="A142" s="81" t="inlineStr">
         <is>
-          <t>13.6</t>
+          <t>12.1</t>
         </is>
       </c>
       <c r="B142" s="403" t="inlineStr">
         <is>
-          <t>Cajas de inspección</t>
+          <t>Vidrio templado</t>
         </is>
       </c>
       <c r="C142" s="272" t="inlineStr">
         <is>
-          <t>UND</t>
-        </is>
-      </c>
-      <c r="D142" s="273" t="n"/>
-      <c r="E142" s="1295" t="n"/>
+          <t>M²</t>
+        </is>
+      </c>
       <c r="F142" s="1296">
         <f>D142*E142</f>
         <v/>
@@ -13665,17 +13700,17 @@
     <row r="143">
       <c r="A143" s="81" t="inlineStr">
         <is>
-          <t>13.7</t>
+          <t>12.2</t>
         </is>
       </c>
       <c r="B143" s="403" t="inlineStr">
         <is>
-          <t>Aparatos sanitarios</t>
+          <t>Vidrio laminado</t>
         </is>
       </c>
       <c r="C143" s="272" t="inlineStr">
         <is>
-          <t>UND</t>
+          <t>M²</t>
         </is>
       </c>
       <c r="D143" s="273" t="n"/>
@@ -13688,22 +13723,20 @@
     <row r="144">
       <c r="A144" s="81" t="inlineStr">
         <is>
-          <t>13.8</t>
-        </is>
-      </c>
-      <c r="B144" s="403" t="inlineStr">
-        <is>
-          <t>Lavamanos</t>
+          <t>12.3</t>
+        </is>
+      </c>
+      <c r="B144" s="404" t="inlineStr">
+        <is>
+          <t>Espejos</t>
         </is>
       </c>
       <c r="C144" s="272" t="inlineStr">
         <is>
-          <t>UND</t>
-        </is>
-      </c>
-      <c r="D144" s="273" t="n"/>
-      <c r="E144" s="1295" t="n"/>
-      <c r="F144" s="1296">
+          <t>M²</t>
+        </is>
+      </c>
+      <c r="F144">
         <f>D144*E144</f>
         <v/>
       </c>
@@ -13711,17 +13744,17 @@
     <row r="145">
       <c r="A145" s="81" t="inlineStr">
         <is>
-          <t>13.9</t>
+          <t>12.4</t>
         </is>
       </c>
       <c r="B145" s="403" t="inlineStr">
         <is>
-          <t>Griferías</t>
+          <t>Sellos y silicona</t>
         </is>
       </c>
       <c r="C145" s="272" t="inlineStr">
         <is>
-          <t>UND</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="D145" s="273" t="n"/>
@@ -13732,108 +13765,104 @@
       </c>
     </row>
     <row r="146">
-      <c r="A146" s="81" t="inlineStr">
-        <is>
-          <t>13.10</t>
-        </is>
-      </c>
-      <c r="B146" s="403" t="inlineStr">
-        <is>
-          <t>Duchas</t>
-        </is>
-      </c>
-      <c r="C146" s="272" t="inlineStr">
-        <is>
-          <t>UND</t>
-        </is>
-      </c>
-      <c r="D146" s="273" t="n"/>
-      <c r="E146" s="1295" t="n"/>
-      <c r="F146" s="1296">
-        <f>D146*E146</f>
+      <c r="A146" s="82" t="n"/>
+      <c r="B146" s="693" t="inlineStr">
+        <is>
+          <t>SUBTOTAL CAPÍTULO 12 - VIDRIOS</t>
+        </is>
+      </c>
+      <c r="C146" s="536" t="n"/>
+      <c r="D146" s="536" t="n"/>
+      <c r="E146" s="536" t="n"/>
+      <c r="F146" s="1297">
+        <f>SUM(F142:F145)</f>
         <v/>
       </c>
     </row>
     <row r="147">
-      <c r="A147" s="81" t="inlineStr">
-        <is>
-          <t>13.11</t>
-        </is>
-      </c>
-      <c r="B147" s="403" t="inlineStr">
-        <is>
-          <t>Pruebas hidráulicas y de estanqueidad</t>
-        </is>
-      </c>
-      <c r="C147" s="272" t="inlineStr">
-        <is>
-          <t>GL</t>
-        </is>
-      </c>
-      <c r="D147" s="273" t="n"/>
-      <c r="E147" s="1295" t="n"/>
-      <c r="F147" s="1296">
-        <f>D147*E147</f>
-        <v/>
-      </c>
+      <c r="A147" s="83" t="n"/>
+      <c r="B147" s="694" t="n"/>
+      <c r="C147" s="694" t="n"/>
+      <c r="D147" s="694" t="n"/>
+      <c r="E147" s="694" t="n"/>
+      <c r="F147" s="695" t="n"/>
     </row>
     <row r="148">
-      <c r="A148" s="82" t="n"/>
-      <c r="B148" s="693" t="inlineStr">
-        <is>
-          <t>SUBTOTAL CAPÍTULO 13 - INSTALACIONES HIDROSANITARIAS</t>
+      <c r="A148" s="189" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="B148" s="692" t="inlineStr">
+        <is>
+          <t>INSTALACIONES HIDROSANITARIAS</t>
         </is>
       </c>
       <c r="C148" s="536" t="n"/>
       <c r="D148" s="536" t="n"/>
       <c r="E148" s="536" t="n"/>
-      <c r="F148" s="1297">
-        <f>SUM(F137:F147)</f>
-        <v/>
-      </c>
+      <c r="F148" s="536" t="n"/>
     </row>
     <row r="149">
-      <c r="A149" s="83" t="n"/>
-      <c r="B149" s="694" t="n"/>
-      <c r="C149" s="694" t="n"/>
-      <c r="D149" s="694" t="n"/>
-      <c r="E149" s="694" t="n"/>
-      <c r="F149" s="695" t="n"/>
+      <c r="A149" s="81" t="inlineStr">
+        <is>
+          <t>13.1</t>
+        </is>
+      </c>
+      <c r="B149" s="403" t="inlineStr">
+        <is>
+          <t>Tubería de agua fría</t>
+        </is>
+      </c>
+      <c r="C149" s="272" t="inlineStr">
+        <is>
+          <t>ML</t>
+        </is>
+      </c>
+      <c r="F149" s="1296">
+        <f>D149*E149</f>
+        <v/>
+      </c>
     </row>
     <row r="150">
-      <c r="A150" s="189" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="B150" s="692" t="inlineStr">
-        <is>
-          <t>INSTALACIONES ELÉCTRICAS</t>
-        </is>
-      </c>
-      <c r="C150" s="536" t="n"/>
-      <c r="D150" s="536" t="n"/>
-      <c r="E150" s="536" t="n"/>
-      <c r="F150" s="536" t="n"/>
+      <c r="A150" s="81" t="inlineStr">
+        <is>
+          <t>13.2</t>
+        </is>
+      </c>
+      <c r="B150" s="403" t="inlineStr">
+        <is>
+          <t>Tubería de agua caliente</t>
+        </is>
+      </c>
+      <c r="C150" s="272" t="inlineStr">
+        <is>
+          <t>ML</t>
+        </is>
+      </c>
+      <c r="D150" s="273" t="n"/>
+      <c r="E150" s="1295" t="n"/>
+      <c r="F150" s="1296">
+        <f>D150*E150</f>
+        <v/>
+      </c>
     </row>
     <row r="151">
       <c r="A151" s="81" t="inlineStr">
         <is>
-          <t>14.1</t>
+          <t>13.3</t>
         </is>
       </c>
       <c r="B151" s="403" t="inlineStr">
         <is>
-          <t>Tubería/conduit eléctrica</t>
+          <t>Válvulas y accesorios</t>
         </is>
       </c>
       <c r="C151" s="272" t="inlineStr">
         <is>
-          <t>ML</t>
-        </is>
-      </c>
-      <c r="D151" s="273" t="n"/>
-      <c r="E151" s="1295" t="n"/>
+          <t>UND</t>
+        </is>
+      </c>
       <c r="F151" s="1296">
         <f>D151*E151</f>
         <v/>
@@ -13842,12 +13871,12 @@
     <row r="152">
       <c r="A152" s="81" t="inlineStr">
         <is>
-          <t>14.2</t>
+          <t>13.4</t>
         </is>
       </c>
       <c r="B152" s="403" t="inlineStr">
         <is>
-          <t>Bandejas portacables</t>
+          <t>Tubería sanitaria</t>
         </is>
       </c>
       <c r="C152" s="272" t="inlineStr">
@@ -13865,17 +13894,17 @@
     <row r="153">
       <c r="A153" s="81" t="inlineStr">
         <is>
-          <t>14.3</t>
+          <t>13.5</t>
         </is>
       </c>
       <c r="B153" s="403" t="inlineStr">
         <is>
-          <t>Cajas eléctricas</t>
+          <t>Tubería de aguas lluvias</t>
         </is>
       </c>
       <c r="C153" s="272" t="inlineStr">
         <is>
-          <t>UND</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="D153" s="273" t="n"/>
@@ -13888,17 +13917,17 @@
     <row r="154">
       <c r="A154" s="81" t="inlineStr">
         <is>
-          <t>14.4</t>
+          <t>13.6</t>
         </is>
       </c>
       <c r="B154" s="403" t="inlineStr">
         <is>
-          <t>Cableado de fuerza</t>
+          <t>Cajas de inspección</t>
         </is>
       </c>
       <c r="C154" s="272" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>UND</t>
         </is>
       </c>
       <c r="D154" s="273" t="n"/>
@@ -13911,17 +13940,17 @@
     <row r="155">
       <c r="A155" s="81" t="inlineStr">
         <is>
-          <t>14.5</t>
+          <t>13.7</t>
         </is>
       </c>
       <c r="B155" s="403" t="inlineStr">
         <is>
-          <t>Cableado de iluminación</t>
+          <t>Aparatos sanitarios</t>
         </is>
       </c>
       <c r="C155" s="272" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>UND</t>
         </is>
       </c>
       <c r="D155" s="273" t="n"/>
@@ -13934,12 +13963,12 @@
     <row r="156">
       <c r="A156" s="81" t="inlineStr">
         <is>
-          <t>14.6</t>
+          <t>13.8</t>
         </is>
       </c>
       <c r="B156" s="403" t="inlineStr">
         <is>
-          <t>Tableros eléctricos</t>
+          <t>Lavamanos</t>
         </is>
       </c>
       <c r="C156" s="272" t="inlineStr">
@@ -13957,12 +13986,12 @@
     <row r="157">
       <c r="A157" s="81" t="inlineStr">
         <is>
-          <t>14.7</t>
+          <t>13.9</t>
         </is>
       </c>
       <c r="B157" s="403" t="inlineStr">
         <is>
-          <t>Tomacorrientes</t>
+          <t>Griferías</t>
         </is>
       </c>
       <c r="C157" s="272" t="inlineStr">
@@ -13980,12 +14009,12 @@
     <row r="158">
       <c r="A158" s="81" t="inlineStr">
         <is>
-          <t>14.8</t>
+          <t>13.10</t>
         </is>
       </c>
       <c r="B158" s="403" t="inlineStr">
         <is>
-          <t>Interruptores</t>
+          <t>Duchas</t>
         </is>
       </c>
       <c r="C158" s="272" t="inlineStr">
@@ -14003,17 +14032,17 @@
     <row r="159">
       <c r="A159" s="81" t="inlineStr">
         <is>
-          <t>14.9</t>
+          <t>13.11</t>
         </is>
       </c>
       <c r="B159" s="403" t="inlineStr">
         <is>
-          <t>Luminarias</t>
+          <t>Pruebas hidráulicas y de estanqueidad</t>
         </is>
       </c>
       <c r="C159" s="272" t="inlineStr">
         <is>
-          <t>UND</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="D159" s="273" t="n"/>
@@ -14026,17 +14055,17 @@
     <row r="160">
       <c r="A160" s="81" t="inlineStr">
         <is>
-          <t>14.10</t>
+          <t>13.12</t>
         </is>
       </c>
       <c r="B160" s="403" t="inlineStr">
         <is>
-          <t>Sistema de puesta a tierra</t>
+          <t>Orinal institucional</t>
         </is>
       </c>
       <c r="C160" s="272" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>UND</t>
         </is>
       </c>
       <c r="D160" s="273" t="n"/>
@@ -14047,76 +14076,76 @@
       </c>
     </row>
     <row r="161">
-      <c r="A161" s="81" t="inlineStr">
-        <is>
-          <t>14.11</t>
-        </is>
-      </c>
-      <c r="B161" s="403" t="inlineStr">
-        <is>
-          <t>Pruebas y certificaciones</t>
-        </is>
-      </c>
-      <c r="C161" s="272" t="inlineStr">
-        <is>
-          <t>GL</t>
-        </is>
-      </c>
-      <c r="D161" s="273" t="n"/>
-      <c r="E161" s="1295" t="n"/>
-      <c r="F161" s="1296">
-        <f>D161*E161</f>
+      <c r="A161" s="82" t="n"/>
+      <c r="B161" s="693" t="inlineStr">
+        <is>
+          <t>SUBTOTAL CAPÍTULO 13 - INSTALACIONES HIDROSANITARIAS</t>
+        </is>
+      </c>
+      <c r="C161" s="536" t="n"/>
+      <c r="D161" s="536" t="n"/>
+      <c r="E161" s="536" t="n"/>
+      <c r="F161" s="1297">
+        <f>SUM(F149:F160)</f>
         <v/>
       </c>
     </row>
     <row r="162">
-      <c r="A162" s="82" t="n"/>
-      <c r="B162" s="693" t="inlineStr">
-        <is>
-          <t>SUBTOTAL CAPÍTULO 14 - INSTALACIONES ELÉCTRICAS</t>
-        </is>
-      </c>
-      <c r="C162" s="536" t="n"/>
-      <c r="D162" s="536" t="n"/>
-      <c r="E162" s="536" t="n"/>
-      <c r="F162" s="1297">
-        <f>SUM(F151:F161)</f>
-        <v/>
-      </c>
+      <c r="A162" s="83" t="n"/>
+      <c r="B162" s="694" t="n"/>
+      <c r="C162" s="694" t="n"/>
+      <c r="D162" s="694" t="n"/>
+      <c r="E162" s="694" t="n"/>
+      <c r="F162" s="695" t="n"/>
     </row>
     <row r="163">
-      <c r="A163" s="83" t="n"/>
-      <c r="B163" s="694" t="n"/>
-      <c r="C163" s="694" t="n"/>
-      <c r="D163" s="694" t="n"/>
-      <c r="E163" s="694" t="n"/>
-      <c r="F163" s="695" t="n"/>
+      <c r="A163" s="189" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="B163" s="692" t="inlineStr">
+        <is>
+          <t>INSTALACIONES ELÉCTRICAS</t>
+        </is>
+      </c>
+      <c r="C163" s="536" t="n"/>
+      <c r="D163" s="536" t="n"/>
+      <c r="E163" s="536" t="n"/>
+      <c r="F163" s="536" t="n"/>
     </row>
     <row r="164">
-      <c r="A164" s="189" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="B164" s="692" t="inlineStr">
-        <is>
-          <t>COMUNICACIONES Y SEGURIDAD</t>
-        </is>
-      </c>
-      <c r="C164" s="536" t="n"/>
-      <c r="D164" s="536" t="n"/>
-      <c r="E164" s="536" t="n"/>
-      <c r="F164" s="536" t="n"/>
+      <c r="A164" s="81" t="inlineStr">
+        <is>
+          <t>14.1</t>
+        </is>
+      </c>
+      <c r="B164" s="403" t="inlineStr">
+        <is>
+          <t>Tubería/conduit eléctrica</t>
+        </is>
+      </c>
+      <c r="C164" s="272" t="inlineStr">
+        <is>
+          <t>ML</t>
+        </is>
+      </c>
+      <c r="D164" s="273" t="n"/>
+      <c r="E164" s="1295" t="n"/>
+      <c r="F164" s="1296">
+        <f>D164*E164</f>
+        <v/>
+      </c>
     </row>
     <row r="165">
       <c r="A165" s="81" t="inlineStr">
         <is>
-          <t>15.1</t>
+          <t>14.2</t>
         </is>
       </c>
       <c r="B165" s="403" t="inlineStr">
         <is>
-          <t>Cableado estructurado de datos</t>
+          <t>Bandejas portacables</t>
         </is>
       </c>
       <c r="C165" s="272" t="inlineStr">
@@ -14134,12 +14163,12 @@
     <row r="166">
       <c r="A166" s="81" t="inlineStr">
         <is>
-          <t>15.2</t>
+          <t>14.3</t>
         </is>
       </c>
       <c r="B166" s="403" t="inlineStr">
         <is>
-          <t>Rack de comunicaciones</t>
+          <t>Cajas eléctricas</t>
         </is>
       </c>
       <c r="C166" s="272" t="inlineStr">
@@ -14157,17 +14186,17 @@
     <row r="167">
       <c r="A167" s="81" t="inlineStr">
         <is>
-          <t>15.3</t>
+          <t>14.4</t>
         </is>
       </c>
       <c r="B167" s="403" t="inlineStr">
         <is>
-          <t>Cámaras y sistema CCTV</t>
+          <t>Cableado de fuerza</t>
         </is>
       </c>
       <c r="C167" s="272" t="inlineStr">
         <is>
-          <t>UND</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="D167" s="273" t="n"/>
@@ -14180,17 +14209,17 @@
     <row r="168">
       <c r="A168" s="81" t="inlineStr">
         <is>
-          <t>15.4</t>
+          <t>14.5</t>
         </is>
       </c>
       <c r="B168" s="403" t="inlineStr">
         <is>
-          <t>Control de acceso</t>
+          <t>Cableado de iluminación</t>
         </is>
       </c>
       <c r="C168" s="272" t="inlineStr">
         <is>
-          <t>UND</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="D168" s="273" t="n"/>
@@ -14203,12 +14232,12 @@
     <row r="169">
       <c r="A169" s="81" t="inlineStr">
         <is>
-          <t>15.5</t>
+          <t>14.6</t>
         </is>
       </c>
       <c r="B169" s="403" t="inlineStr">
         <is>
-          <t>Sistema de citofonía</t>
+          <t>Tableros eléctricos</t>
         </is>
       </c>
       <c r="C169" s="272" t="inlineStr">
@@ -14226,17 +14255,17 @@
     <row r="170">
       <c r="A170" s="81" t="inlineStr">
         <is>
-          <t>15.6</t>
+          <t>14.7</t>
         </is>
       </c>
       <c r="B170" s="403" t="inlineStr">
         <is>
-          <t>Sistema de detección de incendios</t>
+          <t>Tomacorrientes</t>
         </is>
       </c>
       <c r="C170" s="272" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>UND</t>
         </is>
       </c>
       <c r="D170" s="273" t="n"/>
@@ -14247,58 +14276,88 @@
       </c>
     </row>
     <row r="171">
-      <c r="A171" s="82" t="n"/>
-      <c r="B171" s="693" t="inlineStr">
-        <is>
-          <t>SUBTOTAL CAPÍTULO 15 - COMUNICACIONES Y SEGURIDAD</t>
-        </is>
-      </c>
-      <c r="C171" s="536" t="n"/>
-      <c r="D171" s="536" t="n"/>
-      <c r="E171" s="536" t="n"/>
-      <c r="F171" s="1297">
-        <f>SUM(F165:F170)</f>
+      <c r="A171" s="81" t="inlineStr">
+        <is>
+          <t>14.8</t>
+        </is>
+      </c>
+      <c r="B171" s="403" t="inlineStr">
+        <is>
+          <t>Interruptores</t>
+        </is>
+      </c>
+      <c r="C171" s="272" t="inlineStr">
+        <is>
+          <t>UND</t>
+        </is>
+      </c>
+      <c r="D171" s="273" t="n"/>
+      <c r="E171" s="1295" t="n"/>
+      <c r="F171" s="1296">
+        <f>D171*E171</f>
         <v/>
       </c>
     </row>
     <row r="172">
-      <c r="A172" s="83" t="n"/>
-      <c r="B172" s="694" t="n"/>
-      <c r="C172" s="694" t="n"/>
-      <c r="D172" s="694" t="n"/>
-      <c r="E172" s="694" t="n"/>
-      <c r="F172" s="695" t="n"/>
+      <c r="A172" s="81" t="inlineStr">
+        <is>
+          <t>14.9</t>
+        </is>
+      </c>
+      <c r="B172" s="403" t="inlineStr">
+        <is>
+          <t>Luminarias</t>
+        </is>
+      </c>
+      <c r="C172" s="272" t="inlineStr">
+        <is>
+          <t>UND</t>
+        </is>
+      </c>
+      <c r="D172" s="273" t="n"/>
+      <c r="E172" s="1295" t="n"/>
+      <c r="F172" s="1296">
+        <f>D172*E172</f>
+        <v/>
+      </c>
     </row>
     <row r="173">
-      <c r="A173" s="189" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="B173" s="692" t="inlineStr">
-        <is>
-          <t>CLIMATIZACIÓN Y VENTILACIÓN</t>
-        </is>
-      </c>
-      <c r="C173" s="536" t="n"/>
-      <c r="D173" s="536" t="n"/>
-      <c r="E173" s="536" t="n"/>
-      <c r="F173" s="536" t="n"/>
+      <c r="A173" s="81" t="inlineStr">
+        <is>
+          <t>14.10</t>
+        </is>
+      </c>
+      <c r="B173" s="403" t="inlineStr">
+        <is>
+          <t>Sistema de puesta a tierra</t>
+        </is>
+      </c>
+      <c r="C173" s="272" t="inlineStr">
+        <is>
+          <t>GL</t>
+        </is>
+      </c>
+      <c r="D173" s="273" t="n"/>
+      <c r="E173" s="1295" t="n"/>
+      <c r="F173" s="1296">
+        <f>D173*E173</f>
+        <v/>
+      </c>
     </row>
     <row r="174">
       <c r="A174" s="81" t="inlineStr">
         <is>
-          <t>16.1</t>
+          <t>14.11</t>
         </is>
       </c>
       <c r="B174" s="403" t="inlineStr">
         <is>
-          <t>Equipos de aire acondicionado</t>
+          <t>Pruebas y certificaciones</t>
         </is>
       </c>
       <c r="C174" s="272" t="inlineStr">
         <is>
-          <t>UND</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="D174" s="273" t="n"/>
@@ -14309,127 +14368,127 @@
       </c>
     </row>
     <row r="175">
-      <c r="A175" s="81" t="inlineStr">
-        <is>
-          <t>16.2</t>
-        </is>
-      </c>
-      <c r="B175" s="403" t="inlineStr">
-        <is>
-          <t>Ductos de ventilación</t>
-        </is>
-      </c>
-      <c r="C175" s="272" t="inlineStr">
-        <is>
-          <t>M²</t>
-        </is>
-      </c>
-      <c r="D175" s="273" t="n"/>
-      <c r="E175" s="1295" t="n"/>
-      <c r="F175" s="1296">
-        <f>D175*E175</f>
+      <c r="A175" s="82" t="n"/>
+      <c r="B175" s="693" t="inlineStr">
+        <is>
+          <t>SUBTOTAL CAPÍTULO 14 - INSTALACIONES ELÉCTRICAS</t>
+        </is>
+      </c>
+      <c r="C175" s="536" t="n"/>
+      <c r="D175" s="536" t="n"/>
+      <c r="E175" s="536" t="n"/>
+      <c r="F175" s="1297">
+        <f>SUM(F164:F174)</f>
         <v/>
       </c>
     </row>
     <row r="176">
-      <c r="A176" s="81" t="inlineStr">
-        <is>
-          <t>16.3</t>
-        </is>
-      </c>
-      <c r="B176" s="403" t="inlineStr">
-        <is>
-          <t>Tubería de refrigerante</t>
-        </is>
-      </c>
-      <c r="C176" s="272" t="inlineStr">
+      <c r="A176" s="83" t="n"/>
+      <c r="B176" s="694" t="n"/>
+      <c r="C176" s="694" t="n"/>
+      <c r="D176" s="694" t="n"/>
+      <c r="E176" s="694" t="n"/>
+      <c r="F176" s="695" t="n"/>
+    </row>
+    <row r="177">
+      <c r="A177" s="189" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B177" s="692" t="inlineStr">
+        <is>
+          <t>COMUNICACIONES Y SEGURIDAD</t>
+        </is>
+      </c>
+      <c r="C177" s="536" t="n"/>
+      <c r="D177" s="536" t="n"/>
+      <c r="E177" s="536" t="n"/>
+      <c r="F177" s="536" t="n"/>
+    </row>
+    <row r="178">
+      <c r="A178" s="81" t="inlineStr">
+        <is>
+          <t>15.1</t>
+        </is>
+      </c>
+      <c r="B178" s="403" t="inlineStr">
+        <is>
+          <t>Cableado estructurado de datos</t>
+        </is>
+      </c>
+      <c r="C178" s="272" t="inlineStr">
         <is>
           <t>ML</t>
         </is>
       </c>
-      <c r="D176" s="273" t="n"/>
-      <c r="E176" s="1295" t="n"/>
-      <c r="F176" s="1296">
-        <f>D176*E176</f>
-        <v/>
-      </c>
-    </row>
-    <row r="177">
-      <c r="A177" s="81" t="inlineStr">
-        <is>
-          <t>16.4</t>
-        </is>
-      </c>
-      <c r="B177" s="403" t="inlineStr">
-        <is>
-          <t>Rejillas y difusores</t>
-        </is>
-      </c>
-      <c r="C177" s="272" t="inlineStr">
+      <c r="D178" s="273" t="n"/>
+      <c r="E178" s="1295" t="n"/>
+      <c r="F178" s="1296">
+        <f>D178*E178</f>
+        <v/>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" s="81" t="inlineStr">
+        <is>
+          <t>15.2</t>
+        </is>
+      </c>
+      <c r="B179" s="403" t="inlineStr">
+        <is>
+          <t>Rack de comunicaciones</t>
+        </is>
+      </c>
+      <c r="C179" s="272" t="inlineStr">
         <is>
           <t>UND</t>
         </is>
       </c>
-      <c r="D177" s="273" t="n"/>
-      <c r="E177" s="1295" t="n"/>
-      <c r="F177" s="1296">
-        <f>D177*E177</f>
-        <v/>
-      </c>
-    </row>
-    <row r="178">
-      <c r="A178" s="82" t="n"/>
-      <c r="B178" s="693" t="inlineStr">
-        <is>
-          <t>SUBTOTAL CAPÍTULO 16 - CLIMATIZACIÓN Y VENTILACIÓN</t>
-        </is>
-      </c>
-      <c r="C178" s="536" t="n"/>
-      <c r="D178" s="536" t="n"/>
-      <c r="E178" s="536" t="n"/>
-      <c r="F178" s="1297">
-        <f>SUM(F174:F177)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="179">
-      <c r="A179" s="83" t="n"/>
-      <c r="B179" s="694" t="n"/>
-      <c r="C179" s="694" t="n"/>
-      <c r="D179" s="694" t="n"/>
-      <c r="E179" s="694" t="n"/>
-      <c r="F179" s="695" t="n"/>
+      <c r="D179" s="273" t="n"/>
+      <c r="E179" s="1295" t="n"/>
+      <c r="F179" s="1296">
+        <f>D179*E179</f>
+        <v/>
+      </c>
     </row>
     <row r="180">
-      <c r="A180" s="189" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="B180" s="692" t="inlineStr">
-        <is>
-          <t>GAS</t>
-        </is>
-      </c>
-      <c r="C180" s="536" t="n"/>
-      <c r="D180" s="536" t="n"/>
-      <c r="E180" s="536" t="n"/>
-      <c r="F180" s="536" t="n"/>
+      <c r="A180" s="81" t="inlineStr">
+        <is>
+          <t>15.3</t>
+        </is>
+      </c>
+      <c r="B180" s="403" t="inlineStr">
+        <is>
+          <t>Cámaras y sistema CCTV</t>
+        </is>
+      </c>
+      <c r="C180" s="272" t="inlineStr">
+        <is>
+          <t>UND</t>
+        </is>
+      </c>
+      <c r="D180" s="273" t="n"/>
+      <c r="E180" s="1295" t="n"/>
+      <c r="F180" s="1296">
+        <f>D180*E180</f>
+        <v/>
+      </c>
     </row>
     <row r="181">
       <c r="A181" s="81" t="inlineStr">
         <is>
-          <t>17.1</t>
+          <t>15.4</t>
         </is>
       </c>
       <c r="B181" s="403" t="inlineStr">
         <is>
-          <t>Red interna de gas</t>
+          <t>Control de acceso</t>
         </is>
       </c>
       <c r="C181" s="272" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>UND</t>
         </is>
       </c>
       <c r="D181" s="273" t="n"/>
@@ -14442,12 +14501,12 @@
     <row r="182">
       <c r="A182" s="81" t="inlineStr">
         <is>
-          <t>17.2</t>
+          <t>15.5</t>
         </is>
       </c>
       <c r="B182" s="403" t="inlineStr">
         <is>
-          <t>Válvulas y accesorios</t>
+          <t>Sistema de citofonía</t>
         </is>
       </c>
       <c r="C182" s="272" t="inlineStr">
@@ -14465,12 +14524,12 @@
     <row r="183">
       <c r="A183" s="81" t="inlineStr">
         <is>
-          <t>17.3</t>
+          <t>15.6</t>
         </is>
       </c>
       <c r="B183" s="403" t="inlineStr">
         <is>
-          <t>Pruebas y certificación</t>
+          <t>Sistema de detección de incendios</t>
         </is>
       </c>
       <c r="C183" s="272" t="inlineStr">
@@ -14489,14 +14548,14 @@
       <c r="A184" s="82" t="n"/>
       <c r="B184" s="693" t="inlineStr">
         <is>
-          <t>SUBTOTAL CAPÍTULO 17 - GAS</t>
+          <t>SUBTOTAL CAPÍTULO 15 - COMUNICACIONES Y SEGURIDAD</t>
         </is>
       </c>
       <c r="C184" s="536" t="n"/>
       <c r="D184" s="536" t="n"/>
       <c r="E184" s="536" t="n"/>
       <c r="F184" s="1297">
-        <f>SUM(F181:F183)</f>
+        <f>SUM(F178:F183)</f>
         <v/>
       </c>
     </row>
@@ -14511,12 +14570,12 @@
     <row r="186">
       <c r="A186" s="189" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>16</t>
         </is>
       </c>
       <c r="B186" s="692" t="inlineStr">
         <is>
-          <t>URBANISMO Y EXTERIORES</t>
+          <t>CLIMATIZACIÓN Y VENTILACIÓN</t>
         </is>
       </c>
       <c r="C186" s="536" t="n"/>
@@ -14527,17 +14586,17 @@
     <row r="187">
       <c r="A187" s="81" t="inlineStr">
         <is>
-          <t>18.1</t>
+          <t>16.1</t>
         </is>
       </c>
       <c r="B187" s="403" t="inlineStr">
         <is>
-          <t>Construcción de andenes</t>
+          <t>Equipos de aire acondicionado</t>
         </is>
       </c>
       <c r="C187" s="272" t="inlineStr">
         <is>
-          <t>M²</t>
+          <t>UND</t>
         </is>
       </c>
       <c r="D187" s="273" t="n"/>
@@ -14550,17 +14609,17 @@
     <row r="188">
       <c r="A188" s="81" t="inlineStr">
         <is>
-          <t>18.2</t>
+          <t>16.2</t>
         </is>
       </c>
       <c r="B188" s="403" t="inlineStr">
         <is>
-          <t>Placas de concreto exteriores</t>
+          <t>Ductos de ventilación</t>
         </is>
       </c>
       <c r="C188" s="272" t="inlineStr">
         <is>
-          <t>M³</t>
+          <t>M²</t>
         </is>
       </c>
       <c r="D188" s="273" t="n"/>
@@ -14573,17 +14632,17 @@
     <row r="189">
       <c r="A189" s="81" t="inlineStr">
         <is>
-          <t>18.3</t>
+          <t>16.3</t>
         </is>
       </c>
       <c r="B189" s="403" t="inlineStr">
         <is>
-          <t>Pavimento en adoquín</t>
+          <t>Tubería de refrigerante</t>
         </is>
       </c>
       <c r="C189" s="272" t="inlineStr">
         <is>
-          <t>M²</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="D189" s="273" t="n"/>
@@ -14596,17 +14655,17 @@
     <row r="190">
       <c r="A190" s="81" t="inlineStr">
         <is>
-          <t>18.4</t>
+          <t>16.4</t>
         </is>
       </c>
       <c r="B190" s="403" t="inlineStr">
         <is>
-          <t>Sardineles y bordillos</t>
+          <t>Rejillas y difusores</t>
         </is>
       </c>
       <c r="C190" s="272" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>UND</t>
         </is>
       </c>
       <c r="D190" s="273" t="n"/>
@@ -14617,196 +14676,166 @@
       </c>
     </row>
     <row r="191">
-      <c r="A191" s="81" t="inlineStr">
-        <is>
-          <t>18.5</t>
-        </is>
-      </c>
-      <c r="B191" s="403" t="inlineStr">
-        <is>
-          <t>Sumideros exteriores</t>
-        </is>
-      </c>
-      <c r="C191" s="272" t="inlineStr">
+      <c r="A191" s="82" t="n"/>
+      <c r="B191" s="693" t="inlineStr">
+        <is>
+          <t>SUBTOTAL CAPÍTULO 16 - CLIMATIZACIÓN Y VENTILACIÓN</t>
+        </is>
+      </c>
+      <c r="C191" s="536" t="n"/>
+      <c r="D191" s="536" t="n"/>
+      <c r="E191" s="536" t="n"/>
+      <c r="F191" s="1297">
+        <f>SUM(F187:F190)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" s="83" t="n"/>
+      <c r="B192" s="694" t="n"/>
+      <c r="C192" s="694" t="n"/>
+      <c r="D192" s="694" t="n"/>
+      <c r="E192" s="694" t="n"/>
+      <c r="F192" s="695" t="n"/>
+    </row>
+    <row r="193">
+      <c r="A193" s="189" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B193" s="692" t="inlineStr">
+        <is>
+          <t>GAS</t>
+        </is>
+      </c>
+      <c r="C193" s="536" t="n"/>
+      <c r="D193" s="536" t="n"/>
+      <c r="E193" s="536" t="n"/>
+      <c r="F193" s="536" t="n"/>
+    </row>
+    <row r="194">
+      <c r="A194" s="81" t="inlineStr">
+        <is>
+          <t>17.1</t>
+        </is>
+      </c>
+      <c r="B194" s="403" t="inlineStr">
+        <is>
+          <t>Red interna de gas</t>
+        </is>
+      </c>
+      <c r="C194" s="272" t="inlineStr">
+        <is>
+          <t>ML</t>
+        </is>
+      </c>
+      <c r="D194" s="273" t="n"/>
+      <c r="E194" s="1295" t="n"/>
+      <c r="F194" s="1296">
+        <f>D194*E194</f>
+        <v/>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" s="81" t="inlineStr">
+        <is>
+          <t>17.2</t>
+        </is>
+      </c>
+      <c r="B195" s="403" t="inlineStr">
+        <is>
+          <t>Válvulas y accesorios</t>
+        </is>
+      </c>
+      <c r="C195" s="272" t="inlineStr">
         <is>
           <t>UND</t>
         </is>
       </c>
-      <c r="D191" s="273" t="n"/>
-      <c r="E191" s="1295" t="n"/>
-      <c r="F191" s="1296">
-        <f>D191*E191</f>
-        <v/>
-      </c>
-    </row>
-    <row r="192">
-      <c r="A192" s="81" t="inlineStr">
-        <is>
-          <t>18.6</t>
-        </is>
-      </c>
-      <c r="B192" s="403" t="inlineStr">
-        <is>
-          <t>Suministro y extendido de tierra vegetal</t>
-        </is>
-      </c>
-      <c r="C192" s="272" t="inlineStr">
-        <is>
-          <t>M³</t>
-        </is>
-      </c>
-      <c r="D192" s="273" t="n"/>
-      <c r="E192" s="1295" t="n"/>
-      <c r="F192" s="1296">
-        <f>D192*E192</f>
-        <v/>
-      </c>
-    </row>
-    <row r="193">
-      <c r="A193" s="81" t="inlineStr">
-        <is>
-          <t>18.7</t>
-        </is>
-      </c>
-      <c r="B193" s="403" t="inlineStr">
-        <is>
-          <t>Siembra y jardinería</t>
-        </is>
-      </c>
-      <c r="C193" s="272" t="inlineStr">
-        <is>
-          <t>M²</t>
-        </is>
-      </c>
-      <c r="D193" s="273" t="n"/>
-      <c r="E193" s="1295" t="n"/>
-      <c r="F193" s="1296">
-        <f>D193*E193</f>
-        <v/>
-      </c>
-    </row>
-    <row r="194">
-      <c r="A194" s="82" t="n"/>
-      <c r="B194" s="693" t="inlineStr">
-        <is>
-          <t>SUBTOTAL CAPÍTULO 18 - URBANISMO Y EXTERIORES</t>
-        </is>
-      </c>
-      <c r="C194" s="536" t="n"/>
-      <c r="D194" s="536" t="n"/>
-      <c r="E194" s="536" t="n"/>
-      <c r="F194" s="1297">
-        <f>SUM(F187:F193)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="195">
-      <c r="A195" s="83" t="n"/>
-      <c r="B195" s="694" t="n"/>
-      <c r="C195" s="694" t="n"/>
-      <c r="D195" s="694" t="n"/>
-      <c r="E195" s="694" t="n"/>
-      <c r="F195" s="695" t="n"/>
+      <c r="D195" s="273" t="n"/>
+      <c r="E195" s="1295" t="n"/>
+      <c r="F195" s="1296">
+        <f>D195*E195</f>
+        <v/>
+      </c>
     </row>
     <row r="196">
-      <c r="A196" s="189" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="B196" s="692" t="inlineStr">
-        <is>
-          <t>OBRAS COMPLEMENTARIAS</t>
-        </is>
-      </c>
-      <c r="C196" s="536" t="n"/>
-      <c r="D196" s="536" t="n"/>
-      <c r="E196" s="536" t="n"/>
-      <c r="F196" s="536" t="n"/>
+      <c r="A196" s="81" t="inlineStr">
+        <is>
+          <t>17.3</t>
+        </is>
+      </c>
+      <c r="B196" s="403" t="inlineStr">
+        <is>
+          <t>Pruebas y certificación</t>
+        </is>
+      </c>
+      <c r="C196" s="272" t="inlineStr">
+        <is>
+          <t>GL</t>
+        </is>
+      </c>
+      <c r="D196" s="273" t="n"/>
+      <c r="E196" s="1295" t="n"/>
+      <c r="F196" s="1296">
+        <f>D196*E196</f>
+        <v/>
+      </c>
     </row>
     <row r="197">
-      <c r="A197" s="81" t="inlineStr">
-        <is>
-          <t>19.1</t>
-        </is>
-      </c>
-      <c r="B197" s="403" t="inlineStr">
-        <is>
-          <t>Rejas metálicas</t>
-        </is>
-      </c>
-      <c r="C197" s="272" t="inlineStr">
-        <is>
-          <t>M²</t>
-        </is>
-      </c>
-      <c r="D197" s="273" t="n"/>
-      <c r="E197" s="1295" t="n"/>
-      <c r="F197" s="1296">
-        <f>D197*E197</f>
+      <c r="A197" s="82" t="n"/>
+      <c r="B197" s="693" t="inlineStr">
+        <is>
+          <t>SUBTOTAL CAPÍTULO 17 - GAS</t>
+        </is>
+      </c>
+      <c r="C197" s="536" t="n"/>
+      <c r="D197" s="536" t="n"/>
+      <c r="E197" s="536" t="n"/>
+      <c r="F197" s="1297">
+        <f>SUM(F194:F196)</f>
         <v/>
       </c>
     </row>
     <row r="198">
-      <c r="A198" s="81" t="inlineStr">
-        <is>
-          <t>19.2</t>
-        </is>
-      </c>
-      <c r="B198" s="403" t="inlineStr">
-        <is>
-          <t>Escaleras metálicas</t>
-        </is>
-      </c>
-      <c r="C198" s="272" t="inlineStr">
-        <is>
-          <t>KG</t>
-        </is>
-      </c>
-      <c r="D198" s="273" t="n"/>
-      <c r="E198" s="1295" t="n"/>
-      <c r="F198" s="1296">
-        <f>D198*E198</f>
-        <v/>
-      </c>
+      <c r="A198" s="83" t="n"/>
+      <c r="B198" s="694" t="n"/>
+      <c r="C198" s="694" t="n"/>
+      <c r="D198" s="694" t="n"/>
+      <c r="E198" s="694" t="n"/>
+      <c r="F198" s="695" t="n"/>
     </row>
     <row r="199">
-      <c r="A199" s="81" t="inlineStr">
-        <is>
-          <t>19.3</t>
-        </is>
-      </c>
-      <c r="B199" s="403" t="inlineStr">
-        <is>
-          <t>Elementos metálicos especiales</t>
-        </is>
-      </c>
-      <c r="C199" s="272" t="inlineStr">
-        <is>
-          <t>KG</t>
-        </is>
-      </c>
-      <c r="D199" s="273" t="n"/>
-      <c r="E199" s="1295" t="n"/>
-      <c r="F199" s="1296">
-        <f>D199*E199</f>
-        <v/>
-      </c>
+      <c r="A199" s="189" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B199" s="692" t="inlineStr">
+        <is>
+          <t>URBANISMO Y EXTERIORES</t>
+        </is>
+      </c>
+      <c r="C199" s="536" t="n"/>
+      <c r="D199" s="536" t="n"/>
+      <c r="E199" s="536" t="n"/>
+      <c r="F199" s="536" t="n"/>
     </row>
     <row r="200">
       <c r="A200" s="81" t="inlineStr">
         <is>
-          <t>19.4</t>
+          <t>18.1</t>
         </is>
       </c>
       <c r="B200" s="403" t="inlineStr">
         <is>
-          <t>Mobiliario fijo de obra</t>
+          <t>Construcción de andenes</t>
         </is>
       </c>
       <c r="C200" s="272" t="inlineStr">
         <is>
-          <t>UND</t>
+          <t>M²</t>
         </is>
       </c>
       <c r="D200" s="273" t="n"/>
@@ -14817,58 +14846,88 @@
       </c>
     </row>
     <row r="201">
-      <c r="A201" s="82" t="n"/>
-      <c r="B201" s="693" t="inlineStr">
-        <is>
-          <t>SUBTOTAL CAPÍTULO 19 - OBRAS COMPLEMENTARIAS</t>
-        </is>
-      </c>
-      <c r="C201" s="536" t="n"/>
-      <c r="D201" s="536" t="n"/>
-      <c r="E201" s="536" t="n"/>
-      <c r="F201" s="1297">
-        <f>SUM(F197:F200)</f>
+      <c r="A201" s="81" t="inlineStr">
+        <is>
+          <t>18.2</t>
+        </is>
+      </c>
+      <c r="B201" s="403" t="inlineStr">
+        <is>
+          <t>Placas de concreto exteriores</t>
+        </is>
+      </c>
+      <c r="C201" s="272" t="inlineStr">
+        <is>
+          <t>M³</t>
+        </is>
+      </c>
+      <c r="D201" s="273" t="n"/>
+      <c r="E201" s="1295" t="n"/>
+      <c r="F201" s="1296">
+        <f>D201*E201</f>
         <v/>
       </c>
     </row>
     <row r="202">
-      <c r="A202" s="83" t="n"/>
-      <c r="B202" s="694" t="n"/>
-      <c r="C202" s="694" t="n"/>
-      <c r="D202" s="694" t="n"/>
-      <c r="E202" s="694" t="n"/>
-      <c r="F202" s="695" t="n"/>
+      <c r="A202" s="81" t="inlineStr">
+        <is>
+          <t>18.3</t>
+        </is>
+      </c>
+      <c r="B202" s="403" t="inlineStr">
+        <is>
+          <t>Pavimento en adoquín</t>
+        </is>
+      </c>
+      <c r="C202" s="272" t="inlineStr">
+        <is>
+          <t>M²</t>
+        </is>
+      </c>
+      <c r="D202" s="273" t="n"/>
+      <c r="E202" s="1295" t="n"/>
+      <c r="F202" s="1296">
+        <f>D202*E202</f>
+        <v/>
+      </c>
     </row>
     <row r="203">
-      <c r="A203" s="189" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="B203" s="692" t="inlineStr">
-        <is>
-          <t>ASEO, ENTREGA Y CIERRE</t>
-        </is>
-      </c>
-      <c r="C203" s="536" t="n"/>
-      <c r="D203" s="536" t="n"/>
-      <c r="E203" s="536" t="n"/>
-      <c r="F203" s="536" t="n"/>
+      <c r="A203" s="81" t="inlineStr">
+        <is>
+          <t>18.4</t>
+        </is>
+      </c>
+      <c r="B203" s="403" t="inlineStr">
+        <is>
+          <t>Sardineles y bordillos</t>
+        </is>
+      </c>
+      <c r="C203" s="272" t="inlineStr">
+        <is>
+          <t>ML</t>
+        </is>
+      </c>
+      <c r="D203" s="273" t="n"/>
+      <c r="E203" s="1295" t="n"/>
+      <c r="F203" s="1296">
+        <f>D203*E203</f>
+        <v/>
+      </c>
     </row>
     <row r="204">
       <c r="A204" s="81" t="inlineStr">
         <is>
-          <t>20.1</t>
+          <t>18.5</t>
         </is>
       </c>
       <c r="B204" s="403" t="inlineStr">
         <is>
-          <t>Limpieza gruesa y fina de obra</t>
+          <t>Sumideros exteriores</t>
         </is>
       </c>
       <c r="C204" s="272" t="inlineStr">
         <is>
-          <t>M²</t>
+          <t>UND</t>
         </is>
       </c>
       <c r="D204" s="273" t="n"/>
@@ -14881,17 +14940,17 @@
     <row r="205">
       <c r="A205" s="81" t="inlineStr">
         <is>
-          <t>20.2</t>
+          <t>18.6</t>
         </is>
       </c>
       <c r="B205" s="403" t="inlineStr">
         <is>
-          <t>Limpieza final para entrega</t>
+          <t>Suministro y extendido de tierra vegetal</t>
         </is>
       </c>
       <c r="C205" s="272" t="inlineStr">
         <is>
-          <t>M²</t>
+          <t>M³</t>
         </is>
       </c>
       <c r="D205" s="273" t="n"/>
@@ -14904,17 +14963,17 @@
     <row r="206">
       <c r="A206" s="81" t="inlineStr">
         <is>
-          <t>20.3</t>
+          <t>18.7</t>
         </is>
       </c>
       <c r="B206" s="403" t="inlineStr">
         <is>
-          <t>Pruebas, puesta en marcha y ajustes</t>
+          <t>Siembra y jardinería</t>
         </is>
       </c>
       <c r="C206" s="272" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>M²</t>
         </is>
       </c>
       <c r="D206" s="273" t="n"/>
@@ -14927,17 +14986,17 @@
     <row r="207">
       <c r="A207" s="81" t="inlineStr">
         <is>
-          <t>20.4</t>
+          <t>18.8</t>
         </is>
       </c>
       <c r="B207" s="403" t="inlineStr">
         <is>
-          <t>Actualización de planos récord / as-built</t>
+          <t>Geotextil para drenaje y filtración</t>
         </is>
       </c>
       <c r="C207" s="272" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>M²</t>
         </is>
       </c>
       <c r="D207" s="273" t="n"/>
@@ -14950,17 +15009,17 @@
     <row r="208">
       <c r="A208" s="81" t="inlineStr">
         <is>
-          <t>20.5</t>
+          <t>18.9</t>
         </is>
       </c>
       <c r="B208" s="403" t="inlineStr">
         <is>
-          <t>Entrega, manuales y acta de recibo</t>
+          <t>Gaviones para obras de contención</t>
         </is>
       </c>
       <c r="C208" s="272" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>M³</t>
         </is>
       </c>
       <c r="D208" s="273" t="n"/>
@@ -14971,120 +15030,150 @@
       </c>
     </row>
     <row r="209">
-      <c r="A209" s="82" t="n"/>
-      <c r="B209" s="693" t="inlineStr">
-        <is>
-          <t>SUBTOTAL CAPÍTULO 20 - ASEO, ENTREGA Y CIERRE</t>
-        </is>
-      </c>
-      <c r="C209" s="536" t="n"/>
-      <c r="D209" s="536" t="n"/>
-      <c r="E209" s="536" t="n"/>
-      <c r="F209" s="1297">
-        <f>SUM(F204:F208)</f>
+      <c r="A209" s="81" t="inlineStr">
+        <is>
+          <t>18.10</t>
+        </is>
+      </c>
+      <c r="B209" s="403" t="inlineStr">
+        <is>
+          <t>Filtro francés (drenaje de terrenos)</t>
+        </is>
+      </c>
+      <c r="C209" s="272" t="inlineStr">
+        <is>
+          <t>ML</t>
+        </is>
+      </c>
+      <c r="D209" s="273" t="n"/>
+      <c r="E209" s="1295" t="n"/>
+      <c r="F209" s="1296">
+        <f>D209*E209</f>
         <v/>
       </c>
     </row>
     <row r="210">
-      <c r="A210" s="83" t="n"/>
-      <c r="B210" s="694" t="n"/>
-      <c r="C210" s="694" t="n"/>
-      <c r="D210" s="694" t="n"/>
-      <c r="E210" s="694" t="n"/>
-      <c r="F210" s="695" t="n"/>
+      <c r="A210" s="81" t="inlineStr">
+        <is>
+          <t>18.11</t>
+        </is>
+      </c>
+      <c r="B210" s="403" t="inlineStr">
+        <is>
+          <t>Revegetalización / empradización</t>
+        </is>
+      </c>
+      <c r="C210" s="272" t="inlineStr">
+        <is>
+          <t>M²</t>
+        </is>
+      </c>
+      <c r="D210" s="273" t="n"/>
+      <c r="E210" s="1295" t="n"/>
+      <c r="F210" s="1296">
+        <f>D210*E210</f>
+        <v/>
+      </c>
     </row>
     <row r="211">
-      <c r="A211" s="189" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="B211" s="692" t="inlineStr">
-        <is>
-          <t>ASCENSORES</t>
+      <c r="A211" s="82" t="n"/>
+      <c r="B211" s="693" t="inlineStr">
+        <is>
+          <t>SUBTOTAL CAPÍTULO 18 - URBANISMO Y EXTERIORES</t>
         </is>
       </c>
       <c r="C211" s="536" t="n"/>
       <c r="D211" s="536" t="n"/>
       <c r="E211" s="536" t="n"/>
-      <c r="F211" s="536" t="n"/>
+      <c r="F211" s="1297">
+        <f>SUM(F200:F210)</f>
+        <v/>
+      </c>
     </row>
     <row r="212">
-      <c r="A212" s="81" t="inlineStr">
-        <is>
-          <t>21.1</t>
-        </is>
-      </c>
-      <c r="B212" s="403" t="inlineStr">
-        <is>
-          <t>Suministro e instalación de ascensor eléctrico</t>
-        </is>
-      </c>
-      <c r="C212" s="272" t="inlineStr">
-        <is>
-          <t>UND</t>
-        </is>
-      </c>
-      <c r="D212" s="273" t="n"/>
-      <c r="E212" s="1295" t="n"/>
-      <c r="F212" s="1296">
-        <f>D212*E212</f>
-        <v/>
-      </c>
+      <c r="A212" s="83" t="n"/>
+      <c r="B212" s="694" t="n"/>
+      <c r="C212" s="694" t="n"/>
+      <c r="D212" s="694" t="n"/>
+      <c r="E212" s="694" t="n"/>
+      <c r="F212" s="695" t="n"/>
     </row>
     <row r="213">
-      <c r="A213" s="82" t="n"/>
-      <c r="B213" s="693" t="inlineStr">
-        <is>
-          <t>SUBTOTAL CAPÍTULO 21 - ASCENSORES</t>
+      <c r="A213" s="189" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B213" s="692" t="inlineStr">
+        <is>
+          <t>OBRAS COMPLEMENTARIAS</t>
         </is>
       </c>
       <c r="C213" s="536" t="n"/>
       <c r="D213" s="536" t="n"/>
       <c r="E213" s="536" t="n"/>
-      <c r="F213" s="1297">
-        <f>SUM(F212:F212)</f>
-        <v/>
-      </c>
+      <c r="F213" s="536" t="n"/>
     </row>
     <row r="214">
-      <c r="A214" s="83" t="n"/>
-      <c r="B214" s="694" t="n"/>
-      <c r="C214" s="694" t="n"/>
-      <c r="D214" s="694" t="n"/>
-      <c r="E214" s="694" t="n"/>
-      <c r="F214" s="695" t="n"/>
+      <c r="A214" s="81" t="inlineStr">
+        <is>
+          <t>19.1</t>
+        </is>
+      </c>
+      <c r="B214" s="403" t="inlineStr">
+        <is>
+          <t>Rejas metálicas</t>
+        </is>
+      </c>
+      <c r="C214" s="272" t="inlineStr">
+        <is>
+          <t>M²</t>
+        </is>
+      </c>
+      <c r="D214" s="273" t="n"/>
+      <c r="E214" s="1295" t="n"/>
+      <c r="F214" s="1296">
+        <f>D214*E214</f>
+        <v/>
+      </c>
     </row>
     <row r="215">
-      <c r="A215" s="189" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="B215" s="692" t="inlineStr">
-        <is>
-          <t>GESTIÓN, DISEÑO Y ADMINISTRACIÓN</t>
-        </is>
-      </c>
-      <c r="C215" s="536" t="n"/>
-      <c r="D215" s="536" t="n"/>
-      <c r="E215" s="536" t="n"/>
-      <c r="F215" s="536" t="n"/>
+      <c r="A215" s="81" t="inlineStr">
+        <is>
+          <t>19.2</t>
+        </is>
+      </c>
+      <c r="B215" s="403" t="inlineStr">
+        <is>
+          <t>Escaleras metálicas</t>
+        </is>
+      </c>
+      <c r="C215" s="272" t="inlineStr">
+        <is>
+          <t>KG</t>
+        </is>
+      </c>
+      <c r="D215" s="273" t="n"/>
+      <c r="E215" s="1295" t="n"/>
+      <c r="F215" s="1296">
+        <f>D215*E215</f>
+        <v/>
+      </c>
     </row>
     <row r="216">
       <c r="A216" s="81" t="inlineStr">
         <is>
-          <t>22.1</t>
+          <t>19.3</t>
         </is>
       </c>
       <c r="B216" s="403" t="inlineStr">
         <is>
-          <t>Estudio de suelos y geotecnia</t>
+          <t>Elementos metálicos especiales</t>
         </is>
       </c>
       <c r="C216" s="272" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>KG</t>
         </is>
       </c>
       <c r="D216" s="273" t="n"/>
@@ -15097,17 +15186,17 @@
     <row r="217">
       <c r="A217" s="81" t="inlineStr">
         <is>
-          <t>22.2</t>
+          <t>19.4</t>
         </is>
       </c>
       <c r="B217" s="403" t="inlineStr">
         <is>
-          <t>Diseños arquitectónicos, estructurales, hidrosanitarios y eléctricos</t>
+          <t>Mobiliario fijo de obra</t>
         </is>
       </c>
       <c r="C217" s="272" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>UND</t>
         </is>
       </c>
       <c r="D217" s="273" t="n"/>
@@ -15118,387 +15207,688 @@
       </c>
     </row>
     <row r="218">
-      <c r="A218" s="81" t="inlineStr">
-        <is>
-          <t>22.3</t>
-        </is>
-      </c>
-      <c r="B218" s="403" t="inlineStr">
-        <is>
-          <t>Licencia de construcción y trámites de curaduría urbana</t>
-        </is>
-      </c>
-      <c r="C218" s="272" t="inlineStr">
-        <is>
-          <t>GL</t>
-        </is>
-      </c>
-      <c r="D218" s="273" t="n"/>
-      <c r="E218" s="1295" t="n"/>
-      <c r="F218" s="1296">
-        <f>D218*E218</f>
+      <c r="A218" s="82" t="n"/>
+      <c r="B218" s="693" t="inlineStr">
+        <is>
+          <t>SUBTOTAL CAPÍTULO 19 - OBRAS COMPLEMENTARIAS</t>
+        </is>
+      </c>
+      <c r="C218" s="536" t="n"/>
+      <c r="D218" s="536" t="n"/>
+      <c r="E218" s="536" t="n"/>
+      <c r="F218" s="1297">
+        <f>SUM(F214:F217)</f>
         <v/>
       </c>
     </row>
     <row r="219">
-      <c r="A219" s="81" t="inlineStr">
-        <is>
-          <t>22.4</t>
-        </is>
-      </c>
-      <c r="B219" s="403" t="inlineStr">
-        <is>
-          <t>Póliza de estabilidad de obra y seguros de construcción (todo riesgo)</t>
-        </is>
-      </c>
-      <c r="C219" s="272" t="inlineStr">
-        <is>
-          <t>GL</t>
-        </is>
-      </c>
-      <c r="D219" s="273" t="n"/>
-      <c r="E219" s="1295" t="n"/>
-      <c r="F219" s="1296">
-        <f>D219*E219</f>
-        <v/>
-      </c>
+      <c r="A219" s="83" t="n"/>
+      <c r="B219" s="694" t="n"/>
+      <c r="C219" s="694" t="n"/>
+      <c r="D219" s="694" t="n"/>
+      <c r="E219" s="694" t="n"/>
+      <c r="F219" s="695" t="n"/>
     </row>
     <row r="220">
-      <c r="A220" s="82" t="n"/>
-      <c r="B220" s="693" t="inlineStr">
-        <is>
-          <t>SUBTOTAL CAPÍTULO 22 - GESTIÓN, DISEÑO Y ADMINISTRACIÓN</t>
+      <c r="A220" s="189" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B220" s="692" t="inlineStr">
+        <is>
+          <t>ASEO, ENTREGA Y CIERRE</t>
         </is>
       </c>
       <c r="C220" s="536" t="n"/>
       <c r="D220" s="536" t="n"/>
       <c r="E220" s="536" t="n"/>
-      <c r="F220" s="1297">
-        <f>SUM(F216:F219)</f>
-        <v/>
-      </c>
+      <c r="F220" s="536" t="n"/>
     </row>
     <row r="221">
-      <c r="A221" s="83" t="n"/>
-      <c r="B221" s="694" t="n"/>
-      <c r="C221" s="694" t="n"/>
-      <c r="D221" s="694" t="n"/>
-      <c r="E221" s="694" t="n"/>
-      <c r="F221" s="695" t="n"/>
-    </row>
-    <row r="222" ht="15" customHeight="1" s="539">
-      <c r="A222" s="84" t="n"/>
-      <c r="B222" s="698" t="inlineStr">
-        <is>
-          <t>COSTO DIRECTO TOTAL (suma de capítulos 1 a 14)</t>
-        </is>
-      </c>
-      <c r="C222" s="536" t="n"/>
-      <c r="D222" s="536" t="n"/>
-      <c r="E222" s="536" t="n"/>
-      <c r="F222" s="1298">
-        <f>F24+F38+F48+F65+F75+F85+F91+F98+F109+F117+F127+F134+F148+F162+F171+F178+F184+F194+F201+F209+F213+F220</f>
+      <c r="A221" s="81" t="inlineStr">
+        <is>
+          <t>20.1</t>
+        </is>
+      </c>
+      <c r="B221" s="403" t="inlineStr">
+        <is>
+          <t>Limpieza gruesa y fina de obra</t>
+        </is>
+      </c>
+      <c r="C221" s="272" t="inlineStr">
+        <is>
+          <t>M²</t>
+        </is>
+      </c>
+      <c r="D221" s="273" t="n"/>
+      <c r="E221" s="1295" t="n"/>
+      <c r="F221" s="1296">
+        <f>D221*E221</f>
+        <v/>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" s="81" t="inlineStr">
+        <is>
+          <t>20.2</t>
+        </is>
+      </c>
+      <c r="B222" s="403" t="inlineStr">
+        <is>
+          <t>Limpieza final para entrega</t>
+        </is>
+      </c>
+      <c r="C222" s="272" t="inlineStr">
+        <is>
+          <t>M²</t>
+        </is>
+      </c>
+      <c r="D222" s="273" t="n"/>
+      <c r="E222" s="1295" t="n"/>
+      <c r="F222" s="1296">
+        <f>D222*E222</f>
         <v/>
       </c>
     </row>
     <row r="223">
-      <c r="A223" s="85" t="n"/>
-      <c r="B223" s="28" t="n"/>
-      <c r="C223" s="28" t="n"/>
-      <c r="D223" s="28" t="n"/>
-      <c r="E223" s="28" t="n"/>
-      <c r="F223" s="86" t="n"/>
-    </row>
-    <row r="224" ht="15" customHeight="1" s="539">
-      <c r="A224" s="83" t="n"/>
-      <c r="B224" s="46" t="inlineStr">
+      <c r="A223" s="81" t="inlineStr">
+        <is>
+          <t>20.3</t>
+        </is>
+      </c>
+      <c r="B223" s="403" t="inlineStr">
+        <is>
+          <t>Pruebas, puesta en marcha y ajustes</t>
+        </is>
+      </c>
+      <c r="C223" s="272" t="inlineStr">
+        <is>
+          <t>GL</t>
+        </is>
+      </c>
+      <c r="D223" s="273" t="n"/>
+      <c r="E223" s="1295" t="n"/>
+      <c r="F223" s="1296">
+        <f>D223*E223</f>
+        <v/>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" s="81" t="inlineStr">
+        <is>
+          <t>20.4</t>
+        </is>
+      </c>
+      <c r="B224" s="403" t="inlineStr">
+        <is>
+          <t>Actualización de planos récord / as-built</t>
+        </is>
+      </c>
+      <c r="C224" s="272" t="inlineStr">
+        <is>
+          <t>GL</t>
+        </is>
+      </c>
+      <c r="D224" s="273" t="n"/>
+      <c r="E224" s="1295" t="n"/>
+      <c r="F224" s="1296">
+        <f>D224*E224</f>
+        <v/>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" s="81" t="inlineStr">
+        <is>
+          <t>20.5</t>
+        </is>
+      </c>
+      <c r="B225" s="403" t="inlineStr">
+        <is>
+          <t>Entrega, manuales y acta de recibo</t>
+        </is>
+      </c>
+      <c r="C225" s="272" t="inlineStr">
+        <is>
+          <t>GL</t>
+        </is>
+      </c>
+      <c r="D225" s="273" t="n"/>
+      <c r="E225" s="1295" t="n"/>
+      <c r="F225" s="1296">
+        <f>D225*E225</f>
+        <v/>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" s="82" t="n"/>
+      <c r="B226" s="693" t="inlineStr">
+        <is>
+          <t>SUBTOTAL CAPÍTULO 20 - ASEO, ENTREGA Y CIERRE</t>
+        </is>
+      </c>
+      <c r="C226" s="536" t="n"/>
+      <c r="D226" s="536" t="n"/>
+      <c r="E226" s="536" t="n"/>
+      <c r="F226" s="1297">
+        <f>SUM(F221:F225)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" s="83" t="n"/>
+      <c r="B227" s="694" t="n"/>
+      <c r="C227" s="694" t="n"/>
+      <c r="D227" s="694" t="n"/>
+      <c r="E227" s="694" t="n"/>
+      <c r="F227" s="695" t="n"/>
+    </row>
+    <row r="228">
+      <c r="A228" s="189" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="B228" s="692" t="inlineStr">
+        <is>
+          <t>ASCENSORES</t>
+        </is>
+      </c>
+      <c r="C228" s="536" t="n"/>
+      <c r="D228" s="536" t="n"/>
+      <c r="E228" s="536" t="n"/>
+      <c r="F228" s="536" t="n"/>
+    </row>
+    <row r="229">
+      <c r="A229" s="81" t="inlineStr">
+        <is>
+          <t>21.1</t>
+        </is>
+      </c>
+      <c r="B229" s="403" t="inlineStr">
+        <is>
+          <t>Suministro e instalación de ascensor eléctrico</t>
+        </is>
+      </c>
+      <c r="C229" s="272" t="inlineStr">
+        <is>
+          <t>UND</t>
+        </is>
+      </c>
+      <c r="D229" s="273" t="n"/>
+      <c r="E229" s="1295" t="n"/>
+      <c r="F229" s="1296">
+        <f>D229*E229</f>
+        <v/>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" s="82" t="n"/>
+      <c r="B230" s="693" t="inlineStr">
+        <is>
+          <t>SUBTOTAL CAPÍTULO 21 - ASCENSORES</t>
+        </is>
+      </c>
+      <c r="C230" s="536" t="n"/>
+      <c r="D230" s="536" t="n"/>
+      <c r="E230" s="536" t="n"/>
+      <c r="F230" s="1297">
+        <f>SUM(F229:F229)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" s="83" t="n"/>
+      <c r="B231" s="694" t="n"/>
+      <c r="C231" s="694" t="n"/>
+      <c r="D231" s="694" t="n"/>
+      <c r="E231" s="694" t="n"/>
+      <c r="F231" s="695" t="n"/>
+    </row>
+    <row r="232">
+      <c r="A232" s="189" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="B232" s="692" t="inlineStr">
+        <is>
+          <t>GESTIÓN, DISEÑO Y ADMINISTRACIÓN</t>
+        </is>
+      </c>
+      <c r="C232" s="536" t="n"/>
+      <c r="D232" s="536" t="n"/>
+      <c r="E232" s="536" t="n"/>
+      <c r="F232" s="536" t="n"/>
+    </row>
+    <row r="233">
+      <c r="A233" s="81" t="inlineStr">
+        <is>
+          <t>22.1</t>
+        </is>
+      </c>
+      <c r="B233" s="403" t="inlineStr">
+        <is>
+          <t>Estudio de suelos y geotecnia</t>
+        </is>
+      </c>
+      <c r="C233" s="272" t="inlineStr">
+        <is>
+          <t>GL</t>
+        </is>
+      </c>
+      <c r="D233" s="273" t="n"/>
+      <c r="E233" s="1295" t="n"/>
+      <c r="F233" s="1296">
+        <f>D233*E233</f>
+        <v/>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" s="81" t="inlineStr">
+        <is>
+          <t>22.2</t>
+        </is>
+      </c>
+      <c r="B234" s="403" t="inlineStr">
+        <is>
+          <t>Diseños arquitectónicos, estructurales, hidrosanitarios y eléctricos</t>
+        </is>
+      </c>
+      <c r="C234" s="272" t="inlineStr">
+        <is>
+          <t>GL</t>
+        </is>
+      </c>
+      <c r="D234" s="273" t="n"/>
+      <c r="E234" s="1295" t="n"/>
+      <c r="F234" s="1296">
+        <f>D234*E234</f>
+        <v/>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" s="81" t="inlineStr">
+        <is>
+          <t>22.3</t>
+        </is>
+      </c>
+      <c r="B235" s="403" t="inlineStr">
+        <is>
+          <t>Licencia de construcción y trámites de curaduría urbana</t>
+        </is>
+      </c>
+      <c r="C235" s="272" t="inlineStr">
+        <is>
+          <t>GL</t>
+        </is>
+      </c>
+      <c r="D235" s="273" t="n"/>
+      <c r="E235" s="1295" t="n"/>
+      <c r="F235" s="1296">
+        <f>D235*E235</f>
+        <v/>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" s="81" t="inlineStr">
+        <is>
+          <t>22.4</t>
+        </is>
+      </c>
+      <c r="B236" s="403" t="inlineStr">
+        <is>
+          <t>Póliza de estabilidad de obra y seguros de construcción (todo riesgo)</t>
+        </is>
+      </c>
+      <c r="C236" s="272" t="inlineStr">
+        <is>
+          <t>GL</t>
+        </is>
+      </c>
+      <c r="D236" s="273" t="n"/>
+      <c r="E236" s="1295" t="n"/>
+      <c r="F236" s="1296">
+        <f>D236*E236</f>
+        <v/>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" s="82" t="n"/>
+      <c r="B237" s="693" t="inlineStr">
+        <is>
+          <t>SUBTOTAL CAPÍTULO 22 - GESTIÓN, DISEÑO Y ADMINISTRACIÓN</t>
+        </is>
+      </c>
+      <c r="C237" s="536" t="n"/>
+      <c r="D237" s="536" t="n"/>
+      <c r="E237" s="536" t="n"/>
+      <c r="F237" s="1297">
+        <f>SUM(F233:F236)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" s="83" t="n"/>
+      <c r="B238" s="694" t="n"/>
+      <c r="C238" s="694" t="n"/>
+      <c r="D238" s="694" t="n"/>
+      <c r="E238" s="694" t="n"/>
+      <c r="F238" s="695" t="n"/>
+    </row>
+    <row r="239" ht="15" customHeight="1" s="539">
+      <c r="A239" s="84" t="n"/>
+      <c r="B239" s="698" t="inlineStr">
+        <is>
+          <t>COSTO DIRECTO TOTAL (suma de capítulos 1 a 22)</t>
+        </is>
+      </c>
+      <c r="C239" s="536" t="n"/>
+      <c r="D239" s="536" t="n"/>
+      <c r="E239" s="536" t="n"/>
+      <c r="F239" s="1298">
+        <f>F25+F39+F49+F68+F80+F92+F99+F106+F120+F128+F139+F146+F161+F175+F184+F191+F197+F211+F218+F226+F230+F237</f>
+        <v/>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" s="85" t="n"/>
+      <c r="B240" s="28" t="n"/>
+      <c r="C240" s="28" t="n"/>
+      <c r="D240" s="28" t="n"/>
+      <c r="E240" s="28" t="n"/>
+      <c r="F240" s="86" t="n"/>
+    </row>
+    <row r="241" ht="15" customHeight="1" s="539">
+      <c r="A241" s="83" t="n"/>
+      <c r="B241" s="46" t="inlineStr">
         <is>
           <t>Administración (A)</t>
         </is>
       </c>
-      <c r="C224" s="694" t="n"/>
-      <c r="D224" s="694" t="n"/>
-      <c r="E224" s="1299">
+      <c r="C241" s="694" t="n"/>
+      <c r="D241" s="694" t="n"/>
+      <c r="E241" s="1299">
         <f>'Ficha Técnica del Proyecto'!$B$24</f>
         <v/>
       </c>
-      <c r="F224" s="1300">
-        <f>F222*E224</f>
-        <v/>
-      </c>
-    </row>
-    <row r="225" ht="15" customHeight="1" s="539">
-      <c r="A225" s="83" t="n"/>
-      <c r="B225" s="46" t="inlineStr">
+      <c r="F241" s="1300">
+        <f>F239*E241</f>
+        <v/>
+      </c>
+    </row>
+    <row r="242" ht="15" customHeight="1" s="539">
+      <c r="A242" s="83" t="n"/>
+      <c r="B242" s="46" t="inlineStr">
         <is>
           <t>Imprevistos (I)</t>
         </is>
       </c>
-      <c r="C225" s="694" t="n"/>
-      <c r="D225" s="694" t="n"/>
-      <c r="E225" s="1299">
+      <c r="C242" s="694" t="n"/>
+      <c r="D242" s="694" t="n"/>
+      <c r="E242" s="1299">
         <f>'Ficha Técnica del Proyecto'!$B$25</f>
         <v/>
       </c>
-      <c r="F225" s="1300">
-        <f>F222*E225</f>
-        <v/>
-      </c>
-    </row>
-    <row r="226" ht="15" customHeight="1" s="539">
-      <c r="A226" s="83" t="n"/>
-      <c r="B226" s="46" t="inlineStr">
+      <c r="F242" s="1300">
+        <f>F239*E242</f>
+        <v/>
+      </c>
+    </row>
+    <row r="243" ht="15" customHeight="1" s="539">
+      <c r="A243" s="83" t="n"/>
+      <c r="B243" s="46" t="inlineStr">
         <is>
           <t>Utilidad (U)</t>
         </is>
       </c>
-      <c r="C226" s="694" t="n"/>
-      <c r="D226" s="694" t="n"/>
-      <c r="E226" s="1299">
+      <c r="C243" s="694" t="n"/>
+      <c r="D243" s="694" t="n"/>
+      <c r="E243" s="1299">
         <f>'Ficha Técnica del Proyecto'!$B$26</f>
         <v/>
       </c>
-      <c r="F226" s="1300">
-        <f>F222*E226</f>
-        <v/>
-      </c>
-    </row>
-    <row r="227" ht="15" customHeight="1" s="539">
-      <c r="A227" s="82" t="n"/>
-      <c r="B227" s="693" t="inlineStr">
+      <c r="F243" s="1300">
+        <f>F239*E243</f>
+        <v/>
+      </c>
+    </row>
+    <row r="244" ht="15" customHeight="1" s="539">
+      <c r="A244" s="82" t="n"/>
+      <c r="B244" s="693" t="inlineStr">
         <is>
           <t>SUBTOTAL AIU (A+I+U)</t>
         </is>
       </c>
-      <c r="C227" s="29" t="n"/>
-      <c r="D227" s="29" t="n"/>
-      <c r="E227" s="30" t="n"/>
-      <c r="F227" s="1297">
-        <f>F224+F225+F226</f>
-        <v/>
-      </c>
-    </row>
-    <row r="228" ht="15" customHeight="1" s="539">
-      <c r="A228" s="83" t="n"/>
-      <c r="B228" s="46" t="inlineStr">
+      <c r="C244" s="29" t="n"/>
+      <c r="D244" s="29" t="n"/>
+      <c r="E244" s="30" t="n"/>
+      <c r="F244" s="1297">
+        <f>F241+F242+F243</f>
+        <v/>
+      </c>
+    </row>
+    <row r="245" ht="15" customHeight="1" s="539">
+      <c r="A245" s="83" t="n"/>
+      <c r="B245" s="46" t="inlineStr">
         <is>
           <t>COSTO DIRECTO + AIU</t>
         </is>
       </c>
-      <c r="C228" s="694" t="n"/>
-      <c r="D228" s="694" t="n"/>
-      <c r="E228" s="47" t="n"/>
-      <c r="F228" s="1300">
-        <f>F222+F227</f>
-        <v/>
-      </c>
-    </row>
-    <row r="229" ht="15" customHeight="1" s="539">
-      <c r="A229" s="83" t="n"/>
-      <c r="B229" s="46" t="inlineStr">
+      <c r="C245" s="694" t="n"/>
+      <c r="D245" s="694" t="n"/>
+      <c r="E245" s="47" t="n"/>
+      <c r="F245" s="1300">
+        <f>F239+F244</f>
+        <v/>
+      </c>
+    </row>
+    <row r="246" ht="15" customHeight="1" s="539">
+      <c r="A246" s="83" t="n"/>
+      <c r="B246" s="46" t="inlineStr">
         <is>
           <t>IVA sobre Utilidad (19%)</t>
         </is>
       </c>
-      <c r="C229" s="694" t="n"/>
-      <c r="D229" s="694" t="n"/>
-      <c r="E229" s="1299">
+      <c r="C246" s="694" t="n"/>
+      <c r="D246" s="694" t="n"/>
+      <c r="E246" s="1299">
         <f>'Ficha Técnica del Proyecto'!$B$27</f>
         <v/>
       </c>
-      <c r="F229" s="1300">
-        <f>F226*E229</f>
-        <v/>
-      </c>
-    </row>
-    <row r="230">
-      <c r="A230" s="83" t="n"/>
-      <c r="B230" s="694" t="n"/>
-      <c r="C230" s="694" t="n"/>
-      <c r="D230" s="694" t="n"/>
-      <c r="E230" s="694" t="n"/>
-      <c r="F230" s="695" t="n"/>
-    </row>
-    <row r="231" ht="24" customHeight="1" s="539">
-      <c r="A231" s="87" t="n"/>
-      <c r="B231" s="692" t="inlineStr">
+      <c r="F246" s="1300">
+        <f>F243*E246</f>
+        <v/>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" s="83" t="n"/>
+      <c r="B247" s="694" t="n"/>
+      <c r="C247" s="694" t="n"/>
+      <c r="D247" s="694" t="n"/>
+      <c r="E247" s="694" t="n"/>
+      <c r="F247" s="695" t="n"/>
+    </row>
+    <row r="248" ht="24" customHeight="1" s="539">
+      <c r="A248" s="87" t="n"/>
+      <c r="B248" s="692" t="inlineStr">
         <is>
           <t>PRESUPUESTO TOTAL DE OBRA</t>
         </is>
       </c>
-      <c r="C231" s="536" t="n"/>
-      <c r="D231" s="536" t="n"/>
-      <c r="E231" s="536" t="n"/>
-      <c r="F231" s="1301">
-        <f>F228+F229</f>
-        <v/>
-      </c>
-    </row>
-    <row r="232">
-      <c r="A232" s="88" t="n"/>
-      <c r="B232" s="211" t="inlineStr">
+      <c r="C248" s="536" t="n"/>
+      <c r="D248" s="536" t="n"/>
+      <c r="E248" s="536" t="n"/>
+      <c r="F248" s="1301">
+        <f>F245+F246</f>
+        <v/>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" s="88" t="n"/>
+      <c r="B249" s="211" t="inlineStr">
         <is>
           <t>REV. 10/09/2026</t>
         </is>
       </c>
-      <c r="C232" s="292" t="n"/>
-      <c r="D232" s="292" t="n"/>
-      <c r="E232" s="292" t="n"/>
-      <c r="F232" s="365">
+      <c r="C249" s="292" t="n"/>
+      <c r="D249" s="292" t="n"/>
+      <c r="E249" s="292" t="n"/>
+      <c r="F249" s="365">
         <f>F6</f>
         <v/>
       </c>
     </row>
-    <row r="233">
-      <c r="A233" s="88" t="n"/>
-      <c r="B233" s="211" t="n"/>
-      <c r="C233" s="292" t="n"/>
-      <c r="D233" s="292" t="n"/>
-      <c r="E233" s="292" t="n"/>
-      <c r="F233" s="209" t="n"/>
-    </row>
-    <row r="234" ht="15" customHeight="1" s="539">
-      <c r="A234" s="88" t="n"/>
-      <c r="B234" s="90" t="inlineStr">
+    <row r="250">
+      <c r="A250" s="88" t="n"/>
+      <c r="B250" s="211" t="n"/>
+      <c r="C250" s="292" t="n"/>
+      <c r="D250" s="292" t="n"/>
+      <c r="E250" s="292" t="n"/>
+      <c r="F250" s="209" t="n"/>
+    </row>
+    <row r="251" ht="15" customHeight="1" s="539">
+      <c r="A251" s="88" t="n"/>
+      <c r="B251" s="90" t="inlineStr">
         <is>
           <t>Costo por m² construido (sobre Costo Directo Total)</t>
         </is>
       </c>
-      <c r="C234" s="91" t="n"/>
-      <c r="D234" s="91" t="n"/>
-      <c r="E234" s="91" t="n"/>
-      <c r="F234" s="1302">
-        <f>F222/'Ficha Técnica del Proyecto'!$B$16</f>
-        <v/>
-      </c>
-    </row>
-    <row r="235" ht="15" customHeight="1" s="539">
-      <c r="A235" s="89" t="n"/>
-      <c r="B235" s="92" t="inlineStr">
+      <c r="C251" s="91" t="n"/>
+      <c r="D251" s="91" t="n"/>
+      <c r="E251" s="91" t="n"/>
+      <c r="F251" s="1302">
+        <f>F239/'Ficha Técnica del Proyecto'!$B$16</f>
+        <v/>
+      </c>
+    </row>
+    <row r="252" ht="15" customHeight="1" s="539">
+      <c r="A252" s="89" t="n"/>
+      <c r="B252" s="92" t="inlineStr">
         <is>
           <t>Costo por m² construido (sobre Presupuesto Total)</t>
         </is>
       </c>
-      <c r="C235" s="93" t="n"/>
-      <c r="D235" s="93" t="n"/>
-      <c r="E235" s="93" t="n"/>
-      <c r="F235" s="1303">
-        <f>F231/'Ficha Técnica del Proyecto'!$B$16</f>
-        <v/>
-      </c>
-    </row>
-    <row r="236">
-      <c r="A236" s="27" t="n"/>
-      <c r="B236" s="292" t="n"/>
-      <c r="C236" s="292" t="n"/>
-      <c r="D236" s="292" t="n"/>
-      <c r="E236" s="292" t="n"/>
-      <c r="F236" s="292" t="n"/>
-    </row>
-    <row r="237">
-      <c r="A237" s="27" t="n"/>
-      <c r="B237" s="292" t="n"/>
-      <c r="C237" s="292" t="n"/>
-      <c r="D237" s="292" t="n"/>
-      <c r="E237" s="292" t="n"/>
-      <c r="F237" s="292" t="n"/>
-    </row>
-    <row r="238">
-      <c r="A238" s="27" t="n"/>
-      <c r="B238" s="292" t="n"/>
-      <c r="C238" s="292" t="n"/>
-      <c r="D238" s="292" t="n"/>
-      <c r="E238" s="292" t="n"/>
-      <c r="F238" s="292" t="n"/>
-    </row>
-    <row r="239">
-      <c r="A239" s="27" t="n"/>
-      <c r="B239" s="292" t="n"/>
-      <c r="C239" s="292" t="n"/>
-      <c r="D239" s="292" t="n"/>
-      <c r="E239" s="292" t="n"/>
-      <c r="F239" s="292" t="n"/>
-    </row>
-    <row r="240">
-      <c r="A240" s="27" t="n"/>
-      <c r="B240" s="292" t="n"/>
-      <c r="C240" s="292" t="n"/>
-      <c r="D240" s="292" t="n"/>
-      <c r="E240" s="292" t="n"/>
-      <c r="F240" s="292" t="n"/>
-    </row>
-    <row r="241">
-      <c r="A241" s="27" t="n"/>
-      <c r="B241" s="292" t="n"/>
-      <c r="C241" s="292" t="n"/>
-      <c r="D241" s="292" t="n"/>
-      <c r="E241" s="292" t="n"/>
-      <c r="F241" s="292" t="n"/>
+      <c r="C252" s="93" t="n"/>
+      <c r="D252" s="93" t="n"/>
+      <c r="E252" s="93" t="n"/>
+      <c r="F252" s="1303">
+        <f>F248/'Ficha Técnica del Proyecto'!$B$16</f>
+        <v/>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" s="27" t="n"/>
+      <c r="B253" s="292" t="n"/>
+      <c r="C253" s="292" t="n"/>
+      <c r="D253" s="292" t="n"/>
+      <c r="E253" s="292" t="n"/>
+      <c r="F253" s="292" t="n"/>
+    </row>
+    <row r="254">
+      <c r="A254" s="27" t="n"/>
+      <c r="B254" s="292" t="n"/>
+      <c r="C254" s="292" t="n"/>
+      <c r="D254" s="292" t="n"/>
+      <c r="E254" s="292" t="n"/>
+      <c r="F254" s="292" t="n"/>
+    </row>
+    <row r="255">
+      <c r="A255" s="27" t="n"/>
+      <c r="B255" s="292" t="n"/>
+      <c r="C255" s="292" t="n"/>
+      <c r="D255" s="292" t="n"/>
+      <c r="E255" s="292" t="n"/>
+      <c r="F255" s="292" t="n"/>
+    </row>
+    <row r="256">
+      <c r="A256" s="27" t="n"/>
+      <c r="B256" s="292" t="n"/>
+      <c r="C256" s="292" t="n"/>
+      <c r="D256" s="292" t="n"/>
+      <c r="E256" s="292" t="n"/>
+      <c r="F256" s="292" t="n"/>
+    </row>
+    <row r="257">
+      <c r="A257" s="27" t="n"/>
+      <c r="B257" s="292" t="n"/>
+      <c r="C257" s="292" t="n"/>
+      <c r="D257" s="292" t="n"/>
+      <c r="E257" s="292" t="n"/>
+      <c r="F257" s="292" t="n"/>
+    </row>
+    <row r="258">
+      <c r="A258" s="27" t="n"/>
+      <c r="B258" s="292" t="n"/>
+      <c r="C258" s="292" t="n"/>
+      <c r="D258" s="292" t="n"/>
+      <c r="E258" s="292" t="n"/>
+      <c r="F258" s="292" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="62">
+    <mergeCell ref="B146:E146"/>
+    <mergeCell ref="B211:E211"/>
+    <mergeCell ref="B226:E226"/>
     <mergeCell ref="B129:F129"/>
     <mergeCell ref="C6:D6"/>
-    <mergeCell ref="B65:E65"/>
-    <mergeCell ref="B100:F100"/>
-    <mergeCell ref="B127:E127"/>
+    <mergeCell ref="B49:E49"/>
+    <mergeCell ref="B239:E239"/>
+    <mergeCell ref="B232:F232"/>
+    <mergeCell ref="B141:F141"/>
     <mergeCell ref="B92:E92"/>
-    <mergeCell ref="B201:E201"/>
+    <mergeCell ref="B68:E68"/>
+    <mergeCell ref="B193:F193"/>
+    <mergeCell ref="B139:E139"/>
     <mergeCell ref="C5:D5"/>
-    <mergeCell ref="B150:F150"/>
     <mergeCell ref="E5:F5"/>
-    <mergeCell ref="B215:F215"/>
-    <mergeCell ref="B24:E24"/>
-    <mergeCell ref="B93:F93"/>
+    <mergeCell ref="B199:F199"/>
+    <mergeCell ref="B122:F122"/>
+    <mergeCell ref="B80:E80"/>
     <mergeCell ref="B1:B9"/>
-    <mergeCell ref="B222:E222"/>
-    <mergeCell ref="B85:E85"/>
-    <mergeCell ref="B213:E213"/>
-    <mergeCell ref="B76:E76"/>
-    <mergeCell ref="B180:F180"/>
-    <mergeCell ref="B77:F77"/>
-    <mergeCell ref="B75:E75"/>
-    <mergeCell ref="B111:F111"/>
-    <mergeCell ref="B91:E91"/>
-    <mergeCell ref="B136:F136"/>
-    <mergeCell ref="B67:F67"/>
-    <mergeCell ref="B209:E209"/>
-    <mergeCell ref="B109:E109"/>
-    <mergeCell ref="B134:E134"/>
+    <mergeCell ref="B220:F220"/>
+    <mergeCell ref="B27:F27"/>
+    <mergeCell ref="B70:F70"/>
+    <mergeCell ref="B130:F130"/>
+    <mergeCell ref="B197:E197"/>
+    <mergeCell ref="B228:F228"/>
+    <mergeCell ref="B237:E237"/>
+    <mergeCell ref="B106:E106"/>
+    <mergeCell ref="B218:E218"/>
+    <mergeCell ref="B100:E100"/>
+    <mergeCell ref="B25:E25"/>
+    <mergeCell ref="B107:F107"/>
+    <mergeCell ref="B101:F101"/>
+    <mergeCell ref="B81:E81"/>
     <mergeCell ref="C9:D9"/>
     <mergeCell ref="B14:F14"/>
-    <mergeCell ref="B194:E194"/>
-    <mergeCell ref="B119:F119"/>
+    <mergeCell ref="B148:F148"/>
+    <mergeCell ref="B82:F82"/>
     <mergeCell ref="A12:B12"/>
     <mergeCell ref="C12:D12"/>
     <mergeCell ref="A10:F10"/>
     <mergeCell ref="B184:E184"/>
-    <mergeCell ref="B87:F87"/>
-    <mergeCell ref="B196:F196"/>
-    <mergeCell ref="B220:E220"/>
-    <mergeCell ref="B48:E48"/>
+    <mergeCell ref="B248:E248"/>
+    <mergeCell ref="B161:E161"/>
+    <mergeCell ref="B108:F108"/>
+    <mergeCell ref="B39:E39"/>
     <mergeCell ref="B186:F186"/>
-    <mergeCell ref="B99:F99"/>
-    <mergeCell ref="B117:E117"/>
-    <mergeCell ref="B231:E231"/>
-    <mergeCell ref="B26:F26"/>
-    <mergeCell ref="B40:F40"/>
-    <mergeCell ref="B211:F211"/>
+    <mergeCell ref="B120:E120"/>
+    <mergeCell ref="B230:E230"/>
+    <mergeCell ref="B99:E99"/>
     <mergeCell ref="C8:D8"/>
-    <mergeCell ref="B98:E98"/>
-    <mergeCell ref="B118:F118"/>
     <mergeCell ref="A11:F11"/>
     <mergeCell ref="C7:D7"/>
-    <mergeCell ref="B148:E148"/>
-    <mergeCell ref="B164:F164"/>
+    <mergeCell ref="B177:F177"/>
+    <mergeCell ref="B175:E175"/>
     <mergeCell ref="C1:F3"/>
-    <mergeCell ref="B171:E171"/>
-    <mergeCell ref="B38:E38"/>
-    <mergeCell ref="B162:E162"/>
-    <mergeCell ref="B178:E178"/>
-    <mergeCell ref="B50:F50"/>
-    <mergeCell ref="B203:F203"/>
-    <mergeCell ref="B173:F173"/>
+    <mergeCell ref="B213:F213"/>
+    <mergeCell ref="B191:E191"/>
+    <mergeCell ref="B51:F51"/>
+    <mergeCell ref="B94:F94"/>
+    <mergeCell ref="B128:E128"/>
+    <mergeCell ref="B163:F163"/>
+    <mergeCell ref="B41:F41"/>
   </mergeCells>
   <pageMargins left="0.1968503937007874" right="0.1968503937007874" top="0.1968503937007874" bottom="0.1968503937007874" header="0.5118110236220472" footer="0.5118110236220472"/>
   <pageSetup orientation="portrait" paperSize="9" scale="53" horizontalDpi="300" verticalDpi="300"/>
@@ -15694,7 +16084,7 @@
       <c r="J14" s="536" t="n"/>
       <c r="K14" s="536" t="n"/>
       <c r="L14" s="1366">
-        <f>'Presupuesto '!F231</f>
+        <f>'Presupuesto '!F248</f>
         <v/>
       </c>
       <c r="M14" s="536" t="n"/>
@@ -15928,7 +16318,7 @@
       <c r="B25" s="587" t="n"/>
       <c r="C25" s="587" t="n"/>
       <c r="D25" s="1372">
-        <f>'Presupuesto '!F24/'Presupuesto '!$F$222</f>
+        <f>'Presupuesto '!F25/'Presupuesto '!$F$239</f>
         <v/>
       </c>
       <c r="E25" s="238" t="n"/>
@@ -15962,7 +16352,7 @@
       <c r="B26" s="587" t="n"/>
       <c r="C26" s="587" t="n"/>
       <c r="D26" s="1372">
-        <f>'Presupuesto '!F38/'Presupuesto '!$F$222</f>
+        <f>'Presupuesto '!F39/'Presupuesto '!$F$239</f>
         <v/>
       </c>
       <c r="E26" s="238" t="n"/>
@@ -15993,7 +16383,7 @@
       <c r="B27" s="587" t="n"/>
       <c r="C27" s="587" t="n"/>
       <c r="D27" s="1372">
-        <f>'Presupuesto '!F48/'Presupuesto '!$F$222</f>
+        <f>'Presupuesto '!F49/'Presupuesto '!$F$239</f>
         <v/>
       </c>
       <c r="E27" s="238" t="n"/>
@@ -16024,7 +16414,7 @@
       <c r="B28" s="587" t="n"/>
       <c r="C28" s="587" t="n"/>
       <c r="D28" s="1372">
-        <f>'Presupuesto '!F65/'Presupuesto '!$F$222</f>
+        <f>'Presupuesto '!F68/'Presupuesto '!$F$239</f>
         <v/>
       </c>
       <c r="E28" s="238" t="n"/>
@@ -16055,7 +16445,7 @@
       <c r="B29" s="587" t="n"/>
       <c r="C29" s="587" t="n"/>
       <c r="D29" s="1372">
-        <f>'Presupuesto '!F75/'Presupuesto '!$F$222</f>
+        <f>'Presupuesto '!F80/'Presupuesto '!$F$239</f>
         <v/>
       </c>
       <c r="E29" s="238" t="n"/>
@@ -16086,7 +16476,7 @@
       <c r="B30" s="587" t="n"/>
       <c r="C30" s="587" t="n"/>
       <c r="D30" s="1372">
-        <f>'Presupuesto '!F85/'Presupuesto '!$F$222</f>
+        <f>'Presupuesto '!F92/'Presupuesto '!$F$239</f>
         <v/>
       </c>
       <c r="E30" s="238" t="n"/>
@@ -16117,7 +16507,7 @@
       <c r="B31" s="587" t="n"/>
       <c r="C31" s="587" t="n"/>
       <c r="D31" s="1372">
-        <f>'Presupuesto '!F91/'Presupuesto '!$F$222</f>
+        <f>'Presupuesto '!F99/'Presupuesto '!$F$239</f>
         <v/>
       </c>
       <c r="E31" s="238" t="n"/>
@@ -16148,7 +16538,7 @@
       <c r="B32" s="587" t="n"/>
       <c r="C32" s="587" t="n"/>
       <c r="D32" s="1372">
-        <f>'Presupuesto '!F98/'Presupuesto '!$F$222</f>
+        <f>'Presupuesto '!F106/'Presupuesto '!$F$239</f>
         <v/>
       </c>
       <c r="E32" s="238" t="n"/>
@@ -16179,7 +16569,7 @@
       <c r="B33" s="587" t="n"/>
       <c r="C33" s="587" t="n"/>
       <c r="D33" s="1372">
-        <f>'Presupuesto '!F109/'Presupuesto '!$F$222</f>
+        <f>'Presupuesto '!F120/'Presupuesto '!$F$239</f>
         <v/>
       </c>
       <c r="E33" s="238" t="n"/>
@@ -16210,7 +16600,7 @@
       <c r="B34" s="587" t="n"/>
       <c r="C34" s="587" t="n"/>
       <c r="D34" s="1372">
-        <f>'Presupuesto '!F117/'Presupuesto '!$F$222</f>
+        <f>'Presupuesto '!F128/'Presupuesto '!$F$239</f>
         <v/>
       </c>
       <c r="E34" s="238" t="n"/>
@@ -16241,7 +16631,7 @@
       <c r="B35" s="587" t="n"/>
       <c r="C35" s="587" t="n"/>
       <c r="D35" s="1372">
-        <f>'Presupuesto '!F127/'Presupuesto '!$F$222</f>
+        <f>'Presupuesto '!F139/'Presupuesto '!$F$239</f>
         <v/>
       </c>
       <c r="E35" s="238" t="n"/>
@@ -16272,7 +16662,7 @@
       <c r="B36" s="587" t="n"/>
       <c r="C36" s="587" t="n"/>
       <c r="D36" s="1372">
-        <f>'Presupuesto '!F134/'Presupuesto '!$F$222</f>
+        <f>'Presupuesto '!F146/'Presupuesto '!$F$239</f>
         <v/>
       </c>
       <c r="E36" s="238" t="n"/>
@@ -16303,7 +16693,7 @@
       <c r="B37" s="587" t="n"/>
       <c r="C37" s="587" t="n"/>
       <c r="D37" s="1372">
-        <f>'Presupuesto '!F148/'Presupuesto '!$F$222</f>
+        <f>'Presupuesto '!F161/'Presupuesto '!$F$239</f>
         <v/>
       </c>
       <c r="E37" s="238" t="n"/>
@@ -16334,7 +16724,7 @@
       <c r="B38" s="587" t="n"/>
       <c r="C38" s="587" t="n"/>
       <c r="D38" s="1372">
-        <f>'Presupuesto '!F162/'Presupuesto '!$F$222</f>
+        <f>'Presupuesto '!F175/'Presupuesto '!$F$239</f>
         <v/>
       </c>
       <c r="E38" s="238" t="n"/>
@@ -16365,7 +16755,7 @@
       <c r="B39" s="587" t="n"/>
       <c r="C39" s="587" t="n"/>
       <c r="D39" s="1372">
-        <f>'Presupuesto '!F171/'Presupuesto '!$F$222</f>
+        <f>'Presupuesto '!F184/'Presupuesto '!$F$239</f>
         <v/>
       </c>
       <c r="E39" s="238" t="n"/>
@@ -16396,7 +16786,7 @@
       <c r="B40" s="536" t="n"/>
       <c r="C40" s="536" t="n"/>
       <c r="D40" s="1372">
-        <f>'Presupuesto '!F178/'Presupuesto '!$F$222</f>
+        <f>'Presupuesto '!F191/'Presupuesto '!$F$239</f>
         <v/>
       </c>
       <c r="E40" s="238" t="n"/>
@@ -16427,7 +16817,7 @@
       <c r="B41" s="1049" t="n"/>
       <c r="C41" s="1049" t="n"/>
       <c r="D41" s="1372">
-        <f>'Presupuesto '!F184/'Presupuesto '!$F$222</f>
+        <f>'Presupuesto '!F197/'Presupuesto '!$F$239</f>
         <v/>
       </c>
       <c r="E41" s="1049" t="n"/>
@@ -16458,7 +16848,7 @@
       <c r="B42" s="587" t="n"/>
       <c r="C42" s="587" t="n"/>
       <c r="D42" s="1372">
-        <f>'Presupuesto '!F194/'Presupuesto '!$F$222</f>
+        <f>'Presupuesto '!F211/'Presupuesto '!$F$239</f>
         <v/>
       </c>
       <c r="E42" s="587" t="n"/>
@@ -16489,7 +16879,7 @@
       <c r="B43" s="536" t="n"/>
       <c r="C43" s="536" t="n"/>
       <c r="D43" s="1372">
-        <f>'Presupuesto '!F201/'Presupuesto '!$F$222</f>
+        <f>'Presupuesto '!F218/'Presupuesto '!$F$239</f>
         <v/>
       </c>
       <c r="E43" s="238" t="n"/>
@@ -16520,7 +16910,7 @@
       <c r="B44" s="536" t="n"/>
       <c r="C44" s="536" t="n"/>
       <c r="D44" s="1372">
-        <f>'Presupuesto '!F209/'Presupuesto '!$F$222</f>
+        <f>'Presupuesto '!F226/'Presupuesto '!$F$239</f>
         <v/>
       </c>
       <c r="E44" s="238" t="n"/>
@@ -16551,7 +16941,7 @@
       <c r="B45" s="536" t="n"/>
       <c r="C45" s="536" t="n"/>
       <c r="D45" s="1372">
-        <f>'Presupuesto '!F213/'Presupuesto '!$F$222</f>
+        <f>'Presupuesto '!F230/'Presupuesto '!$F$239</f>
         <v/>
       </c>
       <c r="E45" s="536" t="n"/>
@@ -16582,7 +16972,7 @@
       <c r="B46" s="536" t="n"/>
       <c r="C46" s="536" t="n"/>
       <c r="D46" s="1372">
-        <f>'Presupuesto '!F220/'Presupuesto '!$F$222</f>
+        <f>'Presupuesto '!F237/'Presupuesto '!$F$239</f>
         <v/>
       </c>
       <c r="E46" s="238" t="n"/>
@@ -17665,8 +18055,8 @@
     <mergeCell ref="A105:G120"/>
     <mergeCell ref="H64:J64"/>
     <mergeCell ref="K124:N125"/>
+    <mergeCell ref="F128:I129"/>
     <mergeCell ref="J39:N39"/>
-    <mergeCell ref="F128:I129"/>
     <mergeCell ref="L15:N15"/>
     <mergeCell ref="A66:C66"/>
     <mergeCell ref="G23:G24"/>
@@ -18315,6 +18705,7 @@
     <mergeCell ref="C16:E16"/>
     <mergeCell ref="A39:E39"/>
     <mergeCell ref="A34:E34"/>
+    <mergeCell ref="C29:E29"/>
     <mergeCell ref="C22:E22"/>
     <mergeCell ref="C9:E9"/>
     <mergeCell ref="A36:E36"/>
@@ -18343,11 +18734,10 @@
     <mergeCell ref="C14:E14"/>
     <mergeCell ref="A38:E38"/>
     <mergeCell ref="B5:C5"/>
+    <mergeCell ref="C26:E26"/>
+    <mergeCell ref="A31:E31"/>
+    <mergeCell ref="C20:E20"/>
     <mergeCell ref="A40:E40"/>
-    <mergeCell ref="C26:E26"/>
-    <mergeCell ref="C29:E29"/>
-    <mergeCell ref="C20:E20"/>
-    <mergeCell ref="A31:E31"/>
     <mergeCell ref="B4:C4"/>
     <mergeCell ref="C25:E25"/>
     <mergeCell ref="C10:E10"/>

--- a/public/plantilla-mensual.xlsx
+++ b/public/plantilla-mensual.xlsx
@@ -10098,464 +10098,6 @@
 </styleSheet>
 </file>
 
-<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
-  <chart>
-    <title>
-      <tx>
-        <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0"/>
-          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-            <a:pPr>
-              <a:defRPr lang="es-CO" sz="1800" b="1" strike="noStrike" spc="-1">
-                <a:solidFill>
-                  <a:srgbClr val="000000"/>
-                </a:solidFill>
-                <a:latin typeface="Calibri"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:r>
-              <a:rPr lang="es-CO" sz="1800" b="1" strike="noStrike" spc="-1">
-                <a:solidFill>
-                  <a:srgbClr val="000000"/>
-                </a:solidFill>
-                <a:latin typeface="Calibri"/>
-              </a:rPr>
-              <a:t>Costo directo por capítulo (COP)</a:t>
-            </a:r>
-          </a:p>
-        </rich>
-      </tx>
-      <overlay val="0"/>
-      <spPr>
-        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="0">
-          <a:noFill/>
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </title>
-    <plotArea>
-      <layout/>
-      <barChart>
-        <barDir val="col"/>
-        <grouping val="clustered"/>
-        <varyColors val="0"/>
-        <ser>
-          <idx val="0"/>
-          <order val="0"/>
-          <tx>
-            <strRef>
-              <f>Resumen!$C$11</f>
-              <strCache>
-                <ptCount val="1"/>
-                <pt idx="0">
-                  <v>Valor (COP)</v>
-                </pt>
-              </strCache>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:srgbClr val="4F81BD"/>
-            </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="0">
-              <a:noFill/>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <invertIfNegative val="0"/>
-          <dLbls>
-            <spPr>
-              <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:noFill/>
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-            <txPr>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" wrap="square"/>
-              <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:pPr>
-                  <a:defRPr sz="1000" b="0" strike="noStrike" spc="-1">
-                    <a:solidFill>
-                      <a:srgbClr val="000000"/>
-                    </a:solidFill>
-                    <a:latin typeface="Arial"/>
-                  </a:defRPr>
-                </a:pPr>
-                <a:r>
-                  <a:t>None</a:t>
-                </a:r>
-                <a:endParaRPr lang="es-CO"/>
-              </a:p>
-            </txPr>
-            <dLblPos val="outEnd"/>
-            <showLegendKey val="0"/>
-            <showVal val="0"/>
-            <showCatName val="0"/>
-            <showSerName val="0"/>
-            <showPercent val="0"/>
-            <showBubbleSize val="1"/>
-            <showLeaderLines val="0"/>
-          </dLbls>
-          <cat>
-            <strRef>
-              <f>Resumen!$A$12:$A$25</f>
-              <strCache>
-                <ptCount val="14"/>
-                <pt idx="0">
-                  <v>1</v>
-                </pt>
-                <pt idx="1">
-                  <v>2</v>
-                </pt>
-                <pt idx="2">
-                  <v>3</v>
-                </pt>
-                <pt idx="3">
-                  <v>4</v>
-                </pt>
-                <pt idx="4">
-                  <v>5</v>
-                </pt>
-                <pt idx="5">
-                  <v>6</v>
-                </pt>
-                <pt idx="6">
-                  <v>7</v>
-                </pt>
-                <pt idx="7">
-                  <v>8</v>
-                </pt>
-                <pt idx="8">
-                  <v>9</v>
-                </pt>
-                <pt idx="9">
-                  <v>10</v>
-                </pt>
-                <pt idx="10">
-                  <v>11</v>
-                </pt>
-                <pt idx="11">
-                  <v>12</v>
-                </pt>
-                <pt idx="12">
-                  <v>13</v>
-                </pt>
-                <pt idx="13">
-                  <v>14</v>
-                </pt>
-              </strCache>
-            </strRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>Resumen!$C$12:$C$25</f>
-              <numCache>
-                <formatCode>"$ "#,##0</formatCode>
-                <ptCount val="14"/>
-                <pt idx="0">
-                  <v>0</v>
-                </pt>
-                <pt idx="1">
-                  <v>0</v>
-                </pt>
-                <pt idx="2">
-                  <v>0</v>
-                </pt>
-                <pt idx="3">
-                  <v>0</v>
-                </pt>
-                <pt idx="4">
-                  <v>0</v>
-                </pt>
-                <pt idx="5">
-                  <v>0</v>
-                </pt>
-                <pt idx="6">
-                  <v>0</v>
-                </pt>
-                <pt idx="7">
-                  <v>0</v>
-                </pt>
-                <pt idx="8">
-                  <v>0</v>
-                </pt>
-                <pt idx="9">
-                  <v>0</v>
-                </pt>
-                <pt idx="10">
-                  <v>0</v>
-                </pt>
-                <pt idx="11">
-                  <v>0</v>
-                </pt>
-                <pt idx="12">
-                  <v>0</v>
-                </pt>
-                <pt idx="13">
-                  <v>0</v>
-                </pt>
-              </numCache>
-            </numRef>
-          </val>
-        </ser>
-        <dLbls>
-          <showLegendKey val="0"/>
-          <showVal val="0"/>
-          <showCatName val="0"/>
-          <showSerName val="0"/>
-          <showPercent val="0"/>
-          <showBubbleSize val="0"/>
-        </dLbls>
-        <gapWidth val="150"/>
-        <axId val="50050775"/>
-        <axId val="41416401"/>
-      </barChart>
-      <catAx>
-        <axId val="50050775"/>
-        <scaling>
-          <orientation val="minMax"/>
-        </scaling>
-        <delete val="0"/>
-        <axPos val="b"/>
-        <title>
-          <tx>
-            <rich>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0"/>
-              <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:pPr>
-                  <a:defRPr lang="es-CO" sz="1000" b="1" strike="noStrike" spc="-1">
-                    <a:solidFill>
-                      <a:srgbClr val="000000"/>
-                    </a:solidFill>
-                    <a:latin typeface="Calibri"/>
-                  </a:defRPr>
-                </a:pPr>
-                <a:r>
-                  <a:rPr lang="es-CO" sz="1000" b="1" strike="noStrike" spc="-1">
-                    <a:solidFill>
-                      <a:srgbClr val="000000"/>
-                    </a:solidFill>
-                    <a:latin typeface="Calibri"/>
-                  </a:rPr>
-                  <a:t>Capítulo</a:t>
-                </a:r>
-              </a:p>
-            </rich>
-          </tx>
-          <overlay val="0"/>
-          <spPr>
-            <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="0">
-              <a:noFill/>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-        </title>
-        <numFmt formatCode="General" sourceLinked="0"/>
-        <majorTickMark val="none"/>
-        <minorTickMark val="none"/>
-        <tickLblPos val="nextTo"/>
-        <spPr>
-          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9360">
-            <a:solidFill>
-              <a:srgbClr val="878787"/>
-            </a:solidFill>
-            <a:prstDash val="solid"/>
-            <a:round/>
-          </a:ln>
-        </spPr>
-        <txPr>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-            <a:pPr>
-              <a:defRPr sz="1000" b="0" strike="noStrike" spc="-1">
-                <a:solidFill>
-                  <a:srgbClr val="000000"/>
-                </a:solidFill>
-                <a:latin typeface="Calibri"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:r>
-              <a:t>None</a:t>
-            </a:r>
-            <a:endParaRPr lang="es-CO"/>
-          </a:p>
-        </txPr>
-        <crossAx val="41416401"/>
-        <crosses val="autoZero"/>
-        <auto val="1"/>
-        <lblAlgn val="ctr"/>
-        <lblOffset val="100"/>
-        <noMultiLvlLbl val="0"/>
-      </catAx>
-      <valAx>
-        <axId val="41416401"/>
-        <scaling>
-          <orientation val="minMax"/>
-        </scaling>
-        <delete val="0"/>
-        <axPos val="l"/>
-        <majorGridlines>
-          <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9360">
-              <a:solidFill>
-                <a:srgbClr val="878787"/>
-              </a:solidFill>
-              <a:prstDash val="solid"/>
-              <a:round/>
-            </a:ln>
-          </spPr>
-        </majorGridlines>
-        <title>
-          <tx>
-            <rich>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="-5400000"/>
-              <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:pPr>
-                  <a:defRPr lang="es-CO" sz="1000" b="1" strike="noStrike" spc="-1">
-                    <a:solidFill>
-                      <a:srgbClr val="000000"/>
-                    </a:solidFill>
-                    <a:latin typeface="Calibri"/>
-                  </a:defRPr>
-                </a:pPr>
-                <a:r>
-                  <a:rPr lang="es-CO" sz="1000" b="1" strike="noStrike" spc="-1">
-                    <a:solidFill>
-                      <a:srgbClr val="000000"/>
-                    </a:solidFill>
-                    <a:latin typeface="Calibri"/>
-                  </a:rPr>
-                  <a:t>COP</a:t>
-                </a:r>
-              </a:p>
-            </rich>
-          </tx>
-          <overlay val="0"/>
-          <spPr>
-            <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="0">
-              <a:noFill/>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-        </title>
-        <numFmt formatCode="&quot;$ &quot;#,##0" sourceLinked="0"/>
-        <majorTickMark val="none"/>
-        <minorTickMark val="none"/>
-        <tickLblPos val="nextTo"/>
-        <spPr>
-          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9360">
-            <a:solidFill>
-              <a:srgbClr val="878787"/>
-            </a:solidFill>
-            <a:prstDash val="solid"/>
-            <a:round/>
-          </a:ln>
-        </spPr>
-        <txPr>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-            <a:pPr>
-              <a:defRPr sz="1000" b="0" strike="noStrike" spc="-1">
-                <a:solidFill>
-                  <a:srgbClr val="000000"/>
-                </a:solidFill>
-                <a:latin typeface="Calibri"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:r>
-              <a:t>None</a:t>
-            </a:r>
-            <a:endParaRPr lang="es-CO"/>
-          </a:p>
-        </txPr>
-        <crossAx val="50050775"/>
-        <crosses val="autoZero"/>
-        <crossBetween val="between"/>
-      </valAx>
-    </plotArea>
-    <legend>
-      <legendPos val="r"/>
-      <overlay val="0"/>
-      <spPr>
-        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="0">
-          <a:noFill/>
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-      <txPr>
-        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:pPr>
-            <a:defRPr sz="1000" b="0" strike="noStrike" spc="-1">
-              <a:solidFill>
-                <a:srgbClr val="000000"/>
-              </a:solidFill>
-              <a:latin typeface="Calibri"/>
-            </a:defRPr>
-          </a:pPr>
-          <a:r>
-            <a:t>None</a:t>
-          </a:r>
-          <a:endParaRPr lang="es-CO"/>
-        </a:p>
-      </txPr>
-    </legend>
-    <plotVisOnly val="1"/>
-    <dispBlanksAs val="gap"/>
-  </chart>
-  <spPr>
-    <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-      <a:srgbClr val="FFFFFF"/>
-    </a:solidFill>
-    <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9360">
-      <a:solidFill>
-        <a:srgbClr val="D9D9D9"/>
-      </a:solidFill>
-      <a:prstDash val="solid"/>
-      <a:round/>
-    </a:ln>
-  </spPr>
-</chartSpace>
-</file>
-
-<file path=xl/comments/comment1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <authors>
-    <author>OpenAI</author>
-  </authors>
-  <commentList>
-    <comment ref="I26" authorId="0" shapeId="0">
-      <text>
-        <t>Cantidad acumulada = cantidad anterior + cantidad del presente acta.</t>
-      </text>
-    </comment>
-    <comment ref="J26" authorId="0" shapeId="0">
-      <text>
-        <t>Saldo = cantidad contractual - cantidad acumulada. No permite saldos negativos.</t>
-      </text>
-    </comment>
-    <comment ref="K26" authorId="0" shapeId="0">
-      <text>
-        <t>% ejecución = cantidad acumulada / cantidad contractual.</t>
-      </text>
-    </comment>
-  </commentList>
-</comments>
-</file>
-
 <file path=xl/drawings/drawing12.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <xdr:twoCellAnchor editAs="oneCell">

--- a/public/plantilla-mensual.xlsx
+++ b/public/plantilla-mensual.xlsx
@@ -10021,7 +10021,7 @@
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
-                  <a:t/>
+                  <a:t>None</a:t>
                 </a:r>
                 <a:endParaRPr lang="es-CO"/>
               </a:p>
@@ -10217,7 +10217,7 @@
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:t/>
+              <a:t>None</a:t>
             </a:r>
             <a:endParaRPr lang="es-CO"/>
           </a:p>
@@ -10308,7 +10308,7 @@
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:t/>
+              <a:t>None</a:t>
             </a:r>
             <a:endParaRPr lang="es-CO"/>
           </a:p>
@@ -10341,7 +10341,7 @@
             </a:defRPr>
           </a:pPr>
           <a:r>
-            <a:t/>
+            <a:t>None</a:t>
           </a:r>
           <a:endParaRPr lang="es-CO"/>
         </a:p>
@@ -10749,7 +10749,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E42"/>
+  <dimension ref="A1:E47"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
   <cols>
     <col width="42" customWidth="1" style="1223" min="1" max="1"/>
@@ -10849,414 +10849,463 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="15" customHeight="1" s="1223">
+    <row r="8">
       <c r="A8" s="597" t="inlineStr">
         <is>
+          <t>IDENTIFICACIÓN DEL PROYECTO</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="99" t="inlineStr">
+        <is>
+          <t>Proyecto</t>
+        </is>
+      </c>
+      <c r="B9" s="100" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="99" t="inlineStr">
+        <is>
+          <t>No de Contrato</t>
+        </is>
+      </c>
+      <c r="B10" s="100" t="n"/>
+      <c r="C10" s="99" t="inlineStr">
+        <is>
+          <t>Fecha de Emisión</t>
+        </is>
+      </c>
+      <c r="D10" s="100" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="99" t="inlineStr">
+        <is>
+          <t>Contratista</t>
+        </is>
+      </c>
+      <c r="B11" s="100" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="99" t="inlineStr">
+        <is>
+          <t>Ubicación</t>
+        </is>
+      </c>
+      <c r="B12" s="100" t="n"/>
+    </row>
+    <row r="13" ht="15" customHeight="1" s="1223">
+      <c r="A13" s="597" t="inlineStr">
+        <is>
           <t>DATOS GENERALES DEL PROYECTO</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="15" customHeight="1" s="1223">
-      <c r="A9" s="99" t="inlineStr">
+    <row r="14" ht="15" customHeight="1" s="1223">
+      <c r="A14" s="99" t="inlineStr">
         <is>
           <t>Número de pisos (torre)</t>
         </is>
       </c>
-      <c r="B9" s="100" t="n"/>
-      <c r="C9" s="593" t="inlineStr">
+      <c r="B14" s="100" t="n"/>
+      <c r="C14" s="593" t="inlineStr">
         <is>
           <t>pisos</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="15" customHeight="1" s="1223">
-      <c r="A10" s="101" t="inlineStr">
+    <row r="15" ht="15" customHeight="1" s="1223">
+      <c r="A15" s="101" t="inlineStr">
         <is>
           <t>Número de sótanos (parqueaderos)</t>
         </is>
       </c>
-      <c r="B10" s="102" t="n"/>
-      <c r="C10" s="590" t="inlineStr">
+      <c r="B15" s="102" t="n"/>
+      <c r="C15" s="590" t="inlineStr">
         <is>
           <t>niveles</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="15" customHeight="1" s="1223">
-      <c r="A11" s="99" t="inlineStr">
+    <row r="16" ht="15" customHeight="1" s="1223">
+      <c r="A16" s="99" t="inlineStr">
         <is>
           <t>Área del lote</t>
         </is>
       </c>
-      <c r="B11" s="100" t="n"/>
-      <c r="C11" s="593" t="inlineStr">
+      <c r="B16" s="100" t="n"/>
+      <c r="C16" s="593" t="inlineStr">
         <is>
           <t>m²</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="15" customHeight="1" s="1223">
-      <c r="A12" s="101" t="inlineStr">
+    <row r="17" ht="15" customHeight="1" s="1223">
+      <c r="A17" s="101" t="inlineStr">
         <is>
           <t>Área construida típica por piso</t>
         </is>
       </c>
-      <c r="B12" s="102" t="n"/>
-      <c r="C12" s="590" t="inlineStr">
+      <c r="B17" s="102" t="n"/>
+      <c r="C17" s="590" t="inlineStr">
         <is>
           <t>m²</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="15" customHeight="1" s="1223">
-      <c r="A13" s="99" t="inlineStr">
+    <row r="18" ht="15" customHeight="1" s="1223">
+      <c r="A18" s="99" t="inlineStr">
         <is>
           <t>Área construida - torre (12 pisos)</t>
         </is>
       </c>
-      <c r="B13" s="103">
-        <f>B9*B12</f>
-        <v/>
-      </c>
-      <c r="C13" s="593" t="inlineStr">
+      <c r="B18" s="103">
+        <f>B14*B17</f>
+        <v/>
+      </c>
+      <c r="C18" s="593" t="inlineStr">
         <is>
           <t>m²</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="15" customHeight="1" s="1223">
-      <c r="A14" s="101" t="inlineStr">
+    <row r="19" ht="15" customHeight="1" s="1223">
+      <c r="A19" s="101" t="inlineStr">
         <is>
           <t>Área construida - sótanos (2 niveles)</t>
         </is>
       </c>
-      <c r="B14" s="102" t="n"/>
-      <c r="C14" s="590" t="inlineStr">
+      <c r="B19" s="102" t="n"/>
+      <c r="C19" s="590" t="inlineStr">
         <is>
           <t>m²</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="15" customHeight="1" s="1223">
-      <c r="A15" s="99" t="inlineStr">
+    <row r="20" ht="15" customHeight="1" s="1223">
+      <c r="A20" s="99" t="inlineStr">
         <is>
           <t>Área cubierta / cuarto de máquinas / tanques</t>
         </is>
       </c>
-      <c r="B15" s="100" t="n"/>
-      <c r="C15" s="593" t="inlineStr">
+      <c r="B20" s="100" t="n"/>
+      <c r="C20" s="593" t="inlineStr">
         <is>
           <t>m²</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="15" customHeight="1" s="1223">
-      <c r="A16" s="101" t="inlineStr">
+    <row r="21" ht="15" customHeight="1" s="1223">
+      <c r="A21" s="101" t="inlineStr">
         <is>
           <t>ÁREA TOTAL CONSTRUIDA</t>
         </is>
       </c>
-      <c r="B16" s="104">
-        <f>B13+B14+B15</f>
-        <v/>
-      </c>
-      <c r="C16" s="590" t="inlineStr">
+      <c r="B21" s="104">
+        <f>B18+B19+B20</f>
+        <v/>
+      </c>
+      <c r="C21" s="590" t="inlineStr">
         <is>
           <t>m²</t>
         </is>
       </c>
     </row>
-    <row r="17" ht="15" customHeight="1" s="1223">
-      <c r="A17" s="99" t="inlineStr">
+    <row r="22" ht="15" customHeight="1" s="1223">
+      <c r="A22" s="99" t="inlineStr">
         <is>
           <t>Número de apartamentos</t>
         </is>
       </c>
-      <c r="B17" s="100" t="n"/>
-      <c r="C17" s="593" t="inlineStr">
+      <c r="B22" s="100" t="n"/>
+      <c r="C22" s="593" t="inlineStr">
         <is>
           <t>und</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="15" customHeight="1" s="1223">
-      <c r="A18" s="101" t="inlineStr">
+    <row r="23" ht="15" customHeight="1" s="1223">
+      <c r="A23" s="101" t="inlineStr">
         <is>
           <t>Área promedio por apartamento (vendible)</t>
         </is>
       </c>
-      <c r="B18" s="102" t="n"/>
-      <c r="C18" s="590" t="inlineStr">
+      <c r="B23" s="102" t="n"/>
+      <c r="C23" s="590" t="inlineStr">
         <is>
           <t>m²</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="15" customHeight="1" s="1223">
-      <c r="A19" s="99" t="inlineStr">
-        <is>
-          <t>Número de parqueaderos</t>
-        </is>
-      </c>
-      <c r="B19" s="100" t="n"/>
-      <c r="C19" s="593" t="inlineStr">
-        <is>
-          <t>und</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="15" customHeight="1" s="1223">
-      <c r="A20" s="101" t="inlineStr">
-        <is>
-          <t>Número de ascensores</t>
-        </is>
-      </c>
-      <c r="B20" s="102" t="n"/>
-      <c r="C20" s="590" t="inlineStr">
-        <is>
-          <t>und</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="15" customHeight="1" s="1223">
-      <c r="A21" s="99" t="inlineStr">
-        <is>
-          <t>Altura total aproximada (sótano a cubierta)</t>
-        </is>
-      </c>
-      <c r="B21" s="100" t="n"/>
-      <c r="C21" s="593" t="inlineStr">
-        <is>
-          <t>m</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="592" t="n"/>
-      <c r="B22" s="592" t="n"/>
-      <c r="C22" s="592" t="n"/>
-    </row>
-    <row r="23" ht="15" customHeight="1" s="1223">
-      <c r="A23" s="594" t="inlineStr">
-        <is>
-          <t>PARÁMETROS ECONÓMICOS DEL PRESUPUESTO</t>
         </is>
       </c>
     </row>
     <row r="24" ht="15" customHeight="1" s="1223">
       <c r="A24" s="99" t="inlineStr">
         <is>
-          <t>Administración (A)</t>
-        </is>
-      </c>
-      <c r="B24" s="466" t="n">
-        <v>0.1</v>
-      </c>
+          <t>Número de parqueaderos</t>
+        </is>
+      </c>
+      <c r="B24" s="100" t="n"/>
       <c r="C24" s="593" t="inlineStr">
         <is>
-          <t>% s/costo directo</t>
+          <t>und</t>
         </is>
       </c>
     </row>
     <row r="25" ht="15" customHeight="1" s="1223">
       <c r="A25" s="101" t="inlineStr">
         <is>
-          <t>Imprevistos (I)</t>
-        </is>
-      </c>
-      <c r="B25" s="467" t="n">
-        <v>0.04</v>
-      </c>
+          <t>Número de ascensores</t>
+        </is>
+      </c>
+      <c r="B25" s="102" t="n"/>
       <c r="C25" s="590" t="inlineStr">
         <is>
-          <t>% s/costo directo</t>
+          <t>und</t>
         </is>
       </c>
     </row>
     <row r="26" ht="15" customHeight="1" s="1223">
       <c r="A26" s="99" t="inlineStr">
         <is>
+          <t>Altura total aproximada (sótano a cubierta)</t>
+        </is>
+      </c>
+      <c r="B26" s="100" t="n"/>
+      <c r="C26" s="593" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="592" t="n"/>
+      <c r="B27" s="592" t="n"/>
+      <c r="C27" s="592" t="n"/>
+    </row>
+    <row r="28" ht="15" customHeight="1" s="1223">
+      <c r="A28" s="594" t="inlineStr">
+        <is>
+          <t>PARÁMETROS ECONÓMICOS DEL PRESUPUESTO</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="15" customHeight="1" s="1223">
+      <c r="A29" s="99" t="inlineStr">
+        <is>
+          <t>Administración (A)</t>
+        </is>
+      </c>
+      <c r="B29" s="466" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="C29" s="593" t="inlineStr">
+        <is>
+          <t>% s/costo directo</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="15" customHeight="1" s="1223">
+      <c r="A30" s="101" t="inlineStr">
+        <is>
+          <t>Imprevistos (I)</t>
+        </is>
+      </c>
+      <c r="B30" s="467" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="C30" s="590" t="inlineStr">
+        <is>
+          <t>% s/costo directo</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="15" customHeight="1" s="1223">
+      <c r="A31" s="99" t="inlineStr">
+        <is>
           <t>Utilidad (U)</t>
         </is>
       </c>
-      <c r="B26" s="466" t="n">
+      <c r="B31" s="466" t="n">
         <v>0.12</v>
       </c>
-      <c r="C26" s="593" t="inlineStr">
+      <c r="C31" s="593" t="inlineStr">
         <is>
           <t>% s/costo directo</t>
         </is>
       </c>
     </row>
-    <row r="27" ht="15" customHeight="1" s="1223">
-      <c r="A27" s="101" t="inlineStr">
+    <row r="32" ht="15" customHeight="1" s="1223">
+      <c r="A32" s="101" t="inlineStr">
         <is>
           <t>IVA sobre Utilidad</t>
         </is>
       </c>
-      <c r="B27" s="467" t="n">
+      <c r="B32" s="467" t="n">
         <v>0.19</v>
       </c>
-      <c r="C27" s="590" t="inlineStr">
+      <c r="C32" s="590" t="inlineStr">
         <is>
           <t>% s/utilidad (Ley 1943 / práctica AIU en Colombia)</t>
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="592" t="n"/>
-      <c r="B28" s="592" t="n"/>
-      <c r="C28" s="592" t="n"/>
-    </row>
-    <row r="29" ht="15" customHeight="1" s="1223">
-      <c r="A29" s="105" t="inlineStr">
+    <row r="33">
+      <c r="A33" s="592" t="n"/>
+      <c r="B33" s="592" t="n"/>
+      <c r="C33" s="592" t="n"/>
+    </row>
+    <row r="34" ht="15" customHeight="1" s="1223">
+      <c r="A34" s="105" t="inlineStr">
         <is>
           <t>AIU TOTAL (A+I+U)</t>
         </is>
       </c>
-      <c r="B29" s="468">
-        <f>B24+B25+B26</f>
-        <v/>
-      </c>
-      <c r="C29" s="592" t="n"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="592" t="n"/>
-      <c r="B30" s="592" t="n"/>
-      <c r="C30" s="592" t="n"/>
-    </row>
-    <row r="31" ht="15" customHeight="1" s="1223">
-      <c r="A31" s="594" t="inlineStr">
+      <c r="B34" s="468">
+        <f>B29+B30+B31</f>
+        <v/>
+      </c>
+      <c r="C34" s="592" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="592" t="n"/>
+      <c r="B35" s="592" t="n"/>
+      <c r="C35" s="592" t="n"/>
+    </row>
+    <row r="36" ht="15" customHeight="1" s="1223">
+      <c r="A36" s="594" t="inlineStr">
         <is>
           <t>FUENTES Y NOTAS METODOLÓGICAS</t>
         </is>
       </c>
     </row>
-    <row r="32" ht="15" customFormat="1" customHeight="1" s="202">
-      <c r="A32" s="203" t="inlineStr">
+    <row r="37" ht="15" customFormat="1" customHeight="1" s="202">
+      <c r="A37" s="203" t="inlineStr">
         <is>
           <t>REV. 10/09/2026</t>
         </is>
       </c>
-      <c r="B32" s="201" t="n"/>
-      <c r="C32" s="201" t="n"/>
-      <c r="D32" s="201" t="n"/>
-      <c r="E32" s="342">
+      <c r="B37" s="201" t="n"/>
+      <c r="C37" s="201" t="n"/>
+      <c r="D37" s="201" t="n"/>
+      <c r="E37" s="342">
         <f>E4</f>
         <v/>
-      </c>
-    </row>
-    <row r="33" ht="25.5" customHeight="1" s="1223">
-      <c r="A33" s="591" t="inlineStr">
-        <is>
-          <t>1. Precios de referencia investigados para Bogotá D.C., 2026 (2° semestre). Son precios promedio de mercado; cada obra requiere cotización formal con proveedores.</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="25.5" customHeight="1" s="1223">
-      <c r="A34" s="591" t="inlineStr">
-        <is>
-          <t>2. Rango de costo directo de construcción en Bogotá 2026 según fuentes de mercado: $2.200.000 - $3.800.000 COP/m² (Aliados de Obras, 2026); promedio de estabilización Ene-Abr 2026: ~$3.050.000 COP/m².</t>
-        </is>
-      </c>
-    </row>
-    <row r="35" ht="25.5" customHeight="1" s="1223">
-      <c r="A35" s="591" t="inlineStr">
-        <is>
-          <t>3. Concreto 3000 PSI para estructura con formaletería: referencia ~$868.306 COP/m³ (Listado de Precios Unitarios, Secretaría de Infraestructura / Fidubogotá, ajustado a 2026).</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" ht="25.5" customHeight="1" s="1223">
-      <c r="A36" s="591" t="inlineStr">
-        <is>
-          <t>4. Acero de refuerzo figurado e instalado: referencia ~$6.500-7.000 COP/kg (Comando Construcciones, 2026; incremento por alza del 23,7% en el SMMLV 2026 según DANE-ICOCED).</t>
-        </is>
-      </c>
-    </row>
-    <row r="37" ht="25.5" customHeight="1" s="1223">
-      <c r="A37" s="591" t="inlineStr">
-        <is>
-          <t>5. Ascensor eléctrico para edificio de 10+ pisos, alta velocidad, instalado: $450M-$750M COP por unidad (OTA Vertical, 2026). Se tomó valor medio.</t>
-        </is>
       </c>
     </row>
     <row r="38" ht="25.5" customHeight="1" s="1223">
       <c r="A38" s="591" t="inlineStr">
         <is>
-          <t>6. Índice de Costos de la Construcción de Edificaciones (ICOCED-DANE): variación interanual ene.2025-ene.2026 de +8,7% en Bogotá, impulsada por incremento salarial.</t>
+          <t>1. Precios de referencia investigados para Bogotá D.C., 2026 (2° semestre). Son precios promedio de mercado; cada obra requiere cotización formal con proveedores.</t>
         </is>
       </c>
     </row>
     <row r="39" ht="25.5" customHeight="1" s="1223">
       <c r="A39" s="591" t="inlineStr">
         <is>
-          <t>7. AIU recomendado para edificaciones en Colombia: 25%-30% sobre costos directos (Administración 10-12%, Imprevistos 3-5%, Utilidad 10-15%). Se usó 26% (10%+4%+12%).</t>
+          <t>2. Rango de costo directo de construcción en Bogotá 2026 según fuentes de mercado: $2.200.000 - $3.800.000 COP/m² (Aliados de Obras, 2026); promedio de estabilización Ene-Abr 2026: ~$3.050.000 COP/m².</t>
         </is>
       </c>
     </row>
     <row r="40" ht="25.5" customHeight="1" s="1223">
       <c r="A40" s="591" t="inlineStr">
         <is>
-          <t>8. IVA: en Colombia, para contratos de obra el IVA se causa típicamente sobre el componente de Utilidad (AIU), no sobre el costo directo de materiales de construcción de vivienda (parcialmente exentos). Verificar con contador/tributarista para el régimen aplicable a cada proyecto.</t>
+          <t>3. Concreto 3000 PSI para estructura con formaletería: referencia ~$868.306 COP/m³ (Listado de Precios Unitarios, Secretaría de Infraestructura / Fidubogotá, ajustado a 2026).</t>
         </is>
       </c>
     </row>
     <row r="41" ht="25.5" customHeight="1" s="1223">
       <c r="A41" s="591" t="inlineStr">
         <is>
-          <t>9. Este documento es una ESTIMACIÓN DE PRESUPUESTO (clase de precisión ±15-20%), útil para prefactibilidad y anteproyecto. No reemplaza un presupuesto detallado con cubicación (cantidades de obra) tomada de planos definitivos y cotizaciones de proveedores.</t>
+          <t>4. Acero de refuerzo figurado e instalado: referencia ~$6.500-7.000 COP/kg (Comando Construcciones, 2026; incremento por alza del 23,7% en el SMMLV 2026 según DANE-ICOCED).</t>
         </is>
       </c>
     </row>
     <row r="42" ht="25.5" customHeight="1" s="1223">
       <c r="A42" s="591" t="inlineStr">
         <is>
+          <t>5. Ascensor eléctrico para edificio de 10+ pisos, alta velocidad, instalado: $450M-$750M COP por unidad (OTA Vertical, 2026). Se tomó valor medio.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="25.5" customHeight="1" s="1223">
+      <c r="A43" s="591" t="inlineStr">
+        <is>
+          <t>6. Índice de Costos de la Construcción de Edificaciones (ICOCED-DANE): variación interanual ene.2025-ene.2026 de +8,7% en Bogotá, impulsada por incremento salarial.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="25.5" customHeight="1" s="1223">
+      <c r="A44" s="591" t="inlineStr">
+        <is>
+          <t>7. AIU recomendado para edificaciones en Colombia: 25%-30% sobre costos directos (Administración 10-12%, Imprevistos 3-5%, Utilidad 10-15%). Se usó 26% (10%+4%+12%).</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="25.5" customHeight="1" s="1223">
+      <c r="A45" s="591" t="inlineStr">
+        <is>
+          <t>8. IVA: en Colombia, para contratos de obra el IVA se causa típicamente sobre el componente de Utilidad (AIU), no sobre el costo directo de materiales de construcción de vivienda (parcialmente exentos). Verificar con contador/tributarista para el régimen aplicable a cada proyecto.</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="25.5" customHeight="1" s="1223">
+      <c r="A46" s="591" t="inlineStr">
+        <is>
+          <t>9. Este documento es una ESTIMACIÓN DE PRESUPUESTO (clase de precisión ±15-20%), útil para prefactibilidad y anteproyecto. No reemplaza un presupuesto detallado con cubicación (cantidades de obra) tomada de planos definitivos y cotizaciones de proveedores.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="25.5" customHeight="1" s="1223">
+      <c r="A47" s="591" t="inlineStr">
+        <is>
           <t>10. Celdas en color AZUL = dato de entrada editable. Celdas en NEGRO = fórmula (se recalculan automáticamente). Cambie cantidades y precios unitarios en la hoja 'Presupuesto' según su proyecto real.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="39">
+  <mergeCells count="43">
     <mergeCell ref="C16:E16"/>
     <mergeCell ref="A39:E39"/>
-    <mergeCell ref="A34:E34"/>
+    <mergeCell ref="B9:E9"/>
+    <mergeCell ref="D10:E10"/>
+    <mergeCell ref="C31:E31"/>
     <mergeCell ref="C22:E22"/>
-    <mergeCell ref="C9:E9"/>
+    <mergeCell ref="A45:E45"/>
     <mergeCell ref="A36:E36"/>
     <mergeCell ref="C21:E21"/>
-    <mergeCell ref="C12:E12"/>
-    <mergeCell ref="C11:E11"/>
     <mergeCell ref="C27:E27"/>
+    <mergeCell ref="C23:E23"/>
     <mergeCell ref="A41:E41"/>
     <mergeCell ref="C17:E17"/>
-    <mergeCell ref="A37:E37"/>
-    <mergeCell ref="C28:E28"/>
-    <mergeCell ref="C13:E13"/>
+    <mergeCell ref="A46:E46"/>
+    <mergeCell ref="C32:E32"/>
     <mergeCell ref="C19:E19"/>
+    <mergeCell ref="B12:E12"/>
     <mergeCell ref="A42:E42"/>
-    <mergeCell ref="A33:E33"/>
     <mergeCell ref="C18:E18"/>
-    <mergeCell ref="A23:E23"/>
+    <mergeCell ref="A47:E47"/>
+    <mergeCell ref="B11:E11"/>
     <mergeCell ref="B2:E2"/>
-    <mergeCell ref="A8:E8"/>
     <mergeCell ref="C30:E30"/>
+    <mergeCell ref="C34:E34"/>
     <mergeCell ref="D3:E3"/>
     <mergeCell ref="C15:E15"/>
     <mergeCell ref="C24:E24"/>
-    <mergeCell ref="A35:E35"/>
+    <mergeCell ref="C33:E33"/>
     <mergeCell ref="C14:E14"/>
     <mergeCell ref="B1:E1"/>
+    <mergeCell ref="A43:E43"/>
     <mergeCell ref="A38:E38"/>
     <mergeCell ref="B5:C5"/>
+    <mergeCell ref="A28:E28"/>
     <mergeCell ref="A40:E40"/>
     <mergeCell ref="C26:E26"/>
+    <mergeCell ref="A13:E13"/>
     <mergeCell ref="C29:E29"/>
+    <mergeCell ref="A44:E44"/>
     <mergeCell ref="C20:E20"/>
-    <mergeCell ref="A31:E31"/>
+    <mergeCell ref="C35:E35"/>
     <mergeCell ref="B4:C4"/>
     <mergeCell ref="C25:E25"/>
-    <mergeCell ref="C10:E10"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup orientation="portrait" paperSize="9" horizontalDpi="300" verticalDpi="300"/>
@@ -15969,7 +16018,7 @@
       <c r="C241" s="681" t="n"/>
       <c r="D241" s="681" t="n"/>
       <c r="E241" s="481">
-        <f>'Ficha Técnica del Proyecto'!$B$24</f>
+        <f>'Ficha Técnica del Proyecto'!$B$29</f>
         <v/>
       </c>
       <c r="F241" s="482">
@@ -15987,7 +16036,7 @@
       <c r="C242" s="681" t="n"/>
       <c r="D242" s="681" t="n"/>
       <c r="E242" s="481">
-        <f>'Ficha Técnica del Proyecto'!$B$25</f>
+        <f>'Ficha Técnica del Proyecto'!$B$30</f>
         <v/>
       </c>
       <c r="F242" s="482">
@@ -16005,7 +16054,7 @@
       <c r="C243" s="681" t="n"/>
       <c r="D243" s="681" t="n"/>
       <c r="E243" s="481">
-        <f>'Ficha Técnica del Proyecto'!$B$26</f>
+        <f>'Ficha Técnica del Proyecto'!$B$31</f>
         <v/>
       </c>
       <c r="F243" s="482">
@@ -16053,7 +16102,7 @@
       <c r="C246" s="681" t="n"/>
       <c r="D246" s="681" t="n"/>
       <c r="E246" s="481">
-        <f>'Ficha Técnica del Proyecto'!$B$27</f>
+        <f>'Ficha Técnica del Proyecto'!$B$32</f>
         <v/>
       </c>
       <c r="F246" s="482">
@@ -16118,7 +16167,7 @@
       <c r="D251" s="91" t="n"/>
       <c r="E251" s="91" t="n"/>
       <c r="F251" s="484">
-        <f>F239/'Ficha Técnica del Proyecto'!$B$16</f>
+        <f>F239/'Ficha Técnica del Proyecto'!$B$21</f>
         <v/>
       </c>
     </row>
@@ -16133,7 +16182,7 @@
       <c r="D252" s="93" t="n"/>
       <c r="E252" s="93" t="n"/>
       <c r="F252" s="485">
-        <f>F248/'Ficha Técnica del Proyecto'!$B$16</f>
+        <f>F248/'Ficha Técnica del Proyecto'!$B$21</f>
         <v/>
       </c>
     </row>

--- a/public/plantilla-mensual.xlsx
+++ b/public/plantilla-mensual.xlsx
@@ -26,7 +26,7 @@
     <numFmt numFmtId="170" formatCode="\$\ #,##0.00"/>
     <numFmt numFmtId="171" formatCode="$ #,##0.00"/>
   </numFmts>
-  <fonts count="168">
+  <fonts count="169">
     <font>
       <name val="Calibri"/>
       <charset val="1"/>
@@ -1231,6 +1231,11 @@
       <color rgb="FF8A8F99"/>
       <sz val="8"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <color rgb="FF000000"/>
+      <sz val="10"/>
+    </font>
   </fonts>
   <fills count="76">
     <fill>
@@ -6575,7 +6580,7 @@
     <xf numFmtId="0" fontId="28" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1307">
+  <cellXfs count="1308">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
@@ -9800,6 +9805,9 @@
     </xf>
     <xf numFmtId="165" fontId="38" fillId="4" borderId="77" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="168" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="5">
@@ -10862,7 +10870,7 @@
           <t>Proyecto</t>
         </is>
       </c>
-      <c r="B9" s="100" t="n"/>
+      <c r="B9" s="1307" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="99" t="inlineStr">
@@ -10870,13 +10878,13 @@
           <t>No de Contrato</t>
         </is>
       </c>
-      <c r="B10" s="100" t="n"/>
+      <c r="B10" s="1307" t="n"/>
       <c r="C10" s="99" t="inlineStr">
         <is>
           <t>Fecha de Emisión</t>
         </is>
       </c>
-      <c r="D10" s="100" t="n"/>
+      <c r="D10" s="1307" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="99" t="inlineStr">
@@ -10884,7 +10892,7 @@
           <t>Contratista</t>
         </is>
       </c>
-      <c r="B11" s="100" t="n"/>
+      <c r="B11" s="1307" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="99" t="inlineStr">
@@ -10892,7 +10900,7 @@
           <t>Ubicación</t>
         </is>
       </c>
-      <c r="B12" s="100" t="n"/>
+      <c r="B12" s="1307" t="n"/>
     </row>
     <row r="13" ht="15" customHeight="1" s="1223">
       <c r="A13" s="597" t="inlineStr">
@@ -11297,13 +11305,13 @@
     <mergeCell ref="A38:E38"/>
     <mergeCell ref="B5:C5"/>
     <mergeCell ref="A28:E28"/>
-    <mergeCell ref="A40:E40"/>
     <mergeCell ref="C26:E26"/>
+    <mergeCell ref="C35:E35"/>
     <mergeCell ref="A13:E13"/>
     <mergeCell ref="C29:E29"/>
     <mergeCell ref="A44:E44"/>
     <mergeCell ref="C20:E20"/>
-    <mergeCell ref="C35:E35"/>
+    <mergeCell ref="A40:E40"/>
     <mergeCell ref="B4:C4"/>
     <mergeCell ref="C25:E25"/>
   </mergeCells>
@@ -11532,12 +11540,12 @@
       </c>
       <c r="B15" s="373" t="inlineStr">
         <is>
-          <t>Replanteo general de ejes y niveles</t>
+          <t>Localización y Replanteo</t>
         </is>
       </c>
       <c r="C15" s="261" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>M²</t>
         </is>
       </c>
       <c r="D15" s="262" t="n"/>

--- a/public/plantilla-mensual.xlsx
+++ b/public/plantilla-mensual.xlsx
@@ -26,7 +26,7 @@
     <numFmt numFmtId="170" formatCode="\$\ #,##0.00"/>
     <numFmt numFmtId="171" formatCode="$ #,##0.00"/>
   </numFmts>
-  <fonts count="169">
+  <fonts count="170">
     <font>
       <name val="Calibri"/>
       <charset val="1"/>
@@ -1236,6 +1236,10 @@
       <color rgb="FF000000"/>
       <sz val="10"/>
     </font>
+    <font>
+      <color rgb="008A8F99"/>
+      <sz val="8"/>
+    </font>
   </fonts>
   <fills count="76">
     <fill>
@@ -6580,7 +6584,7 @@
     <xf numFmtId="0" fontId="28" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1308">
+  <cellXfs count="1309">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
@@ -9809,6 +9813,7 @@
     <xf numFmtId="4" fontId="168" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="169" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="5">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -11328,7 +11333,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F258"/>
+  <dimension ref="A1:F259"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
   <cols>
     <col width="8" customWidth="1" style="586" min="1" max="1"/>
@@ -12656,76 +12661,76 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="82" t="n"/>
-      <c r="B68" s="674" t="inlineStr">
+      <c r="A68" s="81" t="inlineStr">
+        <is>
+          <t>4.17</t>
+        </is>
+      </c>
+      <c r="B68" s="373" t="inlineStr">
+        <is>
+          <t>Concreto premezclado o de planta (suministro)</t>
+        </is>
+      </c>
+      <c r="C68" s="261" t="inlineStr">
+        <is>
+          <t>M³</t>
+        </is>
+      </c>
+      <c r="D68" s="262" t="n"/>
+      <c r="E68" s="477" t="n"/>
+      <c r="F68" s="478">
+        <f>D68*E68</f>
+        <v/>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="82" t="n"/>
+      <c r="B69" s="674" t="inlineStr">
         <is>
           <t>SUBTOTAL CAPÍTULO 4 - ESTRUCTURA</t>
         </is>
       </c>
-      <c r="C68" s="530" t="n"/>
-      <c r="D68" s="530" t="n"/>
-      <c r="E68" s="530" t="n"/>
-      <c r="F68" s="479">
-        <f>SUM(F52:F67)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" s="83" t="n"/>
-      <c r="B69" s="681" t="n"/>
-      <c r="C69" s="681" t="n"/>
-      <c r="D69" s="681" t="n"/>
-      <c r="E69" s="681" t="n"/>
-      <c r="F69" s="675" t="n"/>
+      <c r="C69" s="530" t="n"/>
+      <c r="D69" s="530" t="n"/>
+      <c r="E69" s="530" t="n"/>
+      <c r="F69" s="479">
+        <f>SUM(F51:F68)</f>
+        <v/>
+      </c>
     </row>
     <row r="70">
-      <c r="A70" s="185" t="inlineStr">
+      <c r="A70" s="83" t="n"/>
+      <c r="B70" s="681" t="n"/>
+      <c r="C70" s="681" t="n"/>
+      <c r="D70" s="681" t="n"/>
+      <c r="E70" s="681" t="n"/>
+      <c r="F70" s="675" t="n"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="185" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="B70" s="680" t="inlineStr">
+      <c r="B71" s="680" t="inlineStr">
         <is>
           <t>MAMPOSTERÍA</t>
         </is>
       </c>
-      <c r="C70" s="581" t="n"/>
-      <c r="D70" s="581" t="n"/>
-      <c r="E70" s="581" t="n"/>
-      <c r="F70" s="582" t="n"/>
-    </row>
-    <row r="71">
-      <c r="A71" s="81" t="inlineStr">
-        <is>
-          <t>5.1</t>
-        </is>
-      </c>
-      <c r="B71" s="373" t="inlineStr">
-        <is>
-          <t>Mampostería en bloque de concreto</t>
-        </is>
-      </c>
-      <c r="C71" s="261" t="inlineStr">
-        <is>
-          <t>M²</t>
-        </is>
-      </c>
-      <c r="D71" s="262" t="n"/>
-      <c r="E71" s="477" t="n"/>
-      <c r="F71" s="478">
-        <f>D71*E71</f>
-        <v/>
-      </c>
+      <c r="C71" s="581" t="n"/>
+      <c r="D71" s="581" t="n"/>
+      <c r="E71" s="581" t="n"/>
+      <c r="F71" s="582" t="n"/>
     </row>
     <row r="72">
       <c r="A72" s="81" t="inlineStr">
         <is>
-          <t>5.2</t>
+          <t>5.1</t>
         </is>
       </c>
       <c r="B72" s="373" t="inlineStr">
         <is>
-          <t>Mampostería en ladrillo</t>
+          <t>Mampostería en bloque de concreto</t>
         </is>
       </c>
       <c r="C72" s="261" t="inlineStr">
@@ -12743,12 +12748,12 @@
     <row r="73">
       <c r="A73" s="81" t="inlineStr">
         <is>
-          <t>5.3</t>
+          <t>5.2</t>
         </is>
       </c>
       <c r="B73" s="373" t="inlineStr">
         <is>
-          <t>Mampostería estructural</t>
+          <t>Mampostería en ladrillo</t>
         </is>
       </c>
       <c r="C73" s="261" t="inlineStr">
@@ -12766,12 +12771,12 @@
     <row r="74">
       <c r="A74" s="81" t="inlineStr">
         <is>
-          <t>5.4</t>
+          <t>5.3</t>
         </is>
       </c>
       <c r="B74" s="373" t="inlineStr">
         <is>
-          <t>Muros en sistema liviano / drywall</t>
+          <t>Mampostería estructural</t>
         </is>
       </c>
       <c r="C74" s="261" t="inlineStr">
@@ -12789,17 +12794,17 @@
     <row r="75">
       <c r="A75" s="81" t="inlineStr">
         <is>
-          <t>5.5</t>
+          <t>5.4</t>
         </is>
       </c>
       <c r="B75" s="373" t="inlineStr">
         <is>
-          <t>Dinteles sobre vanos</t>
+          <t>Muros en sistema liviano / drywall</t>
         </is>
       </c>
       <c r="C75" s="261" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>M²</t>
         </is>
       </c>
       <c r="D75" s="262" t="n"/>
@@ -12812,12 +12817,12 @@
     <row r="76">
       <c r="A76" s="81" t="inlineStr">
         <is>
-          <t>5.6</t>
+          <t>5.5</t>
         </is>
       </c>
       <c r="B76" s="373" t="inlineStr">
         <is>
-          <t>Alfajías y remates</t>
+          <t>Dinteles sobre vanos</t>
         </is>
       </c>
       <c r="C76" s="261" t="inlineStr">
@@ -12835,17 +12840,17 @@
     <row r="77">
       <c r="A77" s="81" t="inlineStr">
         <is>
-          <t>5.7</t>
+          <t>5.6</t>
         </is>
       </c>
       <c r="B77" s="373" t="inlineStr">
         <is>
-          <t>Anclajes y refuerzos de mampostería</t>
+          <t>Alfajías y remates</t>
         </is>
       </c>
       <c r="C77" s="261" t="inlineStr">
         <is>
-          <t>UND</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="D77" s="262" t="n"/>
@@ -12858,17 +12863,17 @@
     <row r="78">
       <c r="A78" s="81" t="inlineStr">
         <is>
-          <t>5.8</t>
+          <t>5.7</t>
         </is>
       </c>
       <c r="B78" s="373" t="inlineStr">
         <is>
-          <t>Mampostería en ladrillo tolete a la vista (reforzada)</t>
+          <t>Anclajes y refuerzos de mampostería</t>
         </is>
       </c>
       <c r="C78" s="261" t="inlineStr">
         <is>
-          <t>M²</t>
+          <t>UND</t>
         </is>
       </c>
       <c r="D78" s="262" t="n"/>
@@ -12881,12 +12886,12 @@
     <row r="79">
       <c r="A79" s="81" t="inlineStr">
         <is>
-          <t>5.9</t>
+          <t>5.8</t>
         </is>
       </c>
       <c r="B79" s="373" t="inlineStr">
         <is>
-          <t>Mampostería en ladrillo a la vista (no reforzada)</t>
+          <t>Mampostería en ladrillo tolete a la vista (reforzada)</t>
         </is>
       </c>
       <c r="C79" s="261" t="inlineStr">
@@ -12902,74 +12907,76 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="82" t="n"/>
-      <c r="B80" s="674" t="inlineStr">
+      <c r="A80" s="81" t="inlineStr">
+        <is>
+          <t>5.9</t>
+        </is>
+      </c>
+      <c r="B80" s="373" t="inlineStr">
+        <is>
+          <t>Mampostería en ladrillo a la vista (no reforzada)</t>
+        </is>
+      </c>
+      <c r="C80" s="261" t="inlineStr">
+        <is>
+          <t>M²</t>
+        </is>
+      </c>
+      <c r="D80" s="262" t="n"/>
+      <c r="E80" s="477" t="n"/>
+      <c r="F80" s="478">
+        <f>D80*E80</f>
+        <v/>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="82" t="n"/>
+      <c r="B81" s="674" t="inlineStr">
         <is>
           <t>SUBTOTAL CAPÍTULO 5 - MAMPOSTERÍA</t>
         </is>
       </c>
-      <c r="C80" s="530" t="n"/>
-      <c r="D80" s="530" t="n"/>
-      <c r="E80" s="530" t="n"/>
-      <c r="F80" s="479">
-        <f>SUM(F71:F79)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" s="83" t="n"/>
-      <c r="B81" s="681" t="n"/>
       <c r="C81" s="530" t="n"/>
       <c r="D81" s="530" t="n"/>
       <c r="E81" s="530" t="n"/>
-      <c r="F81" s="675" t="n"/>
+      <c r="F81" s="479">
+        <f>SUM(F72:F80)</f>
+        <v/>
+      </c>
     </row>
     <row r="82">
-      <c r="A82" s="185" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="B82" s="682" t="inlineStr">
-        <is>
-          <t>CUBIERTAS</t>
-        </is>
-      </c>
+      <c r="A82" s="83" t="n"/>
+      <c r="B82" s="681" t="n"/>
       <c r="C82" s="530" t="n"/>
       <c r="D82" s="530" t="n"/>
       <c r="E82" s="530" t="n"/>
-      <c r="F82" s="530" t="n"/>
+      <c r="F82" s="675" t="n"/>
     </row>
     <row r="83">
-      <c r="A83" s="81" t="inlineStr">
-        <is>
-          <t>6.1</t>
-        </is>
-      </c>
-      <c r="B83" s="374" t="inlineStr">
-        <is>
-          <t>Estructura metálica o de madera para cubierta</t>
-        </is>
-      </c>
-      <c r="C83" s="261" t="inlineStr">
-        <is>
-          <t>KG</t>
-        </is>
-      </c>
-      <c r="F83">
-        <f>D83*E83</f>
-        <v/>
-      </c>
+      <c r="A83" s="185" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B83" s="682" t="inlineStr">
+        <is>
+          <t>CUBIERTAS</t>
+        </is>
+      </c>
+      <c r="C83" s="530" t="n"/>
+      <c r="D83" s="530" t="n"/>
+      <c r="E83" s="530" t="n"/>
+      <c r="F83" s="530" t="n"/>
     </row>
     <row r="84">
       <c r="A84" s="81" t="inlineStr">
         <is>
-          <t>6.2</t>
-        </is>
-      </c>
-      <c r="B84" s="373" t="inlineStr">
-        <is>
-          <t>Cerchas y elementos estructurales</t>
+          <t>6.1</t>
+        </is>
+      </c>
+      <c r="B84" s="374" t="inlineStr">
+        <is>
+          <t>Estructura metálica o de madera para cubierta</t>
         </is>
       </c>
       <c r="C84" s="261" t="inlineStr">
@@ -12977,9 +12984,7 @@
           <t>KG</t>
         </is>
       </c>
-      <c r="D84" s="262" t="n"/>
-      <c r="E84" s="477" t="n"/>
-      <c r="F84" s="478">
+      <c r="F84">
         <f>D84*E84</f>
         <v/>
       </c>
@@ -12987,17 +12992,17 @@
     <row r="85">
       <c r="A85" s="81" t="inlineStr">
         <is>
-          <t>6.3</t>
+          <t>6.2</t>
         </is>
       </c>
       <c r="B85" s="373" t="inlineStr">
         <is>
-          <t>Suministro e instalación de teja</t>
+          <t>Cerchas y elementos estructurales</t>
         </is>
       </c>
       <c r="C85" s="261" t="inlineStr">
         <is>
-          <t>M²</t>
+          <t>KG</t>
         </is>
       </c>
       <c r="D85" s="262" t="n"/>
@@ -13010,12 +13015,12 @@
     <row r="86">
       <c r="A86" s="81" t="inlineStr">
         <is>
-          <t>6.4</t>
+          <t>6.3</t>
         </is>
       </c>
       <c r="B86" s="373" t="inlineStr">
         <is>
-          <t>Impermeabilización de cubierta</t>
+          <t>Suministro e instalación de teja</t>
         </is>
       </c>
       <c r="C86" s="261" t="inlineStr">
@@ -13033,12 +13038,12 @@
     <row r="87">
       <c r="A87" s="81" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>6.4</t>
         </is>
       </c>
       <c r="B87" s="373" t="inlineStr">
         <is>
-          <t>Aislamiento térmico/acústico</t>
+          <t>Impermeabilización de cubierta</t>
         </is>
       </c>
       <c r="C87" s="261" t="inlineStr">
@@ -13056,17 +13061,17 @@
     <row r="88">
       <c r="A88" s="81" t="inlineStr">
         <is>
-          <t>6.6</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="B88" s="373" t="inlineStr">
         <is>
-          <t>Canales de aguas lluvias</t>
+          <t>Aislamiento térmico/acústico</t>
         </is>
       </c>
       <c r="C88" s="261" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>M²</t>
         </is>
       </c>
       <c r="D88" s="262" t="n"/>
@@ -13079,12 +13084,12 @@
     <row r="89">
       <c r="A89" s="81" t="inlineStr">
         <is>
-          <t>6.7</t>
+          <t>6.6</t>
         </is>
       </c>
       <c r="B89" s="373" t="inlineStr">
         <is>
-          <t>Bajantes de aguas lluvias</t>
+          <t>Canales de aguas lluvias</t>
         </is>
       </c>
       <c r="C89" s="261" t="inlineStr">
@@ -13102,17 +13107,17 @@
     <row r="90">
       <c r="A90" s="81" t="inlineStr">
         <is>
-          <t>6.8</t>
+          <t>6.7</t>
         </is>
       </c>
       <c r="B90" s="373" t="inlineStr">
         <is>
-          <t>Cielo raso Dry Wall</t>
+          <t>Bajantes de aguas lluvias</t>
         </is>
       </c>
       <c r="C90" s="261" t="inlineStr">
         <is>
-          <t>M²</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="D90" s="262" t="n"/>
@@ -13125,12 +13130,12 @@
     <row r="91">
       <c r="A91" s="81" t="inlineStr">
         <is>
-          <t>6.9</t>
+          <t>6.8</t>
         </is>
       </c>
       <c r="B91" s="373" t="inlineStr">
         <is>
-          <t>Cielo raso en lámina acústica de fibra mineral</t>
+          <t>Cielo raso Dry Wall</t>
         </is>
       </c>
       <c r="C91" s="261" t="inlineStr">
@@ -13146,76 +13151,76 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="82" t="n"/>
-      <c r="B92" s="674" t="inlineStr">
+      <c r="A92" s="81" t="inlineStr">
+        <is>
+          <t>6.9</t>
+        </is>
+      </c>
+      <c r="B92" s="373" t="inlineStr">
+        <is>
+          <t>Cielo raso en lámina acústica de fibra mineral</t>
+        </is>
+      </c>
+      <c r="C92" s="261" t="inlineStr">
+        <is>
+          <t>M²</t>
+        </is>
+      </c>
+      <c r="D92" s="262" t="n"/>
+      <c r="E92" s="477" t="n"/>
+      <c r="F92" s="478">
+        <f>D92*E92</f>
+        <v/>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="82" t="n"/>
+      <c r="B93" s="674" t="inlineStr">
         <is>
           <t>SUBTOTAL CAPÍTULO 6 - CUBIERTAS</t>
         </is>
       </c>
-      <c r="C92" s="530" t="n"/>
-      <c r="D92" s="530" t="n"/>
-      <c r="E92" s="530" t="n"/>
-      <c r="F92" s="479">
-        <f>SUM(F83:F91)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" s="83" t="n"/>
-      <c r="B93" s="681" t="n"/>
-      <c r="C93" s="681" t="n"/>
-      <c r="D93" s="681" t="n"/>
-      <c r="E93" s="681" t="n"/>
-      <c r="F93" s="675" t="n"/>
+      <c r="C93" s="530" t="n"/>
+      <c r="D93" s="530" t="n"/>
+      <c r="E93" s="530" t="n"/>
+      <c r="F93" s="479">
+        <f>SUM(F84:F92)</f>
+        <v/>
+      </c>
     </row>
     <row r="94">
-      <c r="A94" s="185" t="inlineStr">
+      <c r="A94" s="83" t="n"/>
+      <c r="B94" s="681" t="n"/>
+      <c r="C94" s="681" t="n"/>
+      <c r="D94" s="681" t="n"/>
+      <c r="E94" s="681" t="n"/>
+      <c r="F94" s="675" t="n"/>
+    </row>
+    <row r="95">
+      <c r="A95" s="185" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="B94" s="677" t="inlineStr">
+      <c r="B95" s="677" t="inlineStr">
         <is>
           <t>IMPERMEABILIZACIONES</t>
         </is>
       </c>
-      <c r="C94" s="530" t="n"/>
-      <c r="D94" s="530" t="n"/>
-      <c r="E94" s="530" t="n"/>
-      <c r="F94" s="530" t="n"/>
-    </row>
-    <row r="95">
-      <c r="A95" s="81" t="inlineStr">
-        <is>
-          <t>7.1</t>
-        </is>
-      </c>
-      <c r="B95" s="373" t="inlineStr">
-        <is>
-          <t>Impermeabilización de losas y terrazas</t>
-        </is>
-      </c>
-      <c r="C95" s="261" t="inlineStr">
-        <is>
-          <t>M²</t>
-        </is>
-      </c>
-      <c r="D95" s="262" t="n"/>
-      <c r="E95" s="477" t="n"/>
-      <c r="F95" s="478">
-        <f>D95*E95</f>
-        <v/>
-      </c>
+      <c r="C95" s="530" t="n"/>
+      <c r="D95" s="530" t="n"/>
+      <c r="E95" s="530" t="n"/>
+      <c r="F95" s="530" t="n"/>
     </row>
     <row r="96">
       <c r="A96" s="81" t="inlineStr">
         <is>
-          <t>7.2</t>
-        </is>
-      </c>
-      <c r="B96" s="374" t="inlineStr">
-        <is>
-          <t>Impermeabilización de muros</t>
+          <t>7.1</t>
+        </is>
+      </c>
+      <c r="B96" s="373" t="inlineStr">
+        <is>
+          <t>Impermeabilización de losas y terrazas</t>
         </is>
       </c>
       <c r="C96" s="261" t="inlineStr">
@@ -13223,7 +13228,9 @@
           <t>M²</t>
         </is>
       </c>
-      <c r="F96">
+      <c r="D96" s="262" t="n"/>
+      <c r="E96" s="477" t="n"/>
+      <c r="F96" s="478">
         <f>D96*E96</f>
         <v/>
       </c>
@@ -13231,12 +13238,12 @@
     <row r="97">
       <c r="A97" s="81" t="inlineStr">
         <is>
-          <t>7.3</t>
-        </is>
-      </c>
-      <c r="B97" s="373" t="inlineStr">
-        <is>
-          <t>Impermeabilización de zonas húmedas</t>
+          <t>7.2</t>
+        </is>
+      </c>
+      <c r="B97" s="374" t="inlineStr">
+        <is>
+          <t>Impermeabilización de muros</t>
         </is>
       </c>
       <c r="C97" s="261" t="inlineStr">
@@ -13244,9 +13251,7 @@
           <t>M²</t>
         </is>
       </c>
-      <c r="D97" s="262" t="n"/>
-      <c r="E97" s="477" t="n"/>
-      <c r="F97" s="478">
+      <c r="F97">
         <f>D97*E97</f>
         <v/>
       </c>
@@ -13254,12 +13259,12 @@
     <row r="98">
       <c r="A98" s="81" t="inlineStr">
         <is>
-          <t>7.4</t>
+          <t>7.3</t>
         </is>
       </c>
       <c r="B98" s="373" t="inlineStr">
         <is>
-          <t>Geomembrana HDPE para impermeabilización de terrenos</t>
+          <t>Impermeabilización de zonas húmedas</t>
         </is>
       </c>
       <c r="C98" s="261" t="inlineStr">
@@ -13275,74 +13280,76 @@
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="82" t="n"/>
-      <c r="B99" s="674" t="inlineStr">
+      <c r="A99" s="81" t="inlineStr">
+        <is>
+          <t>7.4</t>
+        </is>
+      </c>
+      <c r="B99" s="373" t="inlineStr">
+        <is>
+          <t>Geomembrana HDPE para impermeabilización de terrenos</t>
+        </is>
+      </c>
+      <c r="C99" s="261" t="inlineStr">
+        <is>
+          <t>M²</t>
+        </is>
+      </c>
+      <c r="D99" s="262" t="n"/>
+      <c r="E99" s="477" t="n"/>
+      <c r="F99" s="478">
+        <f>D99*E99</f>
+        <v/>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="82" t="n"/>
+      <c r="B100" s="674" t="inlineStr">
         <is>
           <t>SUBTOTAL CAPÍTULO 7 - IMPERMEABILIZACIONES</t>
         </is>
       </c>
-      <c r="C99" s="530" t="n"/>
-      <c r="D99" s="530" t="n"/>
-      <c r="E99" s="530" t="n"/>
-      <c r="F99" s="479">
-        <f>SUM(F95:F98)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" s="83" t="n"/>
-      <c r="B100" s="681" t="n"/>
       <c r="C100" s="530" t="n"/>
       <c r="D100" s="530" t="n"/>
       <c r="E100" s="530" t="n"/>
-      <c r="F100" s="675" t="n"/>
+      <c r="F100" s="479">
+        <f>SUM(F96:F99)</f>
+        <v/>
+      </c>
     </row>
     <row r="101">
-      <c r="A101" s="185" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="B101" s="677" t="inlineStr">
-        <is>
-          <t>PAÑETES Y REVOQUES</t>
-        </is>
-      </c>
+      <c r="A101" s="83" t="n"/>
+      <c r="B101" s="681" t="n"/>
       <c r="C101" s="530" t="n"/>
       <c r="D101" s="530" t="n"/>
       <c r="E101" s="530" t="n"/>
-      <c r="F101" s="530" t="n"/>
+      <c r="F101" s="675" t="n"/>
     </row>
     <row r="102">
-      <c r="A102" s="81" t="inlineStr">
-        <is>
-          <t>8.1</t>
-        </is>
-      </c>
-      <c r="B102" s="374" t="inlineStr">
-        <is>
-          <t>Pañete / revoque interior</t>
-        </is>
-      </c>
-      <c r="C102" s="261" t="inlineStr">
-        <is>
-          <t>M²</t>
-        </is>
-      </c>
-      <c r="F102">
-        <f>D102*E102</f>
-        <v/>
-      </c>
+      <c r="A102" s="185" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B102" s="677" t="inlineStr">
+        <is>
+          <t>PAÑETES Y REVOQUES</t>
+        </is>
+      </c>
+      <c r="C102" s="530" t="n"/>
+      <c r="D102" s="530" t="n"/>
+      <c r="E102" s="530" t="n"/>
+      <c r="F102" s="530" t="n"/>
     </row>
     <row r="103">
       <c r="A103" s="81" t="inlineStr">
         <is>
-          <t>8.2</t>
-        </is>
-      </c>
-      <c r="B103" s="373" t="inlineStr">
-        <is>
-          <t>Pañete / revoque exterior</t>
+          <t>8.1</t>
+        </is>
+      </c>
+      <c r="B103" s="374" t="inlineStr">
+        <is>
+          <t>Pañete / revoque interior</t>
         </is>
       </c>
       <c r="C103" s="261" t="inlineStr">
@@ -13350,9 +13357,7 @@
           <t>M²</t>
         </is>
       </c>
-      <c r="D103" s="262" t="n"/>
-      <c r="E103" s="477" t="n"/>
-      <c r="F103" s="478">
+      <c r="F103">
         <f>D103*E103</f>
         <v/>
       </c>
@@ -13360,12 +13365,12 @@
     <row r="104">
       <c r="A104" s="81" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="B104" s="373" t="inlineStr">
         <is>
-          <t>Pañete impermeabilizado</t>
+          <t>Pañete / revoque exterior</t>
         </is>
       </c>
       <c r="C104" s="261" t="inlineStr">
@@ -13383,12 +13388,12 @@
     <row r="105">
       <c r="A105" s="81" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="B105" s="373" t="inlineStr">
         <is>
-          <t>Estuco plástico o tradicional</t>
+          <t>Pañete impermeabilizado</t>
         </is>
       </c>
       <c r="C105" s="261" t="inlineStr">
@@ -13396,82 +13401,82 @@
           <t>M²</t>
         </is>
       </c>
+      <c r="D105" s="262" t="n"/>
+      <c r="E105" s="477" t="n"/>
       <c r="F105" s="478">
         <f>D105*E105</f>
         <v/>
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="82" t="n"/>
-      <c r="B106" s="674" t="inlineStr">
+      <c r="A106" s="81" t="inlineStr">
+        <is>
+          <t>8.4</t>
+        </is>
+      </c>
+      <c r="B106" s="373" t="inlineStr">
+        <is>
+          <t>Estuco plástico o tradicional</t>
+        </is>
+      </c>
+      <c r="C106" s="261" t="inlineStr">
+        <is>
+          <t>M²</t>
+        </is>
+      </c>
+      <c r="F106" s="478">
+        <f>D106*E106</f>
+        <v/>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="82" t="n"/>
+      <c r="B107" s="674" t="inlineStr">
         <is>
           <t>SUBTOTAL CAPÍTULO 8 - PAÑETES Y REVOQUES</t>
         </is>
       </c>
-      <c r="C106" s="530" t="n"/>
-      <c r="D106" s="530" t="n"/>
-      <c r="E106" s="530" t="n"/>
-      <c r="F106" s="479">
-        <f>SUM(F102:F105)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" s="83" t="n"/>
-      <c r="B107" s="675" t="n"/>
       <c r="C107" s="530" t="n"/>
       <c r="D107" s="530" t="n"/>
       <c r="E107" s="530" t="n"/>
-      <c r="F107" s="579" t="n"/>
+      <c r="F107" s="479">
+        <f>SUM(F103:F106)</f>
+        <v/>
+      </c>
     </row>
     <row r="108">
-      <c r="A108" s="185" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="B108" s="677" t="inlineStr">
-        <is>
-          <t>PISOS Y ENCHAPES</t>
-        </is>
-      </c>
+      <c r="A108" s="83" t="n"/>
+      <c r="B108" s="675" t="n"/>
       <c r="C108" s="530" t="n"/>
       <c r="D108" s="530" t="n"/>
       <c r="E108" s="530" t="n"/>
-      <c r="F108" s="530" t="n"/>
+      <c r="F108" s="579" t="n"/>
     </row>
     <row r="109">
-      <c r="A109" s="81" t="inlineStr">
-        <is>
-          <t>9.1</t>
-        </is>
-      </c>
-      <c r="B109" s="373" t="inlineStr">
-        <is>
-          <t>Mortero de nivelación</t>
-        </is>
-      </c>
-      <c r="C109" s="261" t="inlineStr">
-        <is>
-          <t>M²</t>
-        </is>
-      </c>
-      <c r="D109" s="262" t="n"/>
-      <c r="E109" s="477" t="n"/>
-      <c r="F109" s="478">
-        <f>D109*E109</f>
-        <v/>
-      </c>
+      <c r="A109" s="185" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B109" s="677" t="inlineStr">
+        <is>
+          <t>PISOS Y ENCHAPES</t>
+        </is>
+      </c>
+      <c r="C109" s="530" t="n"/>
+      <c r="D109" s="530" t="n"/>
+      <c r="E109" s="530" t="n"/>
+      <c r="F109" s="530" t="n"/>
     </row>
     <row r="110">
       <c r="A110" s="81" t="inlineStr">
         <is>
-          <t>9.2</t>
+          <t>9.1</t>
         </is>
       </c>
       <c r="B110" s="373" t="inlineStr">
         <is>
-          <t>Piso cerámico</t>
+          <t>Mortero de nivelación</t>
         </is>
       </c>
       <c r="C110" s="261" t="inlineStr">
@@ -13489,12 +13494,12 @@
     <row r="111">
       <c r="A111" s="81" t="inlineStr">
         <is>
-          <t>9.3</t>
+          <t>9.2</t>
         </is>
       </c>
       <c r="B111" s="373" t="inlineStr">
         <is>
-          <t>Piso en porcelanato</t>
+          <t>Piso cerámico</t>
         </is>
       </c>
       <c r="C111" s="261" t="inlineStr">
@@ -13512,12 +13517,12 @@
     <row r="112">
       <c r="A112" s="81" t="inlineStr">
         <is>
-          <t>9.4</t>
+          <t>9.3</t>
         </is>
       </c>
       <c r="B112" s="373" t="inlineStr">
         <is>
-          <t>Piso vinílico</t>
+          <t>Piso en porcelanato</t>
         </is>
       </c>
       <c r="C112" s="261" t="inlineStr">
@@ -13535,12 +13540,12 @@
     <row r="113">
       <c r="A113" s="81" t="inlineStr">
         <is>
-          <t>9.5</t>
+          <t>9.4</t>
         </is>
       </c>
       <c r="B113" s="373" t="inlineStr">
         <is>
-          <t>Piso laminado</t>
+          <t>Piso vinílico</t>
         </is>
       </c>
       <c r="C113" s="261" t="inlineStr">
@@ -13558,12 +13563,12 @@
     <row r="114">
       <c r="A114" s="81" t="inlineStr">
         <is>
-          <t>9.6</t>
+          <t>9.5</t>
         </is>
       </c>
       <c r="B114" s="373" t="inlineStr">
         <is>
-          <t>Enchape cerámico en muros</t>
+          <t>Piso laminado</t>
         </is>
       </c>
       <c r="C114" s="261" t="inlineStr">
@@ -13571,6 +13576,8 @@
           <t>M²</t>
         </is>
       </c>
+      <c r="D114" s="262" t="n"/>
+      <c r="E114" s="477" t="n"/>
       <c r="F114" s="478">
         <f>D114*E114</f>
         <v/>
@@ -13579,21 +13586,19 @@
     <row r="115">
       <c r="A115" s="81" t="inlineStr">
         <is>
-          <t>9.7</t>
+          <t>9.6</t>
         </is>
       </c>
       <c r="B115" s="373" t="inlineStr">
         <is>
-          <t>Guardaescoba</t>
+          <t>Enchape cerámico en muros</t>
         </is>
       </c>
       <c r="C115" s="261" t="inlineStr">
         <is>
-          <t>ML</t>
-        </is>
-      </c>
-      <c r="D115" s="262" t="n"/>
-      <c r="E115" s="477" t="n"/>
+          <t>M²</t>
+        </is>
+      </c>
       <c r="F115" s="478">
         <f>D115*E115</f>
         <v/>
@@ -13602,12 +13607,12 @@
     <row r="116">
       <c r="A116" s="81" t="inlineStr">
         <is>
-          <t>9.8</t>
-        </is>
-      </c>
-      <c r="B116" s="374" t="inlineStr">
-        <is>
-          <t>Juntas de dilatación / construcción</t>
+          <t>9.7</t>
+        </is>
+      </c>
+      <c r="B116" s="373" t="inlineStr">
+        <is>
+          <t>Guardaescoba</t>
         </is>
       </c>
       <c r="C116" s="261" t="inlineStr">
@@ -13615,7 +13620,9 @@
           <t>ML</t>
         </is>
       </c>
-      <c r="F116">
+      <c r="D116" s="262" t="n"/>
+      <c r="E116" s="477" t="n"/>
+      <c r="F116" s="478">
         <f>D116*E116</f>
         <v/>
       </c>
@@ -13623,17 +13630,17 @@
     <row r="117">
       <c r="A117" s="81" t="inlineStr">
         <is>
-          <t>9.9</t>
+          <t>9.8</t>
         </is>
       </c>
       <c r="B117" s="374" t="inlineStr">
         <is>
-          <t>Piso en concreto afinado con endurecedor de cuarzo</t>
+          <t>Juntas de dilatación / construcción</t>
         </is>
       </c>
       <c r="C117" s="261" t="inlineStr">
         <is>
-          <t>M²</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="F117">
@@ -13644,12 +13651,12 @@
     <row r="118">
       <c r="A118" s="81" t="inlineStr">
         <is>
-          <t>9.10</t>
+          <t>9.9</t>
         </is>
       </c>
       <c r="B118" s="374" t="inlineStr">
         <is>
-          <t>Baldosa de granito</t>
+          <t>Piso en concreto afinado con endurecedor de cuarzo</t>
         </is>
       </c>
       <c r="C118" s="261" t="inlineStr">
@@ -13665,12 +13672,12 @@
     <row r="119">
       <c r="A119" s="81" t="inlineStr">
         <is>
-          <t>9.11</t>
+          <t>9.10</t>
         </is>
       </c>
       <c r="B119" s="374" t="inlineStr">
         <is>
-          <t>Enchape en granito pulido</t>
+          <t>Baldosa de granito</t>
         </is>
       </c>
       <c r="C119" s="261" t="inlineStr">
@@ -13684,76 +13691,74 @@
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="82" t="n"/>
-      <c r="B120" s="674" t="inlineStr">
+      <c r="A120" s="81" t="inlineStr">
+        <is>
+          <t>9.11</t>
+        </is>
+      </c>
+      <c r="B120" s="374" t="inlineStr">
+        <is>
+          <t>Enchape en granito pulido</t>
+        </is>
+      </c>
+      <c r="C120" s="261" t="inlineStr">
+        <is>
+          <t>M²</t>
+        </is>
+      </c>
+      <c r="F120">
+        <f>D120*E120</f>
+        <v/>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="82" t="n"/>
+      <c r="B121" s="674" t="inlineStr">
         <is>
           <t>SUBTOTAL CAPÍTULO 9 - PISOS Y ENCHAPES</t>
         </is>
       </c>
-      <c r="C120" s="530" t="n"/>
-      <c r="D120" s="530" t="n"/>
-      <c r="E120" s="530" t="n"/>
-      <c r="F120" s="479">
-        <f>SUM(F109:F119)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" s="83" t="n"/>
-      <c r="B121" s="681" t="n"/>
-      <c r="C121" s="681" t="n"/>
-      <c r="D121" s="681" t="n"/>
-      <c r="E121" s="681" t="n"/>
-      <c r="F121" s="675" t="n"/>
+      <c r="C121" s="530" t="n"/>
+      <c r="D121" s="530" t="n"/>
+      <c r="E121" s="530" t="n"/>
+      <c r="F121" s="479">
+        <f>SUM(F110:F120)</f>
+        <v/>
+      </c>
     </row>
     <row r="122">
-      <c r="A122" s="185" t="inlineStr">
+      <c r="A122" s="83" t="n"/>
+      <c r="B122" s="681" t="n"/>
+      <c r="C122" s="681" t="n"/>
+      <c r="D122" s="681" t="n"/>
+      <c r="E122" s="681" t="n"/>
+      <c r="F122" s="675" t="n"/>
+    </row>
+    <row r="123">
+      <c r="A123" s="185" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="B122" s="677" t="inlineStr">
+      <c r="B123" s="677" t="inlineStr">
         <is>
           <t>PINTURA</t>
         </is>
       </c>
-      <c r="C122" s="530" t="n"/>
-      <c r="D122" s="530" t="n"/>
-      <c r="E122" s="530" t="n"/>
-      <c r="F122" s="530" t="n"/>
-    </row>
-    <row r="123">
-      <c r="A123" s="81" t="inlineStr">
-        <is>
-          <t>10.1</t>
-        </is>
-      </c>
-      <c r="B123" s="373" t="inlineStr">
-        <is>
-          <t>Pintura vinílica interior</t>
-        </is>
-      </c>
-      <c r="C123" s="261" t="inlineStr">
-        <is>
-          <t>M²</t>
-        </is>
-      </c>
-      <c r="D123" s="262" t="n"/>
-      <c r="E123" s="477" t="n"/>
-      <c r="F123" s="478">
-        <f>D123*E123</f>
-        <v/>
-      </c>
+      <c r="C123" s="530" t="n"/>
+      <c r="D123" s="530" t="n"/>
+      <c r="E123" s="530" t="n"/>
+      <c r="F123" s="530" t="n"/>
     </row>
     <row r="124">
       <c r="A124" s="81" t="inlineStr">
         <is>
-          <t>10.2</t>
+          <t>10.1</t>
         </is>
       </c>
       <c r="B124" s="373" t="inlineStr">
         <is>
-          <t>Pintura exterior</t>
+          <t>Pintura vinílica interior</t>
         </is>
       </c>
       <c r="C124" s="261" t="inlineStr">
@@ -13771,12 +13776,12 @@
     <row r="125">
       <c r="A125" s="81" t="inlineStr">
         <is>
-          <t>10.3</t>
+          <t>10.2</t>
         </is>
       </c>
       <c r="B125" s="373" t="inlineStr">
         <is>
-          <t>Pintura esmalte en superficies metálicas/madera</t>
+          <t>Pintura exterior</t>
         </is>
       </c>
       <c r="C125" s="261" t="inlineStr">
@@ -13794,12 +13799,12 @@
     <row r="126">
       <c r="A126" s="81" t="inlineStr">
         <is>
-          <t>10.4</t>
+          <t>10.3</t>
         </is>
       </c>
       <c r="B126" s="373" t="inlineStr">
         <is>
-          <t>Pintura anticorrosiva</t>
+          <t>Pintura esmalte en superficies metálicas/madera</t>
         </is>
       </c>
       <c r="C126" s="261" t="inlineStr">
@@ -13817,12 +13822,12 @@
     <row r="127">
       <c r="A127" s="81" t="inlineStr">
         <is>
-          <t>10.5</t>
+          <t>10.4</t>
         </is>
       </c>
       <c r="B127" s="373" t="inlineStr">
         <is>
-          <t>Sellador / imprimante</t>
+          <t>Pintura anticorrosiva</t>
         </is>
       </c>
       <c r="C127" s="261" t="inlineStr">
@@ -13830,89 +13835,91 @@
           <t>M²</t>
         </is>
       </c>
+      <c r="D127" s="262" t="n"/>
+      <c r="E127" s="477" t="n"/>
       <c r="F127" s="478">
         <f>D127*E127</f>
         <v/>
       </c>
     </row>
     <row r="128">
-      <c r="A128" s="82" t="n"/>
-      <c r="B128" s="674" t="inlineStr">
+      <c r="A128" s="81" t="inlineStr">
+        <is>
+          <t>10.5</t>
+        </is>
+      </c>
+      <c r="B128" s="373" t="inlineStr">
+        <is>
+          <t>Sellador / imprimante</t>
+        </is>
+      </c>
+      <c r="C128" s="261" t="inlineStr">
+        <is>
+          <t>M²</t>
+        </is>
+      </c>
+      <c r="F128" s="478">
+        <f>D128*E128</f>
+        <v/>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="82" t="n"/>
+      <c r="B129" s="674" t="inlineStr">
         <is>
           <t>SUBTOTAL CAPÍTULO 10 - PINTURA</t>
         </is>
       </c>
-      <c r="C128" s="530" t="n"/>
-      <c r="D128" s="530" t="n"/>
-      <c r="E128" s="530" t="n"/>
-      <c r="F128" s="479">
-        <f>SUM(F123:F127)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" s="83" t="n"/>
-      <c r="B129" s="675" t="n"/>
       <c r="C129" s="530" t="n"/>
       <c r="D129" s="530" t="n"/>
       <c r="E129" s="530" t="n"/>
-      <c r="F129" s="579" t="n"/>
+      <c r="F129" s="479">
+        <f>SUM(F124:F128)</f>
+        <v/>
+      </c>
     </row>
     <row r="130">
-      <c r="A130" s="185" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="B130" s="677" t="inlineStr">
-        <is>
-          <t>CARPINTERÍA</t>
-        </is>
-      </c>
+      <c r="A130" s="83" t="n"/>
+      <c r="B130" s="675" t="n"/>
       <c r="C130" s="530" t="n"/>
       <c r="D130" s="530" t="n"/>
       <c r="E130" s="530" t="n"/>
-      <c r="F130" s="530" t="n"/>
+      <c r="F130" s="579" t="n"/>
     </row>
     <row r="131">
-      <c r="A131" s="81" t="inlineStr">
-        <is>
-          <t>11.1</t>
-        </is>
-      </c>
-      <c r="B131" s="373" t="inlineStr">
-        <is>
-          <t>Puertas de madera</t>
-        </is>
-      </c>
-      <c r="C131" s="261" t="inlineStr">
-        <is>
-          <t>UND</t>
-        </is>
-      </c>
-      <c r="D131" s="262" t="n"/>
-      <c r="E131" s="477" t="n"/>
-      <c r="F131" s="478">
-        <f>D131*E131</f>
-        <v/>
-      </c>
+      <c r="A131" s="185" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B131" s="677" t="inlineStr">
+        <is>
+          <t>CARPINTERÍA</t>
+        </is>
+      </c>
+      <c r="C131" s="530" t="n"/>
+      <c r="D131" s="530" t="n"/>
+      <c r="E131" s="530" t="n"/>
+      <c r="F131" s="530" t="n"/>
     </row>
     <row r="132">
       <c r="A132" s="81" t="inlineStr">
         <is>
-          <t>11.2</t>
+          <t>11.1</t>
         </is>
       </c>
       <c r="B132" s="373" t="inlineStr">
         <is>
-          <t>Muebles fijos de madera</t>
+          <t>Puertas de madera</t>
         </is>
       </c>
       <c r="C132" s="261" t="inlineStr">
         <is>
-          <t>ML</t>
-        </is>
-      </c>
+          <t>UND</t>
+        </is>
+      </c>
+      <c r="D132" s="262" t="n"/>
+      <c r="E132" s="477" t="n"/>
       <c r="F132" s="478">
         <f>D132*E132</f>
         <v/>
@@ -13921,21 +13928,19 @@
     <row r="133">
       <c r="A133" s="81" t="inlineStr">
         <is>
-          <t>11.3</t>
+          <t>11.2</t>
         </is>
       </c>
       <c r="B133" s="373" t="inlineStr">
         <is>
-          <t>Puertas metálicas</t>
+          <t>Muebles fijos de madera</t>
         </is>
       </c>
       <c r="C133" s="261" t="inlineStr">
         <is>
-          <t>UND</t>
-        </is>
-      </c>
-      <c r="D133" s="262" t="n"/>
-      <c r="E133" s="477" t="n"/>
+          <t>ML</t>
+        </is>
+      </c>
       <c r="F133" s="478">
         <f>D133*E133</f>
         <v/>
@@ -13944,20 +13949,22 @@
     <row r="134">
       <c r="A134" s="81" t="inlineStr">
         <is>
-          <t>11.4</t>
-        </is>
-      </c>
-      <c r="B134" s="374" t="inlineStr">
-        <is>
-          <t>Barandas metálicas</t>
+          <t>11.3</t>
+        </is>
+      </c>
+      <c r="B134" s="373" t="inlineStr">
+        <is>
+          <t>Puertas metálicas</t>
         </is>
       </c>
       <c r="C134" s="261" t="inlineStr">
         <is>
-          <t>ML</t>
-        </is>
-      </c>
-      <c r="F134">
+          <t>UND</t>
+        </is>
+      </c>
+      <c r="D134" s="262" t="n"/>
+      <c r="E134" s="477" t="n"/>
+      <c r="F134" s="478">
         <f>D134*E134</f>
         <v/>
       </c>
@@ -13965,12 +13972,12 @@
     <row r="135">
       <c r="A135" s="81" t="inlineStr">
         <is>
-          <t>11.5</t>
-        </is>
-      </c>
-      <c r="B135" s="373" t="inlineStr">
-        <is>
-          <t>Pasamanos</t>
+          <t>11.4</t>
+        </is>
+      </c>
+      <c r="B135" s="374" t="inlineStr">
+        <is>
+          <t>Barandas metálicas</t>
         </is>
       </c>
       <c r="C135" s="261" t="inlineStr">
@@ -13978,9 +13985,7 @@
           <t>ML</t>
         </is>
       </c>
-      <c r="D135" s="262" t="n"/>
-      <c r="E135" s="477" t="n"/>
-      <c r="F135" s="478">
+      <c r="F135">
         <f>D135*E135</f>
         <v/>
       </c>
@@ -13988,17 +13993,17 @@
     <row r="136">
       <c r="A136" s="81" t="inlineStr">
         <is>
-          <t>11.6</t>
+          <t>11.5</t>
         </is>
       </c>
       <c r="B136" s="373" t="inlineStr">
         <is>
-          <t>Ventanas de aluminio</t>
+          <t>Pasamanos</t>
         </is>
       </c>
       <c r="C136" s="261" t="inlineStr">
         <is>
-          <t>M²</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="D136" s="262" t="n"/>
@@ -14011,12 +14016,12 @@
     <row r="137">
       <c r="A137" s="81" t="inlineStr">
         <is>
-          <t>11.7</t>
+          <t>11.6</t>
         </is>
       </c>
       <c r="B137" s="373" t="inlineStr">
         <is>
-          <t>Divisiones de aluminio</t>
+          <t>Ventanas de aluminio</t>
         </is>
       </c>
       <c r="C137" s="261" t="inlineStr">
@@ -14034,17 +14039,17 @@
     <row r="138">
       <c r="A138" s="81" t="inlineStr">
         <is>
-          <t>11.8</t>
+          <t>11.7</t>
         </is>
       </c>
       <c r="B138" s="373" t="inlineStr">
         <is>
-          <t>Puerta antipánico</t>
+          <t>Divisiones de aluminio</t>
         </is>
       </c>
       <c r="C138" s="261" t="inlineStr">
         <is>
-          <t>UND</t>
+          <t>M²</t>
         </is>
       </c>
       <c r="D138" s="262" t="n"/>
@@ -14055,74 +14060,76 @@
       </c>
     </row>
     <row r="139">
-      <c r="A139" s="82" t="n"/>
-      <c r="B139" s="674" t="inlineStr">
+      <c r="A139" s="81" t="inlineStr">
+        <is>
+          <t>11.8</t>
+        </is>
+      </c>
+      <c r="B139" s="373" t="inlineStr">
+        <is>
+          <t>Puerta antipánico</t>
+        </is>
+      </c>
+      <c r="C139" s="261" t="inlineStr">
+        <is>
+          <t>UND</t>
+        </is>
+      </c>
+      <c r="D139" s="262" t="n"/>
+      <c r="E139" s="477" t="n"/>
+      <c r="F139" s="478">
+        <f>D139*E139</f>
+        <v/>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="82" t="n"/>
+      <c r="B140" s="674" t="inlineStr">
         <is>
           <t>SUBTOTAL CAPÍTULO 11 - CARPINTERÍA</t>
         </is>
       </c>
-      <c r="C139" s="530" t="n"/>
-      <c r="D139" s="530" t="n"/>
-      <c r="E139" s="530" t="n"/>
-      <c r="F139" s="479">
-        <f>SUM(F131:F138)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" s="83" t="n"/>
-      <c r="B140" s="681" t="n"/>
-      <c r="C140" s="681" t="n"/>
-      <c r="D140" s="681" t="n"/>
-      <c r="E140" s="681" t="n"/>
-      <c r="F140" s="675" t="n"/>
+      <c r="C140" s="530" t="n"/>
+      <c r="D140" s="530" t="n"/>
+      <c r="E140" s="530" t="n"/>
+      <c r="F140" s="479">
+        <f>SUM(F132:F139)</f>
+        <v/>
+      </c>
     </row>
     <row r="141">
-      <c r="A141" s="185" t="inlineStr">
+      <c r="A141" s="83" t="n"/>
+      <c r="B141" s="681" t="n"/>
+      <c r="C141" s="681" t="n"/>
+      <c r="D141" s="681" t="n"/>
+      <c r="E141" s="681" t="n"/>
+      <c r="F141" s="675" t="n"/>
+    </row>
+    <row r="142">
+      <c r="A142" s="185" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="B141" s="677" t="inlineStr">
+      <c r="B142" s="677" t="inlineStr">
         <is>
           <t>VIDRIOS</t>
         </is>
       </c>
-      <c r="C141" s="530" t="n"/>
-      <c r="D141" s="530" t="n"/>
-      <c r="E141" s="530" t="n"/>
-      <c r="F141" s="530" t="n"/>
-    </row>
-    <row r="142">
-      <c r="A142" s="81" t="inlineStr">
-        <is>
-          <t>12.1</t>
-        </is>
-      </c>
-      <c r="B142" s="373" t="inlineStr">
-        <is>
-          <t>Vidrio templado</t>
-        </is>
-      </c>
-      <c r="C142" s="261" t="inlineStr">
-        <is>
-          <t>M²</t>
-        </is>
-      </c>
-      <c r="F142" s="478">
-        <f>D142*E142</f>
-        <v/>
-      </c>
+      <c r="C142" s="530" t="n"/>
+      <c r="D142" s="530" t="n"/>
+      <c r="E142" s="530" t="n"/>
+      <c r="F142" s="530" t="n"/>
     </row>
     <row r="143">
       <c r="A143" s="81" t="inlineStr">
         <is>
-          <t>12.2</t>
+          <t>12.1</t>
         </is>
       </c>
       <c r="B143" s="373" t="inlineStr">
         <is>
-          <t>Vidrio laminado</t>
+          <t>Vidrio templado</t>
         </is>
       </c>
       <c r="C143" s="261" t="inlineStr">
@@ -14130,8 +14137,6 @@
           <t>M²</t>
         </is>
       </c>
-      <c r="D143" s="262" t="n"/>
-      <c r="E143" s="477" t="n"/>
       <c r="F143" s="478">
         <f>D143*E143</f>
         <v/>
@@ -14140,12 +14145,12 @@
     <row r="144">
       <c r="A144" s="81" t="inlineStr">
         <is>
-          <t>12.3</t>
-        </is>
-      </c>
-      <c r="B144" s="374" t="inlineStr">
-        <is>
-          <t>Espejos</t>
+          <t>12.2</t>
+        </is>
+      </c>
+      <c r="B144" s="373" t="inlineStr">
+        <is>
+          <t>Vidrio laminado</t>
         </is>
       </c>
       <c r="C144" s="261" t="inlineStr">
@@ -14153,7 +14158,9 @@
           <t>M²</t>
         </is>
       </c>
-      <c r="F144">
+      <c r="D144" s="262" t="n"/>
+      <c r="E144" s="477" t="n"/>
+      <c r="F144" s="478">
         <f>D144*E144</f>
         <v/>
       </c>
@@ -14161,95 +14168,95 @@
     <row r="145">
       <c r="A145" s="81" t="inlineStr">
         <is>
+          <t>12.3</t>
+        </is>
+      </c>
+      <c r="B145" s="374" t="inlineStr">
+        <is>
+          <t>Espejos</t>
+        </is>
+      </c>
+      <c r="C145" s="261" t="inlineStr">
+        <is>
+          <t>M²</t>
+        </is>
+      </c>
+      <c r="F145">
+        <f>D145*E145</f>
+        <v/>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="81" t="inlineStr">
+        <is>
           <t>12.4</t>
         </is>
       </c>
-      <c r="B145" s="373" t="inlineStr">
+      <c r="B146" s="373" t="inlineStr">
         <is>
           <t>Sellos y silicona</t>
         </is>
       </c>
-      <c r="C145" s="261" t="inlineStr">
+      <c r="C146" s="261" t="inlineStr">
         <is>
           <t>ML</t>
         </is>
       </c>
-      <c r="D145" s="262" t="n"/>
-      <c r="E145" s="477" t="n"/>
-      <c r="F145" s="478">
-        <f>D145*E145</f>
-        <v/>
-      </c>
-    </row>
-    <row r="146">
-      <c r="A146" s="82" t="n"/>
-      <c r="B146" s="674" t="inlineStr">
+      <c r="D146" s="262" t="n"/>
+      <c r="E146" s="477" t="n"/>
+      <c r="F146" s="478">
+        <f>D146*E146</f>
+        <v/>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="82" t="n"/>
+      <c r="B147" s="674" t="inlineStr">
         <is>
           <t>SUBTOTAL CAPÍTULO 12 - VIDRIOS</t>
         </is>
       </c>
-      <c r="C146" s="530" t="n"/>
-      <c r="D146" s="530" t="n"/>
-      <c r="E146" s="530" t="n"/>
-      <c r="F146" s="479">
-        <f>SUM(F142:F145)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="147">
-      <c r="A147" s="83" t="n"/>
-      <c r="B147" s="681" t="n"/>
-      <c r="C147" s="681" t="n"/>
-      <c r="D147" s="681" t="n"/>
-      <c r="E147" s="681" t="n"/>
-      <c r="F147" s="675" t="n"/>
+      <c r="C147" s="530" t="n"/>
+      <c r="D147" s="530" t="n"/>
+      <c r="E147" s="530" t="n"/>
+      <c r="F147" s="479">
+        <f>SUM(F143:F146)</f>
+        <v/>
+      </c>
     </row>
     <row r="148">
-      <c r="A148" s="185" t="inlineStr">
+      <c r="A148" s="83" t="n"/>
+      <c r="B148" s="681" t="n"/>
+      <c r="C148" s="681" t="n"/>
+      <c r="D148" s="681" t="n"/>
+      <c r="E148" s="681" t="n"/>
+      <c r="F148" s="675" t="n"/>
+    </row>
+    <row r="149">
+      <c r="A149" s="185" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="B148" s="677" t="inlineStr">
+      <c r="B149" s="677" t="inlineStr">
         <is>
           <t>INSTALACIONES HIDROSANITARIAS</t>
         </is>
       </c>
-      <c r="C148" s="530" t="n"/>
-      <c r="D148" s="530" t="n"/>
-      <c r="E148" s="530" t="n"/>
-      <c r="F148" s="530" t="n"/>
-    </row>
-    <row r="149">
-      <c r="A149" s="81" t="inlineStr">
-        <is>
-          <t>13.1</t>
-        </is>
-      </c>
-      <c r="B149" s="373" t="inlineStr">
-        <is>
-          <t>Tubería de agua fría</t>
-        </is>
-      </c>
-      <c r="C149" s="261" t="inlineStr">
-        <is>
-          <t>ML</t>
-        </is>
-      </c>
-      <c r="F149" s="478">
-        <f>D149*E149</f>
-        <v/>
-      </c>
+      <c r="C149" s="530" t="n"/>
+      <c r="D149" s="530" t="n"/>
+      <c r="E149" s="530" t="n"/>
+      <c r="F149" s="530" t="n"/>
     </row>
     <row r="150">
       <c r="A150" s="81" t="inlineStr">
         <is>
-          <t>13.2</t>
+          <t>13.1</t>
         </is>
       </c>
       <c r="B150" s="373" t="inlineStr">
         <is>
-          <t>Tubería de agua caliente</t>
+          <t>Tubería de agua fría</t>
         </is>
       </c>
       <c r="C150" s="261" t="inlineStr">
@@ -14257,8 +14264,6 @@
           <t>ML</t>
         </is>
       </c>
-      <c r="D150" s="262" t="n"/>
-      <c r="E150" s="477" t="n"/>
       <c r="F150" s="478">
         <f>D150*E150</f>
         <v/>
@@ -14267,19 +14272,21 @@
     <row r="151">
       <c r="A151" s="81" t="inlineStr">
         <is>
-          <t>13.3</t>
+          <t>13.2</t>
         </is>
       </c>
       <c r="B151" s="373" t="inlineStr">
         <is>
-          <t>Válvulas y accesorios</t>
+          <t>Tubería de agua caliente</t>
         </is>
       </c>
       <c r="C151" s="261" t="inlineStr">
         <is>
-          <t>UND</t>
-        </is>
-      </c>
+          <t>ML</t>
+        </is>
+      </c>
+      <c r="D151" s="262" t="n"/>
+      <c r="E151" s="477" t="n"/>
       <c r="F151" s="478">
         <f>D151*E151</f>
         <v/>
@@ -14288,21 +14295,19 @@
     <row r="152">
       <c r="A152" s="81" t="inlineStr">
         <is>
-          <t>13.4</t>
+          <t>13.3</t>
         </is>
       </c>
       <c r="B152" s="373" t="inlineStr">
         <is>
-          <t>Tubería sanitaria</t>
+          <t>Válvulas y accesorios</t>
         </is>
       </c>
       <c r="C152" s="261" t="inlineStr">
         <is>
-          <t>ML</t>
-        </is>
-      </c>
-      <c r="D152" s="262" t="n"/>
-      <c r="E152" s="477" t="n"/>
+          <t>UND</t>
+        </is>
+      </c>
       <c r="F152" s="478">
         <f>D152*E152</f>
         <v/>
@@ -14311,12 +14316,12 @@
     <row r="153">
       <c r="A153" s="81" t="inlineStr">
         <is>
-          <t>13.5</t>
+          <t>13.4</t>
         </is>
       </c>
       <c r="B153" s="373" t="inlineStr">
         <is>
-          <t>Tubería de aguas lluvias</t>
+          <t>Tubería sanitaria</t>
         </is>
       </c>
       <c r="C153" s="261" t="inlineStr">
@@ -14334,17 +14339,17 @@
     <row r="154">
       <c r="A154" s="81" t="inlineStr">
         <is>
-          <t>13.6</t>
+          <t>13.5</t>
         </is>
       </c>
       <c r="B154" s="373" t="inlineStr">
         <is>
-          <t>Cajas de inspección</t>
+          <t>Tubería de aguas lluvias</t>
         </is>
       </c>
       <c r="C154" s="261" t="inlineStr">
         <is>
-          <t>UND</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="D154" s="262" t="n"/>
@@ -14357,12 +14362,12 @@
     <row r="155">
       <c r="A155" s="81" t="inlineStr">
         <is>
-          <t>13.7</t>
+          <t>13.6</t>
         </is>
       </c>
       <c r="B155" s="373" t="inlineStr">
         <is>
-          <t>Aparatos sanitarios</t>
+          <t>Cajas de inspección</t>
         </is>
       </c>
       <c r="C155" s="261" t="inlineStr">
@@ -14380,12 +14385,12 @@
     <row r="156">
       <c r="A156" s="81" t="inlineStr">
         <is>
-          <t>13.8</t>
+          <t>13.7</t>
         </is>
       </c>
       <c r="B156" s="373" t="inlineStr">
         <is>
-          <t>Lavamanos</t>
+          <t>Aparatos sanitarios</t>
         </is>
       </c>
       <c r="C156" s="261" t="inlineStr">
@@ -14403,12 +14408,12 @@
     <row r="157">
       <c r="A157" s="81" t="inlineStr">
         <is>
-          <t>13.9</t>
+          <t>13.8</t>
         </is>
       </c>
       <c r="B157" s="373" t="inlineStr">
         <is>
-          <t>Griferías</t>
+          <t>Lavamanos</t>
         </is>
       </c>
       <c r="C157" s="261" t="inlineStr">
@@ -14426,12 +14431,12 @@
     <row r="158">
       <c r="A158" s="81" t="inlineStr">
         <is>
-          <t>13.10</t>
+          <t>13.9</t>
         </is>
       </c>
       <c r="B158" s="373" t="inlineStr">
         <is>
-          <t>Duchas</t>
+          <t>Griferías</t>
         </is>
       </c>
       <c r="C158" s="261" t="inlineStr">
@@ -14449,17 +14454,17 @@
     <row r="159">
       <c r="A159" s="81" t="inlineStr">
         <is>
-          <t>13.11</t>
+          <t>13.10</t>
         </is>
       </c>
       <c r="B159" s="373" t="inlineStr">
         <is>
-          <t>Pruebas hidráulicas y de estanqueidad</t>
+          <t>Duchas</t>
         </is>
       </c>
       <c r="C159" s="261" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>UND</t>
         </is>
       </c>
       <c r="D159" s="262" t="n"/>
@@ -14472,17 +14477,17 @@
     <row r="160">
       <c r="A160" s="81" t="inlineStr">
         <is>
-          <t>13.12</t>
+          <t>13.11</t>
         </is>
       </c>
       <c r="B160" s="373" t="inlineStr">
         <is>
-          <t>Orinal institucional</t>
+          <t>Pruebas hidráulicas y de estanqueidad</t>
         </is>
       </c>
       <c r="C160" s="261" t="inlineStr">
         <is>
-          <t>UND</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="D160" s="262" t="n"/>
@@ -14493,76 +14498,76 @@
       </c>
     </row>
     <row r="161">
-      <c r="A161" s="82" t="n"/>
-      <c r="B161" s="674" t="inlineStr">
+      <c r="A161" s="81" t="inlineStr">
+        <is>
+          <t>13.12</t>
+        </is>
+      </c>
+      <c r="B161" s="373" t="inlineStr">
+        <is>
+          <t>Orinal institucional</t>
+        </is>
+      </c>
+      <c r="C161" s="261" t="inlineStr">
+        <is>
+          <t>UND</t>
+        </is>
+      </c>
+      <c r="D161" s="262" t="n"/>
+      <c r="E161" s="477" t="n"/>
+      <c r="F161" s="478">
+        <f>D161*E161</f>
+        <v/>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="82" t="n"/>
+      <c r="B162" s="674" t="inlineStr">
         <is>
           <t>SUBTOTAL CAPÍTULO 13 - INSTALACIONES HIDROSANITARIAS</t>
         </is>
       </c>
-      <c r="C161" s="530" t="n"/>
-      <c r="D161" s="530" t="n"/>
-      <c r="E161" s="530" t="n"/>
-      <c r="F161" s="479">
-        <f>SUM(F149:F160)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="162">
-      <c r="A162" s="83" t="n"/>
-      <c r="B162" s="681" t="n"/>
-      <c r="C162" s="681" t="n"/>
-      <c r="D162" s="681" t="n"/>
-      <c r="E162" s="681" t="n"/>
-      <c r="F162" s="675" t="n"/>
+      <c r="C162" s="530" t="n"/>
+      <c r="D162" s="530" t="n"/>
+      <c r="E162" s="530" t="n"/>
+      <c r="F162" s="479">
+        <f>SUM(F150:F161)</f>
+        <v/>
+      </c>
     </row>
     <row r="163">
-      <c r="A163" s="185" t="inlineStr">
+      <c r="A163" s="83" t="n"/>
+      <c r="B163" s="681" t="n"/>
+      <c r="C163" s="681" t="n"/>
+      <c r="D163" s="681" t="n"/>
+      <c r="E163" s="681" t="n"/>
+      <c r="F163" s="675" t="n"/>
+    </row>
+    <row r="164">
+      <c r="A164" s="185" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="B163" s="677" t="inlineStr">
+      <c r="B164" s="677" t="inlineStr">
         <is>
           <t>INSTALACIONES ELÉCTRICAS</t>
         </is>
       </c>
-      <c r="C163" s="530" t="n"/>
-      <c r="D163" s="530" t="n"/>
-      <c r="E163" s="530" t="n"/>
-      <c r="F163" s="530" t="n"/>
-    </row>
-    <row r="164">
-      <c r="A164" s="81" t="inlineStr">
-        <is>
-          <t>14.1</t>
-        </is>
-      </c>
-      <c r="B164" s="373" t="inlineStr">
-        <is>
-          <t>Tubería/conduit eléctrica</t>
-        </is>
-      </c>
-      <c r="C164" s="261" t="inlineStr">
-        <is>
-          <t>ML</t>
-        </is>
-      </c>
-      <c r="D164" s="262" t="n"/>
-      <c r="E164" s="477" t="n"/>
-      <c r="F164" s="478">
-        <f>D164*E164</f>
-        <v/>
-      </c>
+      <c r="C164" s="530" t="n"/>
+      <c r="D164" s="530" t="n"/>
+      <c r="E164" s="530" t="n"/>
+      <c r="F164" s="530" t="n"/>
     </row>
     <row r="165">
       <c r="A165" s="81" t="inlineStr">
         <is>
-          <t>14.2</t>
+          <t>14.1</t>
         </is>
       </c>
       <c r="B165" s="373" t="inlineStr">
         <is>
-          <t>Bandejas portacables</t>
+          <t>Tubería/conduit eléctrica</t>
         </is>
       </c>
       <c r="C165" s="261" t="inlineStr">
@@ -14580,17 +14585,17 @@
     <row r="166">
       <c r="A166" s="81" t="inlineStr">
         <is>
-          <t>14.3</t>
+          <t>14.2</t>
         </is>
       </c>
       <c r="B166" s="373" t="inlineStr">
         <is>
-          <t>Cajas eléctricas</t>
+          <t>Bandejas portacables</t>
         </is>
       </c>
       <c r="C166" s="261" t="inlineStr">
         <is>
-          <t>UND</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="D166" s="262" t="n"/>
@@ -14603,17 +14608,17 @@
     <row r="167">
       <c r="A167" s="81" t="inlineStr">
         <is>
-          <t>14.4</t>
+          <t>14.3</t>
         </is>
       </c>
       <c r="B167" s="373" t="inlineStr">
         <is>
-          <t>Cableado de fuerza</t>
+          <t>Cajas eléctricas</t>
         </is>
       </c>
       <c r="C167" s="261" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>UND</t>
         </is>
       </c>
       <c r="D167" s="262" t="n"/>
@@ -14626,12 +14631,12 @@
     <row r="168">
       <c r="A168" s="81" t="inlineStr">
         <is>
-          <t>14.5</t>
+          <t>14.4</t>
         </is>
       </c>
       <c r="B168" s="373" t="inlineStr">
         <is>
-          <t>Cableado de iluminación</t>
+          <t>Cableado de fuerza</t>
         </is>
       </c>
       <c r="C168" s="261" t="inlineStr">
@@ -14649,17 +14654,17 @@
     <row r="169">
       <c r="A169" s="81" t="inlineStr">
         <is>
-          <t>14.6</t>
+          <t>14.5</t>
         </is>
       </c>
       <c r="B169" s="373" t="inlineStr">
         <is>
-          <t>Tableros eléctricos</t>
+          <t>Cableado de iluminación</t>
         </is>
       </c>
       <c r="C169" s="261" t="inlineStr">
         <is>
-          <t>UND</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="D169" s="262" t="n"/>
@@ -14672,12 +14677,12 @@
     <row r="170">
       <c r="A170" s="81" t="inlineStr">
         <is>
-          <t>14.7</t>
+          <t>14.6</t>
         </is>
       </c>
       <c r="B170" s="373" t="inlineStr">
         <is>
-          <t>Tomacorrientes</t>
+          <t>Tableros eléctricos</t>
         </is>
       </c>
       <c r="C170" s="261" t="inlineStr">
@@ -14695,12 +14700,12 @@
     <row r="171">
       <c r="A171" s="81" t="inlineStr">
         <is>
-          <t>14.8</t>
+          <t>14.7</t>
         </is>
       </c>
       <c r="B171" s="373" t="inlineStr">
         <is>
-          <t>Interruptores</t>
+          <t>Tomacorrientes</t>
         </is>
       </c>
       <c r="C171" s="261" t="inlineStr">
@@ -14718,12 +14723,12 @@
     <row r="172">
       <c r="A172" s="81" t="inlineStr">
         <is>
-          <t>14.9</t>
+          <t>14.8</t>
         </is>
       </c>
       <c r="B172" s="373" t="inlineStr">
         <is>
-          <t>Luminarias</t>
+          <t>Interruptores</t>
         </is>
       </c>
       <c r="C172" s="261" t="inlineStr">
@@ -14741,17 +14746,17 @@
     <row r="173">
       <c r="A173" s="81" t="inlineStr">
         <is>
-          <t>14.10</t>
+          <t>14.9</t>
         </is>
       </c>
       <c r="B173" s="373" t="inlineStr">
         <is>
-          <t>Sistema de puesta a tierra</t>
+          <t>Luminarias</t>
         </is>
       </c>
       <c r="C173" s="261" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>UND</t>
         </is>
       </c>
       <c r="D173" s="262" t="n"/>
@@ -14764,12 +14769,12 @@
     <row r="174">
       <c r="A174" s="81" t="inlineStr">
         <is>
-          <t>14.11</t>
+          <t>14.10</t>
         </is>
       </c>
       <c r="B174" s="373" t="inlineStr">
         <is>
-          <t>Pruebas y certificaciones</t>
+          <t>Sistema de puesta a tierra</t>
         </is>
       </c>
       <c r="C174" s="261" t="inlineStr">
@@ -14785,81 +14790,81 @@
       </c>
     </row>
     <row r="175">
-      <c r="A175" s="82" t="n"/>
-      <c r="B175" s="674" t="inlineStr">
+      <c r="A175" s="81" t="inlineStr">
+        <is>
+          <t>14.11</t>
+        </is>
+      </c>
+      <c r="B175" s="373" t="inlineStr">
+        <is>
+          <t>Pruebas y certificaciones</t>
+        </is>
+      </c>
+      <c r="C175" s="261" t="inlineStr">
+        <is>
+          <t>GL</t>
+        </is>
+      </c>
+      <c r="D175" s="262" t="n"/>
+      <c r="E175" s="477" t="n"/>
+      <c r="F175" s="478">
+        <f>D175*E175</f>
+        <v/>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="82" t="n"/>
+      <c r="B176" s="674" t="inlineStr">
         <is>
           <t>SUBTOTAL CAPÍTULO 14 - INSTALACIONES ELÉCTRICAS</t>
         </is>
       </c>
-      <c r="C175" s="530" t="n"/>
-      <c r="D175" s="530" t="n"/>
-      <c r="E175" s="530" t="n"/>
-      <c r="F175" s="479">
-        <f>SUM(F164:F174)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="176">
-      <c r="A176" s="83" t="n"/>
-      <c r="B176" s="681" t="n"/>
-      <c r="C176" s="681" t="n"/>
-      <c r="D176" s="681" t="n"/>
-      <c r="E176" s="681" t="n"/>
-      <c r="F176" s="675" t="n"/>
+      <c r="C176" s="530" t="n"/>
+      <c r="D176" s="530" t="n"/>
+      <c r="E176" s="530" t="n"/>
+      <c r="F176" s="479">
+        <f>SUM(F165:F175)</f>
+        <v/>
+      </c>
     </row>
     <row r="177">
-      <c r="A177" s="185" t="inlineStr">
+      <c r="A177" s="83" t="n"/>
+      <c r="B177" s="681" t="n"/>
+      <c r="C177" s="681" t="n"/>
+      <c r="D177" s="681" t="n"/>
+      <c r="E177" s="681" t="n"/>
+      <c r="F177" s="675" t="n"/>
+    </row>
+    <row r="178">
+      <c r="A178" s="185" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="B177" s="677" t="inlineStr">
+      <c r="B178" s="677" t="inlineStr">
         <is>
           <t>COMUNICACIONES Y SEGURIDAD</t>
         </is>
       </c>
-      <c r="C177" s="530" t="n"/>
-      <c r="D177" s="530" t="n"/>
-      <c r="E177" s="530" t="n"/>
-      <c r="F177" s="530" t="n"/>
-    </row>
-    <row r="178">
-      <c r="A178" s="81" t="inlineStr">
-        <is>
-          <t>15.1</t>
-        </is>
-      </c>
-      <c r="B178" s="373" t="inlineStr">
-        <is>
-          <t>Cableado estructurado de datos</t>
-        </is>
-      </c>
-      <c r="C178" s="261" t="inlineStr">
-        <is>
-          <t>ML</t>
-        </is>
-      </c>
-      <c r="D178" s="262" t="n"/>
-      <c r="E178" s="477" t="n"/>
-      <c r="F178" s="478">
-        <f>D178*E178</f>
-        <v/>
-      </c>
+      <c r="C178" s="530" t="n"/>
+      <c r="D178" s="530" t="n"/>
+      <c r="E178" s="530" t="n"/>
+      <c r="F178" s="530" t="n"/>
     </row>
     <row r="179">
       <c r="A179" s="81" t="inlineStr">
         <is>
-          <t>15.2</t>
+          <t>15.1</t>
         </is>
       </c>
       <c r="B179" s="373" t="inlineStr">
         <is>
-          <t>Rack de comunicaciones</t>
+          <t>Cableado estructurado de datos</t>
         </is>
       </c>
       <c r="C179" s="261" t="inlineStr">
         <is>
-          <t>UND</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="D179" s="262" t="n"/>
@@ -14872,12 +14877,12 @@
     <row r="180">
       <c r="A180" s="81" t="inlineStr">
         <is>
-          <t>15.3</t>
+          <t>15.2</t>
         </is>
       </c>
       <c r="B180" s="373" t="inlineStr">
         <is>
-          <t>Cámaras y sistema CCTV</t>
+          <t>Rack de comunicaciones</t>
         </is>
       </c>
       <c r="C180" s="261" t="inlineStr">
@@ -14895,12 +14900,12 @@
     <row r="181">
       <c r="A181" s="81" t="inlineStr">
         <is>
-          <t>15.4</t>
+          <t>15.3</t>
         </is>
       </c>
       <c r="B181" s="373" t="inlineStr">
         <is>
-          <t>Control de acceso</t>
+          <t>Cámaras y sistema CCTV</t>
         </is>
       </c>
       <c r="C181" s="261" t="inlineStr">
@@ -14918,12 +14923,12 @@
     <row r="182">
       <c r="A182" s="81" t="inlineStr">
         <is>
-          <t>15.5</t>
+          <t>15.4</t>
         </is>
       </c>
       <c r="B182" s="373" t="inlineStr">
         <is>
-          <t>Sistema de citofonía</t>
+          <t>Control de acceso</t>
         </is>
       </c>
       <c r="C182" s="261" t="inlineStr">
@@ -14941,17 +14946,17 @@
     <row r="183">
       <c r="A183" s="81" t="inlineStr">
         <is>
-          <t>15.6</t>
+          <t>15.5</t>
         </is>
       </c>
       <c r="B183" s="373" t="inlineStr">
         <is>
-          <t>Sistema de detección de incendios</t>
+          <t>Sistema de citofonía</t>
         </is>
       </c>
       <c r="C183" s="261" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>UND</t>
         </is>
       </c>
       <c r="D183" s="262" t="n"/>
@@ -14962,81 +14967,81 @@
       </c>
     </row>
     <row r="184">
-      <c r="A184" s="82" t="n"/>
-      <c r="B184" s="674" t="inlineStr">
+      <c r="A184" s="81" t="inlineStr">
+        <is>
+          <t>15.6</t>
+        </is>
+      </c>
+      <c r="B184" s="373" t="inlineStr">
+        <is>
+          <t>Sistema de detección de incendios</t>
+        </is>
+      </c>
+      <c r="C184" s="261" t="inlineStr">
+        <is>
+          <t>GL</t>
+        </is>
+      </c>
+      <c r="D184" s="262" t="n"/>
+      <c r="E184" s="477" t="n"/>
+      <c r="F184" s="478">
+        <f>D184*E184</f>
+        <v/>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" s="82" t="n"/>
+      <c r="B185" s="674" t="inlineStr">
         <is>
           <t>SUBTOTAL CAPÍTULO 15 - COMUNICACIONES Y SEGURIDAD</t>
         </is>
       </c>
-      <c r="C184" s="530" t="n"/>
-      <c r="D184" s="530" t="n"/>
-      <c r="E184" s="530" t="n"/>
-      <c r="F184" s="479">
-        <f>SUM(F178:F183)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="185">
-      <c r="A185" s="83" t="n"/>
-      <c r="B185" s="681" t="n"/>
-      <c r="C185" s="681" t="n"/>
-      <c r="D185" s="681" t="n"/>
-      <c r="E185" s="681" t="n"/>
-      <c r="F185" s="675" t="n"/>
+      <c r="C185" s="530" t="n"/>
+      <c r="D185" s="530" t="n"/>
+      <c r="E185" s="530" t="n"/>
+      <c r="F185" s="479">
+        <f>SUM(F179:F184)</f>
+        <v/>
+      </c>
     </row>
     <row r="186">
-      <c r="A186" s="185" t="inlineStr">
+      <c r="A186" s="83" t="n"/>
+      <c r="B186" s="681" t="n"/>
+      <c r="C186" s="681" t="n"/>
+      <c r="D186" s="681" t="n"/>
+      <c r="E186" s="681" t="n"/>
+      <c r="F186" s="675" t="n"/>
+    </row>
+    <row r="187">
+      <c r="A187" s="185" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="B186" s="677" t="inlineStr">
+      <c r="B187" s="677" t="inlineStr">
         <is>
           <t>CLIMATIZACIÓN Y VENTILACIÓN</t>
         </is>
       </c>
-      <c r="C186" s="530" t="n"/>
-      <c r="D186" s="530" t="n"/>
-      <c r="E186" s="530" t="n"/>
-      <c r="F186" s="530" t="n"/>
-    </row>
-    <row r="187">
-      <c r="A187" s="81" t="inlineStr">
-        <is>
-          <t>16.1</t>
-        </is>
-      </c>
-      <c r="B187" s="373" t="inlineStr">
-        <is>
-          <t>Equipos de aire acondicionado</t>
-        </is>
-      </c>
-      <c r="C187" s="261" t="inlineStr">
-        <is>
-          <t>UND</t>
-        </is>
-      </c>
-      <c r="D187" s="262" t="n"/>
-      <c r="E187" s="477" t="n"/>
-      <c r="F187" s="478">
-        <f>D187*E187</f>
-        <v/>
-      </c>
+      <c r="C187" s="530" t="n"/>
+      <c r="D187" s="530" t="n"/>
+      <c r="E187" s="530" t="n"/>
+      <c r="F187" s="530" t="n"/>
     </row>
     <row r="188">
       <c r="A188" s="81" t="inlineStr">
         <is>
-          <t>16.2</t>
+          <t>16.1</t>
         </is>
       </c>
       <c r="B188" s="373" t="inlineStr">
         <is>
-          <t>Ductos de ventilación</t>
+          <t>Equipos de aire acondicionado</t>
         </is>
       </c>
       <c r="C188" s="261" t="inlineStr">
         <is>
-          <t>M²</t>
+          <t>UND</t>
         </is>
       </c>
       <c r="D188" s="262" t="n"/>
@@ -15049,17 +15054,17 @@
     <row r="189">
       <c r="A189" s="81" t="inlineStr">
         <is>
-          <t>16.3</t>
+          <t>16.2</t>
         </is>
       </c>
       <c r="B189" s="373" t="inlineStr">
         <is>
-          <t>Tubería de refrigerante</t>
+          <t>Ductos de ventilación</t>
         </is>
       </c>
       <c r="C189" s="261" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>M²</t>
         </is>
       </c>
       <c r="D189" s="262" t="n"/>
@@ -15072,17 +15077,17 @@
     <row r="190">
       <c r="A190" s="81" t="inlineStr">
         <is>
-          <t>16.4</t>
+          <t>16.3</t>
         </is>
       </c>
       <c r="B190" s="373" t="inlineStr">
         <is>
-          <t>Rejillas y difusores</t>
+          <t>Tubería de refrigerante</t>
         </is>
       </c>
       <c r="C190" s="261" t="inlineStr">
         <is>
-          <t>UND</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="D190" s="262" t="n"/>
@@ -15093,81 +15098,81 @@
       </c>
     </row>
     <row r="191">
-      <c r="A191" s="82" t="n"/>
-      <c r="B191" s="674" t="inlineStr">
+      <c r="A191" s="81" t="inlineStr">
+        <is>
+          <t>16.4</t>
+        </is>
+      </c>
+      <c r="B191" s="373" t="inlineStr">
+        <is>
+          <t>Rejillas y difusores</t>
+        </is>
+      </c>
+      <c r="C191" s="261" t="inlineStr">
+        <is>
+          <t>UND</t>
+        </is>
+      </c>
+      <c r="D191" s="262" t="n"/>
+      <c r="E191" s="477" t="n"/>
+      <c r="F191" s="478">
+        <f>D191*E191</f>
+        <v/>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" s="82" t="n"/>
+      <c r="B192" s="674" t="inlineStr">
         <is>
           <t>SUBTOTAL CAPÍTULO 16 - CLIMATIZACIÓN Y VENTILACIÓN</t>
         </is>
       </c>
-      <c r="C191" s="530" t="n"/>
-      <c r="D191" s="530" t="n"/>
-      <c r="E191" s="530" t="n"/>
-      <c r="F191" s="479">
-        <f>SUM(F187:F190)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="192">
-      <c r="A192" s="83" t="n"/>
-      <c r="B192" s="681" t="n"/>
-      <c r="C192" s="681" t="n"/>
-      <c r="D192" s="681" t="n"/>
-      <c r="E192" s="681" t="n"/>
-      <c r="F192" s="675" t="n"/>
+      <c r="C192" s="530" t="n"/>
+      <c r="D192" s="530" t="n"/>
+      <c r="E192" s="530" t="n"/>
+      <c r="F192" s="479">
+        <f>SUM(F188:F191)</f>
+        <v/>
+      </c>
     </row>
     <row r="193">
-      <c r="A193" s="185" t="inlineStr">
+      <c r="A193" s="83" t="n"/>
+      <c r="B193" s="681" t="n"/>
+      <c r="C193" s="681" t="n"/>
+      <c r="D193" s="681" t="n"/>
+      <c r="E193" s="681" t="n"/>
+      <c r="F193" s="675" t="n"/>
+    </row>
+    <row r="194">
+      <c r="A194" s="185" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="B193" s="677" t="inlineStr">
+      <c r="B194" s="677" t="inlineStr">
         <is>
           <t>GAS</t>
         </is>
       </c>
-      <c r="C193" s="530" t="n"/>
-      <c r="D193" s="530" t="n"/>
-      <c r="E193" s="530" t="n"/>
-      <c r="F193" s="530" t="n"/>
-    </row>
-    <row r="194">
-      <c r="A194" s="81" t="inlineStr">
-        <is>
-          <t>17.1</t>
-        </is>
-      </c>
-      <c r="B194" s="373" t="inlineStr">
-        <is>
-          <t>Red interna de gas</t>
-        </is>
-      </c>
-      <c r="C194" s="261" t="inlineStr">
-        <is>
-          <t>ML</t>
-        </is>
-      </c>
-      <c r="D194" s="262" t="n"/>
-      <c r="E194" s="477" t="n"/>
-      <c r="F194" s="478">
-        <f>D194*E194</f>
-        <v/>
-      </c>
+      <c r="C194" s="530" t="n"/>
+      <c r="D194" s="530" t="n"/>
+      <c r="E194" s="530" t="n"/>
+      <c r="F194" s="530" t="n"/>
     </row>
     <row r="195">
       <c r="A195" s="81" t="inlineStr">
         <is>
-          <t>17.2</t>
+          <t>17.1</t>
         </is>
       </c>
       <c r="B195" s="373" t="inlineStr">
         <is>
-          <t>Válvulas y accesorios</t>
+          <t>Red interna de gas</t>
         </is>
       </c>
       <c r="C195" s="261" t="inlineStr">
         <is>
-          <t>UND</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="D195" s="262" t="n"/>
@@ -15180,17 +15185,17 @@
     <row r="196">
       <c r="A196" s="81" t="inlineStr">
         <is>
-          <t>17.3</t>
+          <t>17.2</t>
         </is>
       </c>
       <c r="B196" s="373" t="inlineStr">
         <is>
-          <t>Pruebas y certificación</t>
+          <t>Válvulas y accesorios</t>
         </is>
       </c>
       <c r="C196" s="261" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>UND</t>
         </is>
       </c>
       <c r="D196" s="262" t="n"/>
@@ -15201,81 +15206,81 @@
       </c>
     </row>
     <row r="197">
-      <c r="A197" s="82" t="n"/>
-      <c r="B197" s="674" t="inlineStr">
+      <c r="A197" s="81" t="inlineStr">
+        <is>
+          <t>17.3</t>
+        </is>
+      </c>
+      <c r="B197" s="373" t="inlineStr">
+        <is>
+          <t>Pruebas y certificación</t>
+        </is>
+      </c>
+      <c r="C197" s="261" t="inlineStr">
+        <is>
+          <t>GL</t>
+        </is>
+      </c>
+      <c r="D197" s="262" t="n"/>
+      <c r="E197" s="477" t="n"/>
+      <c r="F197" s="478">
+        <f>D197*E197</f>
+        <v/>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" s="82" t="n"/>
+      <c r="B198" s="674" t="inlineStr">
         <is>
           <t>SUBTOTAL CAPÍTULO 17 - GAS</t>
         </is>
       </c>
-      <c r="C197" s="530" t="n"/>
-      <c r="D197" s="530" t="n"/>
-      <c r="E197" s="530" t="n"/>
-      <c r="F197" s="479">
-        <f>SUM(F194:F196)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="198">
-      <c r="A198" s="83" t="n"/>
-      <c r="B198" s="681" t="n"/>
-      <c r="C198" s="681" t="n"/>
-      <c r="D198" s="681" t="n"/>
-      <c r="E198" s="681" t="n"/>
-      <c r="F198" s="675" t="n"/>
+      <c r="C198" s="530" t="n"/>
+      <c r="D198" s="530" t="n"/>
+      <c r="E198" s="530" t="n"/>
+      <c r="F198" s="479">
+        <f>SUM(F195:F197)</f>
+        <v/>
+      </c>
     </row>
     <row r="199">
-      <c r="A199" s="185" t="inlineStr">
+      <c r="A199" s="83" t="n"/>
+      <c r="B199" s="681" t="n"/>
+      <c r="C199" s="681" t="n"/>
+      <c r="D199" s="681" t="n"/>
+      <c r="E199" s="681" t="n"/>
+      <c r="F199" s="675" t="n"/>
+    </row>
+    <row r="200">
+      <c r="A200" s="185" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="B199" s="677" t="inlineStr">
+      <c r="B200" s="677" t="inlineStr">
         <is>
           <t>URBANISMO Y EXTERIORES</t>
         </is>
       </c>
-      <c r="C199" s="530" t="n"/>
-      <c r="D199" s="530" t="n"/>
-      <c r="E199" s="530" t="n"/>
-      <c r="F199" s="530" t="n"/>
-    </row>
-    <row r="200">
-      <c r="A200" s="81" t="inlineStr">
-        <is>
-          <t>18.1</t>
-        </is>
-      </c>
-      <c r="B200" s="373" t="inlineStr">
-        <is>
-          <t>Construcción de andenes</t>
-        </is>
-      </c>
-      <c r="C200" s="261" t="inlineStr">
-        <is>
-          <t>M²</t>
-        </is>
-      </c>
-      <c r="D200" s="262" t="n"/>
-      <c r="E200" s="477" t="n"/>
-      <c r="F200" s="478">
-        <f>D200*E200</f>
-        <v/>
-      </c>
+      <c r="C200" s="530" t="n"/>
+      <c r="D200" s="530" t="n"/>
+      <c r="E200" s="530" t="n"/>
+      <c r="F200" s="530" t="n"/>
     </row>
     <row r="201">
       <c r="A201" s="81" t="inlineStr">
         <is>
-          <t>18.2</t>
+          <t>18.1</t>
         </is>
       </c>
       <c r="B201" s="373" t="inlineStr">
         <is>
-          <t>Placas de concreto exteriores</t>
+          <t>Construcción de andenes</t>
         </is>
       </c>
       <c r="C201" s="261" t="inlineStr">
         <is>
-          <t>M³</t>
+          <t>M²</t>
         </is>
       </c>
       <c r="D201" s="262" t="n"/>
@@ -15288,17 +15293,17 @@
     <row r="202">
       <c r="A202" s="81" t="inlineStr">
         <is>
-          <t>18.3</t>
+          <t>18.2</t>
         </is>
       </c>
       <c r="B202" s="373" t="inlineStr">
         <is>
-          <t>Pavimento en adoquín</t>
+          <t>Placas de concreto exteriores</t>
         </is>
       </c>
       <c r="C202" s="261" t="inlineStr">
         <is>
-          <t>M²</t>
+          <t>M³</t>
         </is>
       </c>
       <c r="D202" s="262" t="n"/>
@@ -15311,17 +15316,17 @@
     <row r="203">
       <c r="A203" s="81" t="inlineStr">
         <is>
-          <t>18.4</t>
+          <t>18.3</t>
         </is>
       </c>
       <c r="B203" s="373" t="inlineStr">
         <is>
-          <t>Sardineles y bordillos</t>
+          <t>Pavimento en adoquín</t>
         </is>
       </c>
       <c r="C203" s="261" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>M²</t>
         </is>
       </c>
       <c r="D203" s="262" t="n"/>
@@ -15334,17 +15339,17 @@
     <row r="204">
       <c r="A204" s="81" t="inlineStr">
         <is>
-          <t>18.5</t>
+          <t>18.4</t>
         </is>
       </c>
       <c r="B204" s="373" t="inlineStr">
         <is>
-          <t>Sumideros exteriores</t>
+          <t>Sardineles y bordillos</t>
         </is>
       </c>
       <c r="C204" s="261" t="inlineStr">
         <is>
-          <t>UND</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="D204" s="262" t="n"/>
@@ -15357,17 +15362,17 @@
     <row r="205">
       <c r="A205" s="81" t="inlineStr">
         <is>
-          <t>18.6</t>
+          <t>18.5</t>
         </is>
       </c>
       <c r="B205" s="373" t="inlineStr">
         <is>
-          <t>Suministro y extendido de tierra vegetal</t>
+          <t>Sumideros exteriores</t>
         </is>
       </c>
       <c r="C205" s="261" t="inlineStr">
         <is>
-          <t>M³</t>
+          <t>UND</t>
         </is>
       </c>
       <c r="D205" s="262" t="n"/>
@@ -15380,17 +15385,17 @@
     <row r="206">
       <c r="A206" s="81" t="inlineStr">
         <is>
-          <t>18.7</t>
+          <t>18.6</t>
         </is>
       </c>
       <c r="B206" s="373" t="inlineStr">
         <is>
-          <t>Siembra y jardinería</t>
+          <t>Suministro y extendido de tierra vegetal</t>
         </is>
       </c>
       <c r="C206" s="261" t="inlineStr">
         <is>
-          <t>M²</t>
+          <t>M³</t>
         </is>
       </c>
       <c r="D206" s="262" t="n"/>
@@ -15403,12 +15408,12 @@
     <row r="207">
       <c r="A207" s="81" t="inlineStr">
         <is>
-          <t>18.8</t>
+          <t>18.7</t>
         </is>
       </c>
       <c r="B207" s="373" t="inlineStr">
         <is>
-          <t>Geotextil para drenaje y filtración</t>
+          <t>Siembra y jardinería</t>
         </is>
       </c>
       <c r="C207" s="261" t="inlineStr">
@@ -15426,17 +15431,17 @@
     <row r="208">
       <c r="A208" s="81" t="inlineStr">
         <is>
-          <t>18.9</t>
+          <t>18.8</t>
         </is>
       </c>
       <c r="B208" s="373" t="inlineStr">
         <is>
-          <t>Gaviones para obras de contención</t>
+          <t>Geotextil para drenaje y filtración</t>
         </is>
       </c>
       <c r="C208" s="261" t="inlineStr">
         <is>
-          <t>M³</t>
+          <t>M²</t>
         </is>
       </c>
       <c r="D208" s="262" t="n"/>
@@ -15449,17 +15454,17 @@
     <row r="209">
       <c r="A209" s="81" t="inlineStr">
         <is>
-          <t>18.10</t>
+          <t>18.9</t>
         </is>
       </c>
       <c r="B209" s="373" t="inlineStr">
         <is>
-          <t>Filtro francés (drenaje de terrenos)</t>
+          <t>Gaviones para obras de contención</t>
         </is>
       </c>
       <c r="C209" s="261" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>M³</t>
         </is>
       </c>
       <c r="D209" s="262" t="n"/>
@@ -15472,17 +15477,17 @@
     <row r="210">
       <c r="A210" s="81" t="inlineStr">
         <is>
-          <t>18.11</t>
+          <t>18.10</t>
         </is>
       </c>
       <c r="B210" s="373" t="inlineStr">
         <is>
-          <t>Revegetalización / empradización</t>
+          <t>Filtro francés (drenaje de terrenos)</t>
         </is>
       </c>
       <c r="C210" s="261" t="inlineStr">
         <is>
-          <t>M²</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="D210" s="262" t="n"/>
@@ -15493,81 +15498,81 @@
       </c>
     </row>
     <row r="211">
-      <c r="A211" s="82" t="n"/>
-      <c r="B211" s="674" t="inlineStr">
+      <c r="A211" s="81" t="inlineStr">
+        <is>
+          <t>18.11</t>
+        </is>
+      </c>
+      <c r="B211" s="373" t="inlineStr">
+        <is>
+          <t>Revegetalización / empradización</t>
+        </is>
+      </c>
+      <c r="C211" s="261" t="inlineStr">
+        <is>
+          <t>M²</t>
+        </is>
+      </c>
+      <c r="D211" s="262" t="n"/>
+      <c r="E211" s="477" t="n"/>
+      <c r="F211" s="478">
+        <f>D211*E211</f>
+        <v/>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" s="82" t="n"/>
+      <c r="B212" s="674" t="inlineStr">
         <is>
           <t>SUBTOTAL CAPÍTULO 18 - URBANISMO Y EXTERIORES</t>
         </is>
       </c>
-      <c r="C211" s="530" t="n"/>
-      <c r="D211" s="530" t="n"/>
-      <c r="E211" s="530" t="n"/>
-      <c r="F211" s="479">
-        <f>SUM(F200:F210)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="212">
-      <c r="A212" s="83" t="n"/>
-      <c r="B212" s="681" t="n"/>
-      <c r="C212" s="681" t="n"/>
-      <c r="D212" s="681" t="n"/>
-      <c r="E212" s="681" t="n"/>
-      <c r="F212" s="675" t="n"/>
+      <c r="C212" s="530" t="n"/>
+      <c r="D212" s="530" t="n"/>
+      <c r="E212" s="530" t="n"/>
+      <c r="F212" s="479">
+        <f>SUM(F201:F211)</f>
+        <v/>
+      </c>
     </row>
     <row r="213">
-      <c r="A213" s="185" t="inlineStr">
+      <c r="A213" s="83" t="n"/>
+      <c r="B213" s="681" t="n"/>
+      <c r="C213" s="681" t="n"/>
+      <c r="D213" s="681" t="n"/>
+      <c r="E213" s="681" t="n"/>
+      <c r="F213" s="675" t="n"/>
+    </row>
+    <row r="214">
+      <c r="A214" s="185" t="inlineStr">
         <is>
           <t>19</t>
         </is>
       </c>
-      <c r="B213" s="677" t="inlineStr">
+      <c r="B214" s="677" t="inlineStr">
         <is>
           <t>OBRAS COMPLEMENTARIAS</t>
         </is>
       </c>
-      <c r="C213" s="530" t="n"/>
-      <c r="D213" s="530" t="n"/>
-      <c r="E213" s="530" t="n"/>
-      <c r="F213" s="530" t="n"/>
-    </row>
-    <row r="214">
-      <c r="A214" s="81" t="inlineStr">
-        <is>
-          <t>19.1</t>
-        </is>
-      </c>
-      <c r="B214" s="373" t="inlineStr">
-        <is>
-          <t>Rejas metálicas</t>
-        </is>
-      </c>
-      <c r="C214" s="261" t="inlineStr">
-        <is>
-          <t>M²</t>
-        </is>
-      </c>
-      <c r="D214" s="262" t="n"/>
-      <c r="E214" s="477" t="n"/>
-      <c r="F214" s="478">
-        <f>D214*E214</f>
-        <v/>
-      </c>
+      <c r="C214" s="530" t="n"/>
+      <c r="D214" s="530" t="n"/>
+      <c r="E214" s="530" t="n"/>
+      <c r="F214" s="530" t="n"/>
     </row>
     <row r="215">
       <c r="A215" s="81" t="inlineStr">
         <is>
-          <t>19.2</t>
+          <t>19.1</t>
         </is>
       </c>
       <c r="B215" s="373" t="inlineStr">
         <is>
-          <t>Escaleras metálicas</t>
+          <t>Rejas metálicas</t>
         </is>
       </c>
       <c r="C215" s="261" t="inlineStr">
         <is>
-          <t>KG</t>
+          <t>M²</t>
         </is>
       </c>
       <c r="D215" s="262" t="n"/>
@@ -15580,12 +15585,12 @@
     <row r="216">
       <c r="A216" s="81" t="inlineStr">
         <is>
-          <t>19.3</t>
+          <t>19.2</t>
         </is>
       </c>
       <c r="B216" s="373" t="inlineStr">
         <is>
-          <t>Elementos metálicos especiales</t>
+          <t>Escaleras metálicas</t>
         </is>
       </c>
       <c r="C216" s="261" t="inlineStr">
@@ -15603,17 +15608,17 @@
     <row r="217">
       <c r="A217" s="81" t="inlineStr">
         <is>
-          <t>19.4</t>
+          <t>19.3</t>
         </is>
       </c>
       <c r="B217" s="373" t="inlineStr">
         <is>
-          <t>Mobiliario fijo de obra</t>
+          <t>Elementos metálicos especiales</t>
         </is>
       </c>
       <c r="C217" s="261" t="inlineStr">
         <is>
-          <t>UND</t>
+          <t>KG</t>
         </is>
       </c>
       <c r="D217" s="262" t="n"/>
@@ -15624,76 +15629,76 @@
       </c>
     </row>
     <row r="218">
-      <c r="A218" s="82" t="n"/>
-      <c r="B218" s="674" t="inlineStr">
+      <c r="A218" s="81" t="inlineStr">
+        <is>
+          <t>19.4</t>
+        </is>
+      </c>
+      <c r="B218" s="373" t="inlineStr">
+        <is>
+          <t>Mobiliario fijo de obra</t>
+        </is>
+      </c>
+      <c r="C218" s="261" t="inlineStr">
+        <is>
+          <t>UND</t>
+        </is>
+      </c>
+      <c r="D218" s="262" t="n"/>
+      <c r="E218" s="477" t="n"/>
+      <c r="F218" s="478">
+        <f>D218*E218</f>
+        <v/>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" s="82" t="n"/>
+      <c r="B219" s="674" t="inlineStr">
         <is>
           <t>SUBTOTAL CAPÍTULO 19 - OBRAS COMPLEMENTARIAS</t>
         </is>
       </c>
-      <c r="C218" s="530" t="n"/>
-      <c r="D218" s="530" t="n"/>
-      <c r="E218" s="530" t="n"/>
-      <c r="F218" s="479">
-        <f>SUM(F214:F217)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="219">
-      <c r="A219" s="83" t="n"/>
-      <c r="B219" s="681" t="n"/>
-      <c r="C219" s="681" t="n"/>
-      <c r="D219" s="681" t="n"/>
-      <c r="E219" s="681" t="n"/>
-      <c r="F219" s="675" t="n"/>
+      <c r="C219" s="530" t="n"/>
+      <c r="D219" s="530" t="n"/>
+      <c r="E219" s="530" t="n"/>
+      <c r="F219" s="479">
+        <f>SUM(F215:F218)</f>
+        <v/>
+      </c>
     </row>
     <row r="220">
-      <c r="A220" s="185" t="inlineStr">
+      <c r="A220" s="83" t="n"/>
+      <c r="B220" s="681" t="n"/>
+      <c r="C220" s="681" t="n"/>
+      <c r="D220" s="681" t="n"/>
+      <c r="E220" s="681" t="n"/>
+      <c r="F220" s="675" t="n"/>
+    </row>
+    <row r="221">
+      <c r="A221" s="185" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="B220" s="677" t="inlineStr">
+      <c r="B221" s="677" t="inlineStr">
         <is>
           <t>ASEO, ENTREGA Y CIERRE</t>
         </is>
       </c>
-      <c r="C220" s="530" t="n"/>
-      <c r="D220" s="530" t="n"/>
-      <c r="E220" s="530" t="n"/>
-      <c r="F220" s="530" t="n"/>
-    </row>
-    <row r="221">
-      <c r="A221" s="81" t="inlineStr">
-        <is>
-          <t>20.1</t>
-        </is>
-      </c>
-      <c r="B221" s="373" t="inlineStr">
-        <is>
-          <t>Limpieza gruesa y fina de obra</t>
-        </is>
-      </c>
-      <c r="C221" s="261" t="inlineStr">
-        <is>
-          <t>M²</t>
-        </is>
-      </c>
-      <c r="D221" s="262" t="n"/>
-      <c r="E221" s="477" t="n"/>
-      <c r="F221" s="478">
-        <f>D221*E221</f>
-        <v/>
-      </c>
+      <c r="C221" s="530" t="n"/>
+      <c r="D221" s="530" t="n"/>
+      <c r="E221" s="530" t="n"/>
+      <c r="F221" s="530" t="n"/>
     </row>
     <row r="222">
       <c r="A222" s="81" t="inlineStr">
         <is>
-          <t>20.2</t>
+          <t>20.1</t>
         </is>
       </c>
       <c r="B222" s="373" t="inlineStr">
         <is>
-          <t>Limpieza final para entrega</t>
+          <t>Limpieza gruesa y fina de obra</t>
         </is>
       </c>
       <c r="C222" s="261" t="inlineStr">
@@ -15711,17 +15716,17 @@
     <row r="223">
       <c r="A223" s="81" t="inlineStr">
         <is>
-          <t>20.3</t>
+          <t>20.2</t>
         </is>
       </c>
       <c r="B223" s="373" t="inlineStr">
         <is>
-          <t>Pruebas, puesta en marcha y ajustes</t>
+          <t>Limpieza final para entrega</t>
         </is>
       </c>
       <c r="C223" s="261" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>M²</t>
         </is>
       </c>
       <c r="D223" s="262" t="n"/>
@@ -15734,12 +15739,12 @@
     <row r="224">
       <c r="A224" s="81" t="inlineStr">
         <is>
-          <t>20.4</t>
+          <t>20.3</t>
         </is>
       </c>
       <c r="B224" s="373" t="inlineStr">
         <is>
-          <t>Actualización de planos récord / as-built</t>
+          <t>Pruebas, puesta en marcha y ajustes</t>
         </is>
       </c>
       <c r="C224" s="261" t="inlineStr">
@@ -15757,12 +15762,12 @@
     <row r="225">
       <c r="A225" s="81" t="inlineStr">
         <is>
-          <t>20.5</t>
+          <t>20.4</t>
         </is>
       </c>
       <c r="B225" s="373" t="inlineStr">
         <is>
-          <t>Entrega, manuales y acta de recibo</t>
+          <t>Actualización de planos récord / as-built</t>
         </is>
       </c>
       <c r="C225" s="261" t="inlineStr">
@@ -15778,138 +15783,138 @@
       </c>
     </row>
     <row r="226">
-      <c r="A226" s="82" t="n"/>
-      <c r="B226" s="674" t="inlineStr">
+      <c r="A226" s="81" t="inlineStr">
+        <is>
+          <t>20.5</t>
+        </is>
+      </c>
+      <c r="B226" s="373" t="inlineStr">
+        <is>
+          <t>Entrega, manuales y acta de recibo</t>
+        </is>
+      </c>
+      <c r="C226" s="261" t="inlineStr">
+        <is>
+          <t>GL</t>
+        </is>
+      </c>
+      <c r="D226" s="262" t="n"/>
+      <c r="E226" s="477" t="n"/>
+      <c r="F226" s="478">
+        <f>D226*E226</f>
+        <v/>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" s="82" t="n"/>
+      <c r="B227" s="674" t="inlineStr">
         <is>
           <t>SUBTOTAL CAPÍTULO 20 - ASEO, ENTREGA Y CIERRE</t>
         </is>
       </c>
-      <c r="C226" s="530" t="n"/>
-      <c r="D226" s="530" t="n"/>
-      <c r="E226" s="530" t="n"/>
-      <c r="F226" s="479">
-        <f>SUM(F221:F225)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="227">
-      <c r="A227" s="83" t="n"/>
-      <c r="B227" s="681" t="n"/>
-      <c r="C227" s="681" t="n"/>
-      <c r="D227" s="681" t="n"/>
-      <c r="E227" s="681" t="n"/>
-      <c r="F227" s="675" t="n"/>
+      <c r="C227" s="530" t="n"/>
+      <c r="D227" s="530" t="n"/>
+      <c r="E227" s="530" t="n"/>
+      <c r="F227" s="479">
+        <f>SUM(F222:F226)</f>
+        <v/>
+      </c>
     </row>
     <row r="228">
-      <c r="A228" s="185" t="inlineStr">
+      <c r="A228" s="83" t="n"/>
+      <c r="B228" s="681" t="n"/>
+      <c r="C228" s="681" t="n"/>
+      <c r="D228" s="681" t="n"/>
+      <c r="E228" s="681" t="n"/>
+      <c r="F228" s="675" t="n"/>
+    </row>
+    <row r="229">
+      <c r="A229" s="185" t="inlineStr">
         <is>
           <t>21</t>
         </is>
       </c>
-      <c r="B228" s="677" t="inlineStr">
+      <c r="B229" s="677" t="inlineStr">
         <is>
           <t>ASCENSORES</t>
         </is>
       </c>
-      <c r="C228" s="530" t="n"/>
-      <c r="D228" s="530" t="n"/>
-      <c r="E228" s="530" t="n"/>
-      <c r="F228" s="530" t="n"/>
-    </row>
-    <row r="229">
-      <c r="A229" s="81" t="inlineStr">
+      <c r="C229" s="530" t="n"/>
+      <c r="D229" s="530" t="n"/>
+      <c r="E229" s="530" t="n"/>
+      <c r="F229" s="530" t="n"/>
+    </row>
+    <row r="230">
+      <c r="A230" s="81" t="inlineStr">
         <is>
           <t>21.1</t>
         </is>
       </c>
-      <c r="B229" s="373" t="inlineStr">
+      <c r="B230" s="373" t="inlineStr">
         <is>
           <t>Suministro e instalación de ascensor eléctrico</t>
         </is>
       </c>
-      <c r="C229" s="261" t="inlineStr">
+      <c r="C230" s="261" t="inlineStr">
         <is>
           <t>UND</t>
         </is>
       </c>
-      <c r="D229" s="262" t="n"/>
-      <c r="E229" s="477" t="n"/>
-      <c r="F229" s="478">
-        <f>D229*E229</f>
-        <v/>
-      </c>
-    </row>
-    <row r="230">
-      <c r="A230" s="82" t="n"/>
-      <c r="B230" s="674" t="inlineStr">
+      <c r="D230" s="262" t="n"/>
+      <c r="E230" s="477" t="n"/>
+      <c r="F230" s="478">
+        <f>D230*E230</f>
+        <v/>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" s="82" t="n"/>
+      <c r="B231" s="674" t="inlineStr">
         <is>
           <t>SUBTOTAL CAPÍTULO 21 - ASCENSORES</t>
         </is>
       </c>
-      <c r="C230" s="530" t="n"/>
-      <c r="D230" s="530" t="n"/>
-      <c r="E230" s="530" t="n"/>
-      <c r="F230" s="479">
-        <f>SUM(F229:F229)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="231">
-      <c r="A231" s="83" t="n"/>
-      <c r="B231" s="681" t="n"/>
-      <c r="C231" s="681" t="n"/>
-      <c r="D231" s="681" t="n"/>
-      <c r="E231" s="681" t="n"/>
-      <c r="F231" s="675" t="n"/>
+      <c r="C231" s="530" t="n"/>
+      <c r="D231" s="530" t="n"/>
+      <c r="E231" s="530" t="n"/>
+      <c r="F231" s="479">
+        <f>SUM(F230:F230)</f>
+        <v/>
+      </c>
     </row>
     <row r="232">
-      <c r="A232" s="185" t="inlineStr">
+      <c r="A232" s="83" t="n"/>
+      <c r="B232" s="681" t="n"/>
+      <c r="C232" s="681" t="n"/>
+      <c r="D232" s="681" t="n"/>
+      <c r="E232" s="681" t="n"/>
+      <c r="F232" s="675" t="n"/>
+    </row>
+    <row r="233">
+      <c r="A233" s="185" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="B232" s="677" t="inlineStr">
+      <c r="B233" s="677" t="inlineStr">
         <is>
           <t>GESTIÓN, DISEÑO Y ADMINISTRACIÓN</t>
         </is>
       </c>
-      <c r="C232" s="530" t="n"/>
-      <c r="D232" s="530" t="n"/>
-      <c r="E232" s="530" t="n"/>
-      <c r="F232" s="530" t="n"/>
-    </row>
-    <row r="233">
-      <c r="A233" s="81" t="inlineStr">
-        <is>
-          <t>22.1</t>
-        </is>
-      </c>
-      <c r="B233" s="373" t="inlineStr">
-        <is>
-          <t>Estudio de suelos y geotecnia</t>
-        </is>
-      </c>
-      <c r="C233" s="261" t="inlineStr">
-        <is>
-          <t>GL</t>
-        </is>
-      </c>
-      <c r="D233" s="262" t="n"/>
-      <c r="E233" s="477" t="n"/>
-      <c r="F233" s="478">
-        <f>D233*E233</f>
-        <v/>
-      </c>
+      <c r="C233" s="530" t="n"/>
+      <c r="D233" s="530" t="n"/>
+      <c r="E233" s="530" t="n"/>
+      <c r="F233" s="530" t="n"/>
     </row>
     <row r="234">
       <c r="A234" s="81" t="inlineStr">
         <is>
-          <t>22.2</t>
+          <t>22.1</t>
         </is>
       </c>
       <c r="B234" s="373" t="inlineStr">
         <is>
-          <t>Diseños arquitectónicos, estructurales, hidrosanitarios y eléctricos</t>
+          <t>Estudio de suelos y geotecnia</t>
         </is>
       </c>
       <c r="C234" s="261" t="inlineStr">
@@ -15927,12 +15932,12 @@
     <row r="235">
       <c r="A235" s="81" t="inlineStr">
         <is>
-          <t>22.3</t>
+          <t>22.2</t>
         </is>
       </c>
       <c r="B235" s="373" t="inlineStr">
         <is>
-          <t>Licencia de construcción y trámites de curaduría urbana</t>
+          <t>Diseños arquitectónicos, estructurales, hidrosanitarios y eléctricos</t>
         </is>
       </c>
       <c r="C235" s="261" t="inlineStr">
@@ -15950,12 +15955,12 @@
     <row r="236">
       <c r="A236" s="81" t="inlineStr">
         <is>
-          <t>22.4</t>
+          <t>22.3</t>
         </is>
       </c>
       <c r="B236" s="373" t="inlineStr">
         <is>
-          <t>Póliza de estabilidad de obra y seguros de construcción (todo riesgo)</t>
+          <t>Licencia de construcción y trámites de curaduría urbana</t>
         </is>
       </c>
       <c r="C236" s="261" t="inlineStr">
@@ -15971,84 +15976,89 @@
       </c>
     </row>
     <row r="237">
-      <c r="A237" s="82" t="n"/>
-      <c r="B237" s="674" t="inlineStr">
+      <c r="A237" s="81" t="inlineStr">
+        <is>
+          <t>22.4</t>
+        </is>
+      </c>
+      <c r="B237" s="373" t="inlineStr">
+        <is>
+          <t>Póliza de estabilidad de obra y seguros de construcción (todo riesgo)</t>
+        </is>
+      </c>
+      <c r="C237" s="261" t="inlineStr">
+        <is>
+          <t>GL</t>
+        </is>
+      </c>
+      <c r="D237" s="262" t="n"/>
+      <c r="E237" s="477" t="n"/>
+      <c r="F237" s="478">
+        <f>D237*E237</f>
+        <v/>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" s="82" t="n"/>
+      <c r="B238" s="674" t="inlineStr">
         <is>
           <t>SUBTOTAL CAPÍTULO 22 - GESTIÓN, DISEÑO Y ADMINISTRACIÓN</t>
         </is>
       </c>
-      <c r="C237" s="530" t="n"/>
-      <c r="D237" s="530" t="n"/>
-      <c r="E237" s="530" t="n"/>
-      <c r="F237" s="479">
-        <f>SUM(F233:F236)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="238">
-      <c r="A238" s="83" t="n"/>
-      <c r="B238" s="681" t="n"/>
-      <c r="C238" s="681" t="n"/>
-      <c r="D238" s="681" t="n"/>
-      <c r="E238" s="681" t="n"/>
-      <c r="F238" s="675" t="n"/>
-    </row>
-    <row r="239" ht="15" customHeight="1" s="1223">
-      <c r="A239" s="84" t="n"/>
-      <c r="B239" s="676" t="inlineStr">
+      <c r="C238" s="530" t="n"/>
+      <c r="D238" s="530" t="n"/>
+      <c r="E238" s="530" t="n"/>
+      <c r="F238" s="479">
+        <f>SUM(F234:F237)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" s="83" t="n"/>
+      <c r="B239" s="681" t="n"/>
+      <c r="C239" s="681" t="n"/>
+      <c r="D239" s="681" t="n"/>
+      <c r="E239" s="681" t="n"/>
+      <c r="F239" s="675" t="n"/>
+    </row>
+    <row r="240" ht="15" customHeight="1" s="1223">
+      <c r="A240" s="84" t="n"/>
+      <c r="B240" s="676" t="inlineStr">
         <is>
           <t>COSTO DIRECTO TOTAL (suma de capítulos 1 a 22)</t>
         </is>
       </c>
-      <c r="C239" s="530" t="n"/>
-      <c r="D239" s="530" t="n"/>
-      <c r="E239" s="530" t="n"/>
-      <c r="F239" s="480">
-        <f>F25+F39+F49+F68+F80+F92+F99+F106+F120+F128+F139+F146+F161+F175+F184+F191+F197+F211+F218+F226+F230+F237</f>
-        <v/>
-      </c>
-    </row>
-    <row r="240">
-      <c r="A240" s="85" t="n"/>
-      <c r="B240" s="28" t="n"/>
-      <c r="C240" s="28" t="n"/>
-      <c r="D240" s="28" t="n"/>
-      <c r="E240" s="28" t="n"/>
-      <c r="F240" s="86" t="n"/>
-    </row>
-    <row r="241" ht="15" customHeight="1" s="1223">
-      <c r="A241" s="83" t="n"/>
-      <c r="B241" s="46" t="inlineStr">
-        <is>
-          <t>Administración (A)</t>
-        </is>
-      </c>
-      <c r="C241" s="681" t="n"/>
-      <c r="D241" s="681" t="n"/>
-      <c r="E241" s="481">
-        <f>'Ficha Técnica del Proyecto'!$B$29</f>
-        <v/>
-      </c>
-      <c r="F241" s="482">
-        <f>F239*E241</f>
-        <v/>
-      </c>
+      <c r="C240" s="530" t="n"/>
+      <c r="D240" s="530" t="n"/>
+      <c r="E240" s="530" t="n"/>
+      <c r="F240" s="480">
+        <f>F25+F39+F49+F69+F81+F93+F100+F107+F121+F129+F140+F147+F162+F176+F185+F192+F198+F212+F219+F227+F231+F238</f>
+        <v/>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" s="85" t="n"/>
+      <c r="B241" s="28" t="n"/>
+      <c r="C241" s="28" t="n"/>
+      <c r="D241" s="28" t="n"/>
+      <c r="E241" s="28" t="n"/>
+      <c r="F241" s="86" t="n"/>
     </row>
     <row r="242" ht="15" customHeight="1" s="1223">
       <c r="A242" s="83" t="n"/>
       <c r="B242" s="46" t="inlineStr">
         <is>
-          <t>Imprevistos (I)</t>
+          <t>Administración (A)</t>
         </is>
       </c>
       <c r="C242" s="681" t="n"/>
       <c r="D242" s="681" t="n"/>
       <c r="E242" s="481">
-        <f>'Ficha Técnica del Proyecto'!$B$30</f>
+        <f>'Ficha Técnica del Proyecto'!$B$29</f>
         <v/>
       </c>
       <c r="F242" s="482">
-        <f>F239*E242</f>
+        <f>F240*E242</f>
         <v/>
       </c>
     </row>
@@ -16056,47 +16066,50 @@
       <c r="A243" s="83" t="n"/>
       <c r="B243" s="46" t="inlineStr">
         <is>
-          <t>Utilidad (U)</t>
+          <t>Imprevistos (I)</t>
         </is>
       </c>
       <c r="C243" s="681" t="n"/>
       <c r="D243" s="681" t="n"/>
       <c r="E243" s="481">
+        <f>'Ficha Técnica del Proyecto'!$B$30</f>
+        <v/>
+      </c>
+      <c r="F243" s="482">
+        <f>F240*E243</f>
+        <v/>
+      </c>
+    </row>
+    <row r="244" ht="15" customHeight="1" s="1223">
+      <c r="A244" s="83" t="n"/>
+      <c r="B244" s="46" t="inlineStr">
+        <is>
+          <t>Utilidad (U)</t>
+        </is>
+      </c>
+      <c r="C244" s="681" t="n"/>
+      <c r="D244" s="681" t="n"/>
+      <c r="E244" s="481">
         <f>'Ficha Técnica del Proyecto'!$B$31</f>
         <v/>
       </c>
-      <c r="F243" s="482">
-        <f>F239*E243</f>
-        <v/>
-      </c>
-    </row>
-    <row r="244" ht="15" customHeight="1" s="1223">
-      <c r="A244" s="82" t="n"/>
-      <c r="B244" s="674" t="inlineStr">
+      <c r="F244" s="482">
+        <f>F240*E244</f>
+        <v/>
+      </c>
+    </row>
+    <row r="245" ht="15" customHeight="1" s="1223">
+      <c r="A245" s="82" t="n"/>
+      <c r="B245" s="674" t="inlineStr">
         <is>
           <t>SUBTOTAL AIU (A+I+U)</t>
         </is>
       </c>
-      <c r="C244" s="29" t="n"/>
-      <c r="D244" s="29" t="n"/>
-      <c r="E244" s="30" t="n"/>
-      <c r="F244" s="479">
-        <f>F241+F242+F243</f>
-        <v/>
-      </c>
-    </row>
-    <row r="245" ht="15" customHeight="1" s="1223">
-      <c r="A245" s="83" t="n"/>
-      <c r="B245" s="46" t="inlineStr">
-        <is>
-          <t>COSTO DIRECTO + AIU</t>
-        </is>
-      </c>
-      <c r="C245" s="681" t="n"/>
-      <c r="D245" s="681" t="n"/>
-      <c r="E245" s="47" t="n"/>
-      <c r="F245" s="482">
-        <f>F239+F244</f>
+      <c r="C245" s="29" t="n"/>
+      <c r="D245" s="29" t="n"/>
+      <c r="E245" s="30" t="n"/>
+      <c r="F245" s="479">
+        <f>F242+F243+F244</f>
         <v/>
       </c>
     </row>
@@ -16104,103 +16117,110 @@
       <c r="A246" s="83" t="n"/>
       <c r="B246" s="46" t="inlineStr">
         <is>
-          <t>IVA sobre Utilidad (19%)</t>
+          <t>COSTO DIRECTO + AIU</t>
         </is>
       </c>
       <c r="C246" s="681" t="n"/>
       <c r="D246" s="681" t="n"/>
-      <c r="E246" s="481">
-        <f>'Ficha Técnica del Proyecto'!$B$32</f>
-        <v/>
-      </c>
+      <c r="E246" s="47" t="n"/>
       <c r="F246" s="482">
-        <f>F243*E246</f>
-        <v/>
-      </c>
-    </row>
-    <row r="247">
+        <f>F240+F245</f>
+        <v/>
+      </c>
+    </row>
+    <row r="247" ht="15" customHeight="1" s="1223">
       <c r="A247" s="83" t="n"/>
-      <c r="B247" s="681" t="n"/>
+      <c r="B247" s="46" t="inlineStr">
+        <is>
+          <t>IVA sobre Utilidad (19%)</t>
+        </is>
+      </c>
       <c r="C247" s="681" t="n"/>
       <c r="D247" s="681" t="n"/>
-      <c r="E247" s="681" t="n"/>
-      <c r="F247" s="675" t="n"/>
-    </row>
-    <row r="248" ht="24" customHeight="1" s="1223">
-      <c r="A248" s="87" t="n"/>
-      <c r="B248" s="677" t="inlineStr">
+      <c r="E247" s="481">
+        <f>'Ficha Técnica del Proyecto'!$B$32</f>
+        <v/>
+      </c>
+      <c r="F247" s="482">
+        <f>F244*E247</f>
+        <v/>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" s="83" t="n"/>
+      <c r="B248" s="681" t="n"/>
+      <c r="C248" s="681" t="n"/>
+      <c r="D248" s="681" t="n"/>
+      <c r="E248" s="681" t="n"/>
+      <c r="F248" s="675" t="n"/>
+    </row>
+    <row r="249" ht="24" customHeight="1" s="1223">
+      <c r="A249" s="87" t="n"/>
+      <c r="B249" s="677" t="inlineStr">
         <is>
           <t>PRESUPUESTO TOTAL DE OBRA</t>
         </is>
       </c>
-      <c r="C248" s="530" t="n"/>
-      <c r="D248" s="530" t="n"/>
-      <c r="E248" s="530" t="n"/>
-      <c r="F248" s="483">
-        <f>F245+F246</f>
-        <v/>
-      </c>
-    </row>
-    <row r="249">
-      <c r="A249" s="88" t="n"/>
-      <c r="B249" s="206" t="inlineStr">
-        <is>
-          <t>REV. 10/09/2026</t>
-        </is>
-      </c>
-      <c r="C249" s="281" t="n"/>
-      <c r="D249" s="281" t="n"/>
-      <c r="E249" s="281" t="n"/>
-      <c r="F249" s="350">
-        <f>F6</f>
+      <c r="C249" s="530" t="n"/>
+      <c r="D249" s="530" t="n"/>
+      <c r="E249" s="530" t="n"/>
+      <c r="F249" s="483">
+        <f>F246+F247</f>
         <v/>
       </c>
     </row>
     <row r="250">
       <c r="A250" s="88" t="n"/>
-      <c r="B250" s="206" t="n"/>
+      <c r="B250" s="206" t="inlineStr">
+        <is>
+          <t>REV. 10/09/2026</t>
+        </is>
+      </c>
       <c r="C250" s="281" t="n"/>
       <c r="D250" s="281" t="n"/>
       <c r="E250" s="281" t="n"/>
-      <c r="F250" s="204" t="n"/>
-    </row>
-    <row r="251" ht="15" customHeight="1" s="1223">
+      <c r="F250" s="350">
+        <f>F6</f>
+        <v/>
+      </c>
+    </row>
+    <row r="251">
       <c r="A251" s="88" t="n"/>
-      <c r="B251" s="90" t="inlineStr">
+      <c r="B251" s="206" t="n"/>
+      <c r="C251" s="281" t="n"/>
+      <c r="D251" s="281" t="n"/>
+      <c r="E251" s="281" t="n"/>
+      <c r="F251" s="204" t="n"/>
+    </row>
+    <row r="252" ht="15" customHeight="1" s="1223">
+      <c r="A252" s="88" t="n"/>
+      <c r="B252" s="90" t="inlineStr">
         <is>
           <t>Costo por m² construido (sobre Costo Directo Total)</t>
         </is>
       </c>
-      <c r="C251" s="91" t="n"/>
-      <c r="D251" s="91" t="n"/>
-      <c r="E251" s="91" t="n"/>
-      <c r="F251" s="484">
-        <f>F239/'Ficha Técnica del Proyecto'!$B$21</f>
-        <v/>
-      </c>
-    </row>
-    <row r="252" ht="15" customHeight="1" s="1223">
-      <c r="A252" s="89" t="n"/>
-      <c r="B252" s="92" t="inlineStr">
+      <c r="C252" s="91" t="n"/>
+      <c r="D252" s="91" t="n"/>
+      <c r="E252" s="91" t="n"/>
+      <c r="F252" s="484">
+        <f>F240/'Ficha Técnica del Proyecto'!$B$21</f>
+        <v/>
+      </c>
+    </row>
+    <row r="253" ht="15" customHeight="1" s="1223">
+      <c r="A253" s="89" t="n"/>
+      <c r="B253" s="92" t="inlineStr">
         <is>
           <t>Costo por m² construido (sobre Presupuesto Total)</t>
         </is>
       </c>
-      <c r="C252" s="93" t="n"/>
-      <c r="D252" s="93" t="n"/>
-      <c r="E252" s="93" t="n"/>
-      <c r="F252" s="485">
-        <f>F248/'Ficha Técnica del Proyecto'!$B$21</f>
-        <v/>
-      </c>
-    </row>
-    <row r="253">
-      <c r="A253" s="27" t="n"/>
-      <c r="B253" s="281" t="n"/>
-      <c r="C253" s="281" t="n"/>
-      <c r="D253" s="281" t="n"/>
-      <c r="E253" s="281" t="n"/>
-      <c r="F253" s="281" t="n"/>
+      <c r="C253" s="93" t="n"/>
+      <c r="D253" s="93" t="n"/>
+      <c r="E253" s="93" t="n"/>
+      <c r="F253" s="485">
+        <f>F249/'Ficha Técnica del Proyecto'!$B$21</f>
+        <v/>
+      </c>
     </row>
     <row r="254">
       <c r="A254" s="27" t="n"/>
@@ -16242,69 +16262,77 @@
       <c r="E258" s="281" t="n"/>
       <c r="F258" s="281" t="n"/>
     </row>
+    <row r="259">
+      <c r="A259" s="27" t="n"/>
+      <c r="B259" s="281" t="n"/>
+      <c r="C259" s="281" t="n"/>
+      <c r="D259" s="281" t="n"/>
+      <c r="E259" s="281" t="n"/>
+      <c r="F259" s="281" t="n"/>
+    </row>
   </sheetData>
   <mergeCells count="61">
-    <mergeCell ref="B146:E146"/>
-    <mergeCell ref="B211:E211"/>
-    <mergeCell ref="B226:E226"/>
-    <mergeCell ref="B129:F129"/>
+    <mergeCell ref="B233:F233"/>
+    <mergeCell ref="B109:F109"/>
     <mergeCell ref="C6:D6"/>
     <mergeCell ref="B49:E49"/>
-    <mergeCell ref="B239:E239"/>
-    <mergeCell ref="B163:F163"/>
-    <mergeCell ref="B232:F232"/>
-    <mergeCell ref="B141:F141"/>
-    <mergeCell ref="B92:E92"/>
+    <mergeCell ref="B200:F200"/>
+    <mergeCell ref="B194:F194"/>
+    <mergeCell ref="B192:E192"/>
     <mergeCell ref="C5:D5"/>
-    <mergeCell ref="B199:F199"/>
-    <mergeCell ref="B68:E68"/>
     <mergeCell ref="E5:F5"/>
-    <mergeCell ref="B193:F193"/>
-    <mergeCell ref="B139:E139"/>
-    <mergeCell ref="B122:F122"/>
-    <mergeCell ref="B80:E80"/>
-    <mergeCell ref="B220:F220"/>
+    <mergeCell ref="B71:F71"/>
+    <mergeCell ref="B131:F131"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B214:F214"/>
+    <mergeCell ref="B198:E198"/>
+    <mergeCell ref="B102:F102"/>
     <mergeCell ref="B27:F27"/>
-    <mergeCell ref="B70:F70"/>
     <mergeCell ref="B130:F130"/>
-    <mergeCell ref="B197:E197"/>
-    <mergeCell ref="B228:F228"/>
-    <mergeCell ref="B237:E237"/>
-    <mergeCell ref="B106:E106"/>
-    <mergeCell ref="B218:E218"/>
+    <mergeCell ref="B212:E212"/>
+    <mergeCell ref="B129:E129"/>
     <mergeCell ref="B100:E100"/>
+    <mergeCell ref="B229:F229"/>
+    <mergeCell ref="B227:E227"/>
     <mergeCell ref="B25:E25"/>
-    <mergeCell ref="B107:F107"/>
-    <mergeCell ref="B101:F101"/>
+    <mergeCell ref="B185:E185"/>
     <mergeCell ref="B81:E81"/>
     <mergeCell ref="C9:D9"/>
     <mergeCell ref="B14:F14"/>
-    <mergeCell ref="B41:F41"/>
-    <mergeCell ref="B148:F148"/>
-    <mergeCell ref="B82:F82"/>
+    <mergeCell ref="B121:E121"/>
+    <mergeCell ref="B93:E93"/>
     <mergeCell ref="A12:B12"/>
     <mergeCell ref="C12:D12"/>
-    <mergeCell ref="B184:E184"/>
+    <mergeCell ref="B140:E140"/>
     <mergeCell ref="A10:F10"/>
-    <mergeCell ref="B248:E248"/>
-    <mergeCell ref="B161:E161"/>
+    <mergeCell ref="B238:E238"/>
+    <mergeCell ref="B178:F178"/>
+    <mergeCell ref="B176:E176"/>
+    <mergeCell ref="B219:E219"/>
     <mergeCell ref="B108:F108"/>
     <mergeCell ref="B39:E39"/>
-    <mergeCell ref="B186:F186"/>
-    <mergeCell ref="B120:E120"/>
+    <mergeCell ref="B231:E231"/>
+    <mergeCell ref="B240:E240"/>
+    <mergeCell ref="B107:E107"/>
+    <mergeCell ref="B101:E101"/>
+    <mergeCell ref="B187:F187"/>
     <mergeCell ref="C8:D8"/>
+    <mergeCell ref="B83:F83"/>
     <mergeCell ref="A11:F11"/>
     <mergeCell ref="C7:D7"/>
-    <mergeCell ref="B177:F177"/>
-    <mergeCell ref="B175:E175"/>
+    <mergeCell ref="B164:F164"/>
+    <mergeCell ref="B95:F95"/>
     <mergeCell ref="C1:F3"/>
+    <mergeCell ref="B69:E69"/>
+    <mergeCell ref="B142:F142"/>
+    <mergeCell ref="B82:E82"/>
+    <mergeCell ref="B147:E147"/>
+    <mergeCell ref="B249:E249"/>
+    <mergeCell ref="B162:E162"/>
     <mergeCell ref="B51:F51"/>
-    <mergeCell ref="B191:E191"/>
-    <mergeCell ref="B213:F213"/>
-    <mergeCell ref="B94:F94"/>
-    <mergeCell ref="B128:E128"/>
-    <mergeCell ref="B230:E230"/>
-    <mergeCell ref="B99:E99"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B221:F221"/>
+    <mergeCell ref="B41:F41"/>
   </mergeCells>
   <pageMargins left="0.1968503937007874" right="0.1968503937007874" top="0.1968503937007874" bottom="0.1968503937007874" header="0.5118110236220472" footer="0.5118110236220472"/>
   <pageSetup orientation="portrait" paperSize="9" scale="53" horizontalDpi="300" verticalDpi="300"/>
@@ -16531,7 +16559,7 @@
       <c r="J14" s="530" t="n"/>
       <c r="K14" s="530" t="n"/>
       <c r="L14" s="1187">
-        <f>'Presupuesto '!F248</f>
+        <f>'Presupuesto '!F249</f>
         <v/>
       </c>
       <c r="M14" s="530" t="n"/>
@@ -16765,7 +16793,7 @@
       <c r="B25" s="581" t="n"/>
       <c r="C25" s="581" t="n"/>
       <c r="D25" s="521">
-        <f>'Presupuesto '!F25/'Presupuesto '!$F$239</f>
+        <f>'Presupuesto '!F25/'Presupuesto '!$F$240</f>
         <v/>
       </c>
       <c r="E25" s="233" t="n"/>
@@ -16799,7 +16827,7 @@
       <c r="B26" s="581" t="n"/>
       <c r="C26" s="581" t="n"/>
       <c r="D26" s="521">
-        <f>'Presupuesto '!F39/'Presupuesto '!$F$239</f>
+        <f>'Presupuesto '!F39/'Presupuesto '!$F$240</f>
         <v/>
       </c>
       <c r="E26" s="233" t="n"/>
@@ -16830,7 +16858,7 @@
       <c r="B27" s="581" t="n"/>
       <c r="C27" s="581" t="n"/>
       <c r="D27" s="521">
-        <f>'Presupuesto '!F49/'Presupuesto '!$F$239</f>
+        <f>'Presupuesto '!F49/'Presupuesto '!$F$240</f>
         <v/>
       </c>
       <c r="E27" s="233" t="n"/>
@@ -16861,7 +16889,7 @@
       <c r="B28" s="581" t="n"/>
       <c r="C28" s="581" t="n"/>
       <c r="D28" s="521">
-        <f>'Presupuesto '!F68/'Presupuesto '!$F$239</f>
+        <f>'Presupuesto '!F69/'Presupuesto '!$F$240</f>
         <v/>
       </c>
       <c r="E28" s="233" t="n"/>
@@ -16892,7 +16920,7 @@
       <c r="B29" s="581" t="n"/>
       <c r="C29" s="581" t="n"/>
       <c r="D29" s="521">
-        <f>'Presupuesto '!F80/'Presupuesto '!$F$239</f>
+        <f>'Presupuesto '!F81/'Presupuesto '!$F$240</f>
         <v/>
       </c>
       <c r="E29" s="233" t="n"/>
@@ -16923,7 +16951,7 @@
       <c r="B30" s="581" t="n"/>
       <c r="C30" s="581" t="n"/>
       <c r="D30" s="521">
-        <f>'Presupuesto '!F92/'Presupuesto '!$F$239</f>
+        <f>'Presupuesto '!F93/'Presupuesto '!$F$240</f>
         <v/>
       </c>
       <c r="E30" s="233" t="n"/>
@@ -16954,7 +16982,7 @@
       <c r="B31" s="581" t="n"/>
       <c r="C31" s="581" t="n"/>
       <c r="D31" s="521">
-        <f>'Presupuesto '!F99/'Presupuesto '!$F$239</f>
+        <f>'Presupuesto '!F100/'Presupuesto '!$F$240</f>
         <v/>
       </c>
       <c r="E31" s="233" t="n"/>
@@ -16985,7 +17013,7 @@
       <c r="B32" s="581" t="n"/>
       <c r="C32" s="581" t="n"/>
       <c r="D32" s="521">
-        <f>'Presupuesto '!F106/'Presupuesto '!$F$239</f>
+        <f>'Presupuesto '!F107/'Presupuesto '!$F$240</f>
         <v/>
       </c>
       <c r="E32" s="233" t="n"/>
@@ -17016,7 +17044,7 @@
       <c r="B33" s="581" t="n"/>
       <c r="C33" s="581" t="n"/>
       <c r="D33" s="521">
-        <f>'Presupuesto '!F120/'Presupuesto '!$F$239</f>
+        <f>'Presupuesto '!F121/'Presupuesto '!$F$240</f>
         <v/>
       </c>
       <c r="E33" s="233" t="n"/>
@@ -17047,7 +17075,7 @@
       <c r="B34" s="581" t="n"/>
       <c r="C34" s="581" t="n"/>
       <c r="D34" s="521">
-        <f>'Presupuesto '!F128/'Presupuesto '!$F$239</f>
+        <f>'Presupuesto '!F129/'Presupuesto '!$F$240</f>
         <v/>
       </c>
       <c r="E34" s="233" t="n"/>
@@ -17078,7 +17106,7 @@
       <c r="B35" s="581" t="n"/>
       <c r="C35" s="581" t="n"/>
       <c r="D35" s="521">
-        <f>'Presupuesto '!F139/'Presupuesto '!$F$239</f>
+        <f>'Presupuesto '!F140/'Presupuesto '!$F$240</f>
         <v/>
       </c>
       <c r="E35" s="233" t="n"/>
@@ -17109,7 +17137,7 @@
       <c r="B36" s="581" t="n"/>
       <c r="C36" s="581" t="n"/>
       <c r="D36" s="521">
-        <f>'Presupuesto '!F146/'Presupuesto '!$F$239</f>
+        <f>'Presupuesto '!F147/'Presupuesto '!$F$240</f>
         <v/>
       </c>
       <c r="E36" s="233" t="n"/>
@@ -17140,7 +17168,7 @@
       <c r="B37" s="581" t="n"/>
       <c r="C37" s="581" t="n"/>
       <c r="D37" s="521">
-        <f>'Presupuesto '!F161/'Presupuesto '!$F$239</f>
+        <f>'Presupuesto '!F162/'Presupuesto '!$F$240</f>
         <v/>
       </c>
       <c r="E37" s="233" t="n"/>
@@ -17171,7 +17199,7 @@
       <c r="B38" s="581" t="n"/>
       <c r="C38" s="581" t="n"/>
       <c r="D38" s="521">
-        <f>'Presupuesto '!F175/'Presupuesto '!$F$239</f>
+        <f>'Presupuesto '!F176/'Presupuesto '!$F$240</f>
         <v/>
       </c>
       <c r="E38" s="233" t="n"/>
@@ -17202,7 +17230,7 @@
       <c r="B39" s="581" t="n"/>
       <c r="C39" s="581" t="n"/>
       <c r="D39" s="521">
-        <f>'Presupuesto '!F184/'Presupuesto '!$F$239</f>
+        <f>'Presupuesto '!F185/'Presupuesto '!$F$240</f>
         <v/>
       </c>
       <c r="E39" s="233" t="n"/>
@@ -17233,7 +17261,7 @@
       <c r="B40" s="530" t="n"/>
       <c r="C40" s="530" t="n"/>
       <c r="D40" s="521">
-        <f>'Presupuesto '!F191/'Presupuesto '!$F$239</f>
+        <f>'Presupuesto '!F192/'Presupuesto '!$F$240</f>
         <v/>
       </c>
       <c r="E40" s="233" t="n"/>
@@ -17264,7 +17292,7 @@
       <c r="B41" s="1018" t="n"/>
       <c r="C41" s="1018" t="n"/>
       <c r="D41" s="521">
-        <f>'Presupuesto '!F197/'Presupuesto '!$F$239</f>
+        <f>'Presupuesto '!F198/'Presupuesto '!$F$240</f>
         <v/>
       </c>
       <c r="E41" s="1018" t="n"/>
@@ -17295,7 +17323,7 @@
       <c r="B42" s="581" t="n"/>
       <c r="C42" s="581" t="n"/>
       <c r="D42" s="521">
-        <f>'Presupuesto '!F211/'Presupuesto '!$F$239</f>
+        <f>'Presupuesto '!F212/'Presupuesto '!$F$240</f>
         <v/>
       </c>
       <c r="E42" s="581" t="n"/>
@@ -17326,7 +17354,7 @@
       <c r="B43" s="530" t="n"/>
       <c r="C43" s="530" t="n"/>
       <c r="D43" s="521">
-        <f>'Presupuesto '!F218/'Presupuesto '!$F$239</f>
+        <f>'Presupuesto '!F219/'Presupuesto '!$F$240</f>
         <v/>
       </c>
       <c r="E43" s="233" t="n"/>
@@ -17357,7 +17385,7 @@
       <c r="B44" s="530" t="n"/>
       <c r="C44" s="530" t="n"/>
       <c r="D44" s="521">
-        <f>'Presupuesto '!F226/'Presupuesto '!$F$239</f>
+        <f>'Presupuesto '!F227/'Presupuesto '!$F$240</f>
         <v/>
       </c>
       <c r="E44" s="233" t="n"/>
@@ -17388,7 +17416,7 @@
       <c r="B45" s="530" t="n"/>
       <c r="C45" s="530" t="n"/>
       <c r="D45" s="521">
-        <f>'Presupuesto '!F230/'Presupuesto '!$F$239</f>
+        <f>'Presupuesto '!F231/'Presupuesto '!$F$240</f>
         <v/>
       </c>
       <c r="E45" s="530" t="n"/>
@@ -17419,7 +17447,7 @@
       <c r="B46" s="530" t="n"/>
       <c r="C46" s="530" t="n"/>
       <c r="D46" s="521">
-        <f>'Presupuesto '!F237/'Presupuesto '!$F$239</f>
+        <f>'Presupuesto '!F238/'Presupuesto '!$F$240</f>
         <v/>
       </c>
       <c r="E46" s="233" t="n"/>

--- a/public/plantilla-mensual.xlsx
+++ b/public/plantilla-mensual.xlsx
@@ -16,7 +16,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="8">
+  <numFmts count="9">
     <numFmt numFmtId="164" formatCode="_-&quot;$ &quot;* #,##0.00_-;&quot;-$ &quot;* #,##0.00_-;_-&quot;$ &quot;* \-??_-;_-@_-"/>
     <numFmt numFmtId="165" formatCode="0.000"/>
     <numFmt numFmtId="166" formatCode="&quot;$&quot;\ #,##0.00"/>
@@ -25,6 +25,7 @@
     <numFmt numFmtId="169" formatCode="&quot;$ &quot;#,##0"/>
     <numFmt numFmtId="170" formatCode="\$\ #,##0.00"/>
     <numFmt numFmtId="171" formatCode="$ #,##0.00"/>
+    <numFmt numFmtId="172" formatCode="$ #,##0"/>
   </numFmts>
   <fonts count="170">
     <font>
@@ -1690,7 +1691,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="411">
+  <borders count="412">
     <border>
       <left/>
       <right/>
@@ -6575,6 +6576,20 @@
       </top>
       <bottom/>
       <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB8C2CC"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB8C2CC"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB8C2CC"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB8C2CC"/>
+      </bottom>
     </border>
   </borders>
   <cellStyleXfs count="5">
@@ -6584,7 +6599,7 @@
     <xf numFmtId="0" fontId="28" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1309">
+  <cellXfs count="1313">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
@@ -9814,6 +9829,18 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="169" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="172" fontId="127" fillId="55" borderId="188" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="172" fontId="124" fillId="17" borderId="188" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="172" fontId="124" fillId="17" borderId="411" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="124" fillId="28" borderId="411" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="5">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -10759,7 +10786,6 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="FFFFFF00"/>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:E47"/>
@@ -11330,7 +11356,6 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="FF2E7D32"/>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:F259"/>
@@ -16344,7 +16369,6 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="FF7030A0"/>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:S131"/>

--- a/public/plantilla-mensual.xlsx
+++ b/public/plantilla-mensual.xlsx
@@ -10405,31 +10405,6 @@
 </chartSpace>
 </file>
 
-<file path=xl/comments/comment1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <authors>
-    <author>OpenAI</author>
-  </authors>
-  <commentList>
-    <comment ref="I26" authorId="0" shapeId="0">
-      <text>
-        <t>Cantidad acumulada = cantidad anterior + cantidad del presente acta.</t>
-      </text>
-    </comment>
-    <comment ref="J26" authorId="0" shapeId="0">
-      <text>
-        <t>Saldo = cantidad contractual - cantidad acumulada. No permite saldos negativos.</t>
-      </text>
-    </comment>
-    <comment ref="K26" authorId="0" shapeId="0">
-      <text>
-        <t>% ejecución = cantidad acumulada / cantidad contractual.</t>
-      </text>
-    </comment>
-  </commentList>
-</comments>
-</file>
-
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <xdr:twoCellAnchor editAs="oneCell">

--- a/public/plantilla-mensual.xlsx
+++ b/public/plantilla-mensual.xlsx
@@ -10771,7 +10771,6 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="FFFFFF00"/>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:E47"/>
@@ -11342,7 +11341,6 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="FF2E7D32"/>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:F259"/>
@@ -16356,7 +16354,6 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="FF7030A0"/>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:S131"/>

--- a/public/plantilla-mensual.xlsx
+++ b/public/plantilla-mensual.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Ficha Técnica del Proyecto" sheetId="1" r:id="rId1"/>
-    <sheet name="Presupuesto " sheetId="2" r:id="rId12"/>
-    <sheet name="Informe Mensual" sheetId="3" r:id="rId19"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ficha Técnica del Proyecto" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Presupuesto " sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Informe Mensual" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
+  <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1" iterateDelta="0.0001"/>
 </workbook>
 </file>
@@ -27,7 +28,7 @@
     <numFmt numFmtId="171" formatCode="$ #,##0.00"/>
     <numFmt numFmtId="172" formatCode="$ #,##0"/>
   </numFmts>
-  <fonts count="170">
+  <fonts count="171">
     <font>
       <name val="Calibri"/>
       <charset val="1"/>
@@ -1241,6 +1242,11 @@
       <color rgb="008A8F99"/>
       <sz val="8"/>
     </font>
+    <font>
+      <i val="1"/>
+      <color rgb="006B7280"/>
+      <sz val="8"/>
+    </font>
   </fonts>
   <fills count="76">
     <fill>
@@ -1691,7 +1697,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="412">
+  <borders count="414">
     <border>
       <left/>
       <right/>
@@ -6589,6 +6595,28 @@
       </top>
       <bottom style="thin">
         <color rgb="FFB8C2CC"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color theme="0" tint="-0.3499862666707358"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color theme="4" tint="0.5999633777886288"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color theme="0" tint="-0.3499862666707358"/>
+      </right>
+      <top style="thin">
+        <color theme="4" tint="0.5999633777886288"/>
+      </top>
+      <bottom style="thin">
+        <color theme="4" tint="0.5999633777886288"/>
       </bottom>
     </border>
   </borders>
@@ -6599,7 +6627,7 @@
     <xf numFmtId="0" fontId="28" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1319">
+  <cellXfs count="1334">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
@@ -9851,6 +9879,51 @@
     <xf numFmtId="167" fontId="0" fillId="0" borderId="33" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="32" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="29" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="53" fillId="30" borderId="412" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="413" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="413" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="60" fillId="22" borderId="33" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="172" fontId="60" fillId="22" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="172" fontId="60" fillId="22" borderId="107" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="172" fontId="1" fillId="0" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="172" fontId="1" fillId="0" borderId="65" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="268" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="172" fontId="39" fillId="3" borderId="268" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="172" fontId="39" fillId="3" borderId="116" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="20" borderId="293" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="293" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="170" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="5">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -9982,439 +10055,6 @@
 </styleSheet>
 </file>
 
-<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
-  <chart>
-    <title>
-      <tx>
-        <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0"/>
-          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-            <a:pPr>
-              <a:defRPr lang="es-CO" sz="1800" b="1" strike="noStrike" spc="-1">
-                <a:solidFill>
-                  <a:srgbClr val="000000"/>
-                </a:solidFill>
-                <a:latin typeface="Calibri"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:r>
-              <a:rPr lang="es-CO" sz="1800" b="1" strike="noStrike" spc="-1">
-                <a:solidFill>
-                  <a:srgbClr val="000000"/>
-                </a:solidFill>
-                <a:latin typeface="Calibri"/>
-              </a:rPr>
-              <a:t>Costo directo por capítulo (COP)</a:t>
-            </a:r>
-          </a:p>
-        </rich>
-      </tx>
-      <overlay val="0"/>
-      <spPr>
-        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="0">
-          <a:noFill/>
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </title>
-    <plotArea>
-      <layout/>
-      <barChart>
-        <barDir val="col"/>
-        <grouping val="clustered"/>
-        <varyColors val="0"/>
-        <ser>
-          <idx val="0"/>
-          <order val="0"/>
-          <tx>
-            <strRef>
-              <f>Resumen!$C$11</f>
-              <strCache>
-                <ptCount val="1"/>
-                <pt idx="0">
-                  <v>Valor (COP)</v>
-                </pt>
-              </strCache>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:srgbClr val="4F81BD"/>
-            </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="0">
-              <a:noFill/>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <invertIfNegative val="0"/>
-          <dLbls>
-            <spPr>
-              <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:noFill/>
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-            <txPr>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" wrap="square"/>
-              <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:pPr>
-                  <a:defRPr sz="1000" b="0" strike="noStrike" spc="-1">
-                    <a:solidFill>
-                      <a:srgbClr val="000000"/>
-                    </a:solidFill>
-                    <a:latin typeface="Arial"/>
-                  </a:defRPr>
-                </a:pPr>
-                <a:r>
-                  <a:t>None</a:t>
-                </a:r>
-                <a:endParaRPr lang="es-CO"/>
-              </a:p>
-            </txPr>
-            <dLblPos val="outEnd"/>
-            <showLegendKey val="0"/>
-            <showVal val="0"/>
-            <showCatName val="0"/>
-            <showSerName val="0"/>
-            <showPercent val="0"/>
-            <showBubbleSize val="1"/>
-            <showLeaderLines val="0"/>
-          </dLbls>
-          <cat>
-            <strRef>
-              <f>Resumen!$A$12:$A$25</f>
-              <strCache>
-                <ptCount val="14"/>
-                <pt idx="0">
-                  <v>1</v>
-                </pt>
-                <pt idx="1">
-                  <v>2</v>
-                </pt>
-                <pt idx="2">
-                  <v>3</v>
-                </pt>
-                <pt idx="3">
-                  <v>4</v>
-                </pt>
-                <pt idx="4">
-                  <v>5</v>
-                </pt>
-                <pt idx="5">
-                  <v>6</v>
-                </pt>
-                <pt idx="6">
-                  <v>7</v>
-                </pt>
-                <pt idx="7">
-                  <v>8</v>
-                </pt>
-                <pt idx="8">
-                  <v>9</v>
-                </pt>
-                <pt idx="9">
-                  <v>10</v>
-                </pt>
-                <pt idx="10">
-                  <v>11</v>
-                </pt>
-                <pt idx="11">
-                  <v>12</v>
-                </pt>
-                <pt idx="12">
-                  <v>13</v>
-                </pt>
-                <pt idx="13">
-                  <v>14</v>
-                </pt>
-              </strCache>
-            </strRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>Resumen!$C$12:$C$25</f>
-              <numCache>
-                <formatCode>"$ "#,##0</formatCode>
-                <ptCount val="14"/>
-                <pt idx="0">
-                  <v>0</v>
-                </pt>
-                <pt idx="1">
-                  <v>0</v>
-                </pt>
-                <pt idx="2">
-                  <v>0</v>
-                </pt>
-                <pt idx="3">
-                  <v>0</v>
-                </pt>
-                <pt idx="4">
-                  <v>0</v>
-                </pt>
-                <pt idx="5">
-                  <v>0</v>
-                </pt>
-                <pt idx="6">
-                  <v>0</v>
-                </pt>
-                <pt idx="7">
-                  <v>0</v>
-                </pt>
-                <pt idx="8">
-                  <v>0</v>
-                </pt>
-                <pt idx="9">
-                  <v>0</v>
-                </pt>
-                <pt idx="10">
-                  <v>0</v>
-                </pt>
-                <pt idx="11">
-                  <v>0</v>
-                </pt>
-                <pt idx="12">
-                  <v>0</v>
-                </pt>
-                <pt idx="13">
-                  <v>0</v>
-                </pt>
-              </numCache>
-            </numRef>
-          </val>
-        </ser>
-        <dLbls>
-          <showLegendKey val="0"/>
-          <showVal val="0"/>
-          <showCatName val="0"/>
-          <showSerName val="0"/>
-          <showPercent val="0"/>
-          <showBubbleSize val="0"/>
-        </dLbls>
-        <gapWidth val="150"/>
-        <axId val="50050775"/>
-        <axId val="41416401"/>
-      </barChart>
-      <catAx>
-        <axId val="50050775"/>
-        <scaling>
-          <orientation val="minMax"/>
-        </scaling>
-        <delete val="0"/>
-        <axPos val="b"/>
-        <title>
-          <tx>
-            <rich>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0"/>
-              <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:pPr>
-                  <a:defRPr lang="es-CO" sz="1000" b="1" strike="noStrike" spc="-1">
-                    <a:solidFill>
-                      <a:srgbClr val="000000"/>
-                    </a:solidFill>
-                    <a:latin typeface="Calibri"/>
-                  </a:defRPr>
-                </a:pPr>
-                <a:r>
-                  <a:rPr lang="es-CO" sz="1000" b="1" strike="noStrike" spc="-1">
-                    <a:solidFill>
-                      <a:srgbClr val="000000"/>
-                    </a:solidFill>
-                    <a:latin typeface="Calibri"/>
-                  </a:rPr>
-                  <a:t>Capítulo</a:t>
-                </a:r>
-              </a:p>
-            </rich>
-          </tx>
-          <overlay val="0"/>
-          <spPr>
-            <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="0">
-              <a:noFill/>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-        </title>
-        <numFmt formatCode="General" sourceLinked="0"/>
-        <majorTickMark val="none"/>
-        <minorTickMark val="none"/>
-        <tickLblPos val="nextTo"/>
-        <spPr>
-          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9360">
-            <a:solidFill>
-              <a:srgbClr val="878787"/>
-            </a:solidFill>
-            <a:prstDash val="solid"/>
-            <a:round/>
-          </a:ln>
-        </spPr>
-        <txPr>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-            <a:pPr>
-              <a:defRPr sz="1000" b="0" strike="noStrike" spc="-1">
-                <a:solidFill>
-                  <a:srgbClr val="000000"/>
-                </a:solidFill>
-                <a:latin typeface="Calibri"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:r>
-              <a:t>None</a:t>
-            </a:r>
-            <a:endParaRPr lang="es-CO"/>
-          </a:p>
-        </txPr>
-        <crossAx val="41416401"/>
-        <crosses val="autoZero"/>
-        <auto val="1"/>
-        <lblAlgn val="ctr"/>
-        <lblOffset val="100"/>
-        <noMultiLvlLbl val="0"/>
-      </catAx>
-      <valAx>
-        <axId val="41416401"/>
-        <scaling>
-          <orientation val="minMax"/>
-        </scaling>
-        <delete val="0"/>
-        <axPos val="l"/>
-        <majorGridlines>
-          <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9360">
-              <a:solidFill>
-                <a:srgbClr val="878787"/>
-              </a:solidFill>
-              <a:prstDash val="solid"/>
-              <a:round/>
-            </a:ln>
-          </spPr>
-        </majorGridlines>
-        <title>
-          <tx>
-            <rich>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="-5400000"/>
-              <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:pPr>
-                  <a:defRPr lang="es-CO" sz="1000" b="1" strike="noStrike" spc="-1">
-                    <a:solidFill>
-                      <a:srgbClr val="000000"/>
-                    </a:solidFill>
-                    <a:latin typeface="Calibri"/>
-                  </a:defRPr>
-                </a:pPr>
-                <a:r>
-                  <a:rPr lang="es-CO" sz="1000" b="1" strike="noStrike" spc="-1">
-                    <a:solidFill>
-                      <a:srgbClr val="000000"/>
-                    </a:solidFill>
-                    <a:latin typeface="Calibri"/>
-                  </a:rPr>
-                  <a:t>COP</a:t>
-                </a:r>
-              </a:p>
-            </rich>
-          </tx>
-          <overlay val="0"/>
-          <spPr>
-            <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="0">
-              <a:noFill/>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-        </title>
-        <numFmt formatCode="&quot;$ &quot;#,##0" sourceLinked="0"/>
-        <majorTickMark val="none"/>
-        <minorTickMark val="none"/>
-        <tickLblPos val="nextTo"/>
-        <spPr>
-          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9360">
-            <a:solidFill>
-              <a:srgbClr val="878787"/>
-            </a:solidFill>
-            <a:prstDash val="solid"/>
-            <a:round/>
-          </a:ln>
-        </spPr>
-        <txPr>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-            <a:pPr>
-              <a:defRPr sz="1000" b="0" strike="noStrike" spc="-1">
-                <a:solidFill>
-                  <a:srgbClr val="000000"/>
-                </a:solidFill>
-                <a:latin typeface="Calibri"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:r>
-              <a:t>None</a:t>
-            </a:r>
-            <a:endParaRPr lang="es-CO"/>
-          </a:p>
-        </txPr>
-        <crossAx val="50050775"/>
-        <crosses val="autoZero"/>
-        <crossBetween val="between"/>
-      </valAx>
-    </plotArea>
-    <legend>
-      <legendPos val="r"/>
-      <overlay val="0"/>
-      <spPr>
-        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="0">
-          <a:noFill/>
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-      <txPr>
-        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:pPr>
-            <a:defRPr sz="1000" b="0" strike="noStrike" spc="-1">
-              <a:solidFill>
-                <a:srgbClr val="000000"/>
-              </a:solidFill>
-              <a:latin typeface="Calibri"/>
-            </a:defRPr>
-          </a:pPr>
-          <a:r>
-            <a:t>None</a:t>
-          </a:r>
-          <a:endParaRPr lang="es-CO"/>
-        </a:p>
-      </txPr>
-    </legend>
-    <plotVisOnly val="1"/>
-    <dispBlanksAs val="gap"/>
-  </chart>
-  <spPr>
-    <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-      <a:srgbClr val="FFFFFF"/>
-    </a:solidFill>
-    <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9360">
-      <a:solidFill>
-        <a:srgbClr val="D9D9D9"/>
-      </a:solidFill>
-      <a:prstDash val="solid"/>
-      <a:round/>
-    </a:ln>
-  </spPr>
-</chartSpace>
-</file>
-
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <xdr:twoCellAnchor editAs="oneCell">
@@ -10460,7 +10100,7 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
@@ -10505,7 +10145,7 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing19.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
@@ -11290,7 +10930,6 @@
     <mergeCell ref="C16:E16"/>
     <mergeCell ref="A39:E39"/>
     <mergeCell ref="B9:E9"/>
-    <mergeCell ref="C29:E29"/>
     <mergeCell ref="D10:E10"/>
     <mergeCell ref="C31:E31"/>
     <mergeCell ref="C22:E22"/>
@@ -11322,12 +10961,13 @@
     <mergeCell ref="A38:E38"/>
     <mergeCell ref="B5:C5"/>
     <mergeCell ref="A28:E28"/>
+    <mergeCell ref="A40:E40"/>
     <mergeCell ref="C26:E26"/>
     <mergeCell ref="A13:E13"/>
-    <mergeCell ref="C35:E35"/>
+    <mergeCell ref="C29:E29"/>
     <mergeCell ref="A44:E44"/>
     <mergeCell ref="C20:E20"/>
-    <mergeCell ref="A40:E40"/>
+    <mergeCell ref="C35:E35"/>
     <mergeCell ref="B4:C4"/>
     <mergeCell ref="C25:E25"/>
   </mergeCells>
@@ -11337,7 +10977,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="FF2E7D32"/>
@@ -16350,7 +15990,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="FF7030A0"/>
@@ -17543,7 +17183,7 @@
         </is>
       </c>
       <c r="J49" s="581" t="n"/>
-      <c r="K49" s="1149" t="inlineStr">
+      <c r="K49" s="1319" t="inlineStr">
         <is>
           <t>OBSERVACIONES</t>
         </is>
@@ -17559,14 +17199,14 @@
       <c r="D50" s="530" t="n"/>
       <c r="E50" s="530" t="n"/>
       <c r="F50" s="530" t="n"/>
-      <c r="G50" s="1199" t="n"/>
+      <c r="G50" s="1150" t="n"/>
       <c r="H50" s="530" t="n"/>
       <c r="I50" s="1079" t="n"/>
       <c r="J50" s="1079" t="n"/>
-      <c r="K50" s="1181" t="n"/>
-      <c r="L50" s="1079" t="n"/>
-      <c r="M50" s="1079" t="n"/>
-      <c r="N50" s="1115" t="n"/>
+      <c r="K50" s="1320" t="n"/>
+      <c r="L50" s="530" t="n"/>
+      <c r="M50" s="530" t="n"/>
+      <c r="N50" s="579" t="n"/>
     </row>
     <row r="51">
       <c r="A51" s="1136" t="n"/>
@@ -17575,14 +17215,14 @@
       <c r="D51" s="530" t="n"/>
       <c r="E51" s="530" t="n"/>
       <c r="F51" s="530" t="n"/>
-      <c r="G51" s="1199" t="n"/>
+      <c r="G51" s="1150" t="n"/>
       <c r="H51" s="530" t="n"/>
       <c r="I51" s="1200" t="n"/>
       <c r="J51" s="1088" t="n"/>
-      <c r="K51" s="1175" t="n"/>
-      <c r="L51" s="1088" t="n"/>
-      <c r="M51" s="1088" t="n"/>
-      <c r="N51" s="1176" t="n"/>
+      <c r="K51" s="1321" t="n"/>
+      <c r="L51" s="530" t="n"/>
+      <c r="M51" s="530" t="n"/>
+      <c r="N51" s="579" t="n"/>
     </row>
     <row r="52">
       <c r="A52" s="1143" t="n"/>
@@ -17591,11 +17231,11 @@
       <c r="D52" s="530" t="n"/>
       <c r="E52" s="530" t="n"/>
       <c r="F52" s="530" t="n"/>
-      <c r="G52" s="1199" t="n"/>
+      <c r="G52" s="1150" t="n"/>
       <c r="H52" s="530" t="n"/>
       <c r="I52" s="1153" t="n"/>
       <c r="J52" s="530" t="n"/>
-      <c r="K52" s="1164" t="n"/>
+      <c r="K52" s="1321" t="n"/>
       <c r="L52" s="530" t="n"/>
       <c r="M52" s="530" t="n"/>
       <c r="N52" s="579" t="n"/>
@@ -17611,7 +17251,7 @@
       <c r="H53" s="530" t="n"/>
       <c r="I53" s="1153" t="n"/>
       <c r="J53" s="530" t="n"/>
-      <c r="K53" s="1164" t="n"/>
+      <c r="K53" s="1321" t="n"/>
       <c r="L53" s="530" t="n"/>
       <c r="M53" s="530" t="n"/>
       <c r="N53" s="579" t="n"/>
@@ -17628,7 +17268,7 @@
       <c r="H54" s="530" t="n"/>
       <c r="I54" s="1153" t="n"/>
       <c r="J54" s="530" t="n"/>
-      <c r="K54" s="1164" t="n"/>
+      <c r="K54" s="1321" t="n"/>
       <c r="L54" s="530" t="n"/>
       <c r="M54" s="530" t="n"/>
       <c r="N54" s="579" t="n"/>
@@ -17644,7 +17284,7 @@
       <c r="H55" s="530" t="n"/>
       <c r="I55" s="1153" t="n"/>
       <c r="J55" s="530" t="n"/>
-      <c r="K55" s="1164" t="n"/>
+      <c r="K55" s="1321" t="n"/>
       <c r="L55" s="530" t="n"/>
       <c r="M55" s="530" t="n"/>
       <c r="N55" s="579" t="n"/>
@@ -17660,7 +17300,7 @@
       <c r="H56" s="530" t="n"/>
       <c r="I56" s="1153" t="n"/>
       <c r="J56" s="530" t="n"/>
-      <c r="K56" s="1164" t="n"/>
+      <c r="K56" s="1321" t="n"/>
       <c r="L56" s="530" t="n"/>
       <c r="M56" s="530" t="n"/>
       <c r="N56" s="579" t="n"/>
@@ -17676,7 +17316,7 @@
       <c r="H57" s="530" t="n"/>
       <c r="I57" s="1153" t="n"/>
       <c r="J57" s="530" t="n"/>
-      <c r="K57" s="1164" t="n"/>
+      <c r="K57" s="1321" t="n"/>
       <c r="L57" s="530" t="n"/>
       <c r="M57" s="530" t="n"/>
       <c r="N57" s="579" t="n"/>
@@ -17692,7 +17332,7 @@
       <c r="H58" s="530" t="n"/>
       <c r="I58" s="1153" t="n"/>
       <c r="J58" s="530" t="n"/>
-      <c r="K58" s="1164" t="n"/>
+      <c r="K58" s="1321" t="n"/>
       <c r="L58" s="530" t="n"/>
       <c r="M58" s="530" t="n"/>
       <c r="N58" s="579" t="n"/>
@@ -17744,12 +17384,12 @@
       </c>
       <c r="B61" s="530" t="n"/>
       <c r="C61" s="530" t="n"/>
-      <c r="D61" s="449" t="inlineStr">
+      <c r="D61" s="1322" t="inlineStr">
         <is>
           <t>FECHA</t>
         </is>
       </c>
-      <c r="E61" s="1189" t="inlineStr">
+      <c r="E61" s="1323" t="inlineStr">
         <is>
           <t>VALOR ($)</t>
         </is>
@@ -17769,7 +17409,7 @@
         </is>
       </c>
       <c r="L61" s="581" t="n"/>
-      <c r="M61" s="1212" t="inlineStr">
+      <c r="M61" s="1324" t="inlineStr">
         <is>
           <t>VALOR ($)</t>
         </is>
@@ -17780,8 +17420,8 @@
       <c r="A62" s="1154" t="n"/>
       <c r="B62" s="530" t="n"/>
       <c r="C62" s="530" t="n"/>
-      <c r="D62" s="1171" t="n"/>
-      <c r="E62" s="1137" t="n"/>
+      <c r="D62" s="1325" t="n"/>
+      <c r="E62" s="1326" t="n"/>
       <c r="F62" s="530" t="n"/>
       <c r="G62" s="448" t="n"/>
       <c r="H62" s="1144" t="n"/>
@@ -17789,15 +17429,15 @@
       <c r="J62" s="530" t="n"/>
       <c r="K62" s="1171" t="n"/>
       <c r="L62" s="530" t="n"/>
-      <c r="M62" s="1165" t="n"/>
+      <c r="M62" s="1327" t="n"/>
       <c r="N62" s="579" t="n"/>
     </row>
     <row r="63">
       <c r="A63" s="1154" t="n"/>
       <c r="B63" s="530" t="n"/>
       <c r="C63" s="530" t="n"/>
-      <c r="D63" s="1171" t="n"/>
-      <c r="E63" s="1137" t="n"/>
+      <c r="D63" s="1325" t="n"/>
+      <c r="E63" s="1326" t="n"/>
       <c r="F63" s="530" t="n"/>
       <c r="G63" s="448" t="n"/>
       <c r="H63" s="1144" t="n"/>
@@ -17805,15 +17445,15 @@
       <c r="J63" s="530" t="n"/>
       <c r="K63" s="1171" t="n"/>
       <c r="L63" s="530" t="n"/>
-      <c r="M63" s="1165" t="n"/>
+      <c r="M63" s="1327" t="n"/>
       <c r="N63" s="579" t="n"/>
     </row>
     <row r="64">
       <c r="A64" s="1154" t="n"/>
       <c r="B64" s="530" t="n"/>
       <c r="C64" s="530" t="n"/>
-      <c r="D64" s="1171" t="n"/>
-      <c r="E64" s="1137" t="n"/>
+      <c r="D64" s="1325" t="n"/>
+      <c r="E64" s="1326" t="n"/>
       <c r="F64" s="530" t="n"/>
       <c r="G64" s="448" t="n"/>
       <c r="H64" s="1144" t="n"/>
@@ -17821,15 +17461,15 @@
       <c r="J64" s="530" t="n"/>
       <c r="K64" s="1171" t="n"/>
       <c r="L64" s="530" t="n"/>
-      <c r="M64" s="1165" t="n"/>
+      <c r="M64" s="1327" t="n"/>
       <c r="N64" s="579" t="n"/>
     </row>
     <row r="65">
       <c r="A65" s="1154" t="n"/>
       <c r="B65" s="530" t="n"/>
       <c r="C65" s="530" t="n"/>
-      <c r="D65" s="1171" t="n"/>
-      <c r="E65" s="1137" t="n"/>
+      <c r="D65" s="1325" t="n"/>
+      <c r="E65" s="1326" t="n"/>
       <c r="F65" s="530" t="n"/>
       <c r="G65" s="448" t="n"/>
       <c r="H65" s="1144" t="n"/>
@@ -17837,15 +17477,15 @@
       <c r="J65" s="530" t="n"/>
       <c r="K65" s="1171" t="n"/>
       <c r="L65" s="530" t="n"/>
-      <c r="M65" s="1165" t="n"/>
+      <c r="M65" s="1327" t="n"/>
       <c r="N65" s="579" t="n"/>
     </row>
     <row r="66">
       <c r="A66" s="1154" t="n"/>
       <c r="B66" s="530" t="n"/>
       <c r="C66" s="530" t="n"/>
-      <c r="D66" s="1171" t="n"/>
-      <c r="E66" s="1137" t="n"/>
+      <c r="D66" s="1325" t="n"/>
+      <c r="E66" s="1326" t="n"/>
       <c r="F66" s="530" t="n"/>
       <c r="G66" s="448" t="n"/>
       <c r="H66" s="1144" t="n"/>
@@ -17853,7 +17493,7 @@
       <c r="J66" s="530" t="n"/>
       <c r="K66" s="1171" t="n"/>
       <c r="L66" s="530" t="n"/>
-      <c r="M66" s="1165" t="n"/>
+      <c r="M66" s="1327" t="n"/>
       <c r="N66" s="579" t="n"/>
     </row>
     <row r="67" ht="14.4" customHeight="1" s="1223">
@@ -17865,7 +17505,7 @@
       <c r="B67" s="1169" t="n"/>
       <c r="C67" s="1169" t="n"/>
       <c r="D67" s="1169" t="n"/>
-      <c r="E67" s="1168">
+      <c r="E67" s="1329">
         <f>SUM(E62:F66)</f>
         <v/>
       </c>
@@ -17880,7 +17520,7 @@
       <c r="J67" s="1018" t="n"/>
       <c r="K67" s="1018" t="n"/>
       <c r="L67" s="1018" t="n"/>
-      <c r="M67" s="1190">
+      <c r="M67" s="1330">
         <f>SUM(M62:N66)</f>
         <v/>
       </c>
@@ -17931,7 +17571,7 @@
       <c r="N70" s="579" t="n"/>
     </row>
     <row r="71" ht="14.25" customHeight="1" s="1223">
-      <c r="A71" s="1158" t="inlineStr">
+      <c r="A71" s="1331" t="inlineStr">
         <is>
           <t>OBSERVACIONES HSE</t>
         </is>
@@ -17939,7 +17579,7 @@
       <c r="N71" s="546" t="n"/>
     </row>
     <row r="72">
-      <c r="A72" s="1203" t="n"/>
+      <c r="A72" s="1332" t="n"/>
       <c r="N72" s="546" t="n"/>
     </row>
     <row r="73">
@@ -18039,33 +17679,26 @@
       <c r="N85" s="741" t="n"/>
     </row>
     <row r="86">
-      <c r="A86" s="1020" t="n"/>
-      <c r="G86" s="741" t="n"/>
-      <c r="H86" s="739" t="n"/>
-      <c r="N86" s="741" t="n"/>
+      <c r="A86" s="1160" t="n"/>
+      <c r="B86" s="743" t="n"/>
+      <c r="C86" s="743" t="n"/>
+      <c r="D86" s="743" t="n"/>
+      <c r="E86" s="743" t="n"/>
+      <c r="F86" s="743" t="n"/>
+      <c r="G86" s="744" t="n"/>
+      <c r="H86" s="742" t="n"/>
+      <c r="I86" s="743" t="n"/>
+      <c r="J86" s="743" t="n"/>
+      <c r="K86" s="743" t="n"/>
+      <c r="L86" s="743" t="n"/>
+      <c r="M86" s="743" t="n"/>
+      <c r="N86" s="744" t="n"/>
     </row>
     <row r="87">
-      <c r="A87" s="1020" t="n"/>
-      <c r="G87" s="741" t="n"/>
-      <c r="H87" s="739" t="n"/>
-      <c r="N87" s="741" t="n"/>
-    </row>
-    <row r="88">
-      <c r="A88" s="1160" t="n"/>
-      <c r="B88" s="743" t="n"/>
-      <c r="C88" s="743" t="n"/>
-      <c r="D88" s="743" t="n"/>
-      <c r="E88" s="743" t="n"/>
-      <c r="F88" s="743" t="n"/>
-      <c r="G88" s="744" t="n"/>
-      <c r="H88" s="742" t="n"/>
-      <c r="I88" s="743" t="n"/>
-      <c r="J88" s="743" t="n"/>
-      <c r="K88" s="743" t="n"/>
-      <c r="L88" s="743" t="n"/>
-      <c r="M88" s="743" t="n"/>
-      <c r="N88" s="744" t="n"/>
-    </row>
+      <c r="A87" s="1333" t="n"/>
+      <c r="H87" s="1333" t="n"/>
+    </row>
+    <row r="88"/>
     <row r="89">
       <c r="A89" s="1159" t="inlineStr">
         <is>
@@ -18163,33 +17796,26 @@
       <c r="N101" s="741" t="n"/>
     </row>
     <row r="102">
-      <c r="A102" s="1020" t="n"/>
-      <c r="G102" s="741" t="n"/>
-      <c r="H102" s="739" t="n"/>
-      <c r="N102" s="741" t="n"/>
+      <c r="A102" s="1160" t="n"/>
+      <c r="B102" s="743" t="n"/>
+      <c r="C102" s="743" t="n"/>
+      <c r="D102" s="743" t="n"/>
+      <c r="E102" s="743" t="n"/>
+      <c r="F102" s="743" t="n"/>
+      <c r="G102" s="744" t="n"/>
+      <c r="H102" s="742" t="n"/>
+      <c r="I102" s="743" t="n"/>
+      <c r="J102" s="743" t="n"/>
+      <c r="K102" s="743" t="n"/>
+      <c r="L102" s="743" t="n"/>
+      <c r="M102" s="743" t="n"/>
+      <c r="N102" s="744" t="n"/>
     </row>
     <row r="103">
-      <c r="A103" s="1020" t="n"/>
-      <c r="G103" s="741" t="n"/>
-      <c r="H103" s="739" t="n"/>
-      <c r="N103" s="741" t="n"/>
-    </row>
-    <row r="104">
-      <c r="A104" s="1160" t="n"/>
-      <c r="B104" s="743" t="n"/>
-      <c r="C104" s="743" t="n"/>
-      <c r="D104" s="743" t="n"/>
-      <c r="E104" s="743" t="n"/>
-      <c r="F104" s="743" t="n"/>
-      <c r="G104" s="744" t="n"/>
-      <c r="H104" s="742" t="n"/>
-      <c r="I104" s="743" t="n"/>
-      <c r="J104" s="743" t="n"/>
-      <c r="K104" s="743" t="n"/>
-      <c r="L104" s="743" t="n"/>
-      <c r="M104" s="743" t="n"/>
-      <c r="N104" s="744" t="n"/>
-    </row>
+      <c r="A103" s="1333" t="n"/>
+      <c r="H103" s="1333" t="n"/>
+    </row>
+    <row r="104"/>
     <row r="105">
       <c r="A105" s="1159" t="inlineStr">
         <is>
@@ -18287,33 +17913,26 @@
       <c r="N117" s="741" t="n"/>
     </row>
     <row r="118">
-      <c r="A118" s="1020" t="n"/>
-      <c r="G118" s="741" t="n"/>
-      <c r="H118" s="739" t="n"/>
-      <c r="N118" s="741" t="n"/>
+      <c r="A118" s="1160" t="n"/>
+      <c r="B118" s="743" t="n"/>
+      <c r="C118" s="743" t="n"/>
+      <c r="D118" s="743" t="n"/>
+      <c r="E118" s="743" t="n"/>
+      <c r="F118" s="743" t="n"/>
+      <c r="G118" s="744" t="n"/>
+      <c r="H118" s="742" t="n"/>
+      <c r="I118" s="743" t="n"/>
+      <c r="J118" s="743" t="n"/>
+      <c r="K118" s="743" t="n"/>
+      <c r="L118" s="743" t="n"/>
+      <c r="M118" s="743" t="n"/>
+      <c r="N118" s="744" t="n"/>
     </row>
     <row r="119">
-      <c r="A119" s="1020" t="n"/>
-      <c r="G119" s="741" t="n"/>
-      <c r="H119" s="739" t="n"/>
-      <c r="N119" s="741" t="n"/>
-    </row>
-    <row r="120">
-      <c r="A120" s="1160" t="n"/>
-      <c r="B120" s="743" t="n"/>
-      <c r="C120" s="743" t="n"/>
-      <c r="D120" s="743" t="n"/>
-      <c r="E120" s="743" t="n"/>
-      <c r="F120" s="743" t="n"/>
-      <c r="G120" s="744" t="n"/>
-      <c r="H120" s="742" t="n"/>
-      <c r="I120" s="743" t="n"/>
-      <c r="J120" s="743" t="n"/>
-      <c r="K120" s="743" t="n"/>
-      <c r="L120" s="743" t="n"/>
-      <c r="M120" s="743" t="n"/>
-      <c r="N120" s="744" t="n"/>
-    </row>
+      <c r="A119" s="1333" t="n"/>
+      <c r="H119" s="1333" t="n"/>
+    </row>
+    <row r="120"/>
     <row r="121">
       <c r="A121" s="1205" t="n"/>
       <c r="G121" s="741" t="n"/>
@@ -18483,7 +18102,7 @@
       <c r="O131" s="25" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="215">
+  <mergeCells count="221">
     <mergeCell ref="C52:F52"/>
     <mergeCell ref="A128:A129"/>
     <mergeCell ref="B124:D125"/>
@@ -18496,11 +18115,11 @@
     <mergeCell ref="E23:E24"/>
     <mergeCell ref="A21:C21"/>
     <mergeCell ref="F124:I125"/>
-    <mergeCell ref="H105:N120"/>
     <mergeCell ref="A26:C26"/>
     <mergeCell ref="A13:D13"/>
     <mergeCell ref="E64:F64"/>
     <mergeCell ref="A54:B54"/>
+    <mergeCell ref="H105:N118"/>
     <mergeCell ref="H66:J66"/>
     <mergeCell ref="H22:J22"/>
     <mergeCell ref="F126:I127"/>
@@ -18522,7 +18141,6 @@
     <mergeCell ref="G58:H58"/>
     <mergeCell ref="C54:F54"/>
     <mergeCell ref="A71:N71"/>
-    <mergeCell ref="A73:G88"/>
     <mergeCell ref="A16:D16"/>
     <mergeCell ref="I52:J52"/>
     <mergeCell ref="A34:C34"/>
@@ -18536,7 +18154,8 @@
     <mergeCell ref="M62:N62"/>
     <mergeCell ref="J46:N46"/>
     <mergeCell ref="H23:H24"/>
-    <mergeCell ref="A105:G120"/>
+    <mergeCell ref="A89:G102"/>
+    <mergeCell ref="H103:N104"/>
     <mergeCell ref="H64:J64"/>
     <mergeCell ref="J39:N39"/>
     <mergeCell ref="F128:I129"/>
@@ -18579,9 +18198,11 @@
     <mergeCell ref="H60:N60"/>
     <mergeCell ref="E124:E125"/>
     <mergeCell ref="K50:N50"/>
+    <mergeCell ref="H89:N102"/>
     <mergeCell ref="K128:N129"/>
     <mergeCell ref="E1:N5"/>
     <mergeCell ref="A52:B52"/>
+    <mergeCell ref="H87:N88"/>
     <mergeCell ref="K56:N56"/>
     <mergeCell ref="K66:L66"/>
     <mergeCell ref="D23:D24"/>
@@ -18592,8 +18213,10 @@
     <mergeCell ref="M63:N63"/>
     <mergeCell ref="K52:N52"/>
     <mergeCell ref="D21:F21"/>
+    <mergeCell ref="A105:G118"/>
     <mergeCell ref="A23:C24"/>
     <mergeCell ref="A25:C25"/>
+    <mergeCell ref="A119:G120"/>
     <mergeCell ref="H67:L67"/>
     <mergeCell ref="J44:N44"/>
     <mergeCell ref="L14:N14"/>
@@ -18603,7 +18226,7 @@
     <mergeCell ref="M67:N67"/>
     <mergeCell ref="M9:N9"/>
     <mergeCell ref="J28:N28"/>
-    <mergeCell ref="A89:G104"/>
+    <mergeCell ref="A103:G104"/>
     <mergeCell ref="J37:N37"/>
     <mergeCell ref="C57:F57"/>
     <mergeCell ref="A42:C42"/>
@@ -18617,6 +18240,7 @@
     <mergeCell ref="F23:F24"/>
     <mergeCell ref="C58:F58"/>
     <mergeCell ref="A20:C20"/>
+    <mergeCell ref="H119:N120"/>
     <mergeCell ref="A55:B55"/>
     <mergeCell ref="A18:N18"/>
     <mergeCell ref="A28:C28"/>
@@ -18635,13 +18259,13 @@
     <mergeCell ref="D20:F20"/>
     <mergeCell ref="I15:K15"/>
     <mergeCell ref="A22:E22"/>
+    <mergeCell ref="H73:N86"/>
     <mergeCell ref="A64:C64"/>
     <mergeCell ref="J47:N47"/>
     <mergeCell ref="G51:H51"/>
     <mergeCell ref="H63:J63"/>
     <mergeCell ref="I51:J51"/>
     <mergeCell ref="A122:N122"/>
-    <mergeCell ref="H89:N104"/>
     <mergeCell ref="G54:H54"/>
     <mergeCell ref="J43:N43"/>
     <mergeCell ref="K65:L65"/>
@@ -18649,7 +18273,6 @@
     <mergeCell ref="A72:N72"/>
     <mergeCell ref="E15:H15"/>
     <mergeCell ref="G50:H50"/>
-    <mergeCell ref="H73:N88"/>
     <mergeCell ref="C51:F51"/>
     <mergeCell ref="I50:J50"/>
     <mergeCell ref="J33:N33"/>
@@ -18669,11 +18292,13 @@
     <mergeCell ref="A67:D67"/>
     <mergeCell ref="A33:C33"/>
     <mergeCell ref="C49:F49"/>
+    <mergeCell ref="A87:G88"/>
     <mergeCell ref="A126:A127"/>
     <mergeCell ref="G53:H53"/>
     <mergeCell ref="J36:N36"/>
     <mergeCell ref="I53:J53"/>
     <mergeCell ref="A35:C35"/>
+    <mergeCell ref="A73:G86"/>
     <mergeCell ref="J45:N45"/>
     <mergeCell ref="A123:D123"/>
     <mergeCell ref="A50:B50"/>

--- a/public/plantilla-mensual.xlsx
+++ b/public/plantilla-mensual.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Ficha Técnica del Proyecto" sheetId="1" r:id="rId1"/>
-    <sheet name="Presupuesto " sheetId="2" r:id="rId12"/>
-    <sheet name="Informe Mensual" sheetId="3" r:id="rId19"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ficha Técnica del Proyecto" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Presupuesto " sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Informe Mensual" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
+  <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1" iterateDelta="0.0001"/>
 </workbook>
 </file>
@@ -10461,7 +10462,7 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
@@ -10506,7 +10507,7 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing18.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
@@ -11291,7 +11292,6 @@
     <mergeCell ref="C16:E16"/>
     <mergeCell ref="A39:E39"/>
     <mergeCell ref="B9:E9"/>
-    <mergeCell ref="C29:E29"/>
     <mergeCell ref="D10:E10"/>
     <mergeCell ref="C31:E31"/>
     <mergeCell ref="C22:E22"/>
@@ -11324,8 +11324,9 @@
     <mergeCell ref="B5:C5"/>
     <mergeCell ref="A28:E28"/>
     <mergeCell ref="C26:E26"/>
+    <mergeCell ref="C35:E35"/>
     <mergeCell ref="A13:E13"/>
-    <mergeCell ref="C35:E35"/>
+    <mergeCell ref="C29:E29"/>
     <mergeCell ref="A44:E44"/>
     <mergeCell ref="C20:E20"/>
     <mergeCell ref="A40:E40"/>
@@ -11338,7 +11339,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="FF2E7D32"/>
@@ -16351,7 +16352,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="FF7030A0"/>
@@ -17048,7 +17049,7 @@
     </row>
     <row r="33">
       <c r="A33" s="1180">
-        <f>'Presupuesto '!B109</f>
+        <f>'Presupuesto '!B108</f>
         <v/>
       </c>
       <c r="B33" s="609" t="n"/>
@@ -17079,7 +17080,7 @@
     </row>
     <row r="34">
       <c r="A34" s="1180">
-        <f>'Presupuesto '!B123</f>
+        <f>'Presupuesto '!B122</f>
         <v/>
       </c>
       <c r="B34" s="609" t="n"/>
@@ -17110,7 +17111,7 @@
     </row>
     <row r="35">
       <c r="A35" s="1180">
-        <f>'Presupuesto '!B131</f>
+        <f>'Presupuesto '!B132</f>
         <v/>
       </c>
       <c r="B35" s="609" t="n"/>
@@ -17141,7 +17142,7 @@
     </row>
     <row r="36">
       <c r="A36" s="1180">
-        <f>'Presupuesto '!B142</f>
+        <f>'Presupuesto '!B143</f>
         <v/>
       </c>
       <c r="B36" s="609" t="n"/>
@@ -17172,7 +17173,7 @@
     </row>
     <row r="37">
       <c r="A37" s="1180">
-        <f>'Presupuesto '!B149</f>
+        <f>'Presupuesto '!B150</f>
         <v/>
       </c>
       <c r="B37" s="609" t="n"/>
@@ -17203,7 +17204,7 @@
     </row>
     <row r="38">
       <c r="A38" s="1180">
-        <f>'Presupuesto '!B164</f>
+        <f>'Presupuesto '!B165</f>
         <v/>
       </c>
       <c r="B38" s="609" t="n"/>
@@ -17234,7 +17235,7 @@
     </row>
     <row r="39">
       <c r="A39" s="1180">
-        <f>'Presupuesto '!B178</f>
+        <f>'Presupuesto '!B179</f>
         <v/>
       </c>
       <c r="B39" s="609" t="n"/>
@@ -17265,7 +17266,7 @@
     </row>
     <row r="40" ht="14.4" customHeight="1" s="550">
       <c r="A40" s="1183">
-        <f>'Presupuesto '!B187</f>
+        <f>'Presupuesto '!B188</f>
         <v/>
       </c>
       <c r="B40" s="567" t="n"/>
@@ -17296,7 +17297,7 @@
     </row>
     <row r="41">
       <c r="A41" s="1253">
-        <f>'Presupuesto '!B194</f>
+        <f>'Presupuesto '!B195</f>
         <v/>
       </c>
       <c r="B41" s="1064" t="n"/>
@@ -17327,7 +17328,7 @@
     </row>
     <row r="42" ht="14.4" customHeight="1" s="550">
       <c r="A42" s="1180">
-        <f>'Presupuesto '!B200</f>
+        <f>'Presupuesto '!B201</f>
         <v/>
       </c>
       <c r="B42" s="609" t="n"/>
@@ -17358,7 +17359,7 @@
     </row>
     <row r="43" ht="14.4" customHeight="1" s="550">
       <c r="A43" s="1183">
-        <f>'Presupuesto '!B214</f>
+        <f>'Presupuesto '!B215</f>
         <v/>
       </c>
       <c r="B43" s="567" t="n"/>
@@ -17389,7 +17390,7 @@
     </row>
     <row r="44" ht="14.4" customHeight="1" s="550">
       <c r="A44" s="1183">
-        <f>'Presupuesto '!B221</f>
+        <f>'Presupuesto '!B222</f>
         <v/>
       </c>
       <c r="B44" s="567" t="n"/>
@@ -17420,7 +17421,7 @@
     </row>
     <row r="45">
       <c r="A45" s="1183">
-        <f>'Presupuesto '!B229</f>
+        <f>'Presupuesto '!B230</f>
         <v/>
       </c>
       <c r="B45" s="567" t="n"/>
@@ -17451,7 +17452,7 @@
     </row>
     <row r="46" ht="14.4" customHeight="1" s="550">
       <c r="A46" s="1183">
-        <f>'Presupuesto '!B233</f>
+        <f>'Presupuesto '!B234</f>
         <v/>
       </c>
       <c r="B46" s="567" t="n"/>

--- a/public/plantilla-mensual.xlsx
+++ b/public/plantilla-mensual.xlsx
@@ -10418,32 +10418,32 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>69253</xdr:colOff>
-      <xdr:row>6</xdr:row>
-      <xdr:rowOff>174506</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="14" name="Imagen 2"/>
-        <xdr:cNvPicPr/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <twoCellAnchor editAs="oneCell">
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>0</row>
+      <rowOff>0</rowOff>
+    </from>
+    <to>
+      <col>1</col>
+      <colOff>69253</colOff>
+      <row>6</row>
+      <rowOff>174506</rowOff>
+    </to>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="14" name="Imagen 2"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
         <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
+      </blipFill>
+      <spPr>
         <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:off x="0" y="0"/>
           <a:ext cx="2952000" cy="1368000"/>
@@ -10455,40 +10455,40 @@
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
+      </spPr>
+    </pic>
+    <clientData/>
+  </twoCellAnchor>
+</wsDr>
 </file>
 
 <file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>2766370</xdr:colOff>
-      <xdr:row>8</xdr:row>
-      <xdr:rowOff>172889</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="Imagen 2"/>
-        <xdr:cNvPicPr/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <twoCellAnchor editAs="oneCell">
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>0</row>
+      <rowOff>0</rowOff>
+    </from>
+    <to>
+      <col>1</col>
+      <colOff>2766370</colOff>
+      <row>8</row>
+      <rowOff>172889</rowOff>
+    </to>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="3" name="Imagen 2"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
         <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
+      </blipFill>
+      <spPr>
         <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:off x="0" y="0"/>
           <a:ext cx="3312000" cy="1584000"/>
@@ -10500,40 +10500,40 @@
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
+      </spPr>
+    </pic>
+    <clientData/>
+  </twoCellAnchor>
+</wsDr>
 </file>
 
 <file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>130</xdr:row>
-      <xdr:rowOff>66959</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>725921</xdr:colOff>
-      <xdr:row>135</xdr:row>
-      <xdr:rowOff>28591</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="23" name="Image 2" descr="Picture"/>
-        <xdr:cNvPicPr/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <twoCellAnchor editAs="oneCell">
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>130</row>
+      <rowOff>66959</rowOff>
+    </from>
+    <to>
+      <col>6</col>
+      <colOff>725921</colOff>
+      <row>135</row>
+      <rowOff>28591</rowOff>
+    </to>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="23" name="Image 2" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
         <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
+      </blipFill>
+      <spPr>
         <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:off x="0" y="24049906"/>
           <a:ext cx="5328000" cy="864000"/>
@@ -10545,35 +10545,35 @@
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>749842</xdr:colOff>
-      <xdr:row>8</xdr:row>
-      <xdr:rowOff>148421</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="4" name="Imagen 2"/>
-        <xdr:cNvPicPr/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
+      </spPr>
+    </pic>
+    <clientData/>
+  </twoCellAnchor>
+  <twoCellAnchor editAs="oneCell">
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>0</row>
+      <rowOff>0</rowOff>
+    </from>
+    <to>
+      <col>3</col>
+      <colOff>749842</colOff>
+      <row>8</row>
+      <rowOff>148421</rowOff>
+    </to>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="4" name="Imagen 2"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
         <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
+      </blipFill>
+      <spPr>
         <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:off x="0" y="0"/>
           <a:ext cx="3096000" cy="1512000"/>
@@ -10585,11 +10585,11 @@
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
+      </spPr>
+    </pic>
+    <clientData/>
+  </twoCellAnchor>
+</wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -10773,6 +10773,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="FFFFFF00"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:E47"/>
@@ -11292,6 +11293,7 @@
     <mergeCell ref="C16:E16"/>
     <mergeCell ref="A39:E39"/>
     <mergeCell ref="B9:E9"/>
+    <mergeCell ref="C29:E29"/>
     <mergeCell ref="D10:E10"/>
     <mergeCell ref="C31:E31"/>
     <mergeCell ref="C22:E22"/>
@@ -11324,9 +11326,8 @@
     <mergeCell ref="B5:C5"/>
     <mergeCell ref="A28:E28"/>
     <mergeCell ref="C26:E26"/>
+    <mergeCell ref="A13:E13"/>
     <mergeCell ref="C35:E35"/>
-    <mergeCell ref="A13:E13"/>
-    <mergeCell ref="C29:E29"/>
     <mergeCell ref="A44:E44"/>
     <mergeCell ref="C20:E20"/>
     <mergeCell ref="A40:E40"/>
@@ -11343,6 +11344,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="FF2E7D32"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:F259"/>
@@ -16356,6 +16358,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="FF7030A0"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:S131"/>
@@ -16894,7 +16897,7 @@
     </row>
     <row r="28">
       <c r="A28" s="1180">
-        <f>'Presupuesto '!B51</f>
+        <f>'Presupuesto '!B52</f>
         <v/>
       </c>
       <c r="B28" s="609" t="n"/>
@@ -16925,7 +16928,7 @@
     </row>
     <row r="29">
       <c r="A29" s="1180">
-        <f>'Presupuesto '!B71</f>
+        <f>'Presupuesto '!B70</f>
         <v/>
       </c>
       <c r="B29" s="609" t="n"/>
@@ -16956,7 +16959,7 @@
     </row>
     <row r="30">
       <c r="A30" s="1180">
-        <f>'Presupuesto '!B83</f>
+        <f>'Presupuesto '!B82</f>
         <v/>
       </c>
       <c r="B30" s="609" t="n"/>
@@ -16987,7 +16990,7 @@
     </row>
     <row r="31">
       <c r="A31" s="1180">
-        <f>'Presupuesto '!B95</f>
+        <f>'Presupuesto '!B94</f>
         <v/>
       </c>
       <c r="B31" s="609" t="n"/>
@@ -17018,7 +17021,7 @@
     </row>
     <row r="32">
       <c r="A32" s="1180">
-        <f>'Presupuesto '!B102</f>
+        <f>'Presupuesto '!B101</f>
         <v/>
       </c>
       <c r="B32" s="609" t="n"/>
@@ -17049,7 +17052,7 @@
     </row>
     <row r="33">
       <c r="A33" s="1180">
-        <f>'Presupuesto '!B108</f>
+        <f>'Presupuesto '!B107</f>
         <v/>
       </c>
       <c r="B33" s="609" t="n"/>
@@ -17080,7 +17083,7 @@
     </row>
     <row r="34">
       <c r="A34" s="1180">
-        <f>'Presupuesto '!B122</f>
+        <f>'Presupuesto '!B121</f>
         <v/>
       </c>
       <c r="B34" s="609" t="n"/>
@@ -17111,7 +17114,7 @@
     </row>
     <row r="35">
       <c r="A35" s="1180">
-        <f>'Presupuesto '!B132</f>
+        <f>'Presupuesto '!B131</f>
         <v/>
       </c>
       <c r="B35" s="609" t="n"/>
@@ -17142,7 +17145,7 @@
     </row>
     <row r="36">
       <c r="A36" s="1180">
-        <f>'Presupuesto '!B143</f>
+        <f>'Presupuesto '!B142</f>
         <v/>
       </c>
       <c r="B36" s="609" t="n"/>
@@ -17173,7 +17176,7 @@
     </row>
     <row r="37">
       <c r="A37" s="1180">
-        <f>'Presupuesto '!B150</f>
+        <f>'Presupuesto '!B149</f>
         <v/>
       </c>
       <c r="B37" s="609" t="n"/>
@@ -17204,7 +17207,7 @@
     </row>
     <row r="38">
       <c r="A38" s="1180">
-        <f>'Presupuesto '!B165</f>
+        <f>'Presupuesto '!B164</f>
         <v/>
       </c>
       <c r="B38" s="609" t="n"/>
@@ -17235,7 +17238,7 @@
     </row>
     <row r="39">
       <c r="A39" s="1180">
-        <f>'Presupuesto '!B179</f>
+        <f>'Presupuesto '!B178</f>
         <v/>
       </c>
       <c r="B39" s="609" t="n"/>
@@ -17266,7 +17269,7 @@
     </row>
     <row r="40" ht="14.4" customHeight="1" s="550">
       <c r="A40" s="1183">
-        <f>'Presupuesto '!B188</f>
+        <f>'Presupuesto '!B187</f>
         <v/>
       </c>
       <c r="B40" s="567" t="n"/>
@@ -17297,7 +17300,7 @@
     </row>
     <row r="41">
       <c r="A41" s="1253">
-        <f>'Presupuesto '!B195</f>
+        <f>'Presupuesto '!B194</f>
         <v/>
       </c>
       <c r="B41" s="1064" t="n"/>
@@ -17328,7 +17331,7 @@
     </row>
     <row r="42" ht="14.4" customHeight="1" s="550">
       <c r="A42" s="1180">
-        <f>'Presupuesto '!B201</f>
+        <f>'Presupuesto '!B200</f>
         <v/>
       </c>
       <c r="B42" s="609" t="n"/>
@@ -17359,7 +17362,7 @@
     </row>
     <row r="43" ht="14.4" customHeight="1" s="550">
       <c r="A43" s="1183">
-        <f>'Presupuesto '!B215</f>
+        <f>'Presupuesto '!B214</f>
         <v/>
       </c>
       <c r="B43" s="567" t="n"/>
@@ -17390,7 +17393,7 @@
     </row>
     <row r="44" ht="14.4" customHeight="1" s="550">
       <c r="A44" s="1183">
-        <f>'Presupuesto '!B222</f>
+        <f>'Presupuesto '!B221</f>
         <v/>
       </c>
       <c r="B44" s="567" t="n"/>
@@ -17421,7 +17424,7 @@
     </row>
     <row r="45">
       <c r="A45" s="1183">
-        <f>'Presupuesto '!B230</f>
+        <f>'Presupuesto '!B229</f>
         <v/>
       </c>
       <c r="B45" s="567" t="n"/>
@@ -17452,7 +17455,7 @@
     </row>
     <row r="46" ht="14.4" customHeight="1" s="550">
       <c r="A46" s="1183">
-        <f>'Presupuesto '!B234</f>
+        <f>'Presupuesto '!B233</f>
         <v/>
       </c>
       <c r="B46" s="567" t="n"/>

--- a/public/plantilla-mensual.xlsx
+++ b/public/plantilla-mensual.xlsx
@@ -11293,7 +11293,6 @@
     <mergeCell ref="C16:E16"/>
     <mergeCell ref="A39:E39"/>
     <mergeCell ref="B9:E9"/>
-    <mergeCell ref="C29:E29"/>
     <mergeCell ref="D10:E10"/>
     <mergeCell ref="C31:E31"/>
     <mergeCell ref="C22:E22"/>
@@ -11326,8 +11325,9 @@
     <mergeCell ref="B5:C5"/>
     <mergeCell ref="A28:E28"/>
     <mergeCell ref="C26:E26"/>
+    <mergeCell ref="C35:E35"/>
     <mergeCell ref="A13:E13"/>
-    <mergeCell ref="C35:E35"/>
+    <mergeCell ref="C29:E29"/>
     <mergeCell ref="A44:E44"/>
     <mergeCell ref="C20:E20"/>
     <mergeCell ref="A40:E40"/>
@@ -16897,7 +16897,7 @@
     </row>
     <row r="28">
       <c r="A28" s="1180">
-        <f>'Presupuesto '!B52</f>
+        <f>'Presupuesto '!B51</f>
         <v/>
       </c>
       <c r="B28" s="609" t="n"/>
@@ -16928,7 +16928,7 @@
     </row>
     <row r="29">
       <c r="A29" s="1180">
-        <f>'Presupuesto '!B70</f>
+        <f>'Presupuesto '!B64</f>
         <v/>
       </c>
       <c r="B29" s="609" t="n"/>
@@ -16959,7 +16959,7 @@
     </row>
     <row r="30">
       <c r="A30" s="1180">
-        <f>'Presupuesto '!B82</f>
+        <f>'Presupuesto '!B76</f>
         <v/>
       </c>
       <c r="B30" s="609" t="n"/>
@@ -16990,7 +16990,7 @@
     </row>
     <row r="31">
       <c r="A31" s="1180">
-        <f>'Presupuesto '!B94</f>
+        <f>'Presupuesto '!B88</f>
         <v/>
       </c>
       <c r="B31" s="609" t="n"/>
@@ -17021,7 +17021,7 @@
     </row>
     <row r="32">
       <c r="A32" s="1180">
-        <f>'Presupuesto '!B101</f>
+        <f>'Presupuesto '!B95</f>
         <v/>
       </c>
       <c r="B32" s="609" t="n"/>
@@ -17052,7 +17052,7 @@
     </row>
     <row r="33">
       <c r="A33" s="1180">
-        <f>'Presupuesto '!B107</f>
+        <f>'Presupuesto '!B101</f>
         <v/>
       </c>
       <c r="B33" s="609" t="n"/>
@@ -17083,7 +17083,7 @@
     </row>
     <row r="34">
       <c r="A34" s="1180">
-        <f>'Presupuesto '!B121</f>
+        <f>'Presupuesto '!B115</f>
         <v/>
       </c>
       <c r="B34" s="609" t="n"/>
@@ -17114,7 +17114,7 @@
     </row>
     <row r="35">
       <c r="A35" s="1180">
-        <f>'Presupuesto '!B131</f>
+        <f>'Presupuesto '!B125</f>
         <v/>
       </c>
       <c r="B35" s="609" t="n"/>
@@ -17145,7 +17145,7 @@
     </row>
     <row r="36">
       <c r="A36" s="1180">
-        <f>'Presupuesto '!B142</f>
+        <f>'Presupuesto '!B136</f>
         <v/>
       </c>
       <c r="B36" s="609" t="n"/>
@@ -17176,7 +17176,7 @@
     </row>
     <row r="37">
       <c r="A37" s="1180">
-        <f>'Presupuesto '!B149</f>
+        <f>'Presupuesto '!B143</f>
         <v/>
       </c>
       <c r="B37" s="609" t="n"/>
@@ -17207,7 +17207,7 @@
     </row>
     <row r="38">
       <c r="A38" s="1180">
-        <f>'Presupuesto '!B164</f>
+        <f>'Presupuesto '!B158</f>
         <v/>
       </c>
       <c r="B38" s="609" t="n"/>
@@ -17238,7 +17238,7 @@
     </row>
     <row r="39">
       <c r="A39" s="1180">
-        <f>'Presupuesto '!B178</f>
+        <f>'Presupuesto '!B172</f>
         <v/>
       </c>
       <c r="B39" s="609" t="n"/>
@@ -17269,7 +17269,7 @@
     </row>
     <row r="40" ht="14.4" customHeight="1" s="550">
       <c r="A40" s="1183">
-        <f>'Presupuesto '!B187</f>
+        <f>'Presupuesto '!B181</f>
         <v/>
       </c>
       <c r="B40" s="567" t="n"/>
@@ -17300,7 +17300,7 @@
     </row>
     <row r="41">
       <c r="A41" s="1253">
-        <f>'Presupuesto '!B194</f>
+        <f>'Presupuesto '!B188</f>
         <v/>
       </c>
       <c r="B41" s="1064" t="n"/>
@@ -17331,7 +17331,7 @@
     </row>
     <row r="42" ht="14.4" customHeight="1" s="550">
       <c r="A42" s="1180">
-        <f>'Presupuesto '!B200</f>
+        <f>'Presupuesto '!B194</f>
         <v/>
       </c>
       <c r="B42" s="609" t="n"/>
@@ -17362,7 +17362,7 @@
     </row>
     <row r="43" ht="14.4" customHeight="1" s="550">
       <c r="A43" s="1183">
-        <f>'Presupuesto '!B214</f>
+        <f>'Presupuesto '!B208</f>
         <v/>
       </c>
       <c r="B43" s="567" t="n"/>
@@ -17393,7 +17393,7 @@
     </row>
     <row r="44" ht="14.4" customHeight="1" s="550">
       <c r="A44" s="1183">
-        <f>'Presupuesto '!B221</f>
+        <f>'Presupuesto '!B215</f>
         <v/>
       </c>
       <c r="B44" s="567" t="n"/>
@@ -17424,7 +17424,7 @@
     </row>
     <row r="45">
       <c r="A45" s="1183">
-        <f>'Presupuesto '!B229</f>
+        <f>'Presupuesto '!B223</f>
         <v/>
       </c>
       <c r="B45" s="567" t="n"/>
@@ -17455,7 +17455,7 @@
     </row>
     <row r="46" ht="14.4" customHeight="1" s="550">
       <c r="A46" s="1183">
-        <f>'Presupuesto '!B233</f>
+        <f>'Presupuesto '!B227</f>
         <v/>
       </c>
       <c r="B46" s="567" t="n"/>

--- a/public/plantilla-mensual.xlsx
+++ b/public/plantilla-mensual.xlsx
@@ -10418,32 +10418,32 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <twoCellAnchor editAs="oneCell">
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>0</row>
-      <rowOff>0</rowOff>
-    </from>
-    <to>
-      <col>1</col>
-      <colOff>69253</colOff>
-      <row>6</row>
-      <rowOff>174506</rowOff>
-    </to>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="14" name="Imagen 2"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>69253</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>174506</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="14" name="Imagen 2"/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
         <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
-      </blipFill>
-      <spPr>
+      </xdr:blipFill>
+      <xdr:spPr>
         <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:off x="0" y="0"/>
           <a:ext cx="2952000" cy="1368000"/>
@@ -10455,40 +10455,40 @@
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </twoCellAnchor>
-</wsDr>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <twoCellAnchor editAs="oneCell">
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>0</row>
-      <rowOff>0</rowOff>
-    </from>
-    <to>
-      <col>1</col>
-      <colOff>2766370</colOff>
-      <row>8</row>
-      <rowOff>172889</rowOff>
-    </to>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="3" name="Imagen 2"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>2766370</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>172889</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="Imagen 2"/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
         <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
-      </blipFill>
-      <spPr>
+      </xdr:blipFill>
+      <xdr:spPr>
         <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:off x="0" y="0"/>
           <a:ext cx="3312000" cy="1584000"/>
@@ -10500,40 +10500,40 @@
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </twoCellAnchor>
-</wsDr>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <twoCellAnchor editAs="oneCell">
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>130</row>
-      <rowOff>66959</rowOff>
-    </from>
-    <to>
-      <col>6</col>
-      <colOff>725921</colOff>
-      <row>135</row>
-      <rowOff>28591</rowOff>
-    </to>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="23" name="Image 2" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>145</xdr:row>
+      <xdr:rowOff>66959</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>725921</xdr:colOff>
+      <xdr:row>150</xdr:row>
+      <xdr:rowOff>28591</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="23" name="Image 2" descr="Picture"/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
         <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
-      </blipFill>
-      <spPr>
+      </xdr:blipFill>
+      <xdr:spPr>
         <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:off x="0" y="24049906"/>
           <a:ext cx="5328000" cy="864000"/>
@@ -10545,35 +10545,35 @@
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </twoCellAnchor>
-  <twoCellAnchor editAs="oneCell">
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>0</row>
-      <rowOff>0</rowOff>
-    </from>
-    <to>
-      <col>3</col>
-      <colOff>749842</colOff>
-      <row>8</row>
-      <rowOff>148421</rowOff>
-    </to>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="4" name="Imagen 2"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>749842</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>148421</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="4" name="Imagen 2"/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
         <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
-      </blipFill>
-      <spPr>
+      </xdr:blipFill>
+      <xdr:spPr>
         <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:off x="0" y="0"/>
           <a:ext cx="3096000" cy="1512000"/>
@@ -10585,11 +10585,11 @@
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </twoCellAnchor>
-</wsDr>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -10773,7 +10773,6 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="FFFFFF00"/>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:E47"/>
@@ -11324,13 +11323,13 @@
     <mergeCell ref="A38:E38"/>
     <mergeCell ref="B5:C5"/>
     <mergeCell ref="A28:E28"/>
+    <mergeCell ref="A40:E40"/>
     <mergeCell ref="C26:E26"/>
-    <mergeCell ref="C35:E35"/>
     <mergeCell ref="A13:E13"/>
     <mergeCell ref="C29:E29"/>
     <mergeCell ref="A44:E44"/>
     <mergeCell ref="C20:E20"/>
-    <mergeCell ref="A40:E40"/>
+    <mergeCell ref="C35:E35"/>
     <mergeCell ref="B4:C4"/>
     <mergeCell ref="C25:E25"/>
   </mergeCells>
@@ -11344,7 +11343,6 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="FF2E7D32"/>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:F259"/>
@@ -16358,10 +16356,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="FF7030A0"/>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:S131"/>
+  <dimension ref="A1:S146"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4"/>
   <cols>
     <col width="11.33203125" customWidth="1" style="1182" min="1" max="3"/>
@@ -16694,11 +16691,11 @@
     </row>
     <row r="21">
       <c r="A21" s="1406">
-        <f>H47</f>
+        <f>H62</f>
         <v/>
       </c>
       <c r="D21" s="1407">
-        <f>I47</f>
+        <f>I62</f>
         <v/>
       </c>
       <c r="G21" s="1407">
@@ -16706,7 +16703,7 @@
         <v/>
       </c>
       <c r="J21" s="1408">
-        <f>IFERROR(J47/$L$14,0)</f>
+        <f>IFERROR(J62/$L$14,0)</f>
         <v/>
       </c>
       <c r="N21" s="562" t="n"/>
@@ -17484,609 +17481,873 @@
       </c>
       <c r="N46" s="562" t="n"/>
     </row>
-    <row r="47">
-      <c r="A47" s="1241" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="B47" s="1217" t="n"/>
-      <c r="C47" s="1217" t="n"/>
-      <c r="D47" s="269">
-        <f>SUM(D25:D46)</f>
-        <v/>
-      </c>
-      <c r="E47" s="1217" t="n"/>
-      <c r="F47" s="1217" t="n"/>
-      <c r="G47" s="15" t="n"/>
-      <c r="H47" s="1421">
-        <f>SUM(H25:H46)</f>
-        <v/>
-      </c>
-      <c r="I47" s="1421">
-        <f>SUM(I25:I46)</f>
-        <v/>
-      </c>
-      <c r="J47" s="1422">
-        <f>SUM(J25:J46)</f>
+    <row r="47" ht="14.4" customHeight="1" s="550">
+      <c r="A47" s="1183" t="n"/>
+      <c r="B47" s="567" t="n"/>
+      <c r="C47" s="567" t="n"/>
+      <c r="D47" s="1411" t="n"/>
+      <c r="E47" s="1412" t="n"/>
+      <c r="F47" s="1412" t="n"/>
+      <c r="G47" s="1413">
+        <f>F47-E47</f>
+        <v/>
+      </c>
+      <c r="H47" s="1414">
+        <f>D47*E47</f>
+        <v/>
+      </c>
+      <c r="I47" s="1414">
+        <f>D47*F47</f>
+        <v/>
+      </c>
+      <c r="J47" s="1416">
+        <f>D47*$L$14*G47</f>
         <v/>
       </c>
       <c r="N47" s="562" t="n"/>
     </row>
-    <row r="48" ht="15.75" customHeight="1" s="550">
-      <c r="A48" s="1181" t="inlineStr">
-        <is>
-          <t>ACTIVIDADES MÁS RELEVANTES DEL PERÍODO</t>
-        </is>
+    <row r="48" ht="14.4" customHeight="1" s="550">
+      <c r="A48" s="1183" t="n"/>
+      <c r="B48" s="567" t="n"/>
+      <c r="C48" s="567" t="n"/>
+      <c r="D48" s="1411" t="n"/>
+      <c r="E48" s="1412" t="n"/>
+      <c r="F48" s="1412" t="n"/>
+      <c r="G48" s="1413">
+        <f>F48-E48</f>
+        <v/>
+      </c>
+      <c r="H48" s="1414">
+        <f>D48*E48</f>
+        <v/>
+      </c>
+      <c r="I48" s="1414">
+        <f>D48*F48</f>
+        <v/>
+      </c>
+      <c r="J48" s="1416">
+        <f>D48*$L$14*G48</f>
+        <v/>
       </c>
       <c r="N48" s="562" t="n"/>
     </row>
-    <row r="49" ht="14.25" customHeight="1" s="550">
-      <c r="A49" s="1237" t="inlineStr">
-        <is>
-          <t>UBICACIÓN</t>
-        </is>
-      </c>
-      <c r="B49" s="609" t="n"/>
-      <c r="C49" s="1222" t="inlineStr">
-        <is>
-          <t>DESCRIPCIÓN DE LA ACTIVIDAD</t>
-        </is>
-      </c>
-      <c r="D49" s="609" t="n"/>
-      <c r="E49" s="609" t="n"/>
-      <c r="F49" s="609" t="n"/>
-      <c r="G49" s="1222" t="inlineStr">
-        <is>
-          <t>AVANCE DEL PERÍODO</t>
-        </is>
-      </c>
-      <c r="H49" s="609" t="n"/>
-      <c r="I49" s="1222" t="inlineStr">
-        <is>
-          <t>RESPONSABLE</t>
-        </is>
-      </c>
-      <c r="J49" s="609" t="n"/>
-      <c r="K49" s="1423" t="inlineStr">
-        <is>
-          <t>OBSERVACIONES</t>
-        </is>
-      </c>
-      <c r="L49" s="609" t="n"/>
-      <c r="M49" s="609" t="n"/>
-      <c r="N49" s="610" t="n"/>
-    </row>
-    <row r="50">
-      <c r="A50" s="1259" t="n"/>
-      <c r="B50" s="1126" t="n"/>
-      <c r="C50" s="1177" t="n"/>
-      <c r="D50" s="567" t="n"/>
-      <c r="E50" s="567" t="n"/>
-      <c r="F50" s="567" t="n"/>
-      <c r="G50" s="1198" t="n"/>
-      <c r="H50" s="567" t="n"/>
-      <c r="I50" s="1126" t="n"/>
-      <c r="J50" s="1126" t="n"/>
-      <c r="K50" s="1424" t="n"/>
-      <c r="L50" s="567" t="n"/>
-      <c r="M50" s="567" t="n"/>
-      <c r="N50" s="607" t="n"/>
-    </row>
-    <row r="51">
-      <c r="A51" s="1184" t="n"/>
-      <c r="B51" s="1136" t="n"/>
-      <c r="C51" s="1177" t="n"/>
-      <c r="D51" s="567" t="n"/>
-      <c r="E51" s="567" t="n"/>
-      <c r="F51" s="567" t="n"/>
-      <c r="G51" s="1198" t="n"/>
-      <c r="H51" s="567" t="n"/>
-      <c r="I51" s="1249" t="n"/>
-      <c r="J51" s="1136" t="n"/>
-      <c r="K51" s="1425" t="n"/>
-      <c r="L51" s="567" t="n"/>
-      <c r="M51" s="567" t="n"/>
-      <c r="N51" s="607" t="n"/>
-    </row>
-    <row r="52">
-      <c r="A52" s="1191" t="n"/>
+    <row r="49" ht="14.4" customHeight="1" s="550">
+      <c r="A49" s="1183" t="n"/>
+      <c r="B49" s="567" t="n"/>
+      <c r="C49" s="567" t="n"/>
+      <c r="D49" s="1411" t="n"/>
+      <c r="E49" s="1412" t="n"/>
+      <c r="F49" s="1412" t="n"/>
+      <c r="G49" s="1413">
+        <f>F49-E49</f>
+        <v/>
+      </c>
+      <c r="H49" s="1414">
+        <f>D49*E49</f>
+        <v/>
+      </c>
+      <c r="I49" s="1414">
+        <f>D49*F49</f>
+        <v/>
+      </c>
+      <c r="J49" s="1416">
+        <f>D49*$L$14*G49</f>
+        <v/>
+      </c>
+      <c r="N49" s="562" t="n"/>
+    </row>
+    <row r="50" ht="14.4" customHeight="1" s="550">
+      <c r="A50" s="1183" t="n"/>
+      <c r="B50" s="567" t="n"/>
+      <c r="C50" s="567" t="n"/>
+      <c r="D50" s="1411" t="n"/>
+      <c r="E50" s="1412" t="n"/>
+      <c r="F50" s="1412" t="n"/>
+      <c r="G50" s="1413">
+        <f>F50-E50</f>
+        <v/>
+      </c>
+      <c r="H50" s="1414">
+        <f>D50*E50</f>
+        <v/>
+      </c>
+      <c r="I50" s="1414">
+        <f>D50*F50</f>
+        <v/>
+      </c>
+      <c r="J50" s="1416">
+        <f>D50*$L$14*G50</f>
+        <v/>
+      </c>
+      <c r="N50" s="562" t="n"/>
+    </row>
+    <row r="51" ht="14.4" customHeight="1" s="550">
+      <c r="A51" s="1183" t="n"/>
+      <c r="B51" s="567" t="n"/>
+      <c r="C51" s="567" t="n"/>
+      <c r="D51" s="1411" t="n"/>
+      <c r="E51" s="1412" t="n"/>
+      <c r="F51" s="1412" t="n"/>
+      <c r="G51" s="1413">
+        <f>F51-E51</f>
+        <v/>
+      </c>
+      <c r="H51" s="1414">
+        <f>D51*E51</f>
+        <v/>
+      </c>
+      <c r="I51" s="1414">
+        <f>D51*F51</f>
+        <v/>
+      </c>
+      <c r="J51" s="1416">
+        <f>D51*$L$14*G51</f>
+        <v/>
+      </c>
+      <c r="N51" s="562" t="n"/>
+    </row>
+    <row r="52" ht="14.4" customHeight="1" s="550">
+      <c r="A52" s="1183" t="n"/>
       <c r="B52" s="567" t="n"/>
-      <c r="C52" s="1177" t="n"/>
-      <c r="D52" s="567" t="n"/>
-      <c r="E52" s="567" t="n"/>
-      <c r="F52" s="567" t="n"/>
-      <c r="G52" s="1198" t="n"/>
-      <c r="H52" s="567" t="n"/>
-      <c r="I52" s="1201" t="n"/>
-      <c r="J52" s="567" t="n"/>
-      <c r="K52" s="1425" t="n"/>
-      <c r="L52" s="567" t="n"/>
-      <c r="M52" s="567" t="n"/>
-      <c r="N52" s="607" t="n"/>
-    </row>
-    <row r="53">
-      <c r="A53" s="1191" t="n"/>
+      <c r="C52" s="567" t="n"/>
+      <c r="D52" s="1411" t="n"/>
+      <c r="E52" s="1412" t="n"/>
+      <c r="F52" s="1412" t="n"/>
+      <c r="G52" s="1413">
+        <f>F52-E52</f>
+        <v/>
+      </c>
+      <c r="H52" s="1414">
+        <f>D52*E52</f>
+        <v/>
+      </c>
+      <c r="I52" s="1414">
+        <f>D52*F52</f>
+        <v/>
+      </c>
+      <c r="J52" s="1416">
+        <f>D52*$L$14*G52</f>
+        <v/>
+      </c>
+      <c r="N52" s="562" t="n"/>
+    </row>
+    <row r="53" ht="14.4" customHeight="1" s="550">
+      <c r="A53" s="1183" t="n"/>
       <c r="B53" s="567" t="n"/>
-      <c r="C53" s="1177" t="n"/>
-      <c r="D53" s="567" t="n"/>
-      <c r="E53" s="567" t="n"/>
-      <c r="F53" s="567" t="n"/>
-      <c r="G53" s="1198" t="n"/>
-      <c r="H53" s="567" t="n"/>
-      <c r="I53" s="1201" t="n"/>
-      <c r="J53" s="567" t="n"/>
-      <c r="K53" s="1425" t="n"/>
-      <c r="L53" s="567" t="n"/>
-      <c r="M53" s="567" t="n"/>
-      <c r="N53" s="607" t="n"/>
-      <c r="S53" s="13" t="n"/>
-    </row>
-    <row r="54">
-      <c r="A54" s="1191" t="n"/>
+      <c r="C53" s="567" t="n"/>
+      <c r="D53" s="1411" t="n"/>
+      <c r="E53" s="1412" t="n"/>
+      <c r="F53" s="1412" t="n"/>
+      <c r="G53" s="1413">
+        <f>F53-E53</f>
+        <v/>
+      </c>
+      <c r="H53" s="1414">
+        <f>D53*E53</f>
+        <v/>
+      </c>
+      <c r="I53" s="1414">
+        <f>D53*F53</f>
+        <v/>
+      </c>
+      <c r="J53" s="1416">
+        <f>D53*$L$14*G53</f>
+        <v/>
+      </c>
+      <c r="N53" s="562" t="n"/>
+    </row>
+    <row r="54" ht="14.4" customHeight="1" s="550">
+      <c r="A54" s="1183" t="n"/>
       <c r="B54" s="567" t="n"/>
-      <c r="C54" s="1177" t="n"/>
-      <c r="D54" s="567" t="n"/>
-      <c r="E54" s="567" t="n"/>
-      <c r="F54" s="567" t="n"/>
-      <c r="G54" s="1198" t="n"/>
-      <c r="H54" s="567" t="n"/>
-      <c r="I54" s="1201" t="n"/>
-      <c r="J54" s="567" t="n"/>
-      <c r="K54" s="1425" t="n"/>
-      <c r="L54" s="567" t="n"/>
-      <c r="M54" s="567" t="n"/>
-      <c r="N54" s="607" t="n"/>
-    </row>
-    <row r="55">
-      <c r="A55" s="1191" t="n"/>
+      <c r="C54" s="567" t="n"/>
+      <c r="D54" s="1411" t="n"/>
+      <c r="E54" s="1412" t="n"/>
+      <c r="F54" s="1412" t="n"/>
+      <c r="G54" s="1413">
+        <f>F54-E54</f>
+        <v/>
+      </c>
+      <c r="H54" s="1414">
+        <f>D54*E54</f>
+        <v/>
+      </c>
+      <c r="I54" s="1414">
+        <f>D54*F54</f>
+        <v/>
+      </c>
+      <c r="J54" s="1416">
+        <f>D54*$L$14*G54</f>
+        <v/>
+      </c>
+      <c r="N54" s="562" t="n"/>
+    </row>
+    <row r="55" ht="14.4" customHeight="1" s="550">
+      <c r="A55" s="1183" t="n"/>
       <c r="B55" s="567" t="n"/>
-      <c r="C55" s="1177" t="n"/>
-      <c r="D55" s="567" t="n"/>
-      <c r="E55" s="567" t="n"/>
-      <c r="F55" s="567" t="n"/>
-      <c r="G55" s="1198" t="n"/>
-      <c r="H55" s="567" t="n"/>
-      <c r="I55" s="1201" t="n"/>
-      <c r="J55" s="567" t="n"/>
-      <c r="K55" s="1425" t="n"/>
-      <c r="L55" s="567" t="n"/>
-      <c r="M55" s="567" t="n"/>
-      <c r="N55" s="607" t="n"/>
-    </row>
-    <row r="56">
-      <c r="A56" s="1191" t="n"/>
+      <c r="C55" s="567" t="n"/>
+      <c r="D55" s="1411" t="n"/>
+      <c r="E55" s="1412" t="n"/>
+      <c r="F55" s="1412" t="n"/>
+      <c r="G55" s="1413">
+        <f>F55-E55</f>
+        <v/>
+      </c>
+      <c r="H55" s="1414">
+        <f>D55*E55</f>
+        <v/>
+      </c>
+      <c r="I55" s="1414">
+        <f>D55*F55</f>
+        <v/>
+      </c>
+      <c r="J55" s="1416">
+        <f>D55*$L$14*G55</f>
+        <v/>
+      </c>
+      <c r="N55" s="562" t="n"/>
+    </row>
+    <row r="56" ht="14.4" customHeight="1" s="550">
+      <c r="A56" s="1183" t="n"/>
       <c r="B56" s="567" t="n"/>
-      <c r="C56" s="1177" t="n"/>
-      <c r="D56" s="567" t="n"/>
-      <c r="E56" s="567" t="n"/>
-      <c r="F56" s="567" t="n"/>
-      <c r="G56" s="1198" t="n"/>
-      <c r="H56" s="567" t="n"/>
-      <c r="I56" s="1201" t="n"/>
-      <c r="J56" s="567" t="n"/>
-      <c r="K56" s="1425" t="n"/>
-      <c r="L56" s="567" t="n"/>
-      <c r="M56" s="567" t="n"/>
-      <c r="N56" s="607" t="n"/>
-    </row>
-    <row r="57">
-      <c r="A57" s="1191" t="n"/>
+      <c r="C56" s="567" t="n"/>
+      <c r="D56" s="1411" t="n"/>
+      <c r="E56" s="1412" t="n"/>
+      <c r="F56" s="1412" t="n"/>
+      <c r="G56" s="1413">
+        <f>F56-E56</f>
+        <v/>
+      </c>
+      <c r="H56" s="1414">
+        <f>D56*E56</f>
+        <v/>
+      </c>
+      <c r="I56" s="1414">
+        <f>D56*F56</f>
+        <v/>
+      </c>
+      <c r="J56" s="1416">
+        <f>D56*$L$14*G56</f>
+        <v/>
+      </c>
+      <c r="N56" s="562" t="n"/>
+    </row>
+    <row r="57" ht="14.4" customHeight="1" s="550">
+      <c r="A57" s="1183" t="n"/>
       <c r="B57" s="567" t="n"/>
-      <c r="C57" s="1177" t="n"/>
-      <c r="D57" s="567" t="n"/>
-      <c r="E57" s="567" t="n"/>
-      <c r="F57" s="567" t="n"/>
-      <c r="G57" s="1198" t="n"/>
-      <c r="H57" s="567" t="n"/>
-      <c r="I57" s="1201" t="n"/>
-      <c r="J57" s="567" t="n"/>
-      <c r="K57" s="1425" t="n"/>
-      <c r="L57" s="567" t="n"/>
-      <c r="M57" s="567" t="n"/>
-      <c r="N57" s="607" t="n"/>
-    </row>
-    <row r="58">
-      <c r="A58" s="1191" t="n"/>
+      <c r="C57" s="567" t="n"/>
+      <c r="D57" s="1411" t="n"/>
+      <c r="E57" s="1412" t="n"/>
+      <c r="F57" s="1412" t="n"/>
+      <c r="G57" s="1413">
+        <f>F57-E57</f>
+        <v/>
+      </c>
+      <c r="H57" s="1414">
+        <f>D57*E57</f>
+        <v/>
+      </c>
+      <c r="I57" s="1414">
+        <f>D57*F57</f>
+        <v/>
+      </c>
+      <c r="J57" s="1416">
+        <f>D57*$L$14*G57</f>
+        <v/>
+      </c>
+      <c r="N57" s="562" t="n"/>
+    </row>
+    <row r="58" ht="14.4" customHeight="1" s="550">
+      <c r="A58" s="1183" t="n"/>
       <c r="B58" s="567" t="n"/>
-      <c r="C58" s="1177" t="n"/>
-      <c r="D58" s="567" t="n"/>
-      <c r="E58" s="567" t="n"/>
-      <c r="F58" s="567" t="n"/>
-      <c r="G58" s="1198" t="n"/>
-      <c r="H58" s="567" t="n"/>
-      <c r="I58" s="1201" t="n"/>
-      <c r="J58" s="567" t="n"/>
-      <c r="K58" s="1425" t="n"/>
-      <c r="L58" s="567" t="n"/>
-      <c r="M58" s="567" t="n"/>
-      <c r="N58" s="607" t="n"/>
+      <c r="C58" s="567" t="n"/>
+      <c r="D58" s="1411" t="n"/>
+      <c r="E58" s="1412" t="n"/>
+      <c r="F58" s="1412" t="n"/>
+      <c r="G58" s="1413">
+        <f>F58-E58</f>
+        <v/>
+      </c>
+      <c r="H58" s="1414">
+        <f>D58*E58</f>
+        <v/>
+      </c>
+      <c r="I58" s="1414">
+        <f>D58*F58</f>
+        <v/>
+      </c>
+      <c r="J58" s="1416">
+        <f>D58*$L$14*G58</f>
+        <v/>
+      </c>
+      <c r="N58" s="562" t="n"/>
     </row>
     <row r="59" ht="14.4" customHeight="1" s="550">
-      <c r="A59" s="1186" t="inlineStr">
-        <is>
-          <t>AVANCE FINANCIERO Y ADMINISTRATIVO</t>
-        </is>
-      </c>
-      <c r="B59" s="1064" t="n"/>
-      <c r="C59" s="1064" t="n"/>
-      <c r="D59" s="1064" t="n"/>
-      <c r="E59" s="1064" t="n"/>
-      <c r="F59" s="1064" t="n"/>
-      <c r="G59" s="1064" t="n"/>
-      <c r="H59" s="1064" t="n"/>
-      <c r="I59" s="1064" t="n"/>
-      <c r="J59" s="1064" t="n"/>
-      <c r="K59" s="1064" t="n"/>
-      <c r="L59" s="1064" t="n"/>
-      <c r="M59" s="1064" t="n"/>
-      <c r="N59" s="1065" t="n"/>
+      <c r="A59" s="1183" t="n"/>
+      <c r="B59" s="567" t="n"/>
+      <c r="C59" s="567" t="n"/>
+      <c r="D59" s="1411" t="n"/>
+      <c r="E59" s="1412" t="n"/>
+      <c r="F59" s="1412" t="n"/>
+      <c r="G59" s="1413">
+        <f>F59-E59</f>
+        <v/>
+      </c>
+      <c r="H59" s="1414">
+        <f>D59*E59</f>
+        <v/>
+      </c>
+      <c r="I59" s="1414">
+        <f>D59*F59</f>
+        <v/>
+      </c>
+      <c r="J59" s="1416">
+        <f>D59*$L$14*G59</f>
+        <v/>
+      </c>
+      <c r="N59" s="562" t="n"/>
     </row>
     <row r="60" ht="14.4" customHeight="1" s="550">
-      <c r="A60" s="1210" t="inlineStr">
-        <is>
-          <t>INGRESOS DEL PERÍODO</t>
-        </is>
-      </c>
+      <c r="A60" s="1183" t="n"/>
       <c r="B60" s="567" t="n"/>
       <c r="C60" s="567" t="n"/>
-      <c r="D60" s="567" t="n"/>
-      <c r="E60" s="567" t="n"/>
-      <c r="F60" s="567" t="n"/>
-      <c r="G60" s="383" t="n"/>
-      <c r="H60" s="1228" t="inlineStr">
-        <is>
-          <t>EGRESOS / GASTOS DEL PERÍODO</t>
-        </is>
+      <c r="D60" s="1411" t="n"/>
+      <c r="E60" s="1412" t="n"/>
+      <c r="F60" s="1412" t="n"/>
+      <c r="G60" s="1413">
+        <f>F60-E60</f>
+        <v/>
+      </c>
+      <c r="H60" s="1414">
+        <f>D60*E60</f>
+        <v/>
+      </c>
+      <c r="I60" s="1414">
+        <f>D60*F60</f>
+        <v/>
+      </c>
+      <c r="J60" s="1416">
+        <f>D60*$L$14*G60</f>
+        <v/>
       </c>
       <c r="N60" s="562" t="n"/>
     </row>
-    <row r="61">
-      <c r="A61" s="1251" t="inlineStr">
-        <is>
-          <t>CONCEPTO</t>
-        </is>
-      </c>
+    <row r="61" ht="14.4" customHeight="1" s="550">
+      <c r="A61" s="1183" t="n"/>
       <c r="B61" s="567" t="n"/>
       <c r="C61" s="567" t="n"/>
-      <c r="D61" s="1426" t="inlineStr">
-        <is>
-          <t>FECHA</t>
-        </is>
-      </c>
-      <c r="E61" s="1427" t="inlineStr">
-        <is>
-          <t>VALOR ($)</t>
-        </is>
-      </c>
-      <c r="F61" s="567" t="n"/>
-      <c r="G61" s="385" t="n"/>
-      <c r="H61" s="1238" t="inlineStr">
-        <is>
-          <t>CONCEPTO</t>
-        </is>
-      </c>
-      <c r="I61" s="567" t="n"/>
-      <c r="J61" s="567" t="n"/>
-      <c r="K61" s="1260" t="inlineStr">
-        <is>
-          <t>FECHA</t>
-        </is>
-      </c>
-      <c r="L61" s="609" t="n"/>
-      <c r="M61" s="1428" t="inlineStr">
-        <is>
-          <t>VALOR ($)</t>
-        </is>
-      </c>
-      <c r="N61" s="610" t="n"/>
+      <c r="D61" s="1411" t="n"/>
+      <c r="E61" s="1412" t="n"/>
+      <c r="F61" s="1412" t="n"/>
+      <c r="G61" s="1413">
+        <f>F61-E61</f>
+        <v/>
+      </c>
+      <c r="H61" s="1414">
+        <f>D61*E61</f>
+        <v/>
+      </c>
+      <c r="I61" s="1414">
+        <f>D61*F61</f>
+        <v/>
+      </c>
+      <c r="J61" s="1416">
+        <f>D61*$L$14*G61</f>
+        <v/>
+      </c>
+      <c r="N61" s="562" t="n"/>
     </row>
     <row r="62">
-      <c r="A62" s="1202" t="n"/>
-      <c r="B62" s="567" t="n"/>
-      <c r="C62" s="567" t="n"/>
-      <c r="D62" s="1429" t="n"/>
-      <c r="E62" s="1430" t="n"/>
-      <c r="F62" s="567" t="n"/>
-      <c r="G62" s="383" t="n"/>
-      <c r="H62" s="1192" t="n"/>
-      <c r="I62" s="567" t="n"/>
-      <c r="J62" s="567" t="n"/>
-      <c r="K62" s="1219" t="n"/>
-      <c r="L62" s="567" t="n"/>
-      <c r="M62" s="1431" t="n"/>
-      <c r="N62" s="607" t="n"/>
-    </row>
-    <row r="63">
-      <c r="A63" s="1202" t="n"/>
-      <c r="B63" s="567" t="n"/>
-      <c r="C63" s="567" t="n"/>
-      <c r="D63" s="1429" t="n"/>
-      <c r="E63" s="1430" t="n"/>
-      <c r="F63" s="567" t="n"/>
-      <c r="G63" s="383" t="n"/>
-      <c r="H63" s="1192" t="n"/>
-      <c r="I63" s="567" t="n"/>
-      <c r="J63" s="567" t="n"/>
-      <c r="K63" s="1219" t="n"/>
-      <c r="L63" s="567" t="n"/>
-      <c r="M63" s="1431" t="n"/>
-      <c r="N63" s="607" t="n"/>
-    </row>
-    <row r="64">
-      <c r="A64" s="1202" t="n"/>
-      <c r="B64" s="567" t="n"/>
-      <c r="C64" s="567" t="n"/>
-      <c r="D64" s="1429" t="n"/>
-      <c r="E64" s="1430" t="n"/>
-      <c r="F64" s="567" t="n"/>
-      <c r="G64" s="383" t="n"/>
-      <c r="H64" s="1192" t="n"/>
-      <c r="I64" s="567" t="n"/>
-      <c r="J64" s="567" t="n"/>
-      <c r="K64" s="1219" t="n"/>
-      <c r="L64" s="567" t="n"/>
-      <c r="M64" s="1431" t="n"/>
-      <c r="N64" s="607" t="n"/>
+      <c r="A62" s="1241" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="B62" s="1217" t="n"/>
+      <c r="C62" s="1217" t="n"/>
+      <c r="D62" s="269">
+        <f>SUM(D25:D61)</f>
+        <v/>
+      </c>
+      <c r="E62" s="1217" t="n"/>
+      <c r="F62" s="1217" t="n"/>
+      <c r="G62" s="15" t="n"/>
+      <c r="H62" s="1421">
+        <f>SUM(H25:H61)</f>
+        <v/>
+      </c>
+      <c r="I62" s="1421">
+        <f>SUM(I25:I61)</f>
+        <v/>
+      </c>
+      <c r="J62" s="1422">
+        <f>SUM(J25:J61)</f>
+        <v/>
+      </c>
+      <c r="N62" s="562" t="n"/>
+    </row>
+    <row r="63" ht="15.75" customHeight="1" s="550">
+      <c r="A63" s="1181" t="inlineStr">
+        <is>
+          <t>ACTIVIDADES MÁS RELEVANTES DEL PERÍODO</t>
+        </is>
+      </c>
+      <c r="N63" s="562" t="n"/>
+    </row>
+    <row r="64" ht="14.25" customHeight="1" s="550">
+      <c r="A64" s="1237" t="inlineStr">
+        <is>
+          <t>UBICACIÓN</t>
+        </is>
+      </c>
+      <c r="B64" s="609" t="n"/>
+      <c r="C64" s="1222" t="inlineStr">
+        <is>
+          <t>DESCRIPCIÓN DE LA ACTIVIDAD</t>
+        </is>
+      </c>
+      <c r="D64" s="609" t="n"/>
+      <c r="E64" s="609" t="n"/>
+      <c r="F64" s="609" t="n"/>
+      <c r="G64" s="1222" t="inlineStr">
+        <is>
+          <t>AVANCE DEL PERÍODO</t>
+        </is>
+      </c>
+      <c r="H64" s="609" t="n"/>
+      <c r="I64" s="1222" t="inlineStr">
+        <is>
+          <t>RESPONSABLE</t>
+        </is>
+      </c>
+      <c r="J64" s="609" t="n"/>
+      <c r="K64" s="1423" t="inlineStr">
+        <is>
+          <t>OBSERVACIONES</t>
+        </is>
+      </c>
+      <c r="L64" s="609" t="n"/>
+      <c r="M64" s="609" t="n"/>
+      <c r="N64" s="610" t="n"/>
     </row>
     <row r="65">
-      <c r="A65" s="1202" t="n"/>
-      <c r="B65" s="567" t="n"/>
-      <c r="C65" s="567" t="n"/>
-      <c r="D65" s="1429" t="n"/>
-      <c r="E65" s="1430" t="n"/>
+      <c r="A65" s="1259" t="n"/>
+      <c r="B65" s="1126" t="n"/>
+      <c r="C65" s="1177" t="n"/>
+      <c r="D65" s="567" t="n"/>
+      <c r="E65" s="567" t="n"/>
       <c r="F65" s="567" t="n"/>
-      <c r="G65" s="383" t="n"/>
-      <c r="H65" s="1192" t="n"/>
-      <c r="I65" s="567" t="n"/>
-      <c r="J65" s="567" t="n"/>
-      <c r="K65" s="1219" t="n"/>
+      <c r="G65" s="1198" t="n"/>
+      <c r="H65" s="567" t="n"/>
+      <c r="I65" s="1126" t="n"/>
+      <c r="J65" s="1126" t="n"/>
+      <c r="K65" s="1424" t="n"/>
       <c r="L65" s="567" t="n"/>
-      <c r="M65" s="1431" t="n"/>
+      <c r="M65" s="567" t="n"/>
       <c r="N65" s="607" t="n"/>
     </row>
     <row r="66">
-      <c r="A66" s="1202" t="n"/>
-      <c r="B66" s="567" t="n"/>
-      <c r="C66" s="567" t="n"/>
-      <c r="D66" s="1429" t="n"/>
-      <c r="E66" s="1430" t="n"/>
+      <c r="A66" s="1184" t="n"/>
+      <c r="B66" s="1136" t="n"/>
+      <c r="C66" s="1177" t="n"/>
+      <c r="D66" s="567" t="n"/>
+      <c r="E66" s="567" t="n"/>
       <c r="F66" s="567" t="n"/>
-      <c r="G66" s="383" t="n"/>
-      <c r="H66" s="1192" t="n"/>
-      <c r="I66" s="567" t="n"/>
-      <c r="J66" s="567" t="n"/>
-      <c r="K66" s="1219" t="n"/>
+      <c r="G66" s="1198" t="n"/>
+      <c r="H66" s="567" t="n"/>
+      <c r="I66" s="1249" t="n"/>
+      <c r="J66" s="1136" t="n"/>
+      <c r="K66" s="1425" t="n"/>
       <c r="L66" s="567" t="n"/>
-      <c r="M66" s="1431" t="n"/>
+      <c r="M66" s="567" t="n"/>
       <c r="N66" s="607" t="n"/>
     </row>
     <row r="67" ht="14.4" customHeight="1" s="550">
-      <c r="A67" s="1257" t="inlineStr">
-        <is>
-          <t>TOTAL INGRESOS</t>
-        </is>
-      </c>
-      <c r="B67" s="1217" t="n"/>
-      <c r="C67" s="1217" t="n"/>
-      <c r="D67" s="1217" t="n"/>
-      <c r="E67" s="1433">
-        <f>SUM(E62:F66)</f>
-        <v/>
-      </c>
-      <c r="F67" s="1217" t="n"/>
-      <c r="G67" s="386" t="n"/>
-      <c r="H67" s="1235" t="inlineStr">
-        <is>
-          <t>TOTAL EGRESOS</t>
-        </is>
-      </c>
-      <c r="I67" s="1064" t="n"/>
-      <c r="J67" s="1064" t="n"/>
-      <c r="K67" s="1064" t="n"/>
-      <c r="L67" s="1064" t="n"/>
-      <c r="M67" s="1434">
-        <f>SUM(M62:N66)</f>
-        <v/>
-      </c>
-      <c r="N67" s="1065" t="n"/>
+      <c r="A67" s="1191" t="n"/>
+      <c r="B67" s="567" t="n"/>
+      <c r="C67" s="1177" t="n"/>
+      <c r="D67" s="567" t="n"/>
+      <c r="E67" s="567" t="n"/>
+      <c r="F67" s="567" t="n"/>
+      <c r="G67" s="1198" t="n"/>
+      <c r="H67" s="567" t="n"/>
+      <c r="I67" s="1201" t="n"/>
+      <c r="J67" s="567" t="n"/>
+      <c r="K67" s="1425" t="n"/>
+      <c r="L67" s="567" t="n"/>
+      <c r="M67" s="567" t="n"/>
+      <c r="N67" s="607" t="n"/>
     </row>
     <row r="68" ht="15.75" customHeight="1" s="550">
-      <c r="A68" s="1181" t="inlineStr">
-        <is>
-          <t>ASPECTOS HSE Y AMBIENTALES</t>
-        </is>
-      </c>
-      <c r="N68" s="562" t="n"/>
+      <c r="A68" s="1191" t="n"/>
+      <c r="B68" s="567" t="n"/>
+      <c r="C68" s="1177" t="n"/>
+      <c r="D68" s="567" t="n"/>
+      <c r="E68" s="567" t="n"/>
+      <c r="F68" s="567" t="n"/>
+      <c r="G68" s="1198" t="n"/>
+      <c r="H68" s="567" t="n"/>
+      <c r="I68" s="1201" t="n"/>
+      <c r="J68" s="567" t="n"/>
+      <c r="K68" s="1425" t="n"/>
+      <c r="L68" s="567" t="n"/>
+      <c r="M68" s="567" t="n"/>
+      <c r="N68" s="607" t="n"/>
+      <c r="S68" s="13" t="n"/>
     </row>
     <row r="69" ht="14.25" customHeight="1" s="550">
-      <c r="A69" s="1221" t="inlineStr">
-        <is>
-          <t>HORAS HOMBRE TRABAJADAS</t>
-        </is>
-      </c>
+      <c r="A69" s="1191" t="n"/>
       <c r="B69" s="567" t="n"/>
-      <c r="C69" s="567" t="n"/>
+      <c r="C69" s="1177" t="n"/>
       <c r="D69" s="567" t="n"/>
       <c r="E69" s="567" t="n"/>
       <c r="F69" s="567" t="n"/>
-      <c r="G69" s="567" t="n"/>
+      <c r="G69" s="1198" t="n"/>
       <c r="H69" s="567" t="n"/>
-      <c r="I69" s="567" t="n"/>
+      <c r="I69" s="1201" t="n"/>
       <c r="J69" s="567" t="n"/>
-      <c r="K69" s="567" t="n"/>
+      <c r="K69" s="1425" t="n"/>
       <c r="L69" s="567" t="n"/>
       <c r="M69" s="567" t="n"/>
       <c r="N69" s="607" t="n"/>
     </row>
     <row r="70">
-      <c r="A70" s="1256" t="n"/>
+      <c r="A70" s="1191" t="n"/>
       <c r="B70" s="567" t="n"/>
-      <c r="C70" s="567" t="n"/>
+      <c r="C70" s="1177" t="n"/>
       <c r="D70" s="567" t="n"/>
       <c r="E70" s="567" t="n"/>
       <c r="F70" s="567" t="n"/>
-      <c r="G70" s="567" t="n"/>
+      <c r="G70" s="1198" t="n"/>
       <c r="H70" s="567" t="n"/>
-      <c r="I70" s="567" t="n"/>
+      <c r="I70" s="1201" t="n"/>
       <c r="J70" s="567" t="n"/>
-      <c r="K70" s="567" t="n"/>
+      <c r="K70" s="1425" t="n"/>
       <c r="L70" s="567" t="n"/>
       <c r="M70" s="567" t="n"/>
       <c r="N70" s="607" t="n"/>
     </row>
     <row r="71" ht="14.25" customHeight="1" s="550">
-      <c r="A71" s="1435" t="inlineStr">
+      <c r="A71" s="1191" t="n"/>
+      <c r="B71" s="567" t="n"/>
+      <c r="C71" s="1177" t="n"/>
+      <c r="D71" s="567" t="n"/>
+      <c r="E71" s="567" t="n"/>
+      <c r="F71" s="567" t="n"/>
+      <c r="G71" s="1198" t="n"/>
+      <c r="H71" s="567" t="n"/>
+      <c r="I71" s="1201" t="n"/>
+      <c r="J71" s="567" t="n"/>
+      <c r="K71" s="1425" t="n"/>
+      <c r="L71" s="567" t="n"/>
+      <c r="M71" s="567" t="n"/>
+      <c r="N71" s="607" t="n"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="1191" t="n"/>
+      <c r="B72" s="567" t="n"/>
+      <c r="C72" s="1177" t="n"/>
+      <c r="D72" s="567" t="n"/>
+      <c r="E72" s="567" t="n"/>
+      <c r="F72" s="567" t="n"/>
+      <c r="G72" s="1198" t="n"/>
+      <c r="H72" s="567" t="n"/>
+      <c r="I72" s="1201" t="n"/>
+      <c r="J72" s="567" t="n"/>
+      <c r="K72" s="1425" t="n"/>
+      <c r="L72" s="567" t="n"/>
+      <c r="M72" s="567" t="n"/>
+      <c r="N72" s="607" t="n"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="1191" t="n"/>
+      <c r="B73" s="567" t="n"/>
+      <c r="C73" s="1177" t="n"/>
+      <c r="D73" s="567" t="n"/>
+      <c r="E73" s="567" t="n"/>
+      <c r="F73" s="567" t="n"/>
+      <c r="G73" s="1198" t="n"/>
+      <c r="H73" s="567" t="n"/>
+      <c r="I73" s="1201" t="n"/>
+      <c r="J73" s="567" t="n"/>
+      <c r="K73" s="1425" t="n"/>
+      <c r="L73" s="567" t="n"/>
+      <c r="M73" s="567" t="n"/>
+      <c r="N73" s="607" t="n"/>
+    </row>
+    <row r="74" ht="14.4" customHeight="1" s="550">
+      <c r="A74" s="1186" t="inlineStr">
+        <is>
+          <t>AVANCE FINANCIERO Y ADMINISTRATIVO</t>
+        </is>
+      </c>
+      <c r="B74" s="1064" t="n"/>
+      <c r="C74" s="1064" t="n"/>
+      <c r="D74" s="1064" t="n"/>
+      <c r="E74" s="1064" t="n"/>
+      <c r="F74" s="1064" t="n"/>
+      <c r="G74" s="1064" t="n"/>
+      <c r="H74" s="1064" t="n"/>
+      <c r="I74" s="1064" t="n"/>
+      <c r="J74" s="1064" t="n"/>
+      <c r="K74" s="1064" t="n"/>
+      <c r="L74" s="1064" t="n"/>
+      <c r="M74" s="1064" t="n"/>
+      <c r="N74" s="1065" t="n"/>
+    </row>
+    <row r="75" ht="14.4" customHeight="1" s="550">
+      <c r="A75" s="1210" t="inlineStr">
+        <is>
+          <t>INGRESOS DEL PERÍODO</t>
+        </is>
+      </c>
+      <c r="B75" s="567" t="n"/>
+      <c r="C75" s="567" t="n"/>
+      <c r="D75" s="567" t="n"/>
+      <c r="E75" s="567" t="n"/>
+      <c r="F75" s="567" t="n"/>
+      <c r="G75" s="383" t="n"/>
+      <c r="H75" s="1228" t="inlineStr">
+        <is>
+          <t>EGRESOS / GASTOS DEL PERÍODO</t>
+        </is>
+      </c>
+      <c r="N75" s="562" t="n"/>
+    </row>
+    <row r="76">
+      <c r="A76" s="1251" t="inlineStr">
+        <is>
+          <t>CONCEPTO</t>
+        </is>
+      </c>
+      <c r="B76" s="567" t="n"/>
+      <c r="C76" s="567" t="n"/>
+      <c r="D76" s="1426" t="inlineStr">
+        <is>
+          <t>FECHA</t>
+        </is>
+      </c>
+      <c r="E76" s="1427" t="inlineStr">
+        <is>
+          <t>VALOR ($)</t>
+        </is>
+      </c>
+      <c r="F76" s="567" t="n"/>
+      <c r="G76" s="385" t="n"/>
+      <c r="H76" s="1238" t="inlineStr">
+        <is>
+          <t>CONCEPTO</t>
+        </is>
+      </c>
+      <c r="I76" s="567" t="n"/>
+      <c r="J76" s="567" t="n"/>
+      <c r="K76" s="1260" t="inlineStr">
+        <is>
+          <t>FECHA</t>
+        </is>
+      </c>
+      <c r="L76" s="609" t="n"/>
+      <c r="M76" s="1428" t="inlineStr">
+        <is>
+          <t>VALOR ($)</t>
+        </is>
+      </c>
+      <c r="N76" s="610" t="n"/>
+    </row>
+    <row r="77" ht="14.25" customHeight="1" s="550">
+      <c r="A77" s="1202" t="n"/>
+      <c r="B77" s="567" t="n"/>
+      <c r="C77" s="567" t="n"/>
+      <c r="D77" s="1429" t="n"/>
+      <c r="E77" s="1430" t="n"/>
+      <c r="F77" s="567" t="n"/>
+      <c r="G77" s="383" t="n"/>
+      <c r="H77" s="1192" t="n"/>
+      <c r="I77" s="567" t="n"/>
+      <c r="J77" s="567" t="n"/>
+      <c r="K77" s="1219" t="n"/>
+      <c r="L77" s="567" t="n"/>
+      <c r="M77" s="1431" t="n"/>
+      <c r="N77" s="607" t="n"/>
+    </row>
+    <row r="78">
+      <c r="A78" s="1202" t="n"/>
+      <c r="B78" s="567" t="n"/>
+      <c r="C78" s="567" t="n"/>
+      <c r="D78" s="1429" t="n"/>
+      <c r="E78" s="1430" t="n"/>
+      <c r="F78" s="567" t="n"/>
+      <c r="G78" s="383" t="n"/>
+      <c r="H78" s="1192" t="n"/>
+      <c r="I78" s="567" t="n"/>
+      <c r="J78" s="567" t="n"/>
+      <c r="K78" s="1219" t="n"/>
+      <c r="L78" s="567" t="n"/>
+      <c r="M78" s="1431" t="n"/>
+      <c r="N78" s="607" t="n"/>
+    </row>
+    <row r="79">
+      <c r="A79" s="1202" t="n"/>
+      <c r="B79" s="567" t="n"/>
+      <c r="C79" s="567" t="n"/>
+      <c r="D79" s="1429" t="n"/>
+      <c r="E79" s="1430" t="n"/>
+      <c r="F79" s="567" t="n"/>
+      <c r="G79" s="383" t="n"/>
+      <c r="H79" s="1192" t="n"/>
+      <c r="I79" s="567" t="n"/>
+      <c r="J79" s="567" t="n"/>
+      <c r="K79" s="1219" t="n"/>
+      <c r="L79" s="567" t="n"/>
+      <c r="M79" s="1431" t="n"/>
+      <c r="N79" s="607" t="n"/>
+    </row>
+    <row r="80" ht="15.75" customHeight="1" s="550">
+      <c r="A80" s="1202" t="n"/>
+      <c r="B80" s="567" t="n"/>
+      <c r="C80" s="567" t="n"/>
+      <c r="D80" s="1429" t="n"/>
+      <c r="E80" s="1430" t="n"/>
+      <c r="F80" s="567" t="n"/>
+      <c r="G80" s="383" t="n"/>
+      <c r="H80" s="1192" t="n"/>
+      <c r="I80" s="567" t="n"/>
+      <c r="J80" s="567" t="n"/>
+      <c r="K80" s="1219" t="n"/>
+      <c r="L80" s="567" t="n"/>
+      <c r="M80" s="1431" t="n"/>
+      <c r="N80" s="607" t="n"/>
+    </row>
+    <row r="81" ht="14.4" customHeight="1" s="550">
+      <c r="A81" s="1202" t="n"/>
+      <c r="B81" s="567" t="n"/>
+      <c r="C81" s="567" t="n"/>
+      <c r="D81" s="1429" t="n"/>
+      <c r="E81" s="1430" t="n"/>
+      <c r="F81" s="567" t="n"/>
+      <c r="G81" s="383" t="n"/>
+      <c r="H81" s="1192" t="n"/>
+      <c r="I81" s="567" t="n"/>
+      <c r="J81" s="567" t="n"/>
+      <c r="K81" s="1219" t="n"/>
+      <c r="L81" s="567" t="n"/>
+      <c r="M81" s="1431" t="n"/>
+      <c r="N81" s="607" t="n"/>
+    </row>
+    <row r="82" ht="14.4" customHeight="1" s="550">
+      <c r="A82" s="1257" t="inlineStr">
+        <is>
+          <t>TOTAL INGRESOS</t>
+        </is>
+      </c>
+      <c r="B82" s="1217" t="n"/>
+      <c r="C82" s="1217" t="n"/>
+      <c r="D82" s="1217" t="n"/>
+      <c r="E82" s="1433">
+        <f>SUM(E77:F81)</f>
+        <v/>
+      </c>
+      <c r="F82" s="1217" t="n"/>
+      <c r="G82" s="386" t="n"/>
+      <c r="H82" s="1235" t="inlineStr">
+        <is>
+          <t>TOTAL EGRESOS</t>
+        </is>
+      </c>
+      <c r="I82" s="1064" t="n"/>
+      <c r="J82" s="1064" t="n"/>
+      <c r="K82" s="1064" t="n"/>
+      <c r="L82" s="1064" t="n"/>
+      <c r="M82" s="1434">
+        <f>SUM(M77:N81)</f>
+        <v/>
+      </c>
+      <c r="N82" s="1065" t="n"/>
+    </row>
+    <row r="83" ht="15.75" customHeight="1" s="550">
+      <c r="A83" s="1181" t="inlineStr">
+        <is>
+          <t>ASPECTOS HSE Y AMBIENTALES</t>
+        </is>
+      </c>
+      <c r="N83" s="562" t="n"/>
+    </row>
+    <row r="84" ht="14.25" customHeight="1" s="550">
+      <c r="A84" s="1221" t="inlineStr">
+        <is>
+          <t>HORAS HOMBRE TRABAJADAS</t>
+        </is>
+      </c>
+      <c r="B84" s="567" t="n"/>
+      <c r="C84" s="567" t="n"/>
+      <c r="D84" s="567" t="n"/>
+      <c r="E84" s="567" t="n"/>
+      <c r="F84" s="567" t="n"/>
+      <c r="G84" s="567" t="n"/>
+      <c r="H84" s="567" t="n"/>
+      <c r="I84" s="567" t="n"/>
+      <c r="J84" s="567" t="n"/>
+      <c r="K84" s="567" t="n"/>
+      <c r="L84" s="567" t="n"/>
+      <c r="M84" s="567" t="n"/>
+      <c r="N84" s="607" t="n"/>
+    </row>
+    <row r="85">
+      <c r="A85" s="1256" t="n"/>
+      <c r="B85" s="567" t="n"/>
+      <c r="C85" s="567" t="n"/>
+      <c r="D85" s="567" t="n"/>
+      <c r="E85" s="567" t="n"/>
+      <c r="F85" s="567" t="n"/>
+      <c r="G85" s="567" t="n"/>
+      <c r="H85" s="567" t="n"/>
+      <c r="I85" s="567" t="n"/>
+      <c r="J85" s="567" t="n"/>
+      <c r="K85" s="567" t="n"/>
+      <c r="L85" s="567" t="n"/>
+      <c r="M85" s="567" t="n"/>
+      <c r="N85" s="607" t="n"/>
+    </row>
+    <row r="86" ht="14.25" customHeight="1" s="550">
+      <c r="A86" s="1435" t="inlineStr">
         <is>
           <t>OBSERVACIONES HSE</t>
         </is>
       </c>
-      <c r="N71" s="562" t="n"/>
-    </row>
-    <row r="72">
-      <c r="A72" s="1436" t="n"/>
-      <c r="N72" s="562" t="n"/>
-    </row>
-    <row r="73">
-      <c r="A73" s="1207" t="inlineStr">
+      <c r="N86" s="562" t="n"/>
+    </row>
+    <row r="87">
+      <c r="A87" s="1436" t="n"/>
+      <c r="N87" s="562" t="n"/>
+    </row>
+    <row r="88">
+      <c r="A88" s="1207" t="inlineStr">
         <is>
           <t>INSERTAR FOTOGRAFÍA</t>
         </is>
       </c>
-      <c r="B73" s="776" t="n"/>
-      <c r="C73" s="776" t="n"/>
-      <c r="D73" s="776" t="n"/>
-      <c r="E73" s="776" t="n"/>
-      <c r="F73" s="776" t="n"/>
-      <c r="G73" s="777" t="n"/>
-      <c r="H73" s="1189" t="inlineStr">
+      <c r="B88" s="776" t="n"/>
+      <c r="C88" s="776" t="n"/>
+      <c r="D88" s="776" t="n"/>
+      <c r="E88" s="776" t="n"/>
+      <c r="F88" s="776" t="n"/>
+      <c r="G88" s="777" t="n"/>
+      <c r="H88" s="1189" t="inlineStr">
         <is>
           <t>INSERTAR FOTOGRAFÍA</t>
         </is>
       </c>
-      <c r="I73" s="776" t="n"/>
-      <c r="J73" s="776" t="n"/>
-      <c r="K73" s="776" t="n"/>
-      <c r="L73" s="776" t="n"/>
-      <c r="M73" s="776" t="n"/>
-      <c r="N73" s="777" t="n"/>
-    </row>
-    <row r="74" ht="14.25" customHeight="1" s="550">
-      <c r="A74" s="1066" t="n"/>
-      <c r="G74" s="780" t="n"/>
-      <c r="H74" s="778" t="n"/>
-      <c r="N74" s="780" t="n"/>
-    </row>
-    <row r="75">
-      <c r="A75" s="1066" t="n"/>
-      <c r="G75" s="780" t="n"/>
-      <c r="H75" s="778" t="n"/>
-      <c r="N75" s="780" t="n"/>
-    </row>
-    <row r="76">
-      <c r="A76" s="1066" t="n"/>
-      <c r="G76" s="780" t="n"/>
-      <c r="H76" s="778" t="n"/>
-      <c r="N76" s="780" t="n"/>
-    </row>
-    <row r="77" ht="14.25" customHeight="1" s="550">
-      <c r="A77" s="1066" t="n"/>
-      <c r="G77" s="780" t="n"/>
-      <c r="H77" s="778" t="n"/>
-      <c r="N77" s="780" t="n"/>
-    </row>
-    <row r="78">
-      <c r="A78" s="1066" t="n"/>
-      <c r="G78" s="780" t="n"/>
-      <c r="H78" s="778" t="n"/>
-      <c r="N78" s="780" t="n"/>
-    </row>
-    <row r="79">
-      <c r="A79" s="1066" t="n"/>
-      <c r="G79" s="780" t="n"/>
-      <c r="H79" s="778" t="n"/>
-      <c r="N79" s="780" t="n"/>
-    </row>
-    <row r="80" ht="15.75" customHeight="1" s="550">
-      <c r="A80" s="1066" t="n"/>
-      <c r="G80" s="780" t="n"/>
-      <c r="H80" s="778" t="n"/>
-      <c r="N80" s="780" t="n"/>
-    </row>
-    <row r="81" ht="14.4" customHeight="1" s="550">
-      <c r="A81" s="1066" t="n"/>
-      <c r="G81" s="780" t="n"/>
-      <c r="H81" s="778" t="n"/>
-      <c r="N81" s="780" t="n"/>
-    </row>
-    <row r="82">
-      <c r="A82" s="1066" t="n"/>
-      <c r="G82" s="780" t="n"/>
-      <c r="H82" s="778" t="n"/>
-      <c r="N82" s="780" t="n"/>
-    </row>
-    <row r="83">
-      <c r="A83" s="1066" t="n"/>
-      <c r="G83" s="780" t="n"/>
-      <c r="H83" s="778" t="n"/>
-      <c r="N83" s="780" t="n"/>
-    </row>
-    <row r="84">
-      <c r="A84" s="1066" t="n"/>
-      <c r="G84" s="780" t="n"/>
-      <c r="H84" s="778" t="n"/>
-      <c r="N84" s="780" t="n"/>
-    </row>
-    <row r="85">
-      <c r="A85" s="1066" t="n"/>
-      <c r="G85" s="780" t="n"/>
-      <c r="H85" s="778" t="n"/>
-      <c r="N85" s="780" t="n"/>
-    </row>
-    <row r="86">
-      <c r="A86" s="1208" t="n"/>
-      <c r="B86" s="782" t="n"/>
-      <c r="C86" s="782" t="n"/>
-      <c r="D86" s="782" t="n"/>
-      <c r="E86" s="782" t="n"/>
-      <c r="F86" s="782" t="n"/>
-      <c r="G86" s="783" t="n"/>
-      <c r="H86" s="781" t="n"/>
-      <c r="I86" s="782" t="n"/>
-      <c r="J86" s="782" t="n"/>
-      <c r="K86" s="782" t="n"/>
-      <c r="L86" s="782" t="n"/>
-      <c r="M86" s="782" t="n"/>
-      <c r="N86" s="783" t="n"/>
-    </row>
-    <row r="87">
-      <c r="A87" s="1404" t="n"/>
-      <c r="H87" s="1404" t="n"/>
-    </row>
-    <row r="88"/>
-    <row r="89">
-      <c r="A89" s="1207" t="inlineStr">
-        <is>
-          <t>INSERTAR FOTOGRAFÍA</t>
-        </is>
-      </c>
-      <c r="B89" s="776" t="n"/>
-      <c r="C89" s="776" t="n"/>
-      <c r="D89" s="776" t="n"/>
-      <c r="E89" s="776" t="n"/>
-      <c r="F89" s="776" t="n"/>
-      <c r="G89" s="777" t="n"/>
-      <c r="H89" s="1189" t="inlineStr">
-        <is>
-          <t>INSERTAR FOTOGRAFÍA</t>
-        </is>
-      </c>
-      <c r="I89" s="776" t="n"/>
-      <c r="J89" s="776" t="n"/>
-      <c r="K89" s="776" t="n"/>
-      <c r="L89" s="776" t="n"/>
-      <c r="M89" s="776" t="n"/>
-      <c r="N89" s="777" t="n"/>
+      <c r="I88" s="776" t="n"/>
+      <c r="J88" s="776" t="n"/>
+      <c r="K88" s="776" t="n"/>
+      <c r="L88" s="776" t="n"/>
+      <c r="M88" s="776" t="n"/>
+      <c r="N88" s="777" t="n"/>
+    </row>
+    <row r="89" ht="14.25" customHeight="1" s="550">
+      <c r="A89" s="1066" t="n"/>
+      <c r="G89" s="780" t="n"/>
+      <c r="H89" s="778" t="n"/>
+      <c r="N89" s="780" t="n"/>
     </row>
     <row r="90">
       <c r="A90" s="1066" t="n"/>
@@ -18100,7 +18361,7 @@
       <c r="H91" s="778" t="n"/>
       <c r="N91" s="780" t="n"/>
     </row>
-    <row r="92">
+    <row r="92" ht="14.25" customHeight="1" s="550">
       <c r="A92" s="1066" t="n"/>
       <c r="G92" s="780" t="n"/>
       <c r="H92" s="778" t="n"/>
@@ -18118,13 +18379,13 @@
       <c r="H94" s="778" t="n"/>
       <c r="N94" s="780" t="n"/>
     </row>
-    <row r="95">
+    <row r="95" ht="15.75" customHeight="1" s="550">
       <c r="A95" s="1066" t="n"/>
       <c r="G95" s="780" t="n"/>
       <c r="H95" s="778" t="n"/>
       <c r="N95" s="780" t="n"/>
     </row>
-    <row r="96">
+    <row r="96" ht="14.4" customHeight="1" s="550">
       <c r="A96" s="1066" t="n"/>
       <c r="G96" s="780" t="n"/>
       <c r="H96" s="778" t="n"/>
@@ -18155,55 +18416,55 @@
       <c r="N100" s="780" t="n"/>
     </row>
     <row r="101">
-      <c r="A101" s="1066" t="n"/>
-      <c r="G101" s="780" t="n"/>
-      <c r="H101" s="778" t="n"/>
-      <c r="N101" s="780" t="n"/>
+      <c r="A101" s="1208" t="n"/>
+      <c r="B101" s="782" t="n"/>
+      <c r="C101" s="782" t="n"/>
+      <c r="D101" s="782" t="n"/>
+      <c r="E101" s="782" t="n"/>
+      <c r="F101" s="782" t="n"/>
+      <c r="G101" s="783" t="n"/>
+      <c r="H101" s="781" t="n"/>
+      <c r="I101" s="782" t="n"/>
+      <c r="J101" s="782" t="n"/>
+      <c r="K101" s="782" t="n"/>
+      <c r="L101" s="782" t="n"/>
+      <c r="M101" s="782" t="n"/>
+      <c r="N101" s="783" t="n"/>
     </row>
     <row r="102">
-      <c r="A102" s="1208" t="n"/>
-      <c r="B102" s="782" t="n"/>
-      <c r="C102" s="782" t="n"/>
-      <c r="D102" s="782" t="n"/>
-      <c r="E102" s="782" t="n"/>
-      <c r="F102" s="782" t="n"/>
-      <c r="G102" s="783" t="n"/>
-      <c r="H102" s="781" t="n"/>
-      <c r="I102" s="782" t="n"/>
-      <c r="J102" s="782" t="n"/>
-      <c r="K102" s="782" t="n"/>
-      <c r="L102" s="782" t="n"/>
-      <c r="M102" s="782" t="n"/>
-      <c r="N102" s="783" t="n"/>
-    </row>
-    <row r="103">
-      <c r="A103" s="1404" t="n"/>
-      <c r="H103" s="1404" t="n"/>
-    </row>
-    <row r="104"/>
+      <c r="A102" s="1404" t="n"/>
+      <c r="H102" s="1404" t="n"/>
+    </row>
+    <row r="103"/>
+    <row r="104">
+      <c r="A104" s="1207" t="inlineStr">
+        <is>
+          <t>INSERTAR FOTOGRAFÍA</t>
+        </is>
+      </c>
+      <c r="B104" s="776" t="n"/>
+      <c r="C104" s="776" t="n"/>
+      <c r="D104" s="776" t="n"/>
+      <c r="E104" s="776" t="n"/>
+      <c r="F104" s="776" t="n"/>
+      <c r="G104" s="777" t="n"/>
+      <c r="H104" s="1189" t="inlineStr">
+        <is>
+          <t>INSERTAR FOTOGRAFÍA</t>
+        </is>
+      </c>
+      <c r="I104" s="776" t="n"/>
+      <c r="J104" s="776" t="n"/>
+      <c r="K104" s="776" t="n"/>
+      <c r="L104" s="776" t="n"/>
+      <c r="M104" s="776" t="n"/>
+      <c r="N104" s="777" t="n"/>
+    </row>
     <row r="105">
-      <c r="A105" s="1207" t="inlineStr">
-        <is>
-          <t>INSERTAR FOTOGRAFÍA</t>
-        </is>
-      </c>
-      <c r="B105" s="776" t="n"/>
-      <c r="C105" s="776" t="n"/>
-      <c r="D105" s="776" t="n"/>
-      <c r="E105" s="776" t="n"/>
-      <c r="F105" s="776" t="n"/>
-      <c r="G105" s="777" t="n"/>
-      <c r="H105" s="1189" t="inlineStr">
-        <is>
-          <t>INSERTAR FOTOGRAFÍA</t>
-        </is>
-      </c>
-      <c r="I105" s="776" t="n"/>
-      <c r="J105" s="776" t="n"/>
-      <c r="K105" s="776" t="n"/>
-      <c r="L105" s="776" t="n"/>
-      <c r="M105" s="776" t="n"/>
-      <c r="N105" s="777" t="n"/>
+      <c r="A105" s="1066" t="n"/>
+      <c r="G105" s="780" t="n"/>
+      <c r="H105" s="778" t="n"/>
+      <c r="N105" s="780" t="n"/>
     </row>
     <row r="106">
       <c r="A106" s="1066" t="n"/>
@@ -18272,423 +18533,564 @@
       <c r="N116" s="780" t="n"/>
     </row>
     <row r="117">
-      <c r="A117" s="1066" t="n"/>
-      <c r="G117" s="780" t="n"/>
-      <c r="H117" s="778" t="n"/>
-      <c r="N117" s="780" t="n"/>
+      <c r="A117" s="1208" t="n"/>
+      <c r="B117" s="782" t="n"/>
+      <c r="C117" s="782" t="n"/>
+      <c r="D117" s="782" t="n"/>
+      <c r="E117" s="782" t="n"/>
+      <c r="F117" s="782" t="n"/>
+      <c r="G117" s="783" t="n"/>
+      <c r="H117" s="781" t="n"/>
+      <c r="I117" s="782" t="n"/>
+      <c r="J117" s="782" t="n"/>
+      <c r="K117" s="782" t="n"/>
+      <c r="L117" s="782" t="n"/>
+      <c r="M117" s="782" t="n"/>
+      <c r="N117" s="783" t="n"/>
     </row>
     <row r="118">
-      <c r="A118" s="1208" t="n"/>
-      <c r="B118" s="782" t="n"/>
-      <c r="C118" s="782" t="n"/>
-      <c r="D118" s="782" t="n"/>
-      <c r="E118" s="782" t="n"/>
-      <c r="F118" s="782" t="n"/>
-      <c r="G118" s="783" t="n"/>
-      <c r="H118" s="781" t="n"/>
-      <c r="I118" s="782" t="n"/>
-      <c r="J118" s="782" t="n"/>
-      <c r="K118" s="782" t="n"/>
-      <c r="L118" s="782" t="n"/>
-      <c r="M118" s="782" t="n"/>
-      <c r="N118" s="783" t="n"/>
-    </row>
-    <row r="119">
-      <c r="A119" s="1404" t="n"/>
-      <c r="H119" s="1404" t="n"/>
-    </row>
-    <row r="120"/>
+      <c r="A118" s="1404" t="n"/>
+      <c r="H118" s="1404" t="n"/>
+    </row>
+    <row r="119"/>
+    <row r="120">
+      <c r="A120" s="1207" t="inlineStr">
+        <is>
+          <t>INSERTAR FOTOGRAFÍA</t>
+        </is>
+      </c>
+      <c r="B120" s="776" t="n"/>
+      <c r="C120" s="776" t="n"/>
+      <c r="D120" s="776" t="n"/>
+      <c r="E120" s="776" t="n"/>
+      <c r="F120" s="776" t="n"/>
+      <c r="G120" s="777" t="n"/>
+      <c r="H120" s="1189" t="inlineStr">
+        <is>
+          <t>INSERTAR FOTOGRAFÍA</t>
+        </is>
+      </c>
+      <c r="I120" s="776" t="n"/>
+      <c r="J120" s="776" t="n"/>
+      <c r="K120" s="776" t="n"/>
+      <c r="L120" s="776" t="n"/>
+      <c r="M120" s="776" t="n"/>
+      <c r="N120" s="777" t="n"/>
+    </row>
     <row r="121">
-      <c r="A121" s="1254" t="n"/>
+      <c r="A121" s="1066" t="n"/>
       <c r="G121" s="780" t="n"/>
-      <c r="H121" s="1226" t="n"/>
+      <c r="H121" s="778" t="n"/>
       <c r="N121" s="780" t="n"/>
     </row>
     <row r="122">
-      <c r="A122" s="1250" t="inlineStr">
+      <c r="A122" s="1066" t="n"/>
+      <c r="G122" s="780" t="n"/>
+      <c r="H122" s="778" t="n"/>
+      <c r="N122" s="780" t="n"/>
+    </row>
+    <row r="123" ht="14.4" customHeight="1" s="550">
+      <c r="A123" s="1066" t="n"/>
+      <c r="G123" s="780" t="n"/>
+      <c r="H123" s="778" t="n"/>
+      <c r="N123" s="780" t="n"/>
+    </row>
+    <row r="124">
+      <c r="A124" s="1066" t="n"/>
+      <c r="G124" s="780" t="n"/>
+      <c r="H124" s="778" t="n"/>
+      <c r="N124" s="780" t="n"/>
+    </row>
+    <row r="125">
+      <c r="A125" s="1066" t="n"/>
+      <c r="G125" s="780" t="n"/>
+      <c r="H125" s="778" t="n"/>
+      <c r="N125" s="780" t="n"/>
+    </row>
+    <row r="126">
+      <c r="A126" s="1066" t="n"/>
+      <c r="G126" s="780" t="n"/>
+      <c r="H126" s="778" t="n"/>
+      <c r="N126" s="780" t="n"/>
+    </row>
+    <row r="127">
+      <c r="A127" s="1066" t="n"/>
+      <c r="G127" s="780" t="n"/>
+      <c r="H127" s="778" t="n"/>
+      <c r="N127" s="780" t="n"/>
+    </row>
+    <row r="128">
+      <c r="A128" s="1066" t="n"/>
+      <c r="G128" s="780" t="n"/>
+      <c r="H128" s="778" t="n"/>
+      <c r="N128" s="780" t="n"/>
+    </row>
+    <row r="129">
+      <c r="A129" s="1066" t="n"/>
+      <c r="G129" s="780" t="n"/>
+      <c r="H129" s="778" t="n"/>
+      <c r="N129" s="780" t="n"/>
+    </row>
+    <row r="130">
+      <c r="A130" s="1066" t="n"/>
+      <c r="G130" s="780" t="n"/>
+      <c r="H130" s="778" t="n"/>
+      <c r="N130" s="780" t="n"/>
+    </row>
+    <row r="131">
+      <c r="A131" s="1066" t="n"/>
+      <c r="G131" s="780" t="n"/>
+      <c r="H131" s="778" t="n"/>
+      <c r="N131" s="780" t="n"/>
+    </row>
+    <row r="132">
+      <c r="A132" s="1066" t="n"/>
+      <c r="G132" s="780" t="n"/>
+      <c r="H132" s="778" t="n"/>
+      <c r="N132" s="780" t="n"/>
+    </row>
+    <row r="133">
+      <c r="A133" s="1208" t="n"/>
+      <c r="B133" s="782" t="n"/>
+      <c r="C133" s="782" t="n"/>
+      <c r="D133" s="782" t="n"/>
+      <c r="E133" s="782" t="n"/>
+      <c r="F133" s="782" t="n"/>
+      <c r="G133" s="783" t="n"/>
+      <c r="H133" s="781" t="n"/>
+      <c r="I133" s="782" t="n"/>
+      <c r="J133" s="782" t="n"/>
+      <c r="K133" s="782" t="n"/>
+      <c r="L133" s="782" t="n"/>
+      <c r="M133" s="782" t="n"/>
+      <c r="N133" s="783" t="n"/>
+    </row>
+    <row r="134">
+      <c r="A134" s="1404" t="n"/>
+      <c r="H134" s="1404" t="n"/>
+    </row>
+    <row r="135"/>
+    <row r="136">
+      <c r="A136" s="1254" t="n"/>
+      <c r="G136" s="780" t="n"/>
+      <c r="H136" s="1226" t="n"/>
+      <c r="N136" s="780" t="n"/>
+    </row>
+    <row r="137">
+      <c r="A137" s="1250" t="inlineStr">
         <is>
           <t>FIRMAS</t>
         </is>
       </c>
-      <c r="N122" s="1100" t="n"/>
-    </row>
-    <row r="123" ht="14.4" customHeight="1" s="550">
-      <c r="A123" s="1258" t="inlineStr">
+      <c r="N137" s="1100" t="n"/>
+    </row>
+    <row r="138" ht="14.4" customHeight="1" s="550">
+      <c r="A138" s="1258" t="inlineStr">
         <is>
           <t>ELABORADO POR</t>
         </is>
       </c>
-      <c r="E123" s="1218" t="inlineStr">
+      <c r="E138" s="1218" t="inlineStr">
         <is>
           <t>REVISADO POR</t>
         </is>
       </c>
-      <c r="J123" s="1220" t="inlineStr">
+      <c r="J138" s="1220" t="inlineStr">
         <is>
           <t>APROBADO POR</t>
         </is>
       </c>
-      <c r="N123" s="562" t="n"/>
-    </row>
-    <row r="124">
-      <c r="A124" s="1255" t="inlineStr">
+      <c r="N138" s="562" t="n"/>
+    </row>
+    <row r="139">
+      <c r="A139" s="1255" t="inlineStr">
         <is>
           <t>FIRMA:</t>
         </is>
       </c>
-      <c r="B124" s="1179" t="n"/>
-      <c r="C124" s="1064" t="n"/>
-      <c r="D124" s="1064" t="n"/>
-      <c r="E124" s="1229" t="inlineStr">
+      <c r="B139" s="1179" t="n"/>
+      <c r="C139" s="1064" t="n"/>
+      <c r="D139" s="1064" t="n"/>
+      <c r="E139" s="1229" t="inlineStr">
         <is>
           <t>FIRMA:</t>
         </is>
       </c>
-      <c r="F124" s="1179" t="n"/>
-      <c r="G124" s="1064" t="n"/>
-      <c r="H124" s="1064" t="n"/>
-      <c r="I124" s="1064" t="n"/>
-      <c r="J124" s="1229" t="inlineStr">
+      <c r="F139" s="1179" t="n"/>
+      <c r="G139" s="1064" t="n"/>
+      <c r="H139" s="1064" t="n"/>
+      <c r="I139" s="1064" t="n"/>
+      <c r="J139" s="1229" t="inlineStr">
         <is>
           <t>FIRMA:</t>
         </is>
       </c>
-      <c r="K124" s="1214" t="n"/>
-      <c r="N124" s="562" t="n"/>
-    </row>
-    <row r="125">
-      <c r="A125" s="1077" t="n"/>
-      <c r="B125" s="609" t="n"/>
-      <c r="C125" s="609" t="n"/>
-      <c r="D125" s="609" t="n"/>
-      <c r="E125" s="609" t="n"/>
-      <c r="F125" s="609" t="n"/>
-      <c r="G125" s="609" t="n"/>
-      <c r="H125" s="609" t="n"/>
-      <c r="I125" s="609" t="n"/>
-      <c r="J125" s="609" t="n"/>
-      <c r="N125" s="562" t="n"/>
-    </row>
-    <row r="126">
-      <c r="A126" s="1255" t="inlineStr">
+      <c r="K139" s="1214" t="n"/>
+      <c r="N139" s="562" t="n"/>
+    </row>
+    <row r="140">
+      <c r="A140" s="1077" t="n"/>
+      <c r="B140" s="609" t="n"/>
+      <c r="C140" s="609" t="n"/>
+      <c r="D140" s="609" t="n"/>
+      <c r="E140" s="609" t="n"/>
+      <c r="F140" s="609" t="n"/>
+      <c r="G140" s="609" t="n"/>
+      <c r="H140" s="609" t="n"/>
+      <c r="I140" s="609" t="n"/>
+      <c r="J140" s="609" t="n"/>
+      <c r="N140" s="562" t="n"/>
+    </row>
+    <row r="141">
+      <c r="A141" s="1255" t="inlineStr">
         <is>
           <t>NOMBRE:</t>
         </is>
       </c>
-      <c r="B126" s="1179" t="n"/>
-      <c r="C126" s="1064" t="n"/>
-      <c r="D126" s="1064" t="n"/>
-      <c r="E126" s="1229" t="inlineStr">
+      <c r="B141" s="1179" t="n"/>
+      <c r="C141" s="1064" t="n"/>
+      <c r="D141" s="1064" t="n"/>
+      <c r="E141" s="1229" t="inlineStr">
         <is>
           <t>NOMBRE:</t>
         </is>
       </c>
-      <c r="F126" s="1179" t="n"/>
-      <c r="G126" s="1064" t="n"/>
-      <c r="H126" s="1064" t="n"/>
-      <c r="I126" s="1064" t="n"/>
-      <c r="J126" s="1229" t="inlineStr">
+      <c r="F141" s="1179" t="n"/>
+      <c r="G141" s="1064" t="n"/>
+      <c r="H141" s="1064" t="n"/>
+      <c r="I141" s="1064" t="n"/>
+      <c r="J141" s="1229" t="inlineStr">
         <is>
           <t>NOMBRE:</t>
         </is>
       </c>
-      <c r="K126" s="1214" t="n"/>
-      <c r="N126" s="562" t="n"/>
-    </row>
-    <row r="127">
-      <c r="A127" s="1077" t="n"/>
-      <c r="B127" s="609" t="n"/>
-      <c r="C127" s="609" t="n"/>
-      <c r="D127" s="609" t="n"/>
-      <c r="E127" s="609" t="n"/>
-      <c r="F127" s="609" t="n"/>
-      <c r="G127" s="609" t="n"/>
-      <c r="H127" s="609" t="n"/>
-      <c r="I127" s="609" t="n"/>
-      <c r="J127" s="609" t="n"/>
-      <c r="N127" s="562" t="n"/>
-    </row>
-    <row r="128">
-      <c r="A128" s="1178" t="inlineStr">
+      <c r="K141" s="1214" t="n"/>
+      <c r="N141" s="562" t="n"/>
+    </row>
+    <row r="142">
+      <c r="A142" s="1077" t="n"/>
+      <c r="B142" s="609" t="n"/>
+      <c r="C142" s="609" t="n"/>
+      <c r="D142" s="609" t="n"/>
+      <c r="E142" s="609" t="n"/>
+      <c r="F142" s="609" t="n"/>
+      <c r="G142" s="609" t="n"/>
+      <c r="H142" s="609" t="n"/>
+      <c r="I142" s="609" t="n"/>
+      <c r="J142" s="609" t="n"/>
+      <c r="N142" s="562" t="n"/>
+    </row>
+    <row r="143">
+      <c r="A143" s="1178" t="inlineStr">
         <is>
           <t>CARGO:</t>
         </is>
       </c>
-      <c r="B128" s="1211" t="n"/>
-      <c r="C128" s="1064" t="n"/>
-      <c r="D128" s="1064" t="n"/>
-      <c r="E128" s="1200" t="inlineStr">
+      <c r="B143" s="1211" t="n"/>
+      <c r="C143" s="1064" t="n"/>
+      <c r="D143" s="1064" t="n"/>
+      <c r="E143" s="1200" t="inlineStr">
         <is>
           <t>CARGO:</t>
         </is>
       </c>
-      <c r="F128" s="1211" t="n"/>
-      <c r="G128" s="1064" t="n"/>
-      <c r="H128" s="1064" t="n"/>
-      <c r="I128" s="1064" t="n"/>
-      <c r="J128" s="1200" t="inlineStr">
+      <c r="F143" s="1211" t="n"/>
+      <c r="G143" s="1064" t="n"/>
+      <c r="H143" s="1064" t="n"/>
+      <c r="I143" s="1064" t="n"/>
+      <c r="J143" s="1200" t="inlineStr">
         <is>
           <t>CARGO:</t>
         </is>
       </c>
-      <c r="K128" s="1231" t="n"/>
-      <c r="N128" s="562" t="n"/>
-    </row>
-    <row r="129">
-      <c r="A129" s="1067" t="n"/>
-      <c r="B129" s="557" t="n"/>
-      <c r="C129" s="557" t="n"/>
-      <c r="D129" s="557" t="n"/>
-      <c r="E129" s="557" t="n"/>
-      <c r="F129" s="557" t="n"/>
-      <c r="G129" s="557" t="n"/>
-      <c r="H129" s="557" t="n"/>
-      <c r="I129" s="557" t="n"/>
-      <c r="J129" s="557" t="n"/>
-      <c r="K129" s="557" t="n"/>
-      <c r="L129" s="557" t="n"/>
-      <c r="M129" s="557" t="n"/>
-      <c r="N129" s="763" t="n"/>
-    </row>
-    <row r="130">
-      <c r="A130" s="205" t="inlineStr">
+      <c r="K143" s="1231" t="n"/>
+      <c r="N143" s="562" t="n"/>
+    </row>
+    <row r="144">
+      <c r="A144" s="1067" t="n"/>
+      <c r="B144" s="557" t="n"/>
+      <c r="C144" s="557" t="n"/>
+      <c r="D144" s="557" t="n"/>
+      <c r="E144" s="557" t="n"/>
+      <c r="F144" s="557" t="n"/>
+      <c r="G144" s="557" t="n"/>
+      <c r="H144" s="557" t="n"/>
+      <c r="I144" s="557" t="n"/>
+      <c r="J144" s="557" t="n"/>
+      <c r="K144" s="557" t="n"/>
+      <c r="L144" s="557" t="n"/>
+      <c r="M144" s="557" t="n"/>
+      <c r="N144" s="763" t="n"/>
+    </row>
+    <row r="145">
+      <c r="A145" s="205" t="inlineStr">
         <is>
           <t>REV. 10/09/2026</t>
         </is>
       </c>
-      <c r="N130" s="215">
+      <c r="N145" s="215">
         <f>M8</f>
         <v/>
       </c>
-      <c r="O130" s="24" t="n"/>
-    </row>
-    <row r="131">
-      <c r="N131" s="216" t="n"/>
-      <c r="O131" s="25" t="n"/>
+      <c r="O145" s="24" t="n"/>
+    </row>
+    <row r="146">
+      <c r="N146" s="216" t="n"/>
+      <c r="O146" s="25" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="221">
-    <mergeCell ref="C52:F52"/>
-    <mergeCell ref="A128:A129"/>
-    <mergeCell ref="B124:D125"/>
+  <mergeCells count="251">
+    <mergeCell ref="A64:B64"/>
     <mergeCell ref="A37:C37"/>
-    <mergeCell ref="A48:N48"/>
-    <mergeCell ref="A46:C46"/>
-    <mergeCell ref="A51:B51"/>
-    <mergeCell ref="E62:F62"/>
-    <mergeCell ref="A59:N59"/>
+    <mergeCell ref="A73:B73"/>
+    <mergeCell ref="G71:H71"/>
     <mergeCell ref="E23:E24"/>
     <mergeCell ref="A21:C21"/>
-    <mergeCell ref="F124:I125"/>
+    <mergeCell ref="J57:N57"/>
+    <mergeCell ref="M79:N79"/>
+    <mergeCell ref="A57:C57"/>
+    <mergeCell ref="A13:D13"/>
+    <mergeCell ref="E79:F79"/>
+    <mergeCell ref="M82:N82"/>
+    <mergeCell ref="H22:J22"/>
+    <mergeCell ref="K81:L81"/>
+    <mergeCell ref="M10:N10"/>
+    <mergeCell ref="A15:D15"/>
+    <mergeCell ref="G66:H66"/>
+    <mergeCell ref="I66:J66"/>
+    <mergeCell ref="A137:N137"/>
+    <mergeCell ref="A43:C43"/>
+    <mergeCell ref="J35:N35"/>
+    <mergeCell ref="A52:C52"/>
+    <mergeCell ref="A141:A142"/>
+    <mergeCell ref="C64:F64"/>
+    <mergeCell ref="G68:H68"/>
+    <mergeCell ref="C73:F73"/>
+    <mergeCell ref="A88:G101"/>
+    <mergeCell ref="A34:C34"/>
+    <mergeCell ref="A143:A144"/>
+    <mergeCell ref="J50:N50"/>
+    <mergeCell ref="A49:C49"/>
+    <mergeCell ref="A136:G136"/>
+    <mergeCell ref="A68:B68"/>
+    <mergeCell ref="J46:N46"/>
+    <mergeCell ref="A63:N63"/>
+    <mergeCell ref="H23:H24"/>
+    <mergeCell ref="J52:N52"/>
+    <mergeCell ref="J61:N61"/>
+    <mergeCell ref="H134:N135"/>
+    <mergeCell ref="J39:N39"/>
+    <mergeCell ref="J48:N48"/>
+    <mergeCell ref="H75:N75"/>
+    <mergeCell ref="G23:G24"/>
+    <mergeCell ref="E8:K9"/>
+    <mergeCell ref="A83:N83"/>
+    <mergeCell ref="H118:N119"/>
+    <mergeCell ref="G67:H67"/>
+    <mergeCell ref="F139:I140"/>
+    <mergeCell ref="A55:C55"/>
+    <mergeCell ref="G70:H70"/>
+    <mergeCell ref="I70:J70"/>
+    <mergeCell ref="A139:A140"/>
+    <mergeCell ref="J143:J144"/>
+    <mergeCell ref="A29:C29"/>
+    <mergeCell ref="A38:C38"/>
+    <mergeCell ref="E14:H14"/>
+    <mergeCell ref="A44:C44"/>
+    <mergeCell ref="A31:C31"/>
+    <mergeCell ref="A58:C58"/>
+    <mergeCell ref="J23:N24"/>
+    <mergeCell ref="A40:C40"/>
+    <mergeCell ref="G65:H65"/>
+    <mergeCell ref="A51:C51"/>
+    <mergeCell ref="B143:D144"/>
+    <mergeCell ref="E1:N5"/>
+    <mergeCell ref="A60:C60"/>
+    <mergeCell ref="M76:N76"/>
+    <mergeCell ref="E76:F76"/>
+    <mergeCell ref="D23:D24"/>
+    <mergeCell ref="D21:F21"/>
+    <mergeCell ref="K139:N140"/>
+    <mergeCell ref="A120:G133"/>
+    <mergeCell ref="A104:G117"/>
+    <mergeCell ref="E16:H16"/>
+    <mergeCell ref="M9:N9"/>
+    <mergeCell ref="A50:C50"/>
+    <mergeCell ref="A69:B69"/>
+    <mergeCell ref="A42:C42"/>
+    <mergeCell ref="M11:N11"/>
+    <mergeCell ref="A65:B65"/>
+    <mergeCell ref="J53:N53"/>
+    <mergeCell ref="A62:C62"/>
+    <mergeCell ref="G69:H69"/>
+    <mergeCell ref="E78:F78"/>
+    <mergeCell ref="A84:N84"/>
+    <mergeCell ref="J55:N55"/>
+    <mergeCell ref="A28:C28"/>
+    <mergeCell ref="E77:F77"/>
+    <mergeCell ref="E80:F80"/>
+    <mergeCell ref="A86:N86"/>
+    <mergeCell ref="A30:C30"/>
+    <mergeCell ref="I23:I24"/>
+    <mergeCell ref="C65:F65"/>
+    <mergeCell ref="E10:K10"/>
+    <mergeCell ref="A59:C59"/>
+    <mergeCell ref="G21:I21"/>
+    <mergeCell ref="D20:F20"/>
+    <mergeCell ref="G64:H64"/>
+    <mergeCell ref="E139:E140"/>
+    <mergeCell ref="I64:J64"/>
+    <mergeCell ref="G73:H73"/>
+    <mergeCell ref="I73:J73"/>
+    <mergeCell ref="A79:C79"/>
+    <mergeCell ref="A61:C61"/>
+    <mergeCell ref="E81:F81"/>
+    <mergeCell ref="E15:H15"/>
+    <mergeCell ref="J58:N58"/>
+    <mergeCell ref="J33:N33"/>
+    <mergeCell ref="A102:G103"/>
+    <mergeCell ref="A67:B67"/>
+    <mergeCell ref="K71:N71"/>
+    <mergeCell ref="A54:C54"/>
+    <mergeCell ref="I65:J65"/>
+    <mergeCell ref="I16:K16"/>
+    <mergeCell ref="A41:C41"/>
+    <mergeCell ref="H82:L82"/>
+    <mergeCell ref="E141:E142"/>
+    <mergeCell ref="K73:N73"/>
+    <mergeCell ref="A27:C27"/>
+    <mergeCell ref="A56:C56"/>
+    <mergeCell ref="E143:E144"/>
+    <mergeCell ref="E82:F82"/>
+    <mergeCell ref="K66:N66"/>
+    <mergeCell ref="A76:C76"/>
+    <mergeCell ref="F141:I142"/>
+    <mergeCell ref="A82:D82"/>
+    <mergeCell ref="A66:B66"/>
+    <mergeCell ref="K68:N68"/>
+    <mergeCell ref="A74:N74"/>
+    <mergeCell ref="I68:J68"/>
+    <mergeCell ref="I67:J67"/>
+    <mergeCell ref="A85:N85"/>
+    <mergeCell ref="L7:N7"/>
+    <mergeCell ref="E13:N13"/>
+    <mergeCell ref="L16:N16"/>
+    <mergeCell ref="A36:C36"/>
+    <mergeCell ref="A72:B72"/>
+    <mergeCell ref="J21:N21"/>
+    <mergeCell ref="A45:C45"/>
+    <mergeCell ref="J141:J142"/>
+    <mergeCell ref="H88:N101"/>
+    <mergeCell ref="A78:C78"/>
+    <mergeCell ref="G72:H72"/>
+    <mergeCell ref="K70:N70"/>
+    <mergeCell ref="A80:C80"/>
+    <mergeCell ref="A46:C46"/>
+    <mergeCell ref="A75:F75"/>
+    <mergeCell ref="C72:F72"/>
+    <mergeCell ref="A70:B70"/>
     <mergeCell ref="A26:C26"/>
-    <mergeCell ref="A13:D13"/>
-    <mergeCell ref="E64:F64"/>
-    <mergeCell ref="A54:B54"/>
-    <mergeCell ref="H105:N118"/>
-    <mergeCell ref="H66:J66"/>
-    <mergeCell ref="H22:J22"/>
-    <mergeCell ref="F126:I127"/>
-    <mergeCell ref="M10:N10"/>
-    <mergeCell ref="E63:F63"/>
-    <mergeCell ref="K49:N49"/>
-    <mergeCell ref="G57:H57"/>
-    <mergeCell ref="A15:D15"/>
-    <mergeCell ref="A56:B56"/>
+    <mergeCell ref="K65:N65"/>
+    <mergeCell ref="A87:N87"/>
+    <mergeCell ref="K76:L76"/>
+    <mergeCell ref="I71:J71"/>
+    <mergeCell ref="J49:N49"/>
     <mergeCell ref="J27:N27"/>
-    <mergeCell ref="J128:J129"/>
-    <mergeCell ref="A43:C43"/>
-    <mergeCell ref="I58:J58"/>
-    <mergeCell ref="E65:F65"/>
-    <mergeCell ref="J35:N35"/>
-    <mergeCell ref="A63:C63"/>
+    <mergeCell ref="A134:G135"/>
     <mergeCell ref="J20:N20"/>
     <mergeCell ref="J25:N25"/>
-    <mergeCell ref="G58:H58"/>
-    <mergeCell ref="C54:F54"/>
-    <mergeCell ref="A71:N71"/>
+    <mergeCell ref="J139:J140"/>
     <mergeCell ref="A16:D16"/>
-    <mergeCell ref="I52:J52"/>
-    <mergeCell ref="A34:C34"/>
+    <mergeCell ref="A77:C77"/>
     <mergeCell ref="M8:N8"/>
-    <mergeCell ref="A53:B53"/>
-    <mergeCell ref="C50:F50"/>
-    <mergeCell ref="A60:F60"/>
-    <mergeCell ref="C56:F56"/>
-    <mergeCell ref="B128:D129"/>
-    <mergeCell ref="K58:N58"/>
-    <mergeCell ref="M62:N62"/>
-    <mergeCell ref="J46:N46"/>
-    <mergeCell ref="H23:H24"/>
-    <mergeCell ref="A89:G102"/>
-    <mergeCell ref="H103:N104"/>
-    <mergeCell ref="H64:J64"/>
-    <mergeCell ref="K124:N125"/>
-    <mergeCell ref="F128:I129"/>
-    <mergeCell ref="J39:N39"/>
+    <mergeCell ref="H78:J78"/>
+    <mergeCell ref="K67:N67"/>
+    <mergeCell ref="I69:J69"/>
+    <mergeCell ref="K78:L78"/>
     <mergeCell ref="L15:N15"/>
-    <mergeCell ref="A66:C66"/>
-    <mergeCell ref="G23:G24"/>
-    <mergeCell ref="E8:K9"/>
     <mergeCell ref="J29:N29"/>
-    <mergeCell ref="K53:N53"/>
-    <mergeCell ref="E67:F67"/>
     <mergeCell ref="J38:N38"/>
-    <mergeCell ref="K126:N127"/>
-    <mergeCell ref="E123:I123"/>
-    <mergeCell ref="K64:L64"/>
-    <mergeCell ref="E128:E129"/>
-    <mergeCell ref="M64:N64"/>
+    <mergeCell ref="K80:L80"/>
+    <mergeCell ref="C67:F67"/>
+    <mergeCell ref="K79:L79"/>
+    <mergeCell ref="H136:N136"/>
     <mergeCell ref="J40:N40"/>
-    <mergeCell ref="I57:J57"/>
-    <mergeCell ref="J123:N123"/>
-    <mergeCell ref="A69:N69"/>
-    <mergeCell ref="I54:J54"/>
+    <mergeCell ref="H120:N133"/>
+    <mergeCell ref="K69:N69"/>
+    <mergeCell ref="C69:F69"/>
     <mergeCell ref="I14:K14"/>
     <mergeCell ref="A32:C32"/>
-    <mergeCell ref="K63:L63"/>
-    <mergeCell ref="A29:C29"/>
-    <mergeCell ref="I56:J56"/>
-    <mergeCell ref="A38:C38"/>
-    <mergeCell ref="E14:H14"/>
-    <mergeCell ref="G49:H49"/>
+    <mergeCell ref="A118:G119"/>
+    <mergeCell ref="I72:J72"/>
+    <mergeCell ref="H104:N117"/>
+    <mergeCell ref="A81:C81"/>
+    <mergeCell ref="H77:J77"/>
     <mergeCell ref="J26:N26"/>
-    <mergeCell ref="M65:N65"/>
-    <mergeCell ref="A44:C44"/>
     <mergeCell ref="A12:N12"/>
-    <mergeCell ref="A31:C31"/>
-    <mergeCell ref="K51:N51"/>
-    <mergeCell ref="A40:C40"/>
-    <mergeCell ref="H121:N121"/>
-    <mergeCell ref="J23:N24"/>
-    <mergeCell ref="H60:N60"/>
-    <mergeCell ref="E124:E125"/>
-    <mergeCell ref="K50:N50"/>
-    <mergeCell ref="H89:N102"/>
-    <mergeCell ref="K128:N129"/>
-    <mergeCell ref="E1:N5"/>
-    <mergeCell ref="A52:B52"/>
-    <mergeCell ref="H87:N88"/>
-    <mergeCell ref="K56:N56"/>
-    <mergeCell ref="K66:L66"/>
-    <mergeCell ref="D23:D24"/>
-    <mergeCell ref="M66:N66"/>
-    <mergeCell ref="E126:E127"/>
+    <mergeCell ref="K64:N64"/>
+    <mergeCell ref="A71:B71"/>
+    <mergeCell ref="K72:N72"/>
     <mergeCell ref="J42:N42"/>
-    <mergeCell ref="E66:F66"/>
-    <mergeCell ref="M63:N63"/>
-    <mergeCell ref="K52:N52"/>
-    <mergeCell ref="D21:F21"/>
-    <mergeCell ref="A105:G118"/>
+    <mergeCell ref="F143:I144"/>
+    <mergeCell ref="C71:F71"/>
     <mergeCell ref="A23:C24"/>
     <mergeCell ref="A25:C25"/>
-    <mergeCell ref="A119:G120"/>
-    <mergeCell ref="H67:L67"/>
     <mergeCell ref="J44:N44"/>
     <mergeCell ref="L14:N14"/>
-    <mergeCell ref="A49:B49"/>
-    <mergeCell ref="E16:H16"/>
-    <mergeCell ref="H61:J61"/>
-    <mergeCell ref="M67:N67"/>
-    <mergeCell ref="M9:N9"/>
+    <mergeCell ref="H79:J79"/>
     <mergeCell ref="J28:N28"/>
-    <mergeCell ref="A103:G104"/>
     <mergeCell ref="J37:N37"/>
-    <mergeCell ref="C57:F57"/>
-    <mergeCell ref="A42:C42"/>
-    <mergeCell ref="C53:F53"/>
-    <mergeCell ref="M11:N11"/>
+    <mergeCell ref="H102:N103"/>
+    <mergeCell ref="C66:F66"/>
+    <mergeCell ref="H81:J81"/>
     <mergeCell ref="J30:N30"/>
     <mergeCell ref="A47:C47"/>
-    <mergeCell ref="H65:J65"/>
-    <mergeCell ref="A62:C62"/>
+    <mergeCell ref="M78:N78"/>
+    <mergeCell ref="E138:I138"/>
+    <mergeCell ref="C68:F68"/>
     <mergeCell ref="G20:I20"/>
     <mergeCell ref="F23:F24"/>
-    <mergeCell ref="C58:F58"/>
     <mergeCell ref="A20:C20"/>
-    <mergeCell ref="H119:N120"/>
-    <mergeCell ref="A55:B55"/>
     <mergeCell ref="A18:N18"/>
-    <mergeCell ref="A28:C28"/>
-    <mergeCell ref="J124:J125"/>
-    <mergeCell ref="K54:N54"/>
-    <mergeCell ref="A57:B57"/>
-    <mergeCell ref="K55:N55"/>
+    <mergeCell ref="K141:N142"/>
+    <mergeCell ref="M81:N81"/>
+    <mergeCell ref="H76:J76"/>
+    <mergeCell ref="J54:N54"/>
     <mergeCell ref="J32:N32"/>
     <mergeCell ref="F22:G22"/>
     <mergeCell ref="J41:N41"/>
-    <mergeCell ref="I23:I24"/>
-    <mergeCell ref="A30:C30"/>
-    <mergeCell ref="E10:K10"/>
-    <mergeCell ref="E61:F61"/>
-    <mergeCell ref="G21:I21"/>
-    <mergeCell ref="D20:F20"/>
+    <mergeCell ref="A22:E22"/>
     <mergeCell ref="I15:K15"/>
-    <mergeCell ref="A22:E22"/>
-    <mergeCell ref="H73:N86"/>
     <mergeCell ref="J47:N47"/>
-    <mergeCell ref="A64:C64"/>
-    <mergeCell ref="G51:H51"/>
-    <mergeCell ref="H63:J63"/>
-    <mergeCell ref="I51:J51"/>
-    <mergeCell ref="A122:N122"/>
-    <mergeCell ref="G54:H54"/>
+    <mergeCell ref="J56:N56"/>
     <mergeCell ref="J43:N43"/>
-    <mergeCell ref="K65:L65"/>
-    <mergeCell ref="A61:C61"/>
-    <mergeCell ref="A72:N72"/>
-    <mergeCell ref="E15:H15"/>
-    <mergeCell ref="G50:H50"/>
-    <mergeCell ref="C51:F51"/>
-    <mergeCell ref="I50:J50"/>
-    <mergeCell ref="J33:N33"/>
-    <mergeCell ref="G56:H56"/>
+    <mergeCell ref="J138:N138"/>
     <mergeCell ref="A14:D14"/>
-    <mergeCell ref="I16:K16"/>
-    <mergeCell ref="A41:C41"/>
-    <mergeCell ref="G52:H52"/>
-    <mergeCell ref="I49:J49"/>
-    <mergeCell ref="B126:D127"/>
-    <mergeCell ref="A27:C27"/>
-    <mergeCell ref="A121:G121"/>
-    <mergeCell ref="K57:N57"/>
-    <mergeCell ref="A124:A125"/>
-    <mergeCell ref="A70:N70"/>
+    <mergeCell ref="C70:F70"/>
+    <mergeCell ref="B141:D142"/>
+    <mergeCell ref="J59:N59"/>
+    <mergeCell ref="J60:N60"/>
     <mergeCell ref="J34:N34"/>
-    <mergeCell ref="A67:D67"/>
     <mergeCell ref="A33:C33"/>
-    <mergeCell ref="C49:F49"/>
-    <mergeCell ref="A87:G88"/>
-    <mergeCell ref="A126:A127"/>
-    <mergeCell ref="G53:H53"/>
+    <mergeCell ref="H80:J80"/>
     <mergeCell ref="J36:N36"/>
-    <mergeCell ref="I53:J53"/>
+    <mergeCell ref="A53:C53"/>
     <mergeCell ref="A35:C35"/>
-    <mergeCell ref="A73:G86"/>
     <mergeCell ref="J45:N45"/>
-    <mergeCell ref="A123:D123"/>
-    <mergeCell ref="A50:B50"/>
-    <mergeCell ref="H62:J62"/>
-    <mergeCell ref="I55:J55"/>
+    <mergeCell ref="A138:D138"/>
+    <mergeCell ref="K77:L77"/>
+    <mergeCell ref="M77:N77"/>
+    <mergeCell ref="M80:N80"/>
     <mergeCell ref="A39:C39"/>
-    <mergeCell ref="K61:L61"/>
     <mergeCell ref="J31:N31"/>
-    <mergeCell ref="M61:N61"/>
-    <mergeCell ref="C55:F55"/>
-    <mergeCell ref="L7:N7"/>
-    <mergeCell ref="E13:N13"/>
+    <mergeCell ref="A48:C48"/>
     <mergeCell ref="A17:N17"/>
-    <mergeCell ref="G55:H55"/>
-    <mergeCell ref="L16:N16"/>
-    <mergeCell ref="A36:C36"/>
     <mergeCell ref="K22:N22"/>
-    <mergeCell ref="J21:N21"/>
-    <mergeCell ref="A45:C45"/>
-    <mergeCell ref="J126:J127"/>
+    <mergeCell ref="J51:N51"/>
+    <mergeCell ref="K143:N144"/>
+    <mergeCell ref="J62:N62"/>
     <mergeCell ref="A19:N19"/>
-    <mergeCell ref="A68:N68"/>
-    <mergeCell ref="K62:L62"/>
-    <mergeCell ref="A65:C65"/>
-    <mergeCell ref="A58:B58"/>
+    <mergeCell ref="B139:D140"/>
   </mergeCells>
   <pageMargins left="0.2952755905511811" right="0.2952755905511811" top="0.1968503937007874" bottom="0.1968503937007874" header="0.5118110236220472" footer="0.5118110236220472"/>
   <pageSetup orientation="portrait" scale="65" fitToHeight="0" horizontalDpi="300" verticalDpi="300"/>
